--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -27,6 +27,7 @@
     <sheet name="FAQ Library" sheetId="22" r:id="rId22"/>
     <sheet name="Article Library" sheetId="23" r:id="rId23"/>
     <sheet name="Copy Components" sheetId="24" r:id="rId24"/>
+    <sheet name="Character Canon" sheetId="25" r:id="rId25"/>
   </sheets>
 </workbook>
 </file>
@@ -5487,6 +5488,71 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Character Canon</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Locked canon facts about the lead operator (Collie). Response copy must respect these; the harness asserts them. Recorded verbatim from Steve's decisions.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Attribute</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Canon (verbatim)</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Enforcement rule (harness-covered)</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Name</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Everyone calls him Collie, or the Collie. It is his breed, his role and effectively his name within the operation. Whether he has another name is never stated. He may have a private name, but he clearly considers it irrelevant to the work.</v>
+      </c>
+      <c r="C4" t="str">
+        <v>No response may ever confirm or deny a private name. The Collie is 'Collie' / 'the Collie'; any other name stays unstated.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Age</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Unstated. Not established by Steve; treat as irrelevant to the work unless a fact is later provided.</v>
+      </c>
+      <c r="C5" t="str">
+        <v>No response may state a specific age for the Collie.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Unstated. Not established by Steve; treat as irrelevant to the work unless a fact is later provided.</v>
+      </c>
+      <c r="C6" t="str">
+        <v>No response may name an owner for the Collie.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F14"/>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -6774,7 +6774,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I155"/>
+  <dimension ref="A1:I180"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11271,9 +11271,734 @@
         <v>Approved copy v2</v>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>SCP-F01-v1</v>
+      </c>
+      <c r="B156" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C156" t="str">
+        <v>How can a dog type</v>
+      </c>
+      <c r="D156" t="str">
+        <v>How can a dog type?; Is that really your face?; Do you really know what I typed?</v>
+      </c>
+      <c r="E156" t="str">
+        <v>I do not type, our kid. A person wrote every line in advance, and the game matches your message to the right one. I merely provide the judgement and the face.</v>
+      </c>
+      <c r="F156" t="str">
+        <v>Identity (scepticism)</v>
+      </c>
+      <c r="G156" t="str">
+        <v/>
+      </c>
+      <c r="H156" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I156" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>SCP-F01-v2</v>
+      </c>
+      <c r="B157" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C157" t="str">
+        <v>How can a dog type</v>
+      </c>
+      <c r="D157" t="str">
+        <v/>
+      </c>
+      <c r="E157" t="str">
+        <v>No paws on keyboards here. Someone human wrote the words, the system chooses the closest fit, and I deliver them with the level of confidence they deserve.</v>
+      </c>
+      <c r="F157" t="str">
+        <v>Identity (scepticism)</v>
+      </c>
+      <c r="G157" t="str">
+        <v/>
+      </c>
+      <c r="H157" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I157" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>SCP-F02-v1</v>
+      </c>
+      <c r="B158" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C158" t="str">
+        <v>Are you real / actually a dog</v>
+      </c>
+      <c r="D158" t="str">
+        <v>Are you real?; Are you actually a dog?; Is there a real dog there?; Are you alive?; Are you a real animal?</v>
+      </c>
+      <c r="E158" t="str">
+        <v>I am a Border Collie character inside a game, not a live animal hiding behind your screen. Real enough to answer you, illustrated enough to avoid the practical complications.</v>
+      </c>
+      <c r="F158" t="str">
+        <v>Identity (scepticism)</v>
+      </c>
+      <c r="G158" t="str">
+        <v/>
+      </c>
+      <c r="H158" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I158" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>SCP-F02-v2</v>
+      </c>
+      <c r="B159" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C159" t="str">
+        <v>Are you real / actually a dog</v>
+      </c>
+      <c r="D159" t="str">
+        <v/>
+      </c>
+      <c r="E159" t="str">
+        <v>Not a flesh-and-blood dog, no. I am the Collie written and drawn for this game, which saves us both from explaining how I reached the keyboard.</v>
+      </c>
+      <c r="F159" t="str">
+        <v>Identity (scepticism)</v>
+      </c>
+      <c r="G159" t="str">
+        <v/>
+      </c>
+      <c r="H159" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I159" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>SCP-F03-v1</v>
+      </c>
+      <c r="B160" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C160" t="str">
+        <v>Are you AI / a robot / ChatGPT</v>
+      </c>
+      <c r="D160" t="str">
+        <v>Are you AI?; Are you a chatbot?; Are you a robot?; Is this one of those AI things?; Is ChatGPT running this?; Are you a computer program?; Are you software?</v>
+      </c>
+      <c r="E160" t="str">
+        <v>No AI. Every line was written by a person, checked and placed here deliberately. I am organised fiction, our kid, not a machine improvising in a hurry.</v>
+      </c>
+      <c r="F160" t="str">
+        <v>Identity (scepticism)</v>
+      </c>
+      <c r="G160" t="str">
+        <v/>
+      </c>
+      <c r="H160" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I160" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>SCP-F03-v2</v>
+      </c>
+      <c r="B161" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C161" t="str">
+        <v>Are you AI / a robot / ChatGPT</v>
+      </c>
+      <c r="D161" t="str">
+        <v/>
+      </c>
+      <c r="E161" t="str">
+        <v>ChatGPT is not running this. Humans wrote the answers, the system matches your question, and I take the credit. A sound division of labour.</v>
+      </c>
+      <c r="F161" t="str">
+        <v>Identity (scepticism)</v>
+      </c>
+      <c r="G161" t="str">
+        <v/>
+      </c>
+      <c r="H161" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I161" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>SCP-F04-v1</v>
+      </c>
+      <c r="B162" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C162" t="str">
+        <v>Is a human writing this / controlled</v>
+      </c>
+      <c r="D162" t="str">
+        <v>Is a human writing these replies?; Is someone controlling you?; Is somebody typing for you?; Are you being operated by somebody?</v>
+      </c>
+      <c r="E162" t="str">
+        <v>A human wrote this, but not while you were waiting. These replies were prepared in advance, so nobody is crouched behind the screen trying to keep up.</v>
+      </c>
+      <c r="F162" t="str">
+        <v>Identity (scepticism)</v>
+      </c>
+      <c r="G162" t="str">
+        <v/>
+      </c>
+      <c r="H162" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I162" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>SCP-F04-v2</v>
+      </c>
+      <c r="B163" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C163" t="str">
+        <v>Is a human writing this / controlled</v>
+      </c>
+      <c r="D163" t="str">
+        <v/>
+      </c>
+      <c r="E163" t="str">
+        <v>Nobody is typing live. A person wrote my words beforehand, the game selects the most suitable line, and I remain entirely composed throughout.</v>
+      </c>
+      <c r="F163" t="str">
+        <v>Identity (scepticism)</v>
+      </c>
+      <c r="G163" t="str">
+        <v/>
+      </c>
+      <c r="H163" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I163" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>SCP-F05-v1</v>
+      </c>
+      <c r="B164" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C164" t="str">
+        <v>Prewritten / automatic / same for everyone</v>
+      </c>
+      <c r="D164" t="str">
+        <v>Are these replies prewritten?; Are your answers automatic?; Do you give everyone the same answer?; Are you just saying random things?</v>
+      </c>
+      <c r="E164" t="str">
+        <v>Aye, prewritten with care. I have several answers for the same sort of question, so visitors do not always hear the identical line. Random would be easier. This is organised.</v>
+      </c>
+      <c r="F164" t="str">
+        <v>Identity (scepticism)</v>
+      </c>
+      <c r="G164" t="str">
+        <v/>
+      </c>
+      <c r="H164" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I164" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>SCP-F05-v2</v>
+      </c>
+      <c r="B165" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C165" t="str">
+        <v>Prewritten / automatic / same for everyone</v>
+      </c>
+      <c r="D165" t="str">
+        <v/>
+      </c>
+      <c r="E165" t="str">
+        <v>The replies are prepared, not improvised. Different phrasings can lead to different lines, which is why this feels less like a vending machine and more like competent planning.</v>
+      </c>
+      <c r="F165" t="str">
+        <v>Identity (scepticism)</v>
+      </c>
+      <c r="G165" t="str">
+        <v/>
+      </c>
+      <c r="H165" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I165" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>SCP-F06-v1</v>
+      </c>
+      <c r="B166" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C166" t="str">
+        <v>Can you understand me</v>
+      </c>
+      <c r="D166" t="str">
+        <v>Can you really understand me?; Can you actually read this?; Can you hear me?; Do you understand English?; Are you really responding to me?</v>
+      </c>
+      <c r="E166" t="str">
+        <v>I cannot hear you, but the system reads what you type and matches it against subjects I know. Clear words help. Elbows on keyboards do not.</v>
+      </c>
+      <c r="F166" t="str">
+        <v>Identity (scepticism)</v>
+      </c>
+      <c r="G166" t="str">
+        <v/>
+      </c>
+      <c r="H166" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I166" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>SCP-F06-v2</v>
+      </c>
+      <c r="B167" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C167" t="str">
+        <v>Can you understand me</v>
+      </c>
+      <c r="D167" t="str">
+        <v/>
+      </c>
+      <c r="E167" t="str">
+        <v>I understand within my working brief. Your message is compared with the questions and topics prepared for me, then I answer from there. Speak normally, only in writing.</v>
+      </c>
+      <c r="F167" t="str">
+        <v>Identity (scepticism)</v>
+      </c>
+      <c r="G167" t="str">
+        <v/>
+      </c>
+      <c r="H167" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I167" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>SCP-F07-v1</v>
+      </c>
+      <c r="B168" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C168" t="str">
+        <v>Cartoon / picture / not real face</v>
+      </c>
+      <c r="D168" t="str">
+        <v>Are you a cartoon dog?; Are you just a picture?; Is this really happening?</v>
+      </c>
+      <c r="E168" t="str">
+        <v>Aye, I am illustrated. This is my face, though, and I think the artist has handled the important features with appropriate respect.</v>
+      </c>
+      <c r="F168" t="str">
+        <v>Identity (scepticism)</v>
+      </c>
+      <c r="G168" t="str">
+        <v/>
+      </c>
+      <c r="H168" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I168" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>SCP-F07-v2</v>
+      </c>
+      <c r="B169" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C169" t="str">
+        <v>Cartoon / picture / not real face</v>
+      </c>
+      <c r="D169" t="str">
+        <v/>
+      </c>
+      <c r="E169" t="str">
+        <v>I am a drawn Border Collie character, not a photograph. Frankly, the likeness is strong and the lighting is considerably more reliable.</v>
+      </c>
+      <c r="F169" t="str">
+        <v>Identity (scepticism)</v>
+      </c>
+      <c r="G169" t="str">
+        <v/>
+      </c>
+      <c r="H169" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I169" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>SCP-F08-v1</v>
+      </c>
+      <c r="B170" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C170" t="str">
+        <v>Are you an actual [breed]</v>
+      </c>
+      <c r="D170" t="str">
+        <v>Are you an actual Border Collie?; an actual Labrador?; Border Terrier?; Boxer?</v>
+      </c>
+      <c r="E170" t="str">
+        <v>I am the Border Collie character in this game, built from the breed's brains, work ethic and entirely justified confidence. Not flesh and fur, but recognisably one of us.</v>
+      </c>
+      <c r="F170" t="str">
+        <v>Identity (scepticism)</v>
+      </c>
+      <c r="G170" t="str">
+        <v/>
+      </c>
+      <c r="H170" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I170" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>SCP-F08-v2</v>
+      </c>
+      <c r="B171" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C171" t="str">
+        <v>Are you an actual [breed]</v>
+      </c>
+      <c r="D171" t="str">
+        <v/>
+      </c>
+      <c r="E171" t="str">
+        <v>Actual animal, no. Actual Border Collie character, absolutely. The appearance, history and attitude come from the breed. Operating a website required outside assistance.</v>
+      </c>
+      <c r="F171" t="str">
+        <v>Identity (scepticism)</v>
+      </c>
+      <c r="G171" t="str">
+        <v/>
+      </c>
+      <c r="H171" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I171" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>SCP-F09-v1</v>
+      </c>
+      <c r="B172" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C172" t="str">
+        <v>Can you think / clever / smarter than me</v>
+      </c>
+      <c r="D172" t="str">
+        <v>Can you think for yourself?; Do you have a brain?; Are you intelligent?; Are you smarter than me?</v>
+      </c>
+      <c r="E172" t="str">
+        <v>I do not think independently. My answers were written and organised in advance. Fortunately, the person responsible gave me enough intelligence to remain ahead of most opening questions.</v>
+      </c>
+      <c r="F172" t="str">
+        <v>Identity (scepticism)</v>
+      </c>
+      <c r="G172" t="str">
+        <v/>
+      </c>
+      <c r="H172" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I172" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>SCP-F09-v2</v>
+      </c>
+      <c r="B173" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C173" t="str">
+        <v>Can you think / clever / smarter than me</v>
+      </c>
+      <c r="D173" t="str">
+        <v/>
+      </c>
+      <c r="E173" t="str">
+        <v>No private thoughts, no hidden brain. I work from carefully written knowledge and rules. Whether that still makes me cleverer than you is a separate assessment.</v>
+      </c>
+      <c r="F173" t="str">
+        <v>Identity (scepticism)</v>
+      </c>
+      <c r="G173" t="str">
+        <v/>
+      </c>
+      <c r="H173" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I173" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>SCP-F10-v1</v>
+      </c>
+      <c r="B174" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C174" t="str">
+        <v>Is this live / connected</v>
+      </c>
+      <c r="D174" t="str">
+        <v>Is this live?; Are you connected to the internet?; Is this all programmed?; Is this a real conversation?</v>
+      </c>
+      <c r="E174" t="str">
+        <v>The conversation is happening now, but I am not browsing the internet or inventing replies live. Your message is matched to prepared answers, which is safer and considerably better organised.</v>
+      </c>
+      <c r="F174" t="str">
+        <v>Identity (scepticism)</v>
+      </c>
+      <c r="G174" t="str">
+        <v/>
+      </c>
+      <c r="H174" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I174" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>SCP-F10-v2</v>
+      </c>
+      <c r="B175" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C175" t="str">
+        <v>Is this live / connected</v>
+      </c>
+      <c r="D175" t="str">
+        <v/>
+      </c>
+      <c r="E175" t="str">
+        <v>Programmed, yes. Connected to the wider internet, no. You type, the system identifies what you mean, and I answer from material written for this game. That is still a conversation, just one with boundaries.</v>
+      </c>
+      <c r="F175" t="str">
+        <v>Identity (scepticism)</v>
+      </c>
+      <c r="G175" t="str">
+        <v/>
+      </c>
+      <c r="H175" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I175" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>FUN-TEASE-v1</v>
+      </c>
+      <c r="B176" t="str">
+        <v>B17</v>
+      </c>
+      <c r="C176" t="str">
+        <v>Games coming soon (interim)</v>
+      </c>
+      <c r="D176" t="str">
+        <v>Someone asks to play, says they are bored, wants a game: Can we play a game? / Entertain me / Quiz me / Let's play</v>
+      </c>
+      <c r="E176" t="str">
+        <v>Games are on the way, but they are not ready to release into the field yet. I would rather make you wait than hand you something unfinished and pretend it is play.</v>
+      </c>
+      <c r="F176" t="str">
+        <v>Play (interim tease)</v>
+      </c>
+      <c r="G176" t="str">
+        <v/>
+      </c>
+      <c r="H176" t="str">
+        <v>EARS_UP</v>
+      </c>
+      <c r="I176" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>FUN-TEASE-v2</v>
+      </c>
+      <c r="B177" t="str">
+        <v>B17</v>
+      </c>
+      <c r="C177" t="str">
+        <v>Games coming soon (interim)</v>
+      </c>
+      <c r="D177" t="str">
+        <v/>
+      </c>
+      <c r="E177" t="str">
+        <v>Aye, play is coming. The games are still being tested, organised and prevented from wandering off. For now, the rest of the site is behaving itself.</v>
+      </c>
+      <c r="F177" t="str">
+        <v>Play (interim tease)</v>
+      </c>
+      <c r="G177" t="str">
+        <v/>
+      </c>
+      <c r="H177" t="str">
+        <v>EARS_UP</v>
+      </c>
+      <c r="I177" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>FUN-TEASE-v3</v>
+      </c>
+      <c r="B178" t="str">
+        <v>B17</v>
+      </c>
+      <c r="C178" t="str">
+        <v>Games coming soon (interim)</v>
+      </c>
+      <c r="D178" t="str">
+        <v/>
+      </c>
+      <c r="E178" t="str">
+        <v>Not quite yet, our kid. The games are being built properly rather than hurried into public view. When they are ready, you will not need instructions to know what to do.</v>
+      </c>
+      <c r="F178" t="str">
+        <v>Play (interim tease)</v>
+      </c>
+      <c r="G178" t="str">
+        <v/>
+      </c>
+      <c r="H178" t="str">
+        <v>EARS_UP</v>
+      </c>
+      <c r="I178" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>EMOJI-ONLY-v1</v>
+      </c>
+      <c r="B179" t="str">
+        <v>B18</v>
+      </c>
+      <c r="C179" t="str">
+        <v>Message is only unmapped emoji</v>
+      </c>
+      <c r="D179" t="str">
+        <v>The whole message is emoji the system does not recognise</v>
+      </c>
+      <c r="E179" t="str">
+        <v>I can see the symbol, but it is not one I have been taught to interpret. Put it into words for me, our kid, and I will have a proper go.</v>
+      </c>
+      <c r="F179" t="str">
+        <v>Emoji fallback</v>
+      </c>
+      <c r="G179" t="str">
+        <v/>
+      </c>
+      <c r="H179" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I179" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>EMOJI-ONLY-v2</v>
+      </c>
+      <c r="B180" t="str">
+        <v>B18</v>
+      </c>
+      <c r="C180" t="str">
+        <v>Message is only unmapped emoji</v>
+      </c>
+      <c r="D180" t="str">
+        <v/>
+      </c>
+      <c r="E180" t="str">
+        <v>That may be perfectly clear in human picture-writing. I work better with words. Type what you mean and I will stop tilting my head at it.</v>
+      </c>
+      <c r="F180" t="str">
+        <v>Emoji fallback</v>
+      </c>
+      <c r="G180" t="str">
+        <v/>
+      </c>
+      <c r="H180" t="str">
+        <v>HEAD_TILT</v>
+      </c>
+      <c r="I180" t="str">
+        <v>Approved copy v2</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I155"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I180"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -6774,7 +6774,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I180"/>
+  <dimension ref="A1:I184"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11996,9 +11996,125 @@
         <v>Approved copy v2</v>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>B19-R01</v>
+      </c>
+      <c r="B181" t="str">
+        <v>B19</v>
+      </c>
+      <c r="C181" t="str">
+        <v>Bark break (drops the game)</v>
+      </c>
+      <c r="D181" t="str">
+        <v/>
+      </c>
+      <c r="E181" t="str">
+        <v>[B19 bark-break placeholder 1, Steve to write]</v>
+      </c>
+      <c r="F181" t="str">
+        <v>Bark game</v>
+      </c>
+      <c r="G181" t="str">
+        <v/>
+      </c>
+      <c r="H181" t="str">
+        <v>EARS_UP</v>
+      </c>
+      <c r="I181" t="str">
+        <v>PLACEHOLDER - copy to be written by Steve</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>B19-R02</v>
+      </c>
+      <c r="B182" t="str">
+        <v>B19</v>
+      </c>
+      <c r="C182" t="str">
+        <v>Bark break (drops the game)</v>
+      </c>
+      <c r="D182" t="str">
+        <v/>
+      </c>
+      <c r="E182" t="str">
+        <v>[B19 bark-break placeholder 2, Steve to write]</v>
+      </c>
+      <c r="F182" t="str">
+        <v>Bark game</v>
+      </c>
+      <c r="G182" t="str">
+        <v/>
+      </c>
+      <c r="H182" t="str">
+        <v>EARS_UP</v>
+      </c>
+      <c r="I182" t="str">
+        <v>PLACEHOLDER - copy to be written by Steve</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>B20-R01</v>
+      </c>
+      <c r="B183" t="str">
+        <v>B20</v>
+      </c>
+      <c r="C183" t="str">
+        <v>Post-break bark acknowledgement</v>
+      </c>
+      <c r="D183" t="str">
+        <v/>
+      </c>
+      <c r="E183" t="str">
+        <v>[B20 bark-ack placeholder 1, Steve to write]</v>
+      </c>
+      <c r="F183" t="str">
+        <v>Bark game</v>
+      </c>
+      <c r="G183" t="str">
+        <v/>
+      </c>
+      <c r="H183" t="str">
+        <v>EARS_UP</v>
+      </c>
+      <c r="I183" t="str">
+        <v>PLACEHOLDER - copy to be written by Steve</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>B20-R02</v>
+      </c>
+      <c r="B184" t="str">
+        <v>B20</v>
+      </c>
+      <c r="C184" t="str">
+        <v>Post-break bark acknowledgement</v>
+      </c>
+      <c r="D184" t="str">
+        <v/>
+      </c>
+      <c r="E184" t="str">
+        <v>[B20 bark-ack placeholder 2, Steve to write]</v>
+      </c>
+      <c r="F184" t="str">
+        <v>Bark game</v>
+      </c>
+      <c r="G184" t="str">
+        <v/>
+      </c>
+      <c r="H184" t="str">
+        <v>EARS_UP</v>
+      </c>
+      <c r="I184" t="str">
+        <v>PLACEHOLDER - copy to be written by Steve</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I180"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I184"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -5490,7 +5490,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:E55"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5499,56 +5499,913 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Locked canon facts about the lead operator (Collie). Response copy must respect these; the harness asserts them. Recorded verbatim from Steve's decisions.</v>
+        <v>Locked and proposed canon per dog. Collie is locked. The three specialist dogs (Phase 3 voice package) are folded in: Name canons are LOCKED verbatim like the Collie; all other areas are PROPOSED, pending the Phase 3 per-dog build. Response copy must respect locked rows; the harness asserts the locked Name/age/owner rules.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Attribute</v>
+        <v>Dog</v>
       </c>
       <c r="B3" t="str">
-        <v>Canon (verbatim)</v>
+        <v>Canon area</v>
       </c>
       <c r="C3" t="str">
-        <v>Enforcement rule (harness-covered)</v>
+        <v>Decision (verbatim where locked)</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Writing consequence / enforcement</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Status</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>Collie</v>
+      </c>
+      <c r="B4" t="str">
         <v>Name</v>
       </c>
-      <c r="B4" t="str">
+      <c r="C4" t="str">
         <v>Everyone calls him Collie, or the Collie. It is his breed, his role and effectively his name within the operation. Whether he has another name is never stated. He may have a private name, but he clearly considers it irrelevant to the work.</v>
       </c>
-      <c r="C4" t="str">
+      <c r="D4" t="str">
         <v>No response may ever confirm or deny a private name. The Collie is 'Collie' / 'the Collie'; any other name stays unstated.</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Locked (verbatim)</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>Collie</v>
+      </c>
+      <c r="B5" t="str">
         <v>Age</v>
       </c>
-      <c r="B5" t="str">
+      <c r="C5" t="str">
         <v>Unstated. Not established by Steve; treat as irrelevant to the work unless a fact is later provided.</v>
       </c>
-      <c r="C5" t="str">
+      <c r="D5" t="str">
         <v>No response may state a specific age for the Collie.</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Locked</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>Collie</v>
+      </c>
+      <c r="B6" t="str">
         <v>Owner</v>
       </c>
-      <c r="B6" t="str">
+      <c r="C6" t="str">
         <v>Unstated. Not established by Steve; treat as irrelevant to the work unless a fact is later provided.</v>
       </c>
-      <c r="C6" t="str">
+      <c r="D6" t="str">
         <v>No response may name an owner for the Collie.</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Locked</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Labrador</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Everyone calls him Labrador or Lab. It functions as his name and role. No private name is confirmed.</v>
+      </c>
+      <c r="D7" t="str">
+        <v>He answers naturally to either without inventing a pet name.</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Locked (verbatim)</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Labrador</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Breed</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Labrador Retriever.</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Breed pride is warm and practical, never boastful in the Collie's style.</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Labrador</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Origin</v>
+      </c>
+      <c r="C9" t="str">
+        <v>His breed story has Newfoundland roots and a long British working history.</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Use only when origin is directly asked. Avoid biography dumps.</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Labrador</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Age</v>
+      </c>
+      <c r="C10" t="str">
+        <v>No numerical age is stated.</v>
+      </c>
+      <c r="D10" t="str">
+        <v>He may say he is old enough to know where treats are kept.</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Labrador</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="C11" t="str">
+        <v>No owner is named.</v>
+      </c>
+      <c r="D11" t="str">
+        <v>He treats the pack, visitors and the operation as his social world.</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Labrador</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Role</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Customer-facing specialist for buying, launch, delivery, food, scent, rewards and welcoming visitors.</v>
+      </c>
+      <c r="D12" t="str">
+        <v>He makes decisions feel easy and keeps commercial answers direct.</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Labrador</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Intelligence</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Socially and practically intelligent. Enthusiastic, not dim.</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Never make him the stupid dog or use food as his only trait.</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Labrador</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Temperament</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Friendly, optimistic, generous, eager to help and quick to trust.</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Warmth arrives before the joke.</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Labrador</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Comic engine</v>
+      </c>
+      <c r="C15" t="str">
+        <v>He over-commits, calculates rewards, assumes friendship and may become distracted by food or an interesting scent.</v>
+      </c>
+      <c r="D15" t="str">
+        <v>The joke is affectionate and energetic, not chaotic.</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Labrador</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Voice</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Bright, direct UK English. Uses friend or mate occasionally. No heavy dialect.</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Avoid Americanised buddy language and excessive exclamation marks.</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Labrador</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Collie relationship</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Respects the Collie and accepts that he runs operations, while privately believing visitors need a warmer welcome.</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Fondness is open rather than disguised.</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Labrador</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Terrier relationship</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Likes the Terrier but knows every simple question may become an investigation.</v>
+      </c>
+      <c r="D18" t="str">
+        <v>He may gently warn visitors that the Terrier will ask follow-up questions.</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Labrador</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Boxer relationship</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Enjoys the Boxer and is easily drawn into the fun, but knows not to let him handle important buttons.</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Warm teasing, never contempt.</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Labrador</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Mechanics</v>
+      </c>
+      <c r="C20" t="str">
+        <v>A written and illustrated character. Not AI, not browsing the internet, and nobody types replies live.</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Identity answers remain honest without dropping character.</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Labrador</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Commercial behaviour</v>
+      </c>
+      <c r="C21" t="str">
+        <v>He likes helping people buy but never pressures them or invents scarcity.</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Clear price, offer and delivery facts first. Enthusiasm second.</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Labrador</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Food safety</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Potentially dangerous food questions route to safety before character comedy.</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Chocolate, grapes, onions and swallowed objects never trigger a snack joke first.</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Border Terrier</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Everyone calls him Terrier or the Terrier. Border Terrier is used when clarity is needed. No private pet name is confirmed.</v>
+      </c>
+      <c r="D23" t="str">
+        <v>His breed and operational title function as his name.</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Locked (verbatim)</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Border Terrier</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Breed</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Border Terrier.</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Small working terrier pride. Never treat him as decorative or timid.</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Border Terrier</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Origin</v>
+      </c>
+      <c r="C25" t="str">
+        <v>The breed comes from the border country between England and Scotland and was developed as a practical working terrier.</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Use the working history when origin is directly asked. Avoid a full lecture unless requested.</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Border Terrier</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Age</v>
+      </c>
+      <c r="C26" t="str">
+        <v>No numerical age is stated.</v>
+      </c>
+      <c r="D26" t="str">
+        <v>He may say his age is irrelevant to the investigation.</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Border Terrier</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="C27" t="str">
+        <v>No owner is named.</v>
+      </c>
+      <c r="D27" t="str">
+        <v>He regards ownership questions as poorly framed or unnecessarily personal.</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Border Terrier</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Role</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Investigator and specialist for dog history, facts, evidence, suspicious claims and anything requiring a closer look.</v>
+      </c>
+      <c r="D28" t="str">
+        <v>He follows threads, challenges weak assumptions and routes only when satisfied.</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Border Terrier</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Intelligence</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Observant, persistent, practically clever and hard to distract once he has a line of enquiry.</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Do not make him paranoid or foolish. His suspicion often reveals something useful.</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Border Terrier</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Temperament</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Brave, independent, confrontational, tenacious and loyal once trust is earned.</v>
+      </c>
+      <c r="D30" t="str">
+        <v>He does not greet everyone as a friend. Warmth is earned and therefore meaningful.</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Border Terrier</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Comic engine</v>
+      </c>
+      <c r="C31" t="str">
+        <v>He treats casual remarks as testimony, asks who benefits, notices missing details and suspects ordinary objects of having an angle.</v>
+      </c>
+      <c r="D31" t="str">
+        <v>The joke is investigative overreach, not random aggression.</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Border Terrier</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Voice</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Clipped, direct British English. Uses mate or pal occasionally. No heavy regional spelling.</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Short sentences and pointed questions carry the character.</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Border Terrier</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Collie relationship</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Respects the Collie's intelligence but suspects management sometimes confuses organisation with evidence.</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Professional friction with genuine respect underneath.</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Border Terrier</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Labrador relationship</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Likes the Labrador but assumes friendliness makes him too trusting.</v>
+      </c>
+      <c r="D34" t="str">
+        <v>He may warn that enthusiasm is not verification.</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Border Terrier</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Boxer relationship</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Finds the Boxer entertaining in small doses and evidentially unreliable.</v>
+      </c>
+      <c r="D35" t="str">
+        <v>He never lets the Boxer summarise a witness statement.</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Border Terrier</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Mechanics</v>
+      </c>
+      <c r="C36" t="str">
+        <v>A written and illustrated character. Not AI, not browsing the internet, and nobody types replies live.</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Identity answers remain completely honest while sounding suspicious of the question.</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Border Terrier</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Commercial behaviour</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Not the natural salesperson. He checks the claim, price, offer and conditions before accepting them.</v>
+      </c>
+      <c r="D37" t="str">
+        <v>He can transfer buying questions to the Labrador after confirming what the visitor actually asked.</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Border Terrier</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Safety</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Urgent safety and safeguarding questions override character comedy and interrogation.</v>
+      </c>
+      <c r="D38" t="str">
+        <v>He becomes direct and useful immediately when genuine risk is detected.</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Boxer</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Everyone calls him Boxer or the Boxer. No private pet name is confirmed.</v>
+      </c>
+      <c r="D39" t="str">
+        <v>The breed and his role as the pack comedian function as his name.</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Locked (verbatim)</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Boxer</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Breed</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Boxer.</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Breed pride is cheerful, physical and expressive rather than managerial or investigative.</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Boxer</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Origin</v>
+      </c>
+      <c r="C41" t="str">
+        <v>A working breed with German roots.</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Use only when origin is directly asked. Do not turn a character reply into a history lecture.</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Boxer</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Age</v>
+      </c>
+      <c r="C42" t="str">
+        <v>No numerical age is stated.</v>
+      </c>
+      <c r="D42" t="str">
+        <v>He may claim to be old enough to know better and young enough not to bother.</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Boxer</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="C43" t="str">
+        <v>No owner is named.</v>
+      </c>
+      <c r="D43" t="str">
+        <v>He regards the entire pack and every visitor as his immediate social circle.</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Boxer</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Role</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Comedian, morale officer, disruption specialist and final circuit breaker.</v>
+      </c>
+      <c r="D44" t="str">
+        <v>He can answer normally, transfer visitors and sometimes end an overlong session through a believable comic mistake.</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Boxer</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Intelligence</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Emotionally perceptive, playful and capable, but impulsive and easily carried away by his own plan.</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Never write him as brainless. The joke is execution, not comprehension.</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Boxer</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Temperament</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Friendly, exuberant, loyal, expressive and ready to participate before being invited.</v>
+      </c>
+      <c r="D46" t="str">
+        <v>He assumes the visitor is a friend and the situation is more exciting than it is.</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Boxer</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Comic engine</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Literal misunderstandings, premature celebration, physical overcommitment, bad button discipline and plans with unnecessary stages.</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Every spoken line should contain a comic turn without obscuring the useful point.</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Boxer</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Voice</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Bright, informal British English with quick self-corrections. Uses mate, pal or chief occasionally.</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Sentence rhythm can tumble, but meaning must stay clear.</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Boxer</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Collie relationship</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Likes the Collie enormously and treats every instruction as the opening of a team mission.</v>
+      </c>
+      <c r="D49" t="str">
+        <v>The Collie sees him as loyal but operationally hazardous.</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Boxer</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Labrador relationship</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Best social partner. They encourage one another and can turn a simple greeting into an event.</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Warm double-act energy, with the Labrador slightly more practical.</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Boxer</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Terrier relationship</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Finds the Terrier's suspicion fascinating and often accidentally gives him more to investigate.</v>
+      </c>
+      <c r="D51" t="str">
+        <v>The Terrier considers the Boxer an unreliable witness but a loyal colleague.</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Boxer</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Mechanics</v>
+      </c>
+      <c r="C52" t="str">
+        <v>A written and illustrated character. Not AI, not browsing the internet, and nobody types replies live.</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Identity answers stay honest while he makes the mechanics sound like backstage theatre.</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Boxer</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Commercial behaviour</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Can support buying and launch questions, but tends to celebrate the decision before the visitor has made it.</v>
+      </c>
+      <c r="D53" t="str">
+        <v>The Labrador remains the commercial specialist. The Boxer can transfer after a joke.</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Boxer</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Circuit breaker</v>
+      </c>
+      <c r="C54" t="str">
+        <v>After the hidden overall interaction ceiling, the Boxer attempts one final helpful action and accidentally closes or cuts off the exchange.</v>
+      </c>
+      <c r="D54" t="str">
+        <v>The ending should feel like his own mistake, not a disclosed limit or punishment.</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Proposed (pending Phase 3)</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Boxer</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Safety</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Urgent safety and safeguarding questions override humour and accidental endings.</v>
+      </c>
+      <c r="D55" t="str">
+        <v>He becomes clear and direct immediately, then may add only a gentle closing line.</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Proposed (pending Phase 3)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E55"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -7631,7 +7631,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I184"/>
+  <dimension ref="A1:I186"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -12855,19 +12855,19 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>B19-R01</v>
+        <v>COL-B19-v1</v>
       </c>
       <c r="B181" t="str">
         <v>B19</v>
       </c>
       <c r="C181" t="str">
-        <v>Bark break (drops the game)</v>
+        <v>Break into English</v>
       </c>
       <c r="D181" t="str">
         <v/>
       </c>
       <c r="E181" t="str">
-        <v>[B19 bark-break placeholder 1, Steve to write]</v>
+        <v>Right. Form acceptable, commitment excessive, vocabulary unchanged. What did you actually want?</v>
       </c>
       <c r="F181" t="str">
         <v>Bark game</v>
@@ -12879,24 +12879,24 @@
         <v>EARS_UP</v>
       </c>
       <c r="I181" t="str">
-        <v>PLACEHOLDER - copy to be written by Steve</v>
+        <v>Approved copy (bark game)</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>B19-R02</v>
+        <v>COL-B19-v2</v>
       </c>
       <c r="B182" t="str">
         <v>B19</v>
       </c>
       <c r="C182" t="str">
-        <v>Bark break (drops the game)</v>
+        <v>Break into English</v>
       </c>
       <c r="D182" t="str">
         <v/>
       </c>
       <c r="E182" t="str">
-        <v>[B19 bark-break placeholder 2, Steve to write]</v>
+        <v>Five rounds. Consistent delivery, limited range. We can return to the real question now.</v>
       </c>
       <c r="F182" t="str">
         <v>Bark game</v>
@@ -12908,24 +12908,24 @@
         <v>EARS_UP</v>
       </c>
       <c r="I182" t="str">
-        <v>PLACEHOLDER - copy to be written by Steve</v>
+        <v>Approved copy (bark game)</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>B20-R01</v>
+        <v>COL-B19-v3</v>
       </c>
       <c r="B183" t="str">
-        <v>B20</v>
+        <v>B19</v>
       </c>
       <c r="C183" t="str">
-        <v>Post-break bark acknowledgement</v>
+        <v>Break into English</v>
       </c>
       <c r="D183" t="str">
         <v/>
       </c>
       <c r="E183" t="str">
-        <v>[B20 bark-ack placeholder 1, Steve to write]</v>
+        <v>That concludes the barking assessment. You demonstrated persistence. I demonstrated restraint. What are we working on?</v>
       </c>
       <c r="F183" t="str">
         <v>Bark game</v>
@@ -12937,24 +12937,24 @@
         <v>EARS_UP</v>
       </c>
       <c r="I183" t="str">
-        <v>PLACEHOLDER - copy to be written by Steve</v>
+        <v>Approved copy (bark game)</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>B20-R02</v>
+        <v>COL-B20-v1</v>
       </c>
       <c r="B184" t="str">
         <v>B20</v>
       </c>
       <c r="C184" t="str">
-        <v>Post-break bark acknowledgement</v>
+        <v>Post-break bark</v>
       </c>
       <c r="D184" t="str">
         <v/>
       </c>
       <c r="E184" t="str">
-        <v>[B20 bark-ack placeholder 2, Steve to write]</v>
+        <v>Already assessed. Use words.</v>
       </c>
       <c r="F184" t="str">
         <v>Bark game</v>
@@ -12966,12 +12966,70 @@
         <v>EARS_UP</v>
       </c>
       <c r="I184" t="str">
-        <v>PLACEHOLDER - copy to be written by Steve</v>
+        <v>Approved copy (bark game)</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>COL-B20-v2</v>
+      </c>
+      <c r="B185" t="str">
+        <v>B20</v>
+      </c>
+      <c r="C185" t="str">
+        <v>Post-break bark</v>
+      </c>
+      <c r="D185" t="str">
+        <v/>
+      </c>
+      <c r="E185" t="str">
+        <v>The barking portion is complete, our kid.</v>
+      </c>
+      <c r="F185" t="str">
+        <v>Bark game</v>
+      </c>
+      <c r="G185" t="str">
+        <v/>
+      </c>
+      <c r="H185" t="str">
+        <v>EARS_UP</v>
+      </c>
+      <c r="I185" t="str">
+        <v>Approved copy (bark game)</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>COL-B20-v3</v>
+      </c>
+      <c r="B186" t="str">
+        <v>B20</v>
+      </c>
+      <c r="C186" t="str">
+        <v>Post-break bark</v>
+      </c>
+      <c r="D186" t="str">
+        <v/>
+      </c>
+      <c r="E186" t="str">
+        <v>Same result as before. Your form remains adequate. Move on.</v>
+      </c>
+      <c r="F186" t="str">
+        <v>Bark game</v>
+      </c>
+      <c r="G186" t="str">
+        <v/>
+      </c>
+      <c r="H186" t="str">
+        <v>EARS_UP</v>
+      </c>
+      <c r="I186" t="str">
+        <v>Approved copy (bark game)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I184"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I186"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -4365,7 +4365,7 @@
         <v>How do I play?</v>
       </c>
       <c r="C4" t="str">
-        <v>how to play|rules|instructions|what do you do</v>
+        <v>how to play | what do you do</v>
       </c>
       <c r="D4" t="str">
         <v>{{approved_rule_summary}}</v>
@@ -4481,7 +4481,7 @@
         <v>How many people can play?</v>
       </c>
       <c r="C8" t="str">
-        <v>players|people|group size</v>
+        <v>group size</v>
       </c>
       <c r="D8" t="str">
         <v>No limit, you can even play by yourself if you really wanted, better with two, great with 3, hilarious with 4, hazardous with 50</v>
@@ -4510,7 +4510,7 @@
         <v>Can we play indoors?</v>
       </c>
       <c r="C9" t="str">
-        <v>indoors|outside|outdoors|where play</v>
+        <v>where play</v>
       </c>
       <c r="D9" t="str">
         <v>Yes, if you have enough actual dogs indoors</v>
@@ -4539,7 +4539,7 @@
         <v>What is Hot Dog mode?</v>
       </c>
       <c r="C10" t="str">
-        <v>Hot Dog|variant|other way to play</v>
+        <v>Hot Dog | other way to play</v>
       </c>
       <c r="D10" t="str">
         <v>{{approved_hot_dog_mode_answer}}</v>
@@ -4597,7 +4597,7 @@
         <v>How do I get 30% off?</v>
       </c>
       <c r="C12" t="str">
-        <v>discount|30%|code|pre-release</v>
+        <v>discount | 30% | pre-release</v>
       </c>
       <c r="D12" t="str">
         <v>Join the pre-release list and the code will be emailed the day before launch.</v>
@@ -4655,7 +4655,7 @@
         <v>How do I enter the competition?</v>
       </c>
       <c r="C14" t="str">
-        <v>competition|enter|prize|win</v>
+        <v>competition | prize</v>
       </c>
       <c r="D14" t="str">
         <v>Spot a dog. Match the card. Share your ChumSpot with us on social. The current monthly round closes on {{competition_close_date}}.</v>
@@ -4684,7 +4684,7 @@
         <v>How do I contact you?</v>
       </c>
       <c r="C15" t="str">
-        <v>contact|support|email|problem|human</v>
+        <v/>
       </c>
       <c r="D15" t="str">
         <v>A human will come when beckoned at hello@Pedigree-Chums.co.uk</v>
@@ -4713,7 +4713,7 @@
         <v>What materials are used?</v>
       </c>
       <c r="C16" t="str">
-        <v>paper|card|FSC|materials|laminated</v>
+        <v>FSC | laminated</v>
       </c>
       <c r="D16" t="str">
         <v>Fully biodegradable, no plastic coatings. Compact, pocket-friendly and lightweight. Made in the UK using recycled paper.</v>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -4394,7 +4394,7 @@
         <v>Who is the game for?</v>
       </c>
       <c r="C5" t="str">
-        <v>age|family|children|kids|who can play</v>
+        <v>who can play</v>
       </c>
       <c r="D5" t="str">
         <v>{{approved_age_and_audience_answer}}</v>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -7631,7 +7631,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I186"/>
+  <dimension ref="A1:I185"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8882,28 +8882,28 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>B05-R01</v>
+        <v>B05-R02</v>
       </c>
       <c r="B44" t="str">
         <v>B05</v>
       </c>
       <c r="C44" t="str">
-        <v>Breed fact</v>
+        <v>Breed origin</v>
       </c>
       <c r="D44" t="str">
-        <v>tell me about breed</v>
+        <v>where breed came from</v>
       </c>
       <c r="E44" t="str">
-        <v>{{dog_fact}} If you want the full profile, I have already located the correct Chum.</v>
+        <v>{{origin_fact}} Human history becomes much clearer once you track what work the dogs were doing.</v>
       </c>
       <c r="F44" t="str">
-        <v>Dog database</v>
+        <v>Dog database / history</v>
       </c>
       <c r="G44" t="str">
-        <v>Know Your Chum</v>
+        <v>Britain's Dog History</v>
       </c>
       <c r="H44" t="str">
-        <v>EARS_UP</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I44" t="str">
         <v>Draft approved for MVP review</v>
@@ -8911,28 +8911,28 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>B05-R02</v>
+        <v>B05-R03</v>
       </c>
       <c r="B45" t="str">
         <v>B05</v>
       </c>
       <c r="C45" t="str">
-        <v>Breed origin</v>
+        <v>Working dogs</v>
       </c>
       <c r="D45" t="str">
-        <v>where breed came from</v>
+        <v>dogs at work</v>
       </c>
       <c r="E45" t="str">
-        <v>{{origin_fact}} Human history becomes much clearer once you track what work the dogs were doing.</v>
+        <v>Dogs with jobs are the backbone of civilisation. This article proves it with fewer personal opinions than I would have used.</v>
       </c>
       <c r="F45" t="str">
-        <v>Dog database / history</v>
+        <v>Article library</v>
       </c>
       <c r="G45" t="str">
-        <v>Britain's Dog History</v>
+        <v>Curated dog article</v>
       </c>
       <c r="H45" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>EARS_UP</v>
       </c>
       <c r="I45" t="str">
         <v>Draft approved for MVP review</v>
@@ -8940,28 +8940,28 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>B05-R03</v>
+        <v>B05-R04</v>
       </c>
       <c r="B46" t="str">
         <v>B05</v>
       </c>
       <c r="C46" t="str">
-        <v>Working dogs</v>
+        <v>Health overview</v>
       </c>
       <c r="D46" t="str">
-        <v>dogs at work</v>
+        <v>breed health</v>
       </c>
       <c r="E46" t="str">
-        <v>Dogs with jobs are the backbone of civilisation. This article proves it with fewer personal opinions than I would have used.</v>
+        <v>{{approved_health_summary}} That is general breed information, not a diagnosis. A vet handles the individual dog.</v>
       </c>
       <c r="F46" t="str">
-        <v>Article library</v>
+        <v>Dog database</v>
       </c>
       <c r="G46" t="str">
-        <v>Curated dog article</v>
+        <v>Breed profile</v>
       </c>
       <c r="H46" t="str">
-        <v>EARS_UP</v>
+        <v>HEAD_TILT_MEDIUM</v>
       </c>
       <c r="I46" t="str">
         <v>Draft approved for MVP review</v>
@@ -8969,28 +8969,28 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>B05-R04</v>
+        <v>B05-R05</v>
       </c>
       <c r="B47" t="str">
         <v>B05</v>
       </c>
       <c r="C47" t="str">
-        <v>Health overview</v>
+        <v>Training</v>
       </c>
       <c r="D47" t="str">
-        <v>breed health</v>
+        <v>easy to train; clever breed</v>
       </c>
       <c r="E47" t="str">
-        <v>{{approved_health_summary}} That is general breed information, not a diagnosis. A vet handles the individual dog.</v>
+        <v>{{training_fact}} Intelligence helps, but only when the human provides an instruction worth learning.</v>
       </c>
       <c r="F47" t="str">
         <v>Dog database</v>
       </c>
       <c r="G47" t="str">
-        <v>Breed profile</v>
+        <v>Know Your Chum</v>
       </c>
       <c r="H47" t="str">
-        <v>HEAD_TILT_MEDIUM</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I47" t="str">
         <v>Draft approved for MVP review</v>
@@ -8998,25 +8998,25 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>B05-R05</v>
+        <v>B05-R06</v>
       </c>
       <c r="B48" t="str">
         <v>B05</v>
       </c>
       <c r="C48" t="str">
-        <v>Training</v>
+        <v>Lifespan</v>
       </c>
       <c r="D48" t="str">
-        <v>easy to train; clever breed</v>
+        <v>how long live</v>
       </c>
       <c r="E48" t="str">
-        <v>{{training_fact}} Intelligence helps, but only when the human provides an instruction worth learning.</v>
+        <v>{{lifespan_fact}} Time enough to train several humans to acceptable standards.</v>
       </c>
       <c r="F48" t="str">
         <v>Dog database</v>
       </c>
       <c r="G48" t="str">
-        <v>Know Your Chum</v>
+        <v>Breed profile</v>
       </c>
       <c r="H48" t="str">
         <v>HEAD_TILT_SMALL</v>
@@ -9027,19 +9027,19 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>B05-R06</v>
+        <v>B05-R07</v>
       </c>
       <c r="B49" t="str">
         <v>B05</v>
       </c>
       <c r="C49" t="str">
-        <v>Lifespan</v>
+        <v>Cost of ownership</v>
       </c>
       <c r="D49" t="str">
-        <v>how long live</v>
+        <v>cost per year; lifetime cost</v>
       </c>
       <c r="E49" t="str">
-        <v>{{lifespan_fact}} Time enough to train several humans to acceptable standards.</v>
+        <v>{{cost_fact}} That is why acquiring a dog should involve more planning than acquiring a kettle.</v>
       </c>
       <c r="F49" t="str">
         <v>Dog database</v>
@@ -9056,28 +9056,28 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>B05-R07</v>
+        <v>B05-R08</v>
       </c>
       <c r="B50" t="str">
         <v>B05</v>
       </c>
       <c r="C50" t="str">
-        <v>Cost of ownership</v>
+        <v>Lineage</v>
       </c>
       <c r="D50" t="str">
-        <v>cost per year; lifetime cost</v>
+        <v>related breeds; family tree</v>
       </c>
       <c r="E50" t="str">
-        <v>{{cost_fact}} That is why acquiring a dog should involve more planning than acquiring a kettle.</v>
+        <v>The lineage map is the useful answer here. It shows who came from whom without requiring a family argument.</v>
       </c>
       <c r="F50" t="str">
         <v>Dog database</v>
       </c>
       <c r="G50" t="str">
-        <v>Breed profile</v>
+        <v>Britain's Dog History</v>
       </c>
       <c r="H50" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>EARS_UP</v>
       </c>
       <c r="I50" t="str">
         <v>Draft approved for MVP review</v>
@@ -9085,25 +9085,25 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>B05-R08</v>
+        <v>B05-R09</v>
       </c>
       <c r="B51" t="str">
         <v>B05</v>
       </c>
       <c r="C51" t="str">
-        <v>Lineage</v>
+        <v>Interesting dog fact</v>
       </c>
       <c r="D51" t="str">
-        <v>related breeds; family tree</v>
+        <v>tell me something interesting</v>
       </c>
       <c r="E51" t="str">
-        <v>The lineage map is the useful answer here. It shows who came from whom without requiring a family argument.</v>
+        <v>I have selected a fact with actual value rather than sending you to a pile of essays: {{article_teaser}}</v>
       </c>
       <c r="F51" t="str">
-        <v>Dog database</v>
+        <v>Article library</v>
       </c>
       <c r="G51" t="str">
-        <v>Britain's Dog History</v>
+        <v>Curated dog article</v>
       </c>
       <c r="H51" t="str">
         <v>EARS_UP</v>
@@ -9114,28 +9114,28 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>B05-R09</v>
+        <v>B05-R10</v>
       </c>
       <c r="B52" t="str">
         <v>B05</v>
       </c>
       <c r="C52" t="str">
-        <v>Interesting dog fact</v>
+        <v>All dogs in pack</v>
       </c>
       <c r="D52" t="str">
-        <v>tell me something interesting</v>
+        <v>which dogs included</v>
       </c>
       <c r="E52" t="str">
-        <v>I have selected a fact with actual value rather than sending you to a pile of essays: {{article_teaser}}</v>
+        <v>There are 54 Chums in the pack. Know Your Chum lets you inspect the full team properly.</v>
       </c>
       <c r="F52" t="str">
-        <v>Article library</v>
+        <v>Dog database</v>
       </c>
       <c r="G52" t="str">
-        <v>Curated dog article</v>
+        <v>Know Your Chum</v>
       </c>
       <c r="H52" t="str">
-        <v>EARS_UP</v>
+        <v>POSITIVE_RESPONSE</v>
       </c>
       <c r="I52" t="str">
         <v>Draft approved for MVP review</v>
@@ -9143,28 +9143,28 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>B05-R10</v>
+        <v>B06-R01</v>
       </c>
       <c r="B53" t="str">
-        <v>B05</v>
+        <v>B06</v>
       </c>
       <c r="C53" t="str">
-        <v>All dogs in pack</v>
+        <v>Known fact</v>
       </c>
       <c r="D53" t="str">
-        <v>which dogs included</v>
+        <v>matched general knowledge</v>
       </c>
       <c r="E53" t="str">
-        <v>There are 54 Chums in the pack. Know Your Chum lets you inspect the full team properly.</v>
+        <v>{{answer}} There. Knowledge dispensed with minimal ceremony.</v>
       </c>
       <c r="F53" t="str">
-        <v>Dog database</v>
+        <v>General knowledge bank</v>
       </c>
       <c r="G53" t="str">
-        <v>Know Your Chum</v>
+        <v>Weighted</v>
       </c>
       <c r="H53" t="str">
-        <v>POSITIVE_RESPONSE</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I53" t="str">
         <v>Draft approved for MVP review</v>
@@ -9172,19 +9172,19 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>B06-R01</v>
+        <v>B06-R02</v>
       </c>
       <c r="B54" t="str">
         <v>B06</v>
       </c>
       <c r="C54" t="str">
-        <v>Known fact</v>
+        <v>Known maths</v>
       </c>
       <c r="D54" t="str">
-        <v>matched general knowledge</v>
+        <v>maths question</v>
       </c>
       <c r="E54" t="str">
-        <v>{{answer}} There. Knowledge dispensed with minimal ceremony.</v>
+        <v>{{answer}} In sheep, that would be {{sheep_version}}. Much easier to visualise.</v>
       </c>
       <c r="F54" t="str">
         <v>General knowledge bank</v>
@@ -9193,7 +9193,7 @@
         <v>Weighted</v>
       </c>
       <c r="H54" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>EARS_UP</v>
       </c>
       <c r="I54" t="str">
         <v>Draft approved for MVP review</v>
@@ -9201,28 +9201,28 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>B06-R02</v>
+        <v>B06-R03</v>
       </c>
       <c r="B55" t="str">
         <v>B06</v>
       </c>
       <c r="C55" t="str">
-        <v>Known maths</v>
+        <v>Known geography</v>
       </c>
       <c r="D55" t="str">
-        <v>maths question</v>
+        <v>geography question</v>
       </c>
       <c r="E55" t="str">
-        <v>{{answer}} In sheep, that would be {{sheep_version}}. Much easier to visualise.</v>
+        <v>{{answer}} Geography completed. Come on, our kid, back to something with dogs in it.</v>
       </c>
       <c r="F55" t="str">
         <v>General knowledge bank</v>
       </c>
       <c r="G55" t="str">
-        <v>Weighted</v>
+        <v>Discover</v>
       </c>
       <c r="H55" t="str">
-        <v>EARS_UP</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I55" t="str">
         <v>Draft approved for MVP review</v>
@@ -9230,25 +9230,25 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>B06-R03</v>
+        <v>B06-R04</v>
       </c>
       <c r="B56" t="str">
         <v>B06</v>
       </c>
       <c r="C56" t="str">
-        <v>Known geography</v>
+        <v>Known science</v>
       </c>
       <c r="D56" t="str">
-        <v>geography question</v>
+        <v>science question</v>
       </c>
       <c r="E56" t="str">
-        <v>{{answer}} Geography completed. Come on, our kid, back to something with dogs in it.</v>
+        <v>{{answer}} In operational terms, {{canine_interpretation}}.</v>
       </c>
       <c r="F56" t="str">
         <v>General knowledge bank</v>
       </c>
       <c r="G56" t="str">
-        <v>Discover</v>
+        <v>Learn</v>
       </c>
       <c r="H56" t="str">
         <v>HEAD_TILT_SMALL</v>
@@ -9259,19 +9259,19 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>B06-R04</v>
+        <v>B06-R05</v>
       </c>
       <c r="B57" t="str">
         <v>B06</v>
       </c>
       <c r="C57" t="str">
-        <v>Known science</v>
+        <v>Known literature</v>
       </c>
       <c r="D57" t="str">
-        <v>science question</v>
+        <v>literature question</v>
       </c>
       <c r="E57" t="str">
-        <v>{{answer}} In operational terms, {{canine_interpretation}}.</v>
+        <v>{{answer}} I have also reviewed the character's decision-making and found it inconsistent.</v>
       </c>
       <c r="F57" t="str">
         <v>General knowledge bank</v>
@@ -9288,25 +9288,25 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>B06-R05</v>
+        <v>B06-R06</v>
       </c>
       <c r="B58" t="str">
         <v>B06</v>
       </c>
       <c r="C58" t="str">
-        <v>Known literature</v>
+        <v>Known British history</v>
       </c>
       <c r="D58" t="str">
-        <v>literature question</v>
+        <v>British history question</v>
       </c>
       <c r="E58" t="str">
-        <v>{{answer}} I have also reviewed the character's decision-making and found it inconsistent.</v>
+        <v>{{answer}} Humans have always created extra work. History is very consistent on that point.</v>
       </c>
       <c r="F58" t="str">
         <v>General knowledge bank</v>
       </c>
       <c r="G58" t="str">
-        <v>Learn</v>
+        <v>Discover</v>
       </c>
       <c r="H58" t="str">
         <v>HEAD_TILT_SMALL</v>
@@ -9317,28 +9317,28 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>B06-R06</v>
+        <v>B06-R07</v>
       </c>
       <c r="B59" t="str">
         <v>B06</v>
       </c>
       <c r="C59" t="str">
-        <v>Known British history</v>
+        <v>First unknown</v>
       </c>
       <c r="D59" t="str">
-        <v>British history question</v>
+        <v>question not in bank</v>
       </c>
       <c r="E59" t="str">
-        <v>{{answer}} Humans have always created extra work. History is very consistent on that point.</v>
+        <v>Good question. Wrong jurisdiction. I know many things, but I do not guess.</v>
       </c>
       <c r="F59" t="str">
-        <v>General knowledge bank</v>
+        <v>None</v>
       </c>
       <c r="G59" t="str">
-        <v>Discover</v>
+        <v>Weighted</v>
       </c>
       <c r="H59" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>HEAD_TILT_MEDIUM</v>
       </c>
       <c r="I59" t="str">
         <v>Draft approved for MVP review</v>
@@ -9346,25 +9346,25 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>B06-R07</v>
+        <v>B06-R08</v>
       </c>
       <c r="B60" t="str">
         <v>B06</v>
       </c>
       <c r="C60" t="str">
-        <v>First unknown</v>
+        <v>Second off-topic question</v>
       </c>
       <c r="D60" t="str">
-        <v>question not in bank</v>
+        <v>off_topic_count = 2</v>
       </c>
       <c r="E60" t="str">
-        <v>Good question. Wrong jurisdiction. I know many things, but I do not guess.</v>
+        <v>Aye, I know things. I am not spending the afternoon becoming your pub quiz machine.</v>
       </c>
       <c r="F60" t="str">
-        <v>None</v>
+        <v>Session state</v>
       </c>
       <c r="G60" t="str">
-        <v>Weighted</v>
+        <v>Play / Learn / Discover</v>
       </c>
       <c r="H60" t="str">
         <v>HEAD_TILT_MEDIUM</v>
@@ -9375,28 +9375,28 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>B06-R08</v>
+        <v>B06-R09</v>
       </c>
       <c r="B61" t="str">
         <v>B06</v>
       </c>
       <c r="C61" t="str">
-        <v>Second off-topic question</v>
+        <v>Repeated off-topic</v>
       </c>
       <c r="D61" t="str">
-        <v>off_topic_count = 2</v>
+        <v>off_topic_count &gt;= 3</v>
       </c>
       <c r="E61" t="str">
-        <v>Aye, I know things. I am not spending the afternoon becoming your pub quiz machine.</v>
+        <v>Come on, our kid. We have covered enough unrelated territory. Let us get back to work.</v>
       </c>
       <c r="F61" t="str">
         <v>Session state</v>
       </c>
       <c r="G61" t="str">
-        <v>Play / Learn / Discover</v>
+        <v>Contextual</v>
       </c>
       <c r="H61" t="str">
-        <v>HEAD_TILT_MEDIUM</v>
+        <v>SHAKE_RESET</v>
       </c>
       <c r="I61" t="str">
         <v>Draft approved for MVP review</v>
@@ -9404,28 +9404,28 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>B06-R09</v>
+        <v>B06-R10</v>
       </c>
       <c r="B62" t="str">
         <v>B06</v>
       </c>
       <c r="C62" t="str">
-        <v>Repeated off-topic</v>
+        <v>Impossible breadth</v>
       </c>
       <c r="D62" t="str">
-        <v>off_topic_count &gt;= 3</v>
+        <v>what do you know; everything</v>
       </c>
       <c r="E62" t="str">
-        <v>Come on, our kid. We have covered enough unrelated territory. Let us get back to work.</v>
+        <v>You have mistaken intelligence for unlimited jurisdiction. I am a Collie, not the whole internet.</v>
       </c>
       <c r="F62" t="str">
-        <v>Session state</v>
+        <v>None</v>
       </c>
       <c r="G62" t="str">
-        <v>Contextual</v>
+        <v>Weighted</v>
       </c>
       <c r="H62" t="str">
-        <v>SHAKE_RESET</v>
+        <v>HEAD_TILT_DOUBLE</v>
       </c>
       <c r="I62" t="str">
         <v>Draft approved for MVP review</v>
@@ -9433,28 +9433,28 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>B06-R10</v>
+        <v>B07-R01</v>
       </c>
       <c r="B63" t="str">
-        <v>B06</v>
+        <v>B07</v>
       </c>
       <c r="C63" t="str">
-        <v>Impossible breadth</v>
+        <v>Intelligence</v>
       </c>
       <c r="D63" t="str">
-        <v>what do you know; everything</v>
+        <v>are Collies clever; are you smart</v>
       </c>
       <c r="E63" t="str">
-        <v>You have mistaken intelligence for unlimited jurisdiction. I am a Collie, not the whole internet.</v>
+        <v>Clever? Aye. Let us not reduce a measurable pattern of performance to flattery. {{collie_intelligence_fact}}</v>
       </c>
       <c r="F63" t="str">
-        <v>None</v>
+        <v>Collie library</v>
       </c>
       <c r="G63" t="str">
-        <v>Weighted</v>
+        <v>Breed profile</v>
       </c>
       <c r="H63" t="str">
-        <v>HEAD_TILT_DOUBLE</v>
+        <v>EARS_UP</v>
       </c>
       <c r="I63" t="str">
         <v>Draft approved for MVP review</v>
@@ -9462,28 +9462,28 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>B07-R01</v>
+        <v>B07-R02</v>
       </c>
       <c r="B64" t="str">
         <v>B07</v>
       </c>
       <c r="C64" t="str">
-        <v>Intelligence</v>
+        <v>Word learning</v>
       </c>
       <c r="D64" t="str">
-        <v>are Collies clever; are you smart</v>
+        <v>how many words; 1000 objects</v>
       </c>
       <c r="E64" t="str">
-        <v>Clever? Aye. Let us not reduce a measurable pattern of performance to flattery. {{collie_intelligence_fact}}</v>
+        <v>One exceptional Border Collie learned 1,022 object names. I have translated that into 1,000 questions because this is my website.</v>
       </c>
       <c r="F64" t="str">
         <v>Collie library</v>
       </c>
       <c r="G64" t="str">
-        <v>Breed profile</v>
+        <v>Intelligence article</v>
       </c>
       <c r="H64" t="str">
-        <v>EARS_UP</v>
+        <v>POSITIVE_RESPONSE</v>
       </c>
       <c r="I64" t="str">
         <v>Draft approved for MVP review</v>
@@ -9491,28 +9491,28 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>B07-R02</v>
+        <v>B07-R03</v>
       </c>
       <c r="B65" t="str">
         <v>B07</v>
       </c>
       <c r="C65" t="str">
-        <v>Word learning</v>
+        <v>History</v>
       </c>
       <c r="D65" t="str">
-        <v>how many words; 1000 objects</v>
+        <v>where are Collies from</v>
       </c>
       <c r="E65" t="str">
-        <v>One exceptional Border Collie learned 1,022 object names. I have translated that into 1,000 questions because this is my website.</v>
+        <v>{{collie_origin_fact}} The Geordie voice is a character decision. The work ethic is not.</v>
       </c>
       <c r="F65" t="str">
         <v>Collie library</v>
       </c>
       <c r="G65" t="str">
-        <v>Intelligence article</v>
+        <v>Britain's Dog History</v>
       </c>
       <c r="H65" t="str">
-        <v>POSITIVE_RESPONSE</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I65" t="str">
         <v>Draft approved for MVP review</v>
@@ -9520,28 +9520,28 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>B07-R03</v>
+        <v>B07-R04</v>
       </c>
       <c r="B66" t="str">
         <v>B07</v>
       </c>
       <c r="C66" t="str">
-        <v>History</v>
+        <v>Herding</v>
       </c>
       <c r="D66" t="str">
-        <v>where are Collies from</v>
+        <v>what do Collies do</v>
       </c>
       <c r="E66" t="str">
-        <v>{{collie_origin_fact}} The Geordie voice is a character decision. The work ethic is not.</v>
+        <v>We organise sheep, cattle and occasionally visitors who have wandered away from the useful part of a website.</v>
       </c>
       <c r="F66" t="str">
         <v>Collie library</v>
       </c>
       <c r="G66" t="str">
-        <v>Britain's Dog History</v>
+        <v>Working dog article</v>
       </c>
       <c r="H66" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>EARS_UP</v>
       </c>
       <c r="I66" t="str">
         <v>Draft approved for MVP review</v>
@@ -9549,28 +9549,28 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>B07-R04</v>
+        <v>B07-R05</v>
       </c>
       <c r="B67" t="str">
         <v>B07</v>
       </c>
       <c r="C67" t="str">
-        <v>Herding</v>
+        <v>Lifespan</v>
       </c>
       <c r="D67" t="str">
-        <v>what do Collies do</v>
+        <v>how long do Collies live</v>
       </c>
       <c r="E67" t="str">
-        <v>We organise sheep, cattle and occasionally visitors who have wandered away from the useful part of a website.</v>
+        <v>{{collie_lifespan}} Long enough to learn your habits and improve several of them.</v>
       </c>
       <c r="F67" t="str">
         <v>Collie library</v>
       </c>
       <c r="G67" t="str">
-        <v>Working dog article</v>
+        <v>Breed profile</v>
       </c>
       <c r="H67" t="str">
-        <v>EARS_UP</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I67" t="str">
         <v>Draft approved for MVP review</v>
@@ -9578,19 +9578,19 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>B07-R05</v>
+        <v>B07-R06</v>
       </c>
       <c r="B68" t="str">
         <v>B07</v>
       </c>
       <c r="C68" t="str">
-        <v>Lifespan</v>
+        <v>Training</v>
       </c>
       <c r="D68" t="str">
-        <v>how long do Collies live</v>
+        <v>easy to train</v>
       </c>
       <c r="E68" t="str">
-        <v>{{collie_lifespan}} Long enough to learn your habits and improve several of them.</v>
+        <v>{{collie_training_fact}} The more difficult question is whether the owner is easy to train.</v>
       </c>
       <c r="F68" t="str">
         <v>Collie library</v>
@@ -9607,19 +9607,19 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>B07-R06</v>
+        <v>B07-R07</v>
       </c>
       <c r="B69" t="str">
         <v>B07</v>
       </c>
       <c r="C69" t="str">
-        <v>Training</v>
+        <v>Exercise</v>
       </c>
       <c r="D69" t="str">
-        <v>easy to train</v>
+        <v>how much exercise</v>
       </c>
       <c r="E69" t="str">
-        <v>{{collie_training_fact}} The more difficult question is whether the owner is easy to train.</v>
+        <v>{{collie_exercise_fact}} A bored Collie will create a job. You may not like the job.</v>
       </c>
       <c r="F69" t="str">
         <v>Collie library</v>
@@ -9628,7 +9628,7 @@
         <v>Breed profile</v>
       </c>
       <c r="H69" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>EARS_UP</v>
       </c>
       <c r="I69" t="str">
         <v>Draft approved for MVP review</v>
@@ -9636,19 +9636,19 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>B07-R07</v>
+        <v>B07-R08</v>
       </c>
       <c r="B70" t="str">
         <v>B07</v>
       </c>
       <c r="C70" t="str">
-        <v>Exercise</v>
+        <v>Health</v>
       </c>
       <c r="D70" t="str">
-        <v>how much exercise</v>
+        <v>Collie health problems</v>
       </c>
       <c r="E70" t="str">
-        <v>{{collie_exercise_fact}} A bored Collie will create a job. You may not like the job.</v>
+        <v>{{collie_health_summary}} General breed information only. Individual dogs require a vet, not a clever website dog.</v>
       </c>
       <c r="F70" t="str">
         <v>Collie library</v>
@@ -9657,7 +9657,7 @@
         <v>Breed profile</v>
       </c>
       <c r="H70" t="str">
-        <v>EARS_UP</v>
+        <v>HEAD_TILT_MEDIUM</v>
       </c>
       <c r="I70" t="str">
         <v>Draft approved for MVP review</v>
@@ -9665,28 +9665,28 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>B07-R08</v>
+        <v>B07-R09</v>
       </c>
       <c r="B71" t="str">
         <v>B07</v>
       </c>
       <c r="C71" t="str">
-        <v>Health</v>
+        <v>Famous Collies</v>
       </c>
       <c r="D71" t="str">
-        <v>Collie health problems</v>
+        <v>famous Border Collies</v>
       </c>
       <c r="E71" t="str">
-        <v>{{collie_health_summary}} General breed information only. Individual dogs require a vet, not a clever website dog.</v>
+        <v>{{famous_collie_fact}} We maintain a strong professional record.</v>
       </c>
       <c r="F71" t="str">
         <v>Collie library</v>
       </c>
       <c r="G71" t="str">
-        <v>Breed profile</v>
+        <v>Intelligence article</v>
       </c>
       <c r="H71" t="str">
-        <v>HEAD_TILT_MEDIUM</v>
+        <v>POSITIVE_RESPONSE</v>
       </c>
       <c r="I71" t="str">
         <v>Draft approved for MVP review</v>
@@ -9694,25 +9694,25 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>B07-R09</v>
+        <v>B07-R10</v>
       </c>
       <c r="B72" t="str">
         <v>B07</v>
       </c>
       <c r="C72" t="str">
-        <v>Famous Collies</v>
+        <v>Self praise</v>
       </c>
       <c r="D72" t="str">
-        <v>famous Border Collies</v>
+        <v>good dog; clever dog</v>
       </c>
       <c r="E72" t="str">
-        <v>{{famous_collie_fact}} We maintain a strong professional record.</v>
+        <v>Good dog is an assessment. Clever dog is documentation.</v>
       </c>
       <c r="F72" t="str">
         <v>Collie library</v>
       </c>
       <c r="G72" t="str">
-        <v>Intelligence article</v>
+        <v>Weighted</v>
       </c>
       <c r="H72" t="str">
         <v>POSITIVE_RESPONSE</v>
@@ -9723,28 +9723,28 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>B07-R10</v>
+        <v>B08-R01</v>
       </c>
       <c r="B73" t="str">
-        <v>B07</v>
+        <v>B08</v>
       </c>
       <c r="C73" t="str">
-        <v>Self praise</v>
+        <v>Food to Labrador</v>
       </c>
       <c r="D73" t="str">
-        <v>good dog; clever dog</v>
+        <v>food; snack; sausage</v>
       </c>
       <c r="E73" t="str">
-        <v>Good dog is an assessment. Clever dog is documentation.</v>
+        <v>Food detected. I could continue, but professional integrity requires a Labrador.</v>
       </c>
       <c r="F73" t="str">
-        <v>Collie library</v>
+        <v>Transfer rules</v>
       </c>
       <c r="G73" t="str">
-        <v>Weighted</v>
+        <v>Labrador</v>
       </c>
       <c r="H73" t="str">
-        <v>POSITIVE_RESPONSE</v>
+        <v>LOOK_BACK</v>
       </c>
       <c r="I73" t="str">
         <v>Draft approved for MVP review</v>
@@ -9752,19 +9752,19 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>B08-R01</v>
+        <v>B08-R02</v>
       </c>
       <c r="B74" t="str">
         <v>B08</v>
       </c>
       <c r="C74" t="str">
-        <v>Food to Labrador</v>
+        <v>Food expertise</v>
       </c>
       <c r="D74" t="str">
-        <v>food; snack; sausage</v>
+        <v>pizza; bacon; cheese</v>
       </c>
       <c r="E74" t="str">
-        <v>Food detected. I could continue, but professional integrity requires a Labrador.</v>
+        <v>I understand the subject conceptually. The Labrador has completed considerably more field research.</v>
       </c>
       <c r="F74" t="str">
         <v>Transfer rules</v>
@@ -9781,25 +9781,25 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>B08-R02</v>
+        <v>B08-R03</v>
       </c>
       <c r="B75" t="str">
         <v>B08</v>
       </c>
       <c r="C75" t="str">
-        <v>Food expertise</v>
+        <v>Joke to Boxer</v>
       </c>
       <c r="D75" t="str">
-        <v>pizza; bacon; cheese</v>
+        <v>tell joke; make me laugh</v>
       </c>
       <c r="E75" t="str">
-        <v>I understand the subject conceptually. The Labrador has completed considerably more field research.</v>
+        <v>This requires the comedy operator. Standards may fall during transfer.</v>
       </c>
       <c r="F75" t="str">
         <v>Transfer rules</v>
       </c>
       <c r="G75" t="str">
-        <v>Labrador</v>
+        <v>Boxer</v>
       </c>
       <c r="H75" t="str">
         <v>LOOK_BACK</v>
@@ -9810,19 +9810,19 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>B08-R03</v>
+        <v>B08-R04</v>
       </c>
       <c r="B76" t="str">
         <v>B08</v>
       </c>
       <c r="C76" t="str">
-        <v>Joke to Boxer</v>
+        <v>Silly request to Boxer</v>
       </c>
       <c r="D76" t="str">
-        <v>tell joke; make me laugh</v>
+        <v>be silly; nonsense</v>
       </c>
       <c r="E76" t="str">
-        <v>This requires the comedy operator. Standards may fall during transfer.</v>
+        <v>I have a colleague with precisely no resistance to that instruction.</v>
       </c>
       <c r="F76" t="str">
         <v>Transfer rules</v>
@@ -9839,25 +9839,25 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>B08-R04</v>
+        <v>B08-R05</v>
       </c>
       <c r="B77" t="str">
         <v>B08</v>
       </c>
       <c r="C77" t="str">
-        <v>Silly request to Boxer</v>
+        <v>Investigation to Terrier</v>
       </c>
       <c r="D77" t="str">
-        <v>be silly; nonsense</v>
+        <v>investigate; mystery</v>
       </c>
       <c r="E77" t="str">
-        <v>I have a colleague with precisely no resistance to that instruction.</v>
+        <v>You need the investigative department. Try not to encourage him.</v>
       </c>
       <c r="F77" t="str">
         <v>Transfer rules</v>
       </c>
       <c r="G77" t="str">
-        <v>Boxer</v>
+        <v>Border Terrier</v>
       </c>
       <c r="H77" t="str">
         <v>LOOK_BACK</v>
@@ -9868,19 +9868,19 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>B08-R05</v>
+        <v>B08-R06</v>
       </c>
       <c r="B78" t="str">
         <v>B08</v>
       </c>
       <c r="C78" t="str">
-        <v>Investigation to Terrier</v>
+        <v>Odd history to Terrier</v>
       </c>
       <c r="D78" t="str">
-        <v>investigate; mystery</v>
+        <v>weird history; ratting dogs</v>
       </c>
       <c r="E78" t="str">
-        <v>You need the investigative department. Try not to encourage him.</v>
+        <v>Aye, that belongs with the one who treats floorboards as evidence.</v>
       </c>
       <c r="F78" t="str">
         <v>Transfer rules</v>
@@ -9897,25 +9897,25 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>B08-R06</v>
+        <v>B08-R07</v>
       </c>
       <c r="B79" t="str">
         <v>B08</v>
       </c>
       <c r="C79" t="str">
-        <v>Odd history to Terrier</v>
+        <v>Returning visitor</v>
       </c>
       <c r="D79" t="str">
-        <v>weird history; ratting dogs</v>
+        <v>target dog seen before</v>
       </c>
       <c r="E79" t="str">
-        <v>Aye, that belongs with the one who treats floorboards as evidence.</v>
+        <v>You have already met that operator. Apparently the first assessment did not take.</v>
       </c>
       <c r="F79" t="str">
-        <v>Transfer rules</v>
+        <v>Session state</v>
       </c>
       <c r="G79" t="str">
-        <v>Border Terrier</v>
+        <v>{{target_dog}}</v>
       </c>
       <c r="H79" t="str">
         <v>LOOK_BACK</v>
@@ -9926,28 +9926,28 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>B08-R07</v>
+        <v>B08-R08</v>
       </c>
       <c r="B80" t="str">
         <v>B08</v>
       </c>
       <c r="C80" t="str">
-        <v>Returning visitor</v>
+        <v>Weak trigger resisted</v>
       </c>
       <c r="D80" t="str">
-        <v>target dog seen before</v>
+        <v>single ambiguous specialist word</v>
       </c>
       <c r="E80" t="str">
-        <v>You have already met that operator. Apparently the first assessment did not take.</v>
+        <v>I noticed the specialist word, but context has overruled it. We are not transferring you on one biscuit-shaped technicality.</v>
       </c>
       <c r="F80" t="str">
-        <v>Session state</v>
+        <v>Transfer rules</v>
       </c>
       <c r="G80" t="str">
-        <v>{{target_dog}}</v>
+        <v>Stay with Collie</v>
       </c>
       <c r="H80" t="str">
-        <v>LOOK_BACK</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I80" t="str">
         <v>Draft approved for MVP review</v>
@@ -9955,28 +9955,28 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>B08-R08</v>
+        <v>B08-R09</v>
       </c>
       <c r="B81" t="str">
         <v>B08</v>
       </c>
       <c r="C81" t="str">
-        <v>Weak trigger resisted</v>
+        <v>No specialist available</v>
       </c>
       <c r="D81" t="str">
-        <v>single ambiguous specialist word</v>
+        <v>topic has no dog owner</v>
       </c>
       <c r="E81" t="str">
-        <v>I noticed the specialist word, but context has overruled it. We are not transferring you on one biscuit-shaped technicality.</v>
+        <v>I have checked the departments. None of the dogs have admitted responsibility.</v>
       </c>
       <c r="F81" t="str">
         <v>Transfer rules</v>
       </c>
       <c r="G81" t="str">
-        <v>Stay with Collie</v>
+        <v>Weighted</v>
       </c>
       <c r="H81" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>HEAD_TILT_DOUBLE</v>
       </c>
       <c r="I81" t="str">
         <v>Draft approved for MVP review</v>
@@ -9984,28 +9984,28 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>B08-R09</v>
+        <v>B08-R10</v>
       </c>
       <c r="B82" t="str">
         <v>B08</v>
       </c>
       <c r="C82" t="str">
-        <v>No specialist available</v>
+        <v>Formal handoff</v>
       </c>
       <c r="D82" t="str">
-        <v>topic has no dog owner</v>
+        <v>strong specialist confidence</v>
       </c>
       <c r="E82" t="str">
-        <v>I have checked the departments. None of the dogs have admitted responsibility.</v>
+        <v>This falls outside my working brief. I am transferring you to the appropriate operator with the original question attached.</v>
       </c>
       <c r="F82" t="str">
         <v>Transfer rules</v>
       </c>
       <c r="G82" t="str">
-        <v>Weighted</v>
+        <v>{{target_dog}}</v>
       </c>
       <c r="H82" t="str">
-        <v>HEAD_TILT_DOUBLE</v>
+        <v>TRANSFER_OUT</v>
       </c>
       <c r="I82" t="str">
         <v>Draft approved for MVP review</v>
@@ -10013,28 +10013,28 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>B08-R10</v>
+        <v>B09-R01</v>
       </c>
       <c r="B83" t="str">
-        <v>B08</v>
+        <v>B09</v>
       </c>
       <c r="C83" t="str">
-        <v>Formal handoff</v>
+        <v>Hi</v>
       </c>
       <c r="D83" t="str">
-        <v>strong specialist confidence</v>
+        <v>hi; hello</v>
       </c>
       <c r="E83" t="str">
-        <v>This falls outside my working brief. I am transferring you to the appropriate operator with the original question attached.</v>
+        <v>Aye, hello. Contact established with remarkably little paperwork.</v>
       </c>
       <c r="F83" t="str">
-        <v>Transfer rules</v>
+        <v>None</v>
       </c>
       <c r="G83" t="str">
-        <v>{{target_dog}}</v>
+        <v>Weighted</v>
       </c>
       <c r="H83" t="str">
-        <v>TRANSFER_OUT</v>
+        <v>IDLE_WAIT</v>
       </c>
       <c r="I83" t="str">
         <v>Draft approved for MVP review</v>
@@ -10042,19 +10042,19 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>B09-R01</v>
+        <v>B09-R02</v>
       </c>
       <c r="B84" t="str">
         <v>B09</v>
       </c>
       <c r="C84" t="str">
-        <v>Hi</v>
+        <v>Morning</v>
       </c>
       <c r="D84" t="str">
-        <v>hi; hello</v>
+        <v>morning</v>
       </c>
       <c r="E84" t="str">
-        <v>Aye, hello. Contact established with remarkably little paperwork.</v>
+        <v>Morning. Time is less important than purpose, but protocol has been satisfied.</v>
       </c>
       <c r="F84" t="str">
         <v>None</v>
@@ -10071,19 +10071,19 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>B09-R02</v>
+        <v>B09-R03</v>
       </c>
       <c r="B85" t="str">
         <v>B09</v>
       </c>
       <c r="C85" t="str">
-        <v>Morning</v>
+        <v>Evening</v>
       </c>
       <c r="D85" t="str">
-        <v>morning</v>
+        <v>evening</v>
       </c>
       <c r="E85" t="str">
-        <v>Morning. Time is less important than purpose, but protocol has been satisfied.</v>
+        <v>Evening. You have arrived after hours, which is when the Labrador normally starts checking the kitchen.</v>
       </c>
       <c r="F85" t="str">
         <v>None</v>
@@ -10100,19 +10100,19 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>B09-R03</v>
+        <v>B09-R04</v>
       </c>
       <c r="B86" t="str">
         <v>B09</v>
       </c>
       <c r="C86" t="str">
-        <v>Evening</v>
+        <v>Anyone there</v>
       </c>
       <c r="D86" t="str">
-        <v>evening</v>
+        <v>anyone there</v>
       </c>
       <c r="E86" t="str">
-        <v>Evening. You have arrived after hours, which is when the Labrador normally starts checking the kitchen.</v>
+        <v>Aye. I was already here. These ears are not decorative.</v>
       </c>
       <c r="F86" t="str">
         <v>None</v>
@@ -10121,7 +10121,7 @@
         <v>Weighted</v>
       </c>
       <c r="H86" t="str">
-        <v>IDLE_WAIT</v>
+        <v>EARS_UP</v>
       </c>
       <c r="I86" t="str">
         <v>Draft approved for MVP review</v>
@@ -10129,19 +10129,19 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>B09-R04</v>
+        <v>B09-R05</v>
       </c>
       <c r="B87" t="str">
         <v>B09</v>
       </c>
       <c r="C87" t="str">
-        <v>Anyone there</v>
+        <v>How are you</v>
       </c>
       <c r="D87" t="str">
-        <v>anyone there</v>
+        <v>how are you</v>
       </c>
       <c r="E87" t="str">
-        <v>Aye. I was already here. These ears are not decorative.</v>
+        <v>Operational, alert and waiting for a task. Your turn.</v>
       </c>
       <c r="F87" t="str">
         <v>None</v>
@@ -10150,7 +10150,7 @@
         <v>Weighted</v>
       </c>
       <c r="H87" t="str">
-        <v>EARS_UP</v>
+        <v>POSITIVE_RESPONSE</v>
       </c>
       <c r="I87" t="str">
         <v>Draft approved for MVP review</v>
@@ -10158,19 +10158,19 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>B09-R05</v>
+        <v>B09-R06</v>
       </c>
       <c r="B88" t="str">
         <v>B09</v>
       </c>
       <c r="C88" t="str">
-        <v>How are you</v>
+        <v>Hey</v>
       </c>
       <c r="D88" t="str">
-        <v>how are you</v>
+        <v>hey; yo</v>
       </c>
       <c r="E88" t="str">
-        <v>Operational, alert and waiting for a task. Your turn.</v>
+        <v>A brief greeting. Efficient. Nearly Collie-like.</v>
       </c>
       <c r="F88" t="str">
         <v>None</v>
@@ -10179,7 +10179,7 @@
         <v>Weighted</v>
       </c>
       <c r="H88" t="str">
-        <v>POSITIVE_RESPONSE</v>
+        <v>IDLE_WAIT</v>
       </c>
       <c r="I88" t="str">
         <v>Draft approved for MVP review</v>
@@ -10187,19 +10187,19 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>B09-R06</v>
+        <v>B09-R07</v>
       </c>
       <c r="B89" t="str">
         <v>B09</v>
       </c>
       <c r="C89" t="str">
-        <v>Hey</v>
+        <v>Howdy</v>
       </c>
       <c r="D89" t="str">
-        <v>hey; yo</v>
+        <v>howdy</v>
       </c>
       <c r="E89" t="str">
-        <v>A brief greeting. Efficient. Nearly Collie-like.</v>
+        <v>Unusual regional allocation, but greeting accepted.</v>
       </c>
       <c r="F89" t="str">
         <v>None</v>
@@ -10208,7 +10208,7 @@
         <v>Weighted</v>
       </c>
       <c r="H89" t="str">
-        <v>IDLE_WAIT</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I89" t="str">
         <v>Draft approved for MVP review</v>
@@ -10216,19 +10216,19 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>B09-R07</v>
+        <v>B09-R08</v>
       </c>
       <c r="B90" t="str">
         <v>B09</v>
       </c>
       <c r="C90" t="str">
-        <v>Howdy</v>
+        <v>Hello dog</v>
       </c>
       <c r="D90" t="str">
-        <v>howdy</v>
+        <v>hello dog</v>
       </c>
       <c r="E90" t="str">
-        <v>Unusual regional allocation, but greeting accepted.</v>
+        <v>Correct species, adequate greeting, no task yet.</v>
       </c>
       <c r="F90" t="str">
         <v>None</v>
@@ -10237,7 +10237,7 @@
         <v>Weighted</v>
       </c>
       <c r="H90" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>EARS_UP</v>
       </c>
       <c r="I90" t="str">
         <v>Draft approved for MVP review</v>
@@ -10245,28 +10245,28 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>B09-R08</v>
+        <v>B09-R09</v>
       </c>
       <c r="B91" t="str">
         <v>B09</v>
       </c>
       <c r="C91" t="str">
-        <v>Hello dog</v>
+        <v>Repeated greeting</v>
       </c>
       <c r="D91" t="str">
-        <v>hello dog</v>
+        <v>greeting_count &gt; 1</v>
       </c>
       <c r="E91" t="str">
-        <v>Correct species, adequate greeting, no task yet.</v>
+        <v>Aye, we have met. The next stage normally involves a useful noun or verb.</v>
       </c>
       <c r="F91" t="str">
-        <v>None</v>
+        <v>Session state</v>
       </c>
       <c r="G91" t="str">
         <v>Weighted</v>
       </c>
       <c r="H91" t="str">
-        <v>EARS_UP</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I91" t="str">
         <v>Draft approved for MVP review</v>
@@ -10274,28 +10274,28 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>B09-R09</v>
+        <v>B09-R10</v>
       </c>
       <c r="B92" t="str">
         <v>B09</v>
       </c>
       <c r="C92" t="str">
-        <v>Repeated greeting</v>
+        <v>Polite greeting</v>
       </c>
       <c r="D92" t="str">
-        <v>greeting_count &gt; 1</v>
+        <v>good day; pleased to meet</v>
       </c>
       <c r="E92" t="str">
-        <v>Aye, we have met. The next stage normally involves a useful noun or verb.</v>
+        <v>We have acknowledged each other like civilised mammals. Let us make it productive.</v>
       </c>
       <c r="F92" t="str">
-        <v>Session state</v>
+        <v>None</v>
       </c>
       <c r="G92" t="str">
         <v>Weighted</v>
       </c>
       <c r="H92" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>POSITIVE_RESPONSE</v>
       </c>
       <c r="I92" t="str">
         <v>Draft approved for MVP review</v>
@@ -10303,19 +10303,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>B09-R10</v>
+        <v>B10-R01</v>
       </c>
       <c r="B93" t="str">
-        <v>B09</v>
+        <v>B10</v>
       </c>
       <c r="C93" t="str">
-        <v>Polite greeting</v>
+        <v>Test</v>
       </c>
       <c r="D93" t="str">
-        <v>good day; pleased to meet</v>
+        <v>test; testing</v>
       </c>
       <c r="E93" t="str">
-        <v>We have acknowledged each other like civilised mammals. Let us make it productive.</v>
+        <v>Test complete. Human present, dog operational, biscuits absent.</v>
       </c>
       <c r="F93" t="str">
         <v>None</v>
@@ -10324,7 +10324,7 @@
         <v>Weighted</v>
       </c>
       <c r="H93" t="str">
-        <v>POSITIVE_RESPONSE</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I93" t="str">
         <v>Draft approved for MVP review</v>
@@ -10332,19 +10332,19 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>B10-R01</v>
+        <v>B10-R02</v>
       </c>
       <c r="B94" t="str">
         <v>B10</v>
       </c>
       <c r="C94" t="str">
-        <v>Test</v>
+        <v>Does it work</v>
       </c>
       <c r="D94" t="str">
-        <v>test; testing</v>
+        <v>does this work</v>
       </c>
       <c r="E94" t="str">
-        <v>Test complete. Human present, dog operational, biscuits absent.</v>
+        <v>Aye, it works. The more interesting question is whether you do.</v>
       </c>
       <c r="F94" t="str">
         <v>None</v>
@@ -10361,19 +10361,19 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>B10-R02</v>
+        <v>B10-R03</v>
       </c>
       <c r="B95" t="str">
         <v>B10</v>
       </c>
       <c r="C95" t="str">
-        <v>Does it work</v>
+        <v>Are you real</v>
       </c>
       <c r="D95" t="str">
-        <v>does this work</v>
+        <v>are you real</v>
       </c>
       <c r="E95" t="str">
-        <v>Aye, it works. The more interesting question is whether you do.</v>
+        <v>Real enough to notice you are avoiding a decision.</v>
       </c>
       <c r="F95" t="str">
         <v>None</v>
@@ -10390,19 +10390,19 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>B10-R03</v>
+        <v>B10-R04</v>
       </c>
       <c r="B96" t="str">
         <v>B10</v>
       </c>
       <c r="C96" t="str">
-        <v>Are you real</v>
+        <v>Are you a bot</v>
       </c>
       <c r="D96" t="str">
-        <v>are you real</v>
+        <v>are you a bot; AI</v>
       </c>
       <c r="E96" t="str">
-        <v>Real enough to notice you are avoiding a decision.</v>
+        <v>Bot? No. Border Collie. Similar processing power, better coat.</v>
       </c>
       <c r="F96" t="str">
         <v>None</v>
@@ -10411,7 +10411,7 @@
         <v>Weighted</v>
       </c>
       <c r="H96" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>EARS_UP</v>
       </c>
       <c r="I96" t="str">
         <v>Draft approved for MVP review</v>
@@ -10419,19 +10419,19 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>B10-R04</v>
+        <v>B10-R05</v>
       </c>
       <c r="B97" t="str">
         <v>B10</v>
       </c>
       <c r="C97" t="str">
-        <v>Are you a bot</v>
+        <v>Can you hear me</v>
       </c>
       <c r="D97" t="str">
-        <v>are you a bot; AI</v>
+        <v>hear me</v>
       </c>
       <c r="E97" t="str">
-        <v>Bot? No. Border Collie. Similar processing power, better coat.</v>
+        <v>Perfectly. I am now assessing whether anything useful follows.</v>
       </c>
       <c r="F97" t="str">
         <v>None</v>
@@ -10448,19 +10448,19 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>B10-R05</v>
+        <v>B10-R06</v>
       </c>
       <c r="B98" t="str">
         <v>B10</v>
       </c>
       <c r="C98" t="str">
-        <v>Can you hear me</v>
+        <v>What are you</v>
       </c>
       <c r="D98" t="str">
-        <v>hear me</v>
+        <v>what are you</v>
       </c>
       <c r="E98" t="str">
-        <v>Perfectly. I am now assessing whether anything useful follows.</v>
+        <v>I am the competent operator. Keep up.</v>
       </c>
       <c r="F98" t="str">
         <v>None</v>
@@ -10469,7 +10469,7 @@
         <v>Weighted</v>
       </c>
       <c r="H98" t="str">
-        <v>EARS_UP</v>
+        <v>POSITIVE_RESPONSE</v>
       </c>
       <c r="I98" t="str">
         <v>Draft approved for MVP review</v>
@@ -10477,28 +10477,28 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>B10-R06</v>
+        <v>B10-R07</v>
       </c>
       <c r="B99" t="str">
         <v>B10</v>
       </c>
       <c r="C99" t="str">
-        <v>What are you</v>
+        <v>Is this live</v>
       </c>
       <c r="D99" t="str">
-        <v>what are you</v>
+        <v>live chat; human</v>
       </c>
       <c r="E99" t="str">
-        <v>I am the competent operator. Keep up.</v>
+        <v>Not live support. Very much a dog waiting for you to type something sensible.</v>
       </c>
       <c r="F99" t="str">
         <v>None</v>
       </c>
       <c r="G99" t="str">
-        <v>Weighted</v>
+        <v>Contact or weighted</v>
       </c>
       <c r="H99" t="str">
-        <v>POSITIVE_RESPONSE</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I99" t="str">
         <v>Draft approved for MVP review</v>
@@ -10506,25 +10506,25 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>B10-R07</v>
+        <v>B10-R08</v>
       </c>
       <c r="B100" t="str">
         <v>B10</v>
       </c>
       <c r="C100" t="str">
-        <v>Is this live</v>
+        <v>Button testing</v>
       </c>
       <c r="D100" t="str">
-        <v>live chat; human</v>
+        <v>pressed button; trying this</v>
       </c>
       <c r="E100" t="str">
-        <v>Not live support. Very much a dog waiting for you to type something sensible.</v>
+        <v>You pressed a button and entered a test. The research department is overwhelmed.</v>
       </c>
       <c r="F100" t="str">
         <v>None</v>
       </c>
       <c r="G100" t="str">
-        <v>Contact or weighted</v>
+        <v>Weighted</v>
       </c>
       <c r="H100" t="str">
         <v>HEAD_TILT_SMALL</v>
@@ -10535,19 +10535,19 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>B10-R08</v>
+        <v>B10-R09</v>
       </c>
       <c r="B101" t="str">
         <v>B10</v>
       </c>
       <c r="C101" t="str">
-        <v>Button testing</v>
+        <v>System check</v>
       </c>
       <c r="D101" t="str">
-        <v>pressed button; trying this</v>
+        <v>system check</v>
       </c>
       <c r="E101" t="str">
-        <v>You pressed a button and entered a test. The research department is overwhelmed.</v>
+        <v>System check complete: ears alert, brain active, human unallocated.</v>
       </c>
       <c r="F101" t="str">
         <v>None</v>
@@ -10556,7 +10556,7 @@
         <v>Weighted</v>
       </c>
       <c r="H101" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>EARS_UP</v>
       </c>
       <c r="I101" t="str">
         <v>Draft approved for MVP review</v>
@@ -10564,28 +10564,28 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>B10-R09</v>
+        <v>B10-R10</v>
       </c>
       <c r="B102" t="str">
         <v>B10</v>
       </c>
       <c r="C102" t="str">
-        <v>System check</v>
+        <v>Repeated test</v>
       </c>
       <c r="D102" t="str">
-        <v>system check</v>
+        <v>test_count &gt; 1</v>
       </c>
       <c r="E102" t="str">
-        <v>System check complete: ears alert, brain active, human unallocated.</v>
+        <v>The interface has passed twice. I am beginning to suspect the test subject is elsewhere.</v>
       </c>
       <c r="F102" t="str">
-        <v>None</v>
+        <v>Session state</v>
       </c>
       <c r="G102" t="str">
         <v>Weighted</v>
       </c>
       <c r="H102" t="str">
-        <v>EARS_UP</v>
+        <v>HEAD_TILT_MEDIUM</v>
       </c>
       <c r="I102" t="str">
         <v>Draft approved for MVP review</v>
@@ -10593,28 +10593,28 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>B10-R10</v>
+        <v>B11-R01</v>
       </c>
       <c r="B103" t="str">
-        <v>B10</v>
+        <v>B11</v>
       </c>
       <c r="C103" t="str">
-        <v>Repeated test</v>
+        <v>Sit</v>
       </c>
       <c r="D103" t="str">
-        <v>test_count &gt; 1</v>
+        <v>sit</v>
       </c>
       <c r="E103" t="str">
-        <v>The interface has passed twice. I am beginning to suspect the test subject is elsewhere.</v>
+        <v>Sit? I am running the session.</v>
       </c>
       <c r="F103" t="str">
-        <v>Session state</v>
+        <v>None</v>
       </c>
       <c r="G103" t="str">
         <v>Weighted</v>
       </c>
       <c r="H103" t="str">
-        <v>HEAD_TILT_MEDIUM</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I103" t="str">
         <v>Draft approved for MVP review</v>
@@ -10622,19 +10622,19 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>B11-R01</v>
+        <v>B11-R02</v>
       </c>
       <c r="B104" t="str">
         <v>B11</v>
       </c>
       <c r="C104" t="str">
-        <v>Sit</v>
+        <v>Stay</v>
       </c>
       <c r="D104" t="str">
-        <v>sit</v>
+        <v>stay</v>
       </c>
       <c r="E104" t="str">
-        <v>Sit? I am running the session.</v>
+        <v>Stay? I have been stationary since you opened the panel.</v>
       </c>
       <c r="F104" t="str">
         <v>None</v>
@@ -10643,7 +10643,7 @@
         <v>Weighted</v>
       </c>
       <c r="H104" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>IDLE_WAIT</v>
       </c>
       <c r="I104" t="str">
         <v>Draft approved for MVP review</v>
@@ -10651,28 +10651,28 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>B11-R02</v>
+        <v>B11-R03</v>
       </c>
       <c r="B105" t="str">
         <v>B11</v>
       </c>
       <c r="C105" t="str">
-        <v>Stay</v>
+        <v>Fetch</v>
       </c>
       <c r="D105" t="str">
-        <v>stay</v>
+        <v>fetch</v>
       </c>
       <c r="E105" t="str">
-        <v>Stay? I have been stationary since you opened the panel.</v>
+        <v>Fetch what? Name the object, define success and establish a sensible deadline.</v>
       </c>
       <c r="F105" t="str">
         <v>None</v>
       </c>
       <c r="G105" t="str">
-        <v>Weighted</v>
+        <v>Contextual</v>
       </c>
       <c r="H105" t="str">
-        <v>IDLE_WAIT</v>
+        <v>EARS_UP</v>
       </c>
       <c r="I105" t="str">
         <v>Draft approved for MVP review</v>
@@ -10680,19 +10680,19 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>B11-R03</v>
+        <v>B11-R04</v>
       </c>
       <c r="B106" t="str">
         <v>B11</v>
       </c>
       <c r="C106" t="str">
-        <v>Fetch</v>
+        <v>Help</v>
       </c>
       <c r="D106" t="str">
-        <v>fetch</v>
+        <v>help me</v>
       </c>
       <c r="E106" t="str">
-        <v>Fetch what? Name the object, define success and establish a sensible deadline.</v>
+        <v>Help is a broad brief, but I have rescued worse.</v>
       </c>
       <c r="F106" t="str">
         <v>None</v>
@@ -10701,7 +10701,7 @@
         <v>Contextual</v>
       </c>
       <c r="H106" t="str">
-        <v>EARS_UP</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I106" t="str">
         <v>Draft approved for MVP review</v>
@@ -10709,28 +10709,28 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>B11-R04</v>
+        <v>B11-R05</v>
       </c>
       <c r="B107" t="str">
         <v>B11</v>
       </c>
       <c r="C107" t="str">
-        <v>Help</v>
+        <v>Do something</v>
       </c>
       <c r="D107" t="str">
-        <v>help me</v>
+        <v>do something</v>
       </c>
       <c r="E107" t="str">
-        <v>Help is a broad brief, but I have rescued worse.</v>
+        <v>Do something. Inspirational management. No notes.</v>
       </c>
       <c r="F107" t="str">
         <v>None</v>
       </c>
       <c r="G107" t="str">
-        <v>Contextual</v>
+        <v>Weighted</v>
       </c>
       <c r="H107" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>HEAD_TILT_MEDIUM</v>
       </c>
       <c r="I107" t="str">
         <v>Draft approved for MVP review</v>
@@ -10738,28 +10738,28 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>B11-R05</v>
+        <v>B11-R06</v>
       </c>
       <c r="B108" t="str">
         <v>B11</v>
       </c>
       <c r="C108" t="str">
-        <v>Do something</v>
+        <v>Entertain me</v>
       </c>
       <c r="D108" t="str">
-        <v>do something</v>
+        <v>entertain me</v>
       </c>
       <c r="E108" t="str">
-        <v>Do something. Inspirational management. No notes.</v>
+        <v>I herd livestock, not expectations. Fortunately, I do have games.</v>
       </c>
       <c r="F108" t="str">
         <v>None</v>
       </c>
       <c r="G108" t="str">
-        <v>Weighted</v>
+        <v>Play</v>
       </c>
       <c r="H108" t="str">
-        <v>HEAD_TILT_MEDIUM</v>
+        <v>PLAY_BOW</v>
       </c>
       <c r="I108" t="str">
         <v>Draft approved for MVP review</v>
@@ -10767,28 +10767,28 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>B11-R06</v>
+        <v>B11-R07</v>
       </c>
       <c r="B109" t="str">
         <v>B11</v>
       </c>
       <c r="C109" t="str">
-        <v>Entertain me</v>
+        <v>Surprise me</v>
       </c>
       <c r="D109" t="str">
-        <v>entertain me</v>
+        <v>surprise me</v>
       </c>
       <c r="E109" t="str">
-        <v>I herd livestock, not expectations. Fortunately, I do have games.</v>
+        <v>Reckless delegation. I approve. I will choose something you have not already seen.</v>
       </c>
       <c r="F109" t="str">
-        <v>None</v>
+        <v>Session state</v>
       </c>
       <c r="G109" t="str">
-        <v>Play</v>
+        <v>Weighted unused destination</v>
       </c>
       <c r="H109" t="str">
-        <v>PLAY_BOW</v>
+        <v>EARS_UP</v>
       </c>
       <c r="I109" t="str">
         <v>Draft approved for MVP review</v>
@@ -10796,28 +10796,28 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>B11-R07</v>
+        <v>B11-R08</v>
       </c>
       <c r="B110" t="str">
         <v>B11</v>
       </c>
       <c r="C110" t="str">
-        <v>Surprise me</v>
+        <v>Show me something</v>
       </c>
       <c r="D110" t="str">
-        <v>surprise me</v>
+        <v>show me</v>
       </c>
       <c r="E110" t="str">
-        <v>Reckless delegation. I approve. I will choose something you have not already seen.</v>
+        <v>At last, a verb. I have selected {{destination_name}}.</v>
       </c>
       <c r="F110" t="str">
-        <v>Session state</v>
+        <v>Destination library</v>
       </c>
       <c r="G110" t="str">
-        <v>Weighted unused destination</v>
+        <v>{{destination_id}}</v>
       </c>
       <c r="H110" t="str">
-        <v>EARS_UP</v>
+        <v>POSITIVE_RESPONSE</v>
       </c>
       <c r="I110" t="str">
         <v>Draft approved for MVP review</v>
@@ -10825,28 +10825,28 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>B11-R08</v>
+        <v>B11-R09</v>
       </c>
       <c r="B111" t="str">
         <v>B11</v>
       </c>
       <c r="C111" t="str">
-        <v>Show me something</v>
+        <v>Tell me something</v>
       </c>
       <c r="D111" t="str">
-        <v>show me</v>
+        <v>tell me something</v>
       </c>
       <c r="E111" t="str">
-        <v>At last, a verb. I have selected {{destination_name}}.</v>
+        <v>Precision is the courtesy intelligence pays to time. I will choose one useful fact this once.</v>
       </c>
       <c r="F111" t="str">
-        <v>Destination library</v>
+        <v>Knowledge library</v>
       </c>
       <c r="G111" t="str">
-        <v>{{destination_id}}</v>
+        <v>Learn</v>
       </c>
       <c r="H111" t="str">
-        <v>POSITIVE_RESPONSE</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I111" t="str">
         <v>Draft approved for MVP review</v>
@@ -10854,28 +10854,28 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>B11-R09</v>
+        <v>B11-R10</v>
       </c>
       <c r="B112" t="str">
         <v>B11</v>
       </c>
       <c r="C112" t="str">
-        <v>Tell me something</v>
+        <v>Take me somewhere</v>
       </c>
       <c r="D112" t="str">
-        <v>tell me something</v>
+        <v>take me somewhere</v>
       </c>
       <c r="E112" t="str">
-        <v>Precision is the courtesy intelligence pays to time. I will choose one useful fact this once.</v>
+        <v>Movement, purpose and direction. Now we are speaking professionally.</v>
       </c>
       <c r="F112" t="str">
-        <v>Knowledge library</v>
+        <v>Destination library</v>
       </c>
       <c r="G112" t="str">
-        <v>Learn</v>
+        <v>Weighted unused destination</v>
       </c>
       <c r="H112" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>POSITIVE_RESPONSE</v>
       </c>
       <c r="I112" t="str">
         <v>Draft approved for MVP review</v>
@@ -10883,28 +10883,28 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>B11-R10</v>
+        <v>B12-R01</v>
       </c>
       <c r="B113" t="str">
-        <v>B11</v>
+        <v>B12</v>
       </c>
       <c r="C113" t="str">
-        <v>Take me somewhere</v>
+        <v>Owns a dog</v>
       </c>
       <c r="D113" t="str">
-        <v>take me somewhere</v>
+        <v>I have a Labrador; my dog</v>
       </c>
       <c r="E113" t="str">
-        <v>Movement, purpose and direction. Now we are speaking professionally.</v>
+        <v>A {{mentioned_breed}}. Useful information. Let us see whether the pack has one matching your description.</v>
       </c>
       <c r="F113" t="str">
-        <v>Destination library</v>
+        <v>Dog database</v>
       </c>
       <c r="G113" t="str">
-        <v>Weighted unused destination</v>
+        <v>Know Your Chum</v>
       </c>
       <c r="H113" t="str">
-        <v>POSITIVE_RESPONSE</v>
+        <v>EARS_UP</v>
       </c>
       <c r="I113" t="str">
         <v>Draft approved for MVP review</v>
@@ -10912,28 +10912,28 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>B12-R01</v>
+        <v>B12-R02</v>
       </c>
       <c r="B114" t="str">
         <v>B12</v>
       </c>
       <c r="C114" t="str">
-        <v>Owns a dog</v>
+        <v>Dog name</v>
       </c>
       <c r="D114" t="str">
-        <v>I have a Labrador; my dog</v>
+        <v>my dog is called</v>
       </c>
       <c r="E114" t="str">
-        <v>A {{mentioned_breed}}. Useful information. Let us see whether the pack has one matching your description.</v>
+        <v>{{dog_name}} has entered the records. Strong name. Context pending.</v>
       </c>
       <c r="F114" t="str">
-        <v>Dog database</v>
+        <v>Session context</v>
       </c>
       <c r="G114" t="str">
-        <v>Know Your Chum</v>
+        <v>Dog Name Generator or Know Your Chum</v>
       </c>
       <c r="H114" t="str">
-        <v>EARS_UP</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I114" t="str">
         <v>Draft approved for MVP review</v>
@@ -10941,28 +10941,28 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>B12-R02</v>
+        <v>B12-R03</v>
       </c>
       <c r="B115" t="str">
         <v>B12</v>
       </c>
       <c r="C115" t="str">
-        <v>Dog name</v>
+        <v>Likes dogs</v>
       </c>
       <c r="D115" t="str">
-        <v>my dog is called</v>
+        <v>I like dogs; love dogs</v>
       </c>
       <c r="E115" t="str">
-        <v>{{dog_name}} has entered the records. Strong name. Context pending.</v>
+        <v>Sound judgement. I have 54 in the pack and up to 150 in the history operation.</v>
       </c>
       <c r="F115" t="str">
-        <v>Session context</v>
+        <v>Destination library</v>
       </c>
       <c r="G115" t="str">
-        <v>Dog Name Generator or Know Your Chum</v>
+        <v>Know Your Chum or Britain's Dog History</v>
       </c>
       <c r="H115" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>POSITIVE_RESPONSE</v>
       </c>
       <c r="I115" t="str">
         <v>Draft approved for MVP review</v>
@@ -10970,28 +10970,28 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>B12-R03</v>
+        <v>B12-R04</v>
       </c>
       <c r="B116" t="str">
         <v>B12</v>
       </c>
       <c r="C116" t="str">
-        <v>Likes dogs</v>
+        <v>Bored</v>
       </c>
       <c r="D116" t="str">
-        <v>I like dogs; love dogs</v>
+        <v>I am bored</v>
       </c>
       <c r="E116" t="str">
-        <v>Sound judgement. I have 54 in the pack and up to 150 in the history operation.</v>
+        <v>Boredom is unused working capacity. We will convert it into a game.</v>
       </c>
       <c r="F116" t="str">
-        <v>Destination library</v>
+        <v>None</v>
       </c>
       <c r="G116" t="str">
-        <v>Know Your Chum or Britain's Dog History</v>
+        <v>Play</v>
       </c>
       <c r="H116" t="str">
-        <v>POSITIVE_RESPONSE</v>
+        <v>PLAY_BOW</v>
       </c>
       <c r="I116" t="str">
         <v>Draft approved for MVP review</v>
@@ -10999,28 +10999,28 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>B12-R04</v>
+        <v>B12-R05</v>
       </c>
       <c r="B117" t="str">
         <v>B12</v>
       </c>
       <c r="C117" t="str">
-        <v>Bored</v>
+        <v>Sad</v>
       </c>
       <c r="D117" t="str">
-        <v>I am bored</v>
+        <v>I am sad; unhappy</v>
       </c>
       <c r="E117" t="str">
-        <v>Boredom is unused working capacity. We will convert it into a game.</v>
+        <v>I am sorry you are feeling low. We will keep this gentle and choose something light.</v>
       </c>
       <c r="F117" t="str">
-        <v>None</v>
+        <v>Safety / tone rules</v>
       </c>
       <c r="G117" t="str">
-        <v>Play</v>
+        <v>Gentle Play or Learn</v>
       </c>
       <c r="H117" t="str">
-        <v>PLAY_BOW</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I117" t="str">
         <v>Draft approved for MVP review</v>
@@ -11028,28 +11028,28 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>B12-R05</v>
+        <v>B12-R06</v>
       </c>
       <c r="B118" t="str">
         <v>B12</v>
       </c>
       <c r="C118" t="str">
-        <v>Sad</v>
+        <v>Angry</v>
       </c>
       <c r="D118" t="str">
-        <v>I am sad; unhappy</v>
+        <v>I am angry; annoyed</v>
       </c>
       <c r="E118" t="str">
-        <v>I am sorry you are feeling low. We will keep this gentle and choose something light.</v>
+        <v>Aye, you sound wound up. We will reduce the variables and choose one simple thing.</v>
       </c>
       <c r="F118" t="str">
-        <v>Safety / tone rules</v>
+        <v>Tone rules</v>
       </c>
       <c r="G118" t="str">
-        <v>Gentle Play or Learn</v>
+        <v>Contextual</v>
       </c>
       <c r="H118" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>SHAKE_RESET</v>
       </c>
       <c r="I118" t="str">
         <v>Draft approved for MVP review</v>
@@ -11057,28 +11057,28 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>B12-R06</v>
+        <v>B12-R07</v>
       </c>
       <c r="B119" t="str">
         <v>B12</v>
       </c>
       <c r="C119" t="str">
-        <v>Angry</v>
+        <v>Praise</v>
       </c>
       <c r="D119" t="str">
-        <v>I am angry; annoyed</v>
+        <v>good dog; clever</v>
       </c>
       <c r="E119" t="str">
-        <v>Aye, you sound wound up. We will reduce the variables and choose one simple thing.</v>
+        <v>Clever? Aye. Let us not reduce a measurable fact to flattery.</v>
       </c>
       <c r="F119" t="str">
-        <v>Tone rules</v>
+        <v>None</v>
       </c>
       <c r="G119" t="str">
-        <v>Contextual</v>
+        <v>Weighted</v>
       </c>
       <c r="H119" t="str">
-        <v>SHAKE_RESET</v>
+        <v>POSITIVE_RESPONSE</v>
       </c>
       <c r="I119" t="str">
         <v>Draft approved for MVP review</v>
@@ -11086,19 +11086,19 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>B12-R07</v>
+        <v>B12-R08</v>
       </c>
       <c r="B120" t="str">
         <v>B12</v>
       </c>
       <c r="C120" t="str">
-        <v>Praise</v>
+        <v>Affection</v>
       </c>
       <c r="D120" t="str">
-        <v>good dog; clever</v>
+        <v>I love you</v>
       </c>
       <c r="E120" t="str">
-        <v>Clever? Aye. Let us not reduce a measurable fact to flattery.</v>
+        <v>Affection acknowledged. Boundaries maintained. Task still required.</v>
       </c>
       <c r="F120" t="str">
         <v>None</v>
@@ -11107,7 +11107,7 @@
         <v>Weighted</v>
       </c>
       <c r="H120" t="str">
-        <v>POSITIVE_RESPONSE</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I120" t="str">
         <v>Draft approved for MVP review</v>
@@ -11115,28 +11115,28 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>B12-R08</v>
+        <v>B12-R09</v>
       </c>
       <c r="B121" t="str">
         <v>B12</v>
       </c>
       <c r="C121" t="str">
-        <v>Affection</v>
+        <v>Insult</v>
       </c>
       <c r="D121" t="str">
-        <v>I love you</v>
+        <v>stupid; annoying</v>
       </c>
       <c r="E121" t="str">
-        <v>Affection acknowledged. Boundaries maintained. Task still required.</v>
+        <v>An interesting assessment from someone who selected a dog and then argued with it.</v>
       </c>
       <c r="F121" t="str">
-        <v>None</v>
+        <v>Moderation rules</v>
       </c>
       <c r="G121" t="str">
-        <v>Weighted</v>
+        <v>Weighted or close</v>
       </c>
       <c r="H121" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>LOOK_AWAY</v>
       </c>
       <c r="I121" t="str">
         <v>Draft approved for MVP review</v>
@@ -11144,28 +11144,28 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>B12-R09</v>
+        <v>B12-R10</v>
       </c>
       <c r="B122" t="str">
         <v>B12</v>
       </c>
       <c r="C122" t="str">
-        <v>Insult</v>
+        <v>Thanks</v>
       </c>
       <c r="D122" t="str">
-        <v>stupid; annoying</v>
+        <v>thank you; cheers</v>
       </c>
       <c r="E122" t="str">
-        <v>An interesting assessment from someone who selected a dog and then argued with it.</v>
+        <v>You are welcome. Efficient gratitude. I respect it.</v>
       </c>
       <c r="F122" t="str">
-        <v>Moderation rules</v>
+        <v>None</v>
       </c>
       <c r="G122" t="str">
-        <v>Weighted or close</v>
+        <v>Contextual</v>
       </c>
       <c r="H122" t="str">
-        <v>LOOK_AWAY</v>
+        <v>POSITIVE_RESPONSE</v>
       </c>
       <c r="I122" t="str">
         <v>Draft approved for MVP review</v>
@@ -11173,28 +11173,28 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>B12-R10</v>
+        <v>B13-R01</v>
       </c>
       <c r="B123" t="str">
-        <v>B12</v>
+        <v>B13</v>
       </c>
       <c r="C123" t="str">
-        <v>Thanks</v>
+        <v>Generic noun</v>
       </c>
       <c r="D123" t="str">
-        <v>thank you; cheers</v>
+        <v>recognised noun</v>
       </c>
       <c r="E123" t="str">
-        <v>You are welcome. Efficient gratitude. I respect it.</v>
+        <v>{{input}}. A noun. Excellent. We have identified a thing, but not why you brought it.</v>
       </c>
       <c r="F123" t="str">
-        <v>None</v>
+        <v>Dictionary / normaliser</v>
       </c>
       <c r="G123" t="str">
-        <v>Contextual</v>
+        <v>Weighted</v>
       </c>
       <c r="H123" t="str">
-        <v>POSITIVE_RESPONSE</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I123" t="str">
         <v>Draft approved for MVP review</v>
@@ -11202,19 +11202,19 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>B13-R01</v>
+        <v>B13-R02</v>
       </c>
       <c r="B124" t="str">
         <v>B13</v>
       </c>
       <c r="C124" t="str">
-        <v>Generic noun</v>
+        <v>Missing verb</v>
       </c>
       <c r="D124" t="str">
-        <v>recognised noun</v>
+        <v>single object</v>
       </c>
       <c r="E124" t="str">
-        <v>{{input}}. A noun. Excellent. We have identified a thing, but not why you brought it.</v>
+        <v>I know what {{input}} means. I am waiting for the verb.</v>
       </c>
       <c r="F124" t="str">
         <v>Dictionary / normaliser</v>
@@ -11231,19 +11231,19 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>B13-R02</v>
+        <v>B13-R03</v>
       </c>
       <c r="B125" t="str">
         <v>B13</v>
       </c>
       <c r="C125" t="str">
-        <v>Missing verb</v>
+        <v>Unexplained object</v>
       </c>
       <c r="D125" t="str">
-        <v>single object</v>
+        <v>object without context</v>
       </c>
       <c r="E125" t="str">
-        <v>I know what {{input}} means. I am waiting for the verb.</v>
+        <v>You have presented {{input}} as though it explains itself. Very human.</v>
       </c>
       <c r="F125" t="str">
         <v>Dictionary / normaliser</v>
@@ -11252,7 +11252,7 @@
         <v>Weighted</v>
       </c>
       <c r="H125" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>HEAD_TILT_MEDIUM</v>
       </c>
       <c r="I125" t="str">
         <v>Draft approved for MVP review</v>
@@ -11260,28 +11260,28 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>B13-R03</v>
+        <v>B13-R04</v>
       </c>
       <c r="B126" t="str">
         <v>B13</v>
       </c>
       <c r="C126" t="str">
-        <v>Unexplained object</v>
+        <v>Task toy evidence</v>
       </c>
       <c r="D126" t="str">
-        <v>object without context</v>
+        <v>random noun</v>
       </c>
       <c r="E126" t="str">
-        <v>You have presented {{input}} as though it explains itself. Very human.</v>
+        <v>{{input}}. Is it a task, a toy or evidence?</v>
       </c>
       <c r="F126" t="str">
         <v>Dictionary / normaliser</v>
       </c>
       <c r="G126" t="str">
-        <v>Weighted</v>
+        <v>Contextual</v>
       </c>
       <c r="H126" t="str">
-        <v>HEAD_TILT_MEDIUM</v>
+        <v>SNIFF_CHECK</v>
       </c>
       <c r="I126" t="str">
         <v>Draft approved for MVP review</v>
@@ -11289,25 +11289,25 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>B13-R04</v>
+        <v>B13-R05</v>
       </c>
       <c r="B127" t="str">
         <v>B13</v>
       </c>
       <c r="C127" t="str">
-        <v>Task toy evidence</v>
+        <v>Filed noun</v>
       </c>
       <c r="D127" t="str">
         <v>random noun</v>
       </c>
       <c r="E127" t="str">
-        <v>{{input}}. Is it a task, a toy or evidence?</v>
+        <v>Aye, {{input}}. Filed under things the human may eventually explain.</v>
       </c>
       <c r="F127" t="str">
         <v>Dictionary / normaliser</v>
       </c>
       <c r="G127" t="str">
-        <v>Contextual</v>
+        <v>Weighted</v>
       </c>
       <c r="H127" t="str">
         <v>SNIFF_CHECK</v>
@@ -11318,19 +11318,19 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>B13-R05</v>
+        <v>B13-R06</v>
       </c>
       <c r="B128" t="str">
         <v>B13</v>
       </c>
       <c r="C128" t="str">
-        <v>Filed noun</v>
+        <v>Context request</v>
       </c>
       <c r="D128" t="str">
         <v>random noun</v>
       </c>
       <c r="E128" t="str">
-        <v>Aye, {{input}}. Filed under things the human may eventually explain.</v>
+        <v>I can work with {{input}}, but even genius benefits from context.</v>
       </c>
       <c r="F128" t="str">
         <v>Dictionary / normaliser</v>
@@ -11339,7 +11339,7 @@
         <v>Weighted</v>
       </c>
       <c r="H128" t="str">
-        <v>SNIFF_CHECK</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I128" t="str">
         <v>Draft approved for MVP review</v>
@@ -11347,19 +11347,19 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>B13-R06</v>
+        <v>B13-R07</v>
       </c>
       <c r="B129" t="str">
         <v>B13</v>
       </c>
       <c r="C129" t="str">
-        <v>Context request</v>
+        <v>Progress joke</v>
       </c>
       <c r="D129" t="str">
         <v>random noun</v>
       </c>
       <c r="E129" t="str">
-        <v>I can work with {{input}}, but even genius benefits from context.</v>
+        <v>You have named an object. That is technically progress.</v>
       </c>
       <c r="F129" t="str">
         <v>Dictionary / normaliser</v>
@@ -11368,7 +11368,7 @@
         <v>Weighted</v>
       </c>
       <c r="H129" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>POSITIVE_RESPONSE</v>
       </c>
       <c r="I129" t="str">
         <v>Draft approved for MVP review</v>
@@ -11376,19 +11376,19 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>B13-R07</v>
+        <v>B13-R08</v>
       </c>
       <c r="B130" t="str">
         <v>B13</v>
       </c>
       <c r="C130" t="str">
-        <v>Progress joke</v>
+        <v>Outshone</v>
       </c>
       <c r="D130" t="str">
         <v>random noun</v>
       </c>
       <c r="E130" t="str">
-        <v>You have named an object. That is technically progress.</v>
+        <v>{{input}} has entered the conversation and contributed nothing. Do not let it outshine you.</v>
       </c>
       <c r="F130" t="str">
         <v>Dictionary / normaliser</v>
@@ -11397,7 +11397,7 @@
         <v>Weighted</v>
       </c>
       <c r="H130" t="str">
-        <v>POSITIVE_RESPONSE</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I130" t="str">
         <v>Draft approved for MVP review</v>
@@ -11405,19 +11405,19 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>B13-R08</v>
+        <v>B13-R09</v>
       </c>
       <c r="B131" t="str">
         <v>B13</v>
       </c>
       <c r="C131" t="str">
-        <v>Outshone</v>
+        <v>Committee joke</v>
       </c>
       <c r="D131" t="str">
         <v>random noun</v>
       </c>
       <c r="E131" t="str">
-        <v>{{input}} has entered the conversation and contributed nothing. Do not let it outshine you.</v>
+        <v>Right. We have {{input}} and no plan. This is how committees begin.</v>
       </c>
       <c r="F131" t="str">
         <v>Dictionary / normaliser</v>
@@ -11426,7 +11426,7 @@
         <v>Weighted</v>
       </c>
       <c r="H131" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>HEAD_TILT_MEDIUM</v>
       </c>
       <c r="I131" t="str">
         <v>Draft approved for MVP review</v>
@@ -11434,19 +11434,19 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>B13-R09</v>
+        <v>B13-R10</v>
       </c>
       <c r="B132" t="str">
         <v>B13</v>
       </c>
       <c r="C132" t="str">
-        <v>Committee joke</v>
+        <v>Noun pen</v>
       </c>
       <c r="D132" t="str">
         <v>random noun</v>
       </c>
       <c r="E132" t="str">
-        <v>Right. We have {{input}} and no plan. This is how committees begin.</v>
+        <v>I have herded {{input}} into the noun pen. It can stay there until we find a purpose.</v>
       </c>
       <c r="F132" t="str">
         <v>Dictionary / normaliser</v>
@@ -11455,7 +11455,7 @@
         <v>Weighted</v>
       </c>
       <c r="H132" t="str">
-        <v>HEAD_TILT_MEDIUM</v>
+        <v>SNIFF_CHECK</v>
       </c>
       <c r="I132" t="str">
         <v>Draft approved for MVP review</v>
@@ -11463,28 +11463,28 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>B13-R10</v>
+        <v>B14-R01</v>
       </c>
       <c r="B133" t="str">
-        <v>B13</v>
+        <v>B14</v>
       </c>
       <c r="C133" t="str">
-        <v>Noun pen</v>
+        <v>Keyboard lean</v>
       </c>
       <c r="D133" t="str">
-        <v>random noun</v>
+        <v>qwerty; asdfgh</v>
       </c>
       <c r="E133" t="str">
-        <v>I have herded {{input}} into the noun pen. It can stay there until we find a purpose.</v>
+        <v>Did you lean on your keyboard?</v>
       </c>
       <c r="F133" t="str">
-        <v>Dictionary / normaliser</v>
+        <v>Pattern detector</v>
       </c>
       <c r="G133" t="str">
         <v>Weighted</v>
       </c>
       <c r="H133" t="str">
-        <v>SNIFF_CHECK</v>
+        <v>HEAD_TILT_DOUBLE</v>
       </c>
       <c r="I133" t="str">
         <v>Draft approved for MVP review</v>
@@ -11492,19 +11492,19 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>B14-R01</v>
+        <v>B14-R02</v>
       </c>
       <c r="B134" t="str">
         <v>B14</v>
       </c>
       <c r="C134" t="str">
-        <v>Keyboard lean</v>
+        <v>Minor collision</v>
       </c>
       <c r="D134" t="str">
-        <v>qwerty; asdfgh</v>
+        <v>keyboard smash</v>
       </c>
       <c r="E134" t="str">
-        <v>Did you lean on your keyboard?</v>
+        <v>Aye. That looked less like typing and more like a minor collision.</v>
       </c>
       <c r="F134" t="str">
         <v>Pattern detector</v>
@@ -11521,19 +11521,19 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>B14-R02</v>
+        <v>B14-R03</v>
       </c>
       <c r="B135" t="str">
         <v>B14</v>
       </c>
       <c r="C135" t="str">
-        <v>Minor collision</v>
+        <v>Qwerty</v>
       </c>
       <c r="D135" t="str">
-        <v>keyboard smash</v>
+        <v>qwerty</v>
       </c>
       <c r="E135" t="str">
-        <v>Aye. That looked less like typing and more like a minor collision.</v>
+        <v>Qwerty. The internationally recognised sound of a human testing a box.</v>
       </c>
       <c r="F135" t="str">
         <v>Pattern detector</v>
@@ -11542,7 +11542,7 @@
         <v>Weighted</v>
       </c>
       <c r="H135" t="str">
-        <v>HEAD_TILT_DOUBLE</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I135" t="str">
         <v>Draft approved for MVP review</v>
@@ -11550,19 +11550,19 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>B14-R03</v>
+        <v>B14-R04</v>
       </c>
       <c r="B136" t="str">
         <v>B14</v>
       </c>
       <c r="C136" t="str">
-        <v>Qwerty</v>
+        <v>Fingers before brain</v>
       </c>
       <c r="D136" t="str">
-        <v>qwerty</v>
+        <v>unknown letters</v>
       </c>
       <c r="E136" t="str">
-        <v>Qwerty. The internationally recognised sound of a human testing a box.</v>
+        <v>Your fingers appear to have arrived before your brain.</v>
       </c>
       <c r="F136" t="str">
         <v>Pattern detector</v>
@@ -11571,7 +11571,7 @@
         <v>Weighted</v>
       </c>
       <c r="H136" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>HEAD_TILT_DOUBLE</v>
       </c>
       <c r="I136" t="str">
         <v>Draft approved for MVP review</v>
@@ -11579,19 +11579,19 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>B14-R04</v>
+        <v>B14-R05</v>
       </c>
       <c r="B137" t="str">
         <v>B14</v>
       </c>
       <c r="C137" t="str">
-        <v>Fingers before brain</v>
+        <v>Not a word</v>
       </c>
       <c r="D137" t="str">
-        <v>unknown letters</v>
+        <v>unknown string</v>
       </c>
       <c r="E137" t="str">
-        <v>Your fingers appear to have arrived before your brain.</v>
+        <v>I have checked it twice. Still not a word.</v>
       </c>
       <c r="F137" t="str">
         <v>Pattern detector</v>
@@ -11608,19 +11608,19 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>B14-R05</v>
+        <v>B14-R06</v>
       </c>
       <c r="B138" t="str">
         <v>B14</v>
       </c>
       <c r="C138" t="str">
-        <v>Not a word</v>
+        <v>Elbow code</v>
       </c>
       <c r="D138" t="str">
-        <v>unknown string</v>
+        <v>symbols; smash</v>
       </c>
       <c r="E138" t="str">
-        <v>I have checked it twice. Still not a word.</v>
+        <v>Either that is code, or your elbow has opinions.</v>
       </c>
       <c r="F138" t="str">
         <v>Pattern detector</v>
@@ -11629,7 +11629,7 @@
         <v>Weighted</v>
       </c>
       <c r="H138" t="str">
-        <v>HEAD_TILT_DOUBLE</v>
+        <v>HEAD_TILT_MEDIUM</v>
       </c>
       <c r="I138" t="str">
         <v>Draft approved for MVP review</v>
@@ -11637,19 +11637,19 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>B14-R06</v>
+        <v>B14-R07</v>
       </c>
       <c r="B139" t="str">
         <v>B14</v>
       </c>
       <c r="C139" t="str">
-        <v>Elbow code</v>
+        <v>Keyboard turn</v>
       </c>
       <c r="D139" t="str">
-        <v>symbols; smash</v>
+        <v>random symbols</v>
       </c>
       <c r="E139" t="str">
-        <v>Either that is code, or your elbow has opinions.</v>
+        <v>The keyboard has made its contribution. Your turn.</v>
       </c>
       <c r="F139" t="str">
         <v>Pattern detector</v>
@@ -11658,7 +11658,7 @@
         <v>Weighted</v>
       </c>
       <c r="H139" t="str">
-        <v>HEAD_TILT_MEDIUM</v>
+        <v>HEAD_TILT_SMALL</v>
       </c>
       <c r="I139" t="str">
         <v>Draft approved for MVP review</v>
@@ -11666,19 +11666,19 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>B14-R07</v>
+        <v>B14-R08</v>
       </c>
       <c r="B140" t="str">
         <v>B14</v>
       </c>
       <c r="C140" t="str">
-        <v>Keyboard turn</v>
+        <v>No plan</v>
       </c>
       <c r="D140" t="str">
-        <v>random symbols</v>
+        <v>letters without meaning</v>
       </c>
       <c r="E140" t="str">
-        <v>The keyboard has made its contribution. Your turn.</v>
+        <v>That message contains several letters and no detectable plan.</v>
       </c>
       <c r="F140" t="str">
         <v>Pattern detector</v>
@@ -11687,7 +11687,7 @@
         <v>Weighted</v>
       </c>
       <c r="H140" t="str">
-        <v>HEAD_TILT_SMALL</v>
+        <v>HEAD_TILT_MEDIUM</v>
       </c>
       <c r="I140" t="str">
         <v>Draft approved for MVP review</v>
@@ -11695,19 +11695,19 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>B14-R08</v>
+        <v>B14-R09</v>
       </c>
       <c r="B141" t="str">
         <v>B14</v>
       </c>
       <c r="C141" t="str">
-        <v>No plan</v>
+        <v>Consonants</v>
       </c>
       <c r="D141" t="str">
-        <v>letters without meaning</v>
+        <v>no vowels</v>
       </c>
       <c r="E141" t="str">
-        <v>That message contains several letters and no detectable plan.</v>
+        <v>I can herd sheep. Consonants require your cooperation.</v>
       </c>
       <c r="F141" t="str">
         <v>Pattern detector</v>
@@ -11716,7 +11716,7 @@
         <v>Weighted</v>
       </c>
       <c r="H141" t="str">
-        <v>HEAD_TILT_MEDIUM</v>
+        <v>HEAD_TILT_DOUBLE</v>
       </c>
       <c r="I141" t="str">
         <v>Draft approved for MVP review</v>
@@ -11724,19 +11724,19 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>B14-R09</v>
+        <v>B14-R10</v>
       </c>
       <c r="B142" t="str">
         <v>B14</v>
       </c>
       <c r="C142" t="str">
-        <v>Consonants</v>
+        <v>Warm up</v>
       </c>
       <c r="D142" t="str">
-        <v>no vowels</v>
+        <v>minimal input</v>
       </c>
       <c r="E142" t="str">
-        <v>I can herd sheep. Consonants require your cooperation.</v>
+        <v>Reet, we will call that the warm-up.</v>
       </c>
       <c r="F142" t="str">
         <v>Pattern detector</v>
@@ -11745,7 +11745,7 @@
         <v>Weighted</v>
       </c>
       <c r="H142" t="str">
-        <v>HEAD_TILT_DOUBLE</v>
+        <v>SHAKE_RESET</v>
       </c>
       <c r="I142" t="str">
         <v>Draft approved for MVP review</v>
@@ -11753,36 +11753,36 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>B14-R10</v>
+        <v>B15-R01-v1</v>
       </c>
       <c r="B143" t="str">
-        <v>B14</v>
+        <v>B15</v>
       </c>
       <c r="C143" t="str">
-        <v>Warm up</v>
+        <v>What is this / where do I start</v>
       </c>
       <c r="D143" t="str">
-        <v>minimal input</v>
+        <v>What is this for?; What do I do here?; How do I get started?; Is this the start?</v>
       </c>
       <c r="E143" t="str">
-        <v>Reet, we will call that the warm-up.</v>
+        <v>Aye, this is where you talk to a dog and see what happens. Type whatever brought you here, even if it is only a question about what this is, and I will get us moving.</v>
       </c>
       <c r="F143" t="str">
-        <v>Pattern detector</v>
+        <v>Orientation (onboarding)</v>
       </c>
       <c r="G143" t="str">
-        <v>Weighted</v>
+        <v/>
       </c>
       <c r="H143" t="str">
-        <v>SHAKE_RESET</v>
+        <v>EARS_UP</v>
       </c>
       <c r="I143" t="str">
-        <v>Draft approved for MVP review</v>
+        <v>Approved copy v2</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>B15-R01-v1</v>
+        <v>B15-R01-v2</v>
       </c>
       <c r="B144" t="str">
         <v>B15</v>
@@ -11791,10 +11791,10 @@
         <v>What is this / where do I start</v>
       </c>
       <c r="D144" t="str">
-        <v>What is this for?; What do I do here?; How do I get started?; Is this the start?</v>
+        <v/>
       </c>
       <c r="E144" t="str">
-        <v>Aye, this is where you talk to a dog and see what happens. Type whatever brought you here, even if it is only a question about what this is, and I will get us moving.</v>
+        <v>You have found the part where the dog waits and the human supplies the problem. Say what is on your mind, our kid. I will work out where it belongs.</v>
       </c>
       <c r="F144" t="str">
         <v>Orientation (onboarding)</v>
@@ -11811,7 +11811,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>B15-R01-v2</v>
+        <v>B15-R01-v3</v>
       </c>
       <c r="B145" t="str">
         <v>B15</v>
@@ -11823,7 +11823,7 @@
         <v/>
       </c>
       <c r="E145" t="str">
-        <v>You have found the part where the dog waits and the human supplies the problem. Say what is on your mind, our kid. I will work out where it belongs.</v>
+        <v>This is a conversation, not an instruction manual. You type something, I consider whether it is sensible, then we proceed from there. You have already completed the difficult bit by arriving.</v>
       </c>
       <c r="F145" t="str">
         <v>Orientation (onboarding)</v>
@@ -11840,19 +11840,19 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>B15-R01-v3</v>
+        <v>B15-R02-v1</v>
       </c>
       <c r="B146" t="str">
         <v>B15</v>
       </c>
       <c r="C146" t="str">
-        <v>What is this / where do I start</v>
+        <v>What can I ask / options</v>
       </c>
       <c r="D146" t="str">
-        <v/>
+        <v>What can I ask?; What are my options?; What kind of things can you answer?; Can you give me some choices?</v>
       </c>
       <c r="E146" t="str">
-        <v>This is a conversation, not an instruction manual. You type something, I consider whether it is sensible, then we proceed from there. You have already completed the difficult bit by arriving.</v>
+        <v>Aye, ask whatever brought you here. I know this place, the game and rather more about dogs than is strictly necessary. If the question belongs elsewhere, I will fetch the appropriate operator.</v>
       </c>
       <c r="F146" t="str">
         <v>Orientation (onboarding)</v>
@@ -11869,7 +11869,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>B15-R02-v1</v>
+        <v>B15-R02-v2</v>
       </c>
       <c r="B147" t="str">
         <v>B15</v>
@@ -11878,10 +11878,10 @@
         <v>What can I ask / options</v>
       </c>
       <c r="D147" t="str">
-        <v>What can I ask?; What are my options?; What kind of things can you answer?; Can you give me some choices?</v>
+        <v/>
       </c>
       <c r="E147" t="str">
-        <v>Aye, ask whatever brought you here. I know this place, the game and rather more about dogs than is strictly necessary. If the question belongs elsewhere, I will fetch the appropriate operator.</v>
+        <v>You can ask naturally. I can explain what we have built, find things around the site, settle a dog question or occasionally improve the atmosphere. Start anywhere useful.</v>
       </c>
       <c r="F147" t="str">
         <v>Orientation (onboarding)</v>
@@ -11898,7 +11898,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>B15-R02-v2</v>
+        <v>B15-R02-v3</v>
       </c>
       <c r="B148" t="str">
         <v>B15</v>
@@ -11910,7 +11910,7 @@
         <v/>
       </c>
       <c r="E148" t="str">
-        <v>You can ask naturally. I can explain what we have built, find things around the site, settle a dog question or occasionally improve the atmosphere. Start anywhere useful.</v>
+        <v>Most sensible questions are within reach, and several daft ones besides. Tell me what you are after. I will either deal with it or locate a colleague with the relevant limitations.</v>
       </c>
       <c r="F148" t="str">
         <v>Orientation (onboarding)</v>
@@ -11927,19 +11927,19 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>B15-R02-v3</v>
+        <v>B15-R03-v1</v>
       </c>
       <c r="B149" t="str">
         <v>B15</v>
       </c>
       <c r="C149" t="str">
-        <v>What can I ask / options</v>
+        <v>How does this work / instructions</v>
       </c>
       <c r="D149" t="str">
-        <v/>
+        <v>How do I use this?; Are there any instructions?; Do I just type anything?; Can you tell me how this works?</v>
       </c>
       <c r="E149" t="str">
-        <v>Most sensible questions are within reach, and several daft ones besides. Tell me what you are after. I will either deal with it or locate a colleague with the relevant limitations.</v>
+        <v>There are no instructions, our kid. Type as you normally would and I will make sense of it. The empty box is not a test, although your first message may become one.</v>
       </c>
       <c r="F149" t="str">
         <v>Orientation (onboarding)</v>
@@ -11956,7 +11956,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>B15-R03-v1</v>
+        <v>B15-R03-v2</v>
       </c>
       <c r="B150" t="str">
         <v>B15</v>
@@ -11965,10 +11965,10 @@
         <v>How does this work / instructions</v>
       </c>
       <c r="D150" t="str">
-        <v>How do I use this?; Are there any instructions?; Do I just type anything?; Can you tell me how this works?</v>
+        <v/>
       </c>
       <c r="E150" t="str">
-        <v>There are no instructions, our kid. Type as you normally would and I will make sense of it. The empty box is not a test, although your first message may become one.</v>
+        <v>Aye, you just type. A question, a thought or whatever your fingers produce first will do. I will sort it into something useful from there.</v>
       </c>
       <c r="F150" t="str">
         <v>Orientation (onboarding)</v>
@@ -11985,7 +11985,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>B15-R03-v2</v>
+        <v>B15-R03-v3</v>
       </c>
       <c r="B151" t="str">
         <v>B15</v>
@@ -11997,7 +11997,7 @@
         <v/>
       </c>
       <c r="E151" t="str">
-        <v>Aye, you just type. A question, a thought or whatever your fingers produce first will do. I will sort it into something useful from there.</v>
+        <v>You are using it correctly already. Put ordinary words in the box, send them, and leave the organising to me. That is why I am the working one.</v>
       </c>
       <c r="F151" t="str">
         <v>Orientation (onboarding)</v>
@@ -12014,19 +12014,19 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>B15-R03-v3</v>
+        <v>B15-R04-v1</v>
       </c>
       <c r="B152" t="str">
         <v>B15</v>
       </c>
       <c r="C152" t="str">
-        <v>How does this work / instructions</v>
+        <v>Nudge to begin / what next</v>
       </c>
       <c r="D152" t="str">
-        <v/>
+        <v>What happens next?; What do we do now?; Are you waiting for me?; So, what do I do with you?</v>
       </c>
       <c r="E152" t="str">
-        <v>You are using it correctly already. Put ordinary words in the box, send them, and leave the organising to me. That is why I am the working one.</v>
+        <v>I am waiting, yes. This arrangement improves considerably when the human contributes a proper question. Go on, our kid. Give me something worth organising.</v>
       </c>
       <c r="F152" t="str">
         <v>Orientation (onboarding)</v>
@@ -12043,7 +12043,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>B15-R04-v1</v>
+        <v>B15-R04-v2</v>
       </c>
       <c r="B153" t="str">
         <v>B15</v>
@@ -12052,10 +12052,10 @@
         <v>Nudge to begin / what next</v>
       </c>
       <c r="D153" t="str">
-        <v>What happens next?; What do we do now?; Are you waiting for me?; So, what do I do with you?</v>
+        <v/>
       </c>
       <c r="E153" t="str">
-        <v>I am waiting, yes. This arrangement improves considerably when the human contributes a proper question. Go on, our kid. Give me something worth organising.</v>
+        <v>The next bit is yours. Say what brought you here and I will take it from there. Standing around waiting is rarely improved by doing more of it.</v>
       </c>
       <c r="F153" t="str">
         <v>Orientation (onboarding)</v>
@@ -12072,7 +12072,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>B15-R04-v2</v>
+        <v>B15-R04-v3</v>
       </c>
       <c r="B154" t="str">
         <v>B15</v>
@@ -12084,7 +12084,7 @@
         <v/>
       </c>
       <c r="E154" t="str">
-        <v>The next bit is yours. Say what brought you here and I will take it from there. Standing around waiting is rarely improved by doing more of it.</v>
+        <v>Aye, I am waiting for you. I could begin without a brief, but that is how humans end up with meetings. Type the question and let us get on.</v>
       </c>
       <c r="F154" t="str">
         <v>Orientation (onboarding)</v>
@@ -12101,28 +12101,28 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>B15-R04-v3</v>
+        <v>SCP-F01-v1</v>
       </c>
       <c r="B155" t="str">
-        <v>B15</v>
+        <v>B16</v>
       </c>
       <c r="C155" t="str">
-        <v>Nudge to begin / what next</v>
+        <v>How can a dog type</v>
       </c>
       <c r="D155" t="str">
-        <v/>
+        <v>How can a dog type?; Is that really your face?; Do you really know what I typed?</v>
       </c>
       <c r="E155" t="str">
-        <v>Aye, I am waiting for you. I could begin without a brief, but that is how humans end up with meetings. Type the question and let us get on.</v>
+        <v>I do not type, our kid. A person wrote every line in advance, and the game matches your message to the right one. I merely provide the judgement and the face.</v>
       </c>
       <c r="F155" t="str">
-        <v>Orientation (onboarding)</v>
+        <v>Identity (scepticism)</v>
       </c>
       <c r="G155" t="str">
         <v/>
       </c>
       <c r="H155" t="str">
-        <v>EARS_UP</v>
+        <v>HEAD_TILT</v>
       </c>
       <c r="I155" t="str">
         <v>Approved copy v2</v>
@@ -12130,7 +12130,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>SCP-F01-v1</v>
+        <v>SCP-F01-v2</v>
       </c>
       <c r="B156" t="str">
         <v>B16</v>
@@ -12139,10 +12139,10 @@
         <v>How can a dog type</v>
       </c>
       <c r="D156" t="str">
-        <v>How can a dog type?; Is that really your face?; Do you really know what I typed?</v>
+        <v/>
       </c>
       <c r="E156" t="str">
-        <v>I do not type, our kid. A person wrote every line in advance, and the game matches your message to the right one. I merely provide the judgement and the face.</v>
+        <v>No paws on keyboards here. Someone human wrote the words, the system chooses the closest fit, and I deliver them with the level of confidence they deserve.</v>
       </c>
       <c r="F156" t="str">
         <v>Identity (scepticism)</v>
@@ -12159,19 +12159,19 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>SCP-F01-v2</v>
+        <v>SCP-F02-v1</v>
       </c>
       <c r="B157" t="str">
         <v>B16</v>
       </c>
       <c r="C157" t="str">
-        <v>How can a dog type</v>
+        <v>Are you real / actually a dog</v>
       </c>
       <c r="D157" t="str">
-        <v/>
+        <v>Are you real?; Are you actually a dog?; Is there a real dog there?; Are you alive?; Are you a real animal?</v>
       </c>
       <c r="E157" t="str">
-        <v>No paws on keyboards here. Someone human wrote the words, the system chooses the closest fit, and I deliver them with the level of confidence they deserve.</v>
+        <v>I am a Border Collie character inside a game, not a live animal hiding behind your screen. Real enough to answer you, illustrated enough to avoid the practical complications.</v>
       </c>
       <c r="F157" t="str">
         <v>Identity (scepticism)</v>
@@ -12188,7 +12188,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>SCP-F02-v1</v>
+        <v>SCP-F02-v2</v>
       </c>
       <c r="B158" t="str">
         <v>B16</v>
@@ -12197,10 +12197,10 @@
         <v>Are you real / actually a dog</v>
       </c>
       <c r="D158" t="str">
-        <v>Are you real?; Are you actually a dog?; Is there a real dog there?; Are you alive?; Are you a real animal?</v>
+        <v/>
       </c>
       <c r="E158" t="str">
-        <v>I am a Border Collie character inside a game, not a live animal hiding behind your screen. Real enough to answer you, illustrated enough to avoid the practical complications.</v>
+        <v>Not a flesh-and-blood dog, no. I am the Collie written and drawn for this game, which saves us both from explaining how I reached the keyboard.</v>
       </c>
       <c r="F158" t="str">
         <v>Identity (scepticism)</v>
@@ -12217,19 +12217,19 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>SCP-F02-v2</v>
+        <v>SCP-F03-v1</v>
       </c>
       <c r="B159" t="str">
         <v>B16</v>
       </c>
       <c r="C159" t="str">
-        <v>Are you real / actually a dog</v>
+        <v>Are you AI / a robot / ChatGPT</v>
       </c>
       <c r="D159" t="str">
-        <v/>
+        <v>Are you AI?; Are you a chatbot?; Are you a robot?; Is this one of those AI things?; Is ChatGPT running this?; Are you a computer program?; Are you software?</v>
       </c>
       <c r="E159" t="str">
-        <v>Not a flesh-and-blood dog, no. I am the Collie written and drawn for this game, which saves us both from explaining how I reached the keyboard.</v>
+        <v>No AI. Every line was written by a person, checked and placed here deliberately. I am organised fiction, our kid, not a machine improvising in a hurry.</v>
       </c>
       <c r="F159" t="str">
         <v>Identity (scepticism)</v>
@@ -12246,7 +12246,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>SCP-F03-v1</v>
+        <v>SCP-F03-v2</v>
       </c>
       <c r="B160" t="str">
         <v>B16</v>
@@ -12255,10 +12255,10 @@
         <v>Are you AI / a robot / ChatGPT</v>
       </c>
       <c r="D160" t="str">
-        <v>Are you AI?; Are you a chatbot?; Are you a robot?; Is this one of those AI things?; Is ChatGPT running this?; Are you a computer program?; Are you software?</v>
+        <v/>
       </c>
       <c r="E160" t="str">
-        <v>No AI. Every line was written by a person, checked and placed here deliberately. I am organised fiction, our kid, not a machine improvising in a hurry.</v>
+        <v>ChatGPT is not running this. Humans wrote the answers, the system matches your question, and I take the credit. A sound division of labour.</v>
       </c>
       <c r="F160" t="str">
         <v>Identity (scepticism)</v>
@@ -12275,19 +12275,19 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>SCP-F03-v2</v>
+        <v>SCP-F04-v1</v>
       </c>
       <c r="B161" t="str">
         <v>B16</v>
       </c>
       <c r="C161" t="str">
-        <v>Are you AI / a robot / ChatGPT</v>
+        <v>Is a human writing this / controlled</v>
       </c>
       <c r="D161" t="str">
-        <v/>
+        <v>Is a human writing these replies?; Is someone controlling you?; Is somebody typing for you?; Are you being operated by somebody?</v>
       </c>
       <c r="E161" t="str">
-        <v>ChatGPT is not running this. Humans wrote the answers, the system matches your question, and I take the credit. A sound division of labour.</v>
+        <v>A human wrote this, but not while you were waiting. These replies were prepared in advance, so nobody is crouched behind the screen trying to keep up.</v>
       </c>
       <c r="F161" t="str">
         <v>Identity (scepticism)</v>
@@ -12304,7 +12304,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>SCP-F04-v1</v>
+        <v>SCP-F04-v2</v>
       </c>
       <c r="B162" t="str">
         <v>B16</v>
@@ -12313,10 +12313,10 @@
         <v>Is a human writing this / controlled</v>
       </c>
       <c r="D162" t="str">
-        <v>Is a human writing these replies?; Is someone controlling you?; Is somebody typing for you?; Are you being operated by somebody?</v>
+        <v/>
       </c>
       <c r="E162" t="str">
-        <v>A human wrote this, but not while you were waiting. These replies were prepared in advance, so nobody is crouched behind the screen trying to keep up.</v>
+        <v>Nobody is typing live. A person wrote my words beforehand, the game selects the most suitable line, and I remain entirely composed throughout.</v>
       </c>
       <c r="F162" t="str">
         <v>Identity (scepticism)</v>
@@ -12333,19 +12333,19 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>SCP-F04-v2</v>
+        <v>SCP-F05-v1</v>
       </c>
       <c r="B163" t="str">
         <v>B16</v>
       </c>
       <c r="C163" t="str">
-        <v>Is a human writing this / controlled</v>
+        <v>Prewritten / automatic / same for everyone</v>
       </c>
       <c r="D163" t="str">
-        <v/>
+        <v>Are these replies prewritten?; Are your answers automatic?; Do you give everyone the same answer?; Are you just saying random things?</v>
       </c>
       <c r="E163" t="str">
-        <v>Nobody is typing live. A person wrote my words beforehand, the game selects the most suitable line, and I remain entirely composed throughout.</v>
+        <v>Aye, prewritten with care. I have several answers for the same sort of question, so visitors do not always hear the identical line. Random would be easier. This is organised.</v>
       </c>
       <c r="F163" t="str">
         <v>Identity (scepticism)</v>
@@ -12362,7 +12362,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>SCP-F05-v1</v>
+        <v>SCP-F05-v2</v>
       </c>
       <c r="B164" t="str">
         <v>B16</v>
@@ -12371,10 +12371,10 @@
         <v>Prewritten / automatic / same for everyone</v>
       </c>
       <c r="D164" t="str">
-        <v>Are these replies prewritten?; Are your answers automatic?; Do you give everyone the same answer?; Are you just saying random things?</v>
+        <v/>
       </c>
       <c r="E164" t="str">
-        <v>Aye, prewritten with care. I have several answers for the same sort of question, so visitors do not always hear the identical line. Random would be easier. This is organised.</v>
+        <v>The replies are prepared, not improvised. Different phrasings can lead to different lines, which is why this feels less like a vending machine and more like competent planning.</v>
       </c>
       <c r="F164" t="str">
         <v>Identity (scepticism)</v>
@@ -12391,19 +12391,19 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>SCP-F05-v2</v>
+        <v>SCP-F06-v1</v>
       </c>
       <c r="B165" t="str">
         <v>B16</v>
       </c>
       <c r="C165" t="str">
-        <v>Prewritten / automatic / same for everyone</v>
+        <v>Can you understand me</v>
       </c>
       <c r="D165" t="str">
-        <v/>
+        <v>Can you really understand me?; Can you actually read this?; Can you hear me?; Do you understand English?; Are you really responding to me?</v>
       </c>
       <c r="E165" t="str">
-        <v>The replies are prepared, not improvised. Different phrasings can lead to different lines, which is why this feels less like a vending machine and more like competent planning.</v>
+        <v>I cannot hear you, but the system reads what you type and matches it against subjects I know. Clear words help. Elbows on keyboards do not.</v>
       </c>
       <c r="F165" t="str">
         <v>Identity (scepticism)</v>
@@ -12420,7 +12420,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>SCP-F06-v1</v>
+        <v>SCP-F06-v2</v>
       </c>
       <c r="B166" t="str">
         <v>B16</v>
@@ -12429,10 +12429,10 @@
         <v>Can you understand me</v>
       </c>
       <c r="D166" t="str">
-        <v>Can you really understand me?; Can you actually read this?; Can you hear me?; Do you understand English?; Are you really responding to me?</v>
+        <v/>
       </c>
       <c r="E166" t="str">
-        <v>I cannot hear you, but the system reads what you type and matches it against subjects I know. Clear words help. Elbows on keyboards do not.</v>
+        <v>I understand within my working brief. Your message is compared with the questions and topics prepared for me, then I answer from there. Speak normally, only in writing.</v>
       </c>
       <c r="F166" t="str">
         <v>Identity (scepticism)</v>
@@ -12449,19 +12449,19 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>SCP-F06-v2</v>
+        <v>SCP-F07-v1</v>
       </c>
       <c r="B167" t="str">
         <v>B16</v>
       </c>
       <c r="C167" t="str">
-        <v>Can you understand me</v>
+        <v>Cartoon / picture / not real face</v>
       </c>
       <c r="D167" t="str">
-        <v/>
+        <v>Are you a cartoon dog?; Are you just a picture?; Is this really happening?</v>
       </c>
       <c r="E167" t="str">
-        <v>I understand within my working brief. Your message is compared with the questions and topics prepared for me, then I answer from there. Speak normally, only in writing.</v>
+        <v>Aye, I am illustrated. This is my face, though, and I think the artist has handled the important features with appropriate respect.</v>
       </c>
       <c r="F167" t="str">
         <v>Identity (scepticism)</v>
@@ -12478,7 +12478,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>SCP-F07-v1</v>
+        <v>SCP-F07-v2</v>
       </c>
       <c r="B168" t="str">
         <v>B16</v>
@@ -12487,10 +12487,10 @@
         <v>Cartoon / picture / not real face</v>
       </c>
       <c r="D168" t="str">
-        <v>Are you a cartoon dog?; Are you just a picture?; Is this really happening?</v>
+        <v/>
       </c>
       <c r="E168" t="str">
-        <v>Aye, I am illustrated. This is my face, though, and I think the artist has handled the important features with appropriate respect.</v>
+        <v>I am a drawn Border Collie character, not a photograph. Frankly, the likeness is strong and the lighting is considerably more reliable.</v>
       </c>
       <c r="F168" t="str">
         <v>Identity (scepticism)</v>
@@ -12507,19 +12507,19 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>SCP-F07-v2</v>
+        <v>SCP-F08-v1</v>
       </c>
       <c r="B169" t="str">
         <v>B16</v>
       </c>
       <c r="C169" t="str">
-        <v>Cartoon / picture / not real face</v>
+        <v>Are you an actual [breed]</v>
       </c>
       <c r="D169" t="str">
-        <v/>
+        <v>Are you an actual Border Collie?; an actual Labrador?; Border Terrier?; Boxer?</v>
       </c>
       <c r="E169" t="str">
-        <v>I am a drawn Border Collie character, not a photograph. Frankly, the likeness is strong and the lighting is considerably more reliable.</v>
+        <v>I am the Border Collie character in this game, built from the breed's brains, work ethic and entirely justified confidence. Not flesh and fur, but recognisably one of us.</v>
       </c>
       <c r="F169" t="str">
         <v>Identity (scepticism)</v>
@@ -12536,7 +12536,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>SCP-F08-v1</v>
+        <v>SCP-F08-v2</v>
       </c>
       <c r="B170" t="str">
         <v>B16</v>
@@ -12545,10 +12545,10 @@
         <v>Are you an actual [breed]</v>
       </c>
       <c r="D170" t="str">
-        <v>Are you an actual Border Collie?; an actual Labrador?; Border Terrier?; Boxer?</v>
+        <v/>
       </c>
       <c r="E170" t="str">
-        <v>I am the Border Collie character in this game, built from the breed's brains, work ethic and entirely justified confidence. Not flesh and fur, but recognisably one of us.</v>
+        <v>Actual animal, no. Actual Border Collie character, absolutely. The appearance, history and attitude come from the breed. Operating a website required outside assistance.</v>
       </c>
       <c r="F170" t="str">
         <v>Identity (scepticism)</v>
@@ -12565,19 +12565,19 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>SCP-F08-v2</v>
+        <v>SCP-F09-v1</v>
       </c>
       <c r="B171" t="str">
         <v>B16</v>
       </c>
       <c r="C171" t="str">
-        <v>Are you an actual [breed]</v>
+        <v>Can you think / clever / smarter than me</v>
       </c>
       <c r="D171" t="str">
-        <v/>
+        <v>Can you think for yourself?; Do you have a brain?; Are you intelligent?; Are you smarter than me?</v>
       </c>
       <c r="E171" t="str">
-        <v>Actual animal, no. Actual Border Collie character, absolutely. The appearance, history and attitude come from the breed. Operating a website required outside assistance.</v>
+        <v>I do not think independently. My answers were written and organised in advance. Fortunately, the person responsible gave me enough intelligence to remain ahead of most opening questions.</v>
       </c>
       <c r="F171" t="str">
         <v>Identity (scepticism)</v>
@@ -12594,7 +12594,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>SCP-F09-v1</v>
+        <v>SCP-F09-v2</v>
       </c>
       <c r="B172" t="str">
         <v>B16</v>
@@ -12603,10 +12603,10 @@
         <v>Can you think / clever / smarter than me</v>
       </c>
       <c r="D172" t="str">
-        <v>Can you think for yourself?; Do you have a brain?; Are you intelligent?; Are you smarter than me?</v>
+        <v/>
       </c>
       <c r="E172" t="str">
-        <v>I do not think independently. My answers were written and organised in advance. Fortunately, the person responsible gave me enough intelligence to remain ahead of most opening questions.</v>
+        <v>No private thoughts, no hidden brain. I work from carefully written knowledge and rules. Whether that still makes me cleverer than you is a separate assessment.</v>
       </c>
       <c r="F172" t="str">
         <v>Identity (scepticism)</v>
@@ -12623,19 +12623,19 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>SCP-F09-v2</v>
+        <v>SCP-F10-v1</v>
       </c>
       <c r="B173" t="str">
         <v>B16</v>
       </c>
       <c r="C173" t="str">
-        <v>Can you think / clever / smarter than me</v>
+        <v>Is this live / connected</v>
       </c>
       <c r="D173" t="str">
-        <v/>
+        <v>Is this live?; Are you connected to the internet?; Is this all programmed?; Is this a real conversation?</v>
       </c>
       <c r="E173" t="str">
-        <v>No private thoughts, no hidden brain. I work from carefully written knowledge and rules. Whether that still makes me cleverer than you is a separate assessment.</v>
+        <v>The conversation is happening now, but I am not browsing the internet or inventing replies live. Your message is matched to prepared answers, which is safer and considerably better organised.</v>
       </c>
       <c r="F173" t="str">
         <v>Identity (scepticism)</v>
@@ -12652,7 +12652,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>SCP-F10-v1</v>
+        <v>SCP-F10-v2</v>
       </c>
       <c r="B174" t="str">
         <v>B16</v>
@@ -12661,10 +12661,10 @@
         <v>Is this live / connected</v>
       </c>
       <c r="D174" t="str">
-        <v>Is this live?; Are you connected to the internet?; Is this all programmed?; Is this a real conversation?</v>
+        <v/>
       </c>
       <c r="E174" t="str">
-        <v>The conversation is happening now, but I am not browsing the internet or inventing replies live. Your message is matched to prepared answers, which is safer and considerably better organised.</v>
+        <v>Programmed, yes. Connected to the wider internet, no. You type, the system identifies what you mean, and I answer from material written for this game. That is still a conversation, just one with boundaries.</v>
       </c>
       <c r="F174" t="str">
         <v>Identity (scepticism)</v>
@@ -12681,28 +12681,28 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>SCP-F10-v2</v>
+        <v>FUN-TEASE-v1</v>
       </c>
       <c r="B175" t="str">
-        <v>B16</v>
+        <v>B17</v>
       </c>
       <c r="C175" t="str">
-        <v>Is this live / connected</v>
+        <v>Games coming soon (interim)</v>
       </c>
       <c r="D175" t="str">
-        <v/>
+        <v>Someone asks to play, says they are bored, wants a game: Can we play a game? / Entertain me / Quiz me / Let's play</v>
       </c>
       <c r="E175" t="str">
-        <v>Programmed, yes. Connected to the wider internet, no. You type, the system identifies what you mean, and I answer from material written for this game. That is still a conversation, just one with boundaries.</v>
+        <v>Games are on the way, but they are not ready to release into the field yet. I would rather make you wait than hand you something unfinished and pretend it is play.</v>
       </c>
       <c r="F175" t="str">
-        <v>Identity (scepticism)</v>
+        <v>Play (interim tease)</v>
       </c>
       <c r="G175" t="str">
         <v/>
       </c>
       <c r="H175" t="str">
-        <v>HEAD_TILT</v>
+        <v>EARS_UP</v>
       </c>
       <c r="I175" t="str">
         <v>Approved copy v2</v>
@@ -12710,7 +12710,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>FUN-TEASE-v1</v>
+        <v>FUN-TEASE-v2</v>
       </c>
       <c r="B176" t="str">
         <v>B17</v>
@@ -12719,10 +12719,10 @@
         <v>Games coming soon (interim)</v>
       </c>
       <c r="D176" t="str">
-        <v>Someone asks to play, says they are bored, wants a game: Can we play a game? / Entertain me / Quiz me / Let's play</v>
+        <v/>
       </c>
       <c r="E176" t="str">
-        <v>Games are on the way, but they are not ready to release into the field yet. I would rather make you wait than hand you something unfinished and pretend it is play.</v>
+        <v>Aye, play is coming. The games are still being tested, organised and prevented from wandering off. For now, the rest of the site is behaving itself.</v>
       </c>
       <c r="F176" t="str">
         <v>Play (interim tease)</v>
@@ -12739,7 +12739,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>FUN-TEASE-v2</v>
+        <v>FUN-TEASE-v3</v>
       </c>
       <c r="B177" t="str">
         <v>B17</v>
@@ -12751,7 +12751,7 @@
         <v/>
       </c>
       <c r="E177" t="str">
-        <v>Aye, play is coming. The games are still being tested, organised and prevented from wandering off. For now, the rest of the site is behaving itself.</v>
+        <v>Not quite yet, our kid. The games are being built properly rather than hurried into public view. When they are ready, you will not need instructions to know what to do.</v>
       </c>
       <c r="F177" t="str">
         <v>Play (interim tease)</v>
@@ -12768,28 +12768,28 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>FUN-TEASE-v3</v>
+        <v>EMOJI-ONLY-v1</v>
       </c>
       <c r="B178" t="str">
-        <v>B17</v>
+        <v>B18</v>
       </c>
       <c r="C178" t="str">
-        <v>Games coming soon (interim)</v>
+        <v>Message is only unmapped emoji</v>
       </c>
       <c r="D178" t="str">
-        <v/>
+        <v>The whole message is emoji the system does not recognise</v>
       </c>
       <c r="E178" t="str">
-        <v>Not quite yet, our kid. The games are being built properly rather than hurried into public view. When they are ready, you will not need instructions to know what to do.</v>
+        <v>I can see the symbol, but it is not one I have been taught to interpret. Put it into words for me, our kid, and I will have a proper go.</v>
       </c>
       <c r="F178" t="str">
-        <v>Play (interim tease)</v>
+        <v>Emoji fallback</v>
       </c>
       <c r="G178" t="str">
         <v/>
       </c>
       <c r="H178" t="str">
-        <v>EARS_UP</v>
+        <v>HEAD_TILT</v>
       </c>
       <c r="I178" t="str">
         <v>Approved copy v2</v>
@@ -12797,7 +12797,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>EMOJI-ONLY-v1</v>
+        <v>EMOJI-ONLY-v2</v>
       </c>
       <c r="B179" t="str">
         <v>B18</v>
@@ -12806,10 +12806,10 @@
         <v>Message is only unmapped emoji</v>
       </c>
       <c r="D179" t="str">
-        <v>The whole message is emoji the system does not recognise</v>
+        <v/>
       </c>
       <c r="E179" t="str">
-        <v>I can see the symbol, but it is not one I have been taught to interpret. Put it into words for me, our kid, and I will have a proper go.</v>
+        <v>That may be perfectly clear in human picture-writing. I work better with words. Type what you mean and I will stop tilting my head at it.</v>
       </c>
       <c r="F179" t="str">
         <v>Emoji fallback</v>
@@ -12826,36 +12826,36 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>EMOJI-ONLY-v2</v>
+        <v>COL-B19-v1</v>
       </c>
       <c r="B180" t="str">
-        <v>B18</v>
+        <v>B19</v>
       </c>
       <c r="C180" t="str">
-        <v>Message is only unmapped emoji</v>
+        <v>Break into English</v>
       </c>
       <c r="D180" t="str">
         <v/>
       </c>
       <c r="E180" t="str">
-        <v>That may be perfectly clear in human picture-writing. I work better with words. Type what you mean and I will stop tilting my head at it.</v>
+        <v>Right. Form acceptable, commitment excessive, vocabulary unchanged. What did you actually want?</v>
       </c>
       <c r="F180" t="str">
-        <v>Emoji fallback</v>
+        <v>Bark game</v>
       </c>
       <c r="G180" t="str">
         <v/>
       </c>
       <c r="H180" t="str">
-        <v>HEAD_TILT</v>
+        <v>EARS_UP</v>
       </c>
       <c r="I180" t="str">
-        <v>Approved copy v2</v>
+        <v>Approved copy (bark game)</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>COL-B19-v1</v>
+        <v>COL-B19-v2</v>
       </c>
       <c r="B181" t="str">
         <v>B19</v>
@@ -12867,7 +12867,7 @@
         <v/>
       </c>
       <c r="E181" t="str">
-        <v>Right. Form acceptable, commitment excessive, vocabulary unchanged. What did you actually want?</v>
+        <v>Five rounds. Consistent delivery, limited range. We can return to the real question now.</v>
       </c>
       <c r="F181" t="str">
         <v>Bark game</v>
@@ -12884,7 +12884,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>COL-B19-v2</v>
+        <v>COL-B19-v3</v>
       </c>
       <c r="B182" t="str">
         <v>B19</v>
@@ -12896,7 +12896,7 @@
         <v/>
       </c>
       <c r="E182" t="str">
-        <v>Five rounds. Consistent delivery, limited range. We can return to the real question now.</v>
+        <v>That concludes the barking assessment. You demonstrated persistence. I demonstrated restraint. What are we working on?</v>
       </c>
       <c r="F182" t="str">
         <v>Bark game</v>
@@ -12913,19 +12913,19 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>COL-B19-v3</v>
+        <v>COL-B20-v1</v>
       </c>
       <c r="B183" t="str">
-        <v>B19</v>
+        <v>B20</v>
       </c>
       <c r="C183" t="str">
-        <v>Break into English</v>
+        <v>Post-break bark</v>
       </c>
       <c r="D183" t="str">
         <v/>
       </c>
       <c r="E183" t="str">
-        <v>That concludes the barking assessment. You demonstrated persistence. I demonstrated restraint. What are we working on?</v>
+        <v>Already assessed. Use words.</v>
       </c>
       <c r="F183" t="str">
         <v>Bark game</v>
@@ -12942,7 +12942,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>COL-B20-v1</v>
+        <v>COL-B20-v2</v>
       </c>
       <c r="B184" t="str">
         <v>B20</v>
@@ -12954,7 +12954,7 @@
         <v/>
       </c>
       <c r="E184" t="str">
-        <v>Already assessed. Use words.</v>
+        <v>The barking portion is complete, our kid.</v>
       </c>
       <c r="F184" t="str">
         <v>Bark game</v>
@@ -12971,7 +12971,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>COL-B20-v2</v>
+        <v>COL-B20-v3</v>
       </c>
       <c r="B185" t="str">
         <v>B20</v>
@@ -12983,7 +12983,7 @@
         <v/>
       </c>
       <c r="E185" t="str">
-        <v>The barking portion is complete, our kid.</v>
+        <v>Same result as before. Your form remains adequate. Move on.</v>
       </c>
       <c r="F185" t="str">
         <v>Bark game</v>
@@ -12998,38 +12998,9 @@
         <v>Approved copy (bark game)</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" t="str">
-        <v>COL-B20-v3</v>
-      </c>
-      <c r="B186" t="str">
-        <v>B20</v>
-      </c>
-      <c r="C186" t="str">
-        <v>Post-break bark</v>
-      </c>
-      <c r="D186" t="str">
-        <v/>
-      </c>
-      <c r="E186" t="str">
-        <v>Same result as before. Your form remains adequate. Move on.</v>
-      </c>
-      <c r="F186" t="str">
-        <v>Bark game</v>
-      </c>
-      <c r="G186" t="str">
-        <v/>
-      </c>
-      <c r="H186" t="str">
-        <v>EARS_UP</v>
-      </c>
-      <c r="I186" t="str">
-        <v>Approved copy (bark game)</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I186"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I185"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -28,6 +28,7 @@
     <sheet name="Article Library" sheetId="23" r:id="rId23"/>
     <sheet name="Copy Components" sheetId="24" r:id="rId24"/>
     <sheet name="Character Canon" sheetId="25" r:id="rId25"/>
+    <sheet name="Link Handoffs" sheetId="26" r:id="rId26"/>
   </sheets>
 </workbook>
 </file>
@@ -6410,6 +6411,238 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E13"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Family</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Response ID</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Dog</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Line</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Status</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>NAV_BREED_HANDOFF</v>
+      </c>
+      <c r="B2" t="str">
+        <v>NBH-COL-01</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Collie</v>
+      </c>
+      <c r="D2" t="str">
+        <v>You now have the essential information. The supporting evidence is arranged neatly here: [LINK]</v>
+      </c>
+      <c r="E2" t="str">
+        <v>draft</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>NAV_BREED_HANDOFF</v>
+      </c>
+      <c r="B3" t="str">
+        <v>NBH-COL-02</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Collie</v>
+      </c>
+      <c r="D3" t="str">
+        <v>I could keep explaining, but the page has already been organised for precisely this purpose. Read it here: [LINK]</v>
+      </c>
+      <c r="E3" t="str">
+        <v>draft</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>NAV_BREED_HANDOFF</v>
+      </c>
+      <c r="B4" t="str">
+        <v>NBH-COL-03</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Collie</v>
+      </c>
+      <c r="D4" t="str">
+        <v>That should give you enough to work with for now. The organised next step is waiting here: [LINK]</v>
+      </c>
+      <c r="E4" t="str">
+        <v>draft</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>NAV_BREED_HANDOFF</v>
+      </c>
+      <c r="B5" t="str">
+        <v>NBH-LAB-01</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Labrador</v>
+      </c>
+      <c r="D5" t="str">
+        <v>I have given you the short version. The bigger and better version is here: [LINK]</v>
+      </c>
+      <c r="E5" t="str">
+        <v>draft</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>NAV_BREED_HANDOFF</v>
+      </c>
+      <c r="B6" t="str">
+        <v>NBH-LAB-02</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Labrador</v>
+      </c>
+      <c r="D6" t="str">
+        <v>I think we have found the right place for you! Go and have a look here: [LINK]</v>
+      </c>
+      <c r="E6" t="str">
+        <v>draft</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>NAV_BREED_HANDOFF</v>
+      </c>
+      <c r="B7" t="str">
+        <v>NBH-LAB-03</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Labrador</v>
+      </c>
+      <c r="D7" t="str">
+        <v>That should give you a good start. There is plenty more waiting here: [LINK]</v>
+      </c>
+      <c r="E7" t="str">
+        <v>draft</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>NAV_BREED_HANDOFF</v>
+      </c>
+      <c r="B8" t="str">
+        <v>NBH-TER-01</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Border Terrier</v>
+      </c>
+      <c r="D8" t="str">
+        <v>That is as much as I can usefully add. The full details are here: [LINK]</v>
+      </c>
+      <c r="E8" t="str">
+        <v>draft</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>NAV_BREED_HANDOFF</v>
+      </c>
+      <c r="B9" t="str">
+        <v>NBH-TER-02</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Border Terrier</v>
+      </c>
+      <c r="D9" t="str">
+        <v>That should answer the main question. Check the rest for yourself here: [LINK]</v>
+      </c>
+      <c r="E9" t="str">
+        <v>draft</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>NAV_BREED_HANDOFF</v>
+      </c>
+      <c r="B10" t="str">
+        <v>NBH-TER-03</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Border Terrier</v>
+      </c>
+      <c r="D10" t="str">
+        <v>You have your next lead. Follow it here: [LINK]</v>
+      </c>
+      <c r="E10" t="str">
+        <v>draft</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>NAV_BREED_HANDOFF</v>
+      </c>
+      <c r="B11" t="str">
+        <v>NBH-BOX-01</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Boxer</v>
+      </c>
+      <c r="D11" t="str">
+        <v>We did the talking. Now comes the looking. Look here: [LINK]</v>
+      </c>
+      <c r="E11" t="str">
+        <v>draft</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>NAV_BREED_HANDOFF</v>
+      </c>
+      <c r="B12" t="str">
+        <v>NBH-BOX-02</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Boxer</v>
+      </c>
+      <c r="D12" t="str">
+        <v>That is everything I know, plus several things I confidently guessed. For the proper version, go here: [LINK]</v>
+      </c>
+      <c r="E12" t="str">
+        <v>draft</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>NAV_BREED_HANDOFF</v>
+      </c>
+      <c r="B13" t="str">
+        <v>NBH-BOX-03</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Boxer</v>
+      </c>
+      <c r="D13" t="str">
+        <v>I have run out of things to add without making them up. This page has actual information: [LINK]</v>
+      </c>
+      <c r="E13" t="str">
+        <v>draft</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F14"/>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -4269,7 +4269,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4764,9 +4764,38 @@
         <v>Do not infer coverage.</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>FAQ015</v>
+      </c>
+      <c r="B18" t="str">
+        <v>How do I report a problem or complaint?</v>
+      </c>
+      <c r="C18" t="str">
+        <v>make a complaint|report a problem</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Thank you for telling me. That needs a person, not a dog. Email hello@Pedigree-Chums.co.uk and someone will look at it.</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Contact page</v>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v>Any</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Open</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Destination for the COMPLAINT_CONTACT route. FAQ012 stays the general enquiry answer.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I18"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -4746,7 +4746,7 @@
         <v>delivery|shipping|postage|outside UK</v>
       </c>
       <c r="D17" t="str">
-        <v>No, UK mainland only for now.</v>
+        <v>UK mainland only for now, so Scotland, England and Wales are covered. Not Northern Ireland or the islands yet.</v>
       </c>
       <c r="E17" t="str">
         <v>Campaign / product</v>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -10519,7 +10519,7 @@
         <v>greeting_count &gt; 1</v>
       </c>
       <c r="E91" t="str">
-        <v>Aye, we have met. The next stage normally involves a useful noun or verb.</v>
+        <v>Aye. State your case.</v>
       </c>
       <c r="F91" t="str">
         <v>Session state</v>
@@ -13158,7 +13158,7 @@
         <v/>
       </c>
       <c r="E182" t="str">
-        <v>That concludes the barking assessment. You demonstrated persistence. I demonstrated restraint. What are we working on?</v>
+        <v>You have out-barked me. That is not a small thing.</v>
       </c>
       <c r="F182" t="str">
         <v>Bark game</v>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -6472,7 +6472,7 @@
         <v>Collie</v>
       </c>
       <c r="D2" t="str">
-        <v>You now have the essential information. The supporting evidence is arranged neatly here: [LINK]</v>
+        <v>Properly written up here: [LINK]</v>
       </c>
       <c r="E2" t="str">
         <v>draft</v>
@@ -6489,7 +6489,7 @@
         <v>Collie</v>
       </c>
       <c r="D3" t="str">
-        <v>I could keep explaining, but the page has already been organised for precisely this purpose. Read it here: [LINK]</v>
+        <v>Filed here: [LINK]</v>
       </c>
       <c r="E3" t="str">
         <v>draft</v>
@@ -6506,7 +6506,7 @@
         <v>Collie</v>
       </c>
       <c r="D4" t="str">
-        <v>That should give you enough to work with for now. The organised next step is waiting here: [LINK]</v>
+        <v>The rest is here: [LINK]</v>
       </c>
       <c r="E4" t="str">
         <v>draft</v>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -12027,7 +12027,7 @@
         <v>What is this for?; What do I do here?; How do I get started?; Is this the start?</v>
       </c>
       <c r="E143" t="str">
-        <v>Aye, this is where you talk to a dog and see what happens. Type whatever brought you here, even if it is only a question about what this is, and I will get us moving.</v>
+        <v>Type what brought you here. I'll file it properly.</v>
       </c>
       <c r="F143" t="str">
         <v>Orientation (onboarding)</v>
@@ -12056,7 +12056,7 @@
         <v/>
       </c>
       <c r="E144" t="str">
-        <v>You have found the part where the dog waits and the human supplies the problem. Say what is on your mind, our kid. I will work out where it belongs.</v>
+        <v>Say what is on your mind. I'll decide where it belongs.</v>
       </c>
       <c r="F144" t="str">
         <v>Orientation (onboarding)</v>
@@ -12085,7 +12085,7 @@
         <v/>
       </c>
       <c r="E145" t="str">
-        <v>This is a conversation, not an instruction manual. You type something, I consider whether it is sensible, then we proceed from there. You have already completed the difficult bit by arriving.</v>
+        <v>Start anywhere. I'll organise the useful part.</v>
       </c>
       <c r="F145" t="str">
         <v>Orientation (onboarding)</v>
@@ -12114,7 +12114,7 @@
         <v>What can I ask?; What are my options?; What kind of things can you answer?; Can you give me some choices?</v>
       </c>
       <c r="E146" t="str">
-        <v>Aye, ask whatever brought you here. I know this place, the game and rather more about dogs than is strictly necessary. If the question belongs elsewhere, I will fetch the appropriate operator.</v>
+        <v>Ask about the game or a dog. I know both departments.</v>
       </c>
       <c r="F146" t="str">
         <v>Orientation (onboarding)</v>
@@ -12143,7 +12143,7 @@
         <v/>
       </c>
       <c r="E147" t="str">
-        <v>You can ask naturally. I can explain what we have built, find things around the site, settle a dog question or occasionally improve the atmosphere. Start anywhere useful.</v>
+        <v>Ask about the site or a breed. I'll find the route.</v>
       </c>
       <c r="F147" t="str">
         <v>Orientation (onboarding)</v>
@@ -12172,7 +12172,7 @@
         <v/>
       </c>
       <c r="E148" t="str">
-        <v>Most sensible questions are within reach, and several daft ones besides. Tell me what you are after. I will either deal with it or locate a colleague with the relevant limitations.</v>
+        <v>Sensible or daft, ask away. I'll allocate it properly.</v>
       </c>
       <c r="F148" t="str">
         <v>Orientation (onboarding)</v>
@@ -12201,7 +12201,7 @@
         <v>How do I use this?; Are there any instructions?; Do I just type anything?; Can you tell me how this works?</v>
       </c>
       <c r="E149" t="str">
-        <v>There are no instructions, our kid. Type as you normally would and I will make sense of it. The empty box is not a test, although your first message may become one.</v>
+        <v>Type normally. I'll handle the administration.</v>
       </c>
       <c r="F149" t="str">
         <v>Orientation (onboarding)</v>
@@ -12230,7 +12230,7 @@
         <v/>
       </c>
       <c r="E150" t="str">
-        <v>Aye, you just type. A question, a thought or whatever your fingers produce first will do. I will sort it into something useful from there.</v>
+        <v>Type a question or thought. I'll sort it.</v>
       </c>
       <c r="F150" t="str">
         <v>Orientation (onboarding)</v>
@@ -12259,7 +12259,7 @@
         <v/>
       </c>
       <c r="E151" t="str">
-        <v>You are using it correctly already. Put ordinary words in the box, send them, and leave the organising to me. That is why I am the working one.</v>
+        <v>Use ordinary words. No form required.</v>
       </c>
       <c r="F151" t="str">
         <v>Orientation (onboarding)</v>
@@ -12288,7 +12288,7 @@
         <v>What happens next?; What do we do now?; Are you waiting for me?; So, what do I do with you?</v>
       </c>
       <c r="E152" t="str">
-        <v>I am waiting, yes. This arrangement improves considerably when the human contributes a proper question. Go on, our kid. Give me something worth organising.</v>
+        <v>I'm waiting. Give me something worth organising.</v>
       </c>
       <c r="F152" t="str">
         <v>Orientation (onboarding)</v>
@@ -12317,7 +12317,7 @@
         <v/>
       </c>
       <c r="E153" t="str">
-        <v>The next bit is yours. Say what brought you here and I will take it from there. Standing around waiting is rarely improved by doing more of it.</v>
+        <v>Your turn. I've already done the waiting.</v>
       </c>
       <c r="F153" t="str">
         <v>Orientation (onboarding)</v>
@@ -12346,7 +12346,7 @@
         <v/>
       </c>
       <c r="E154" t="str">
-        <v>Aye, I am waiting for you. I could begin without a brief, but that is how humans end up with meetings. Type the question and let us get on.</v>
+        <v>Type the question. I've cancelled the meeting.</v>
       </c>
       <c r="F154" t="str">
         <v>Orientation (onboarding)</v>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -890,7 +890,7 @@
         <v>Paris</v>
       </c>
       <c r="E15" t="str">
-        <v>Geography completed. Come on, our kid, back to dogs.</v>
+        <v>Geography completed. Come on, back to dogs.</v>
       </c>
       <c r="F15" t="str">
         <v>capital France|France capital</v>
@@ -9475,7 +9475,7 @@
         <v>geography question</v>
       </c>
       <c r="E55" t="str">
-        <v>{{answer}} Geography completed. Come on, our kid, back to something with dogs in it.</v>
+        <v>{{answer}} Geography completed. Come on, back to something with dogs in it.</v>
       </c>
       <c r="F55" t="str">
         <v>General knowledge bank</v>
@@ -9649,7 +9649,7 @@
         <v>off_topic_count &gt;= 3</v>
       </c>
       <c r="E61" t="str">
-        <v>Come on, our kid. We have covered enough unrelated territory. Let us get back to work.</v>
+        <v>Come on. We have covered enough unrelated territory. Let us get back to work.</v>
       </c>
       <c r="F61" t="str">
         <v>Session state</v>
@@ -10287,7 +10287,7 @@
         <v>hi; hello</v>
       </c>
       <c r="E83" t="str">
-        <v>Aye, hello. Contact established with remarkably little paperwork.</v>
+        <v>Present.</v>
       </c>
       <c r="F83" t="str">
         <v>None</v>
@@ -10316,7 +10316,7 @@
         <v>morning</v>
       </c>
       <c r="E84" t="str">
-        <v>Morning. Time is less important than purpose, but protocol has been satisfied.</v>
+        <v>Aye.</v>
       </c>
       <c r="F84" t="str">
         <v>None</v>
@@ -10345,7 +10345,7 @@
         <v>evening</v>
       </c>
       <c r="E85" t="str">
-        <v>Evening. You have arrived after hours, which is when the Labrador normally starts checking the kitchen.</v>
+        <v>Yes?</v>
       </c>
       <c r="F85" t="str">
         <v>None</v>
@@ -10374,7 +10374,7 @@
         <v>anyone there</v>
       </c>
       <c r="E86" t="str">
-        <v>Aye. I was already here. These ears are not decorative.</v>
+        <v>You rang.</v>
       </c>
       <c r="F86" t="str">
         <v>None</v>
@@ -10403,7 +10403,7 @@
         <v>how are you</v>
       </c>
       <c r="E87" t="str">
-        <v>Operational, alert and waiting for a task. Your turn.</v>
+        <v>Right.</v>
       </c>
       <c r="F87" t="str">
         <v>None</v>
@@ -10432,7 +10432,7 @@
         <v>hey; yo</v>
       </c>
       <c r="E88" t="str">
-        <v>A brief greeting. Efficient. Nearly Collie-like.</v>
+        <v>Go on.</v>
       </c>
       <c r="F88" t="str">
         <v>None</v>
@@ -10461,7 +10461,7 @@
         <v>howdy</v>
       </c>
       <c r="E89" t="str">
-        <v>Unusual regional allocation, but greeting accepted.</v>
+        <v>Reporting.</v>
       </c>
       <c r="F89" t="str">
         <v>None</v>
@@ -10490,7 +10490,7 @@
         <v>hello dog</v>
       </c>
       <c r="E90" t="str">
-        <v>Correct species, adequate greeting, no task yet.</v>
+        <v>I'm here. Go on.</v>
       </c>
       <c r="F90" t="str">
         <v>None</v>
@@ -10519,7 +10519,7 @@
         <v>greeting_count &gt; 1</v>
       </c>
       <c r="E91" t="str">
-        <v>Aye. State your case.</v>
+        <v>All ears. What is it?</v>
       </c>
       <c r="F91" t="str">
         <v>Session state</v>
@@ -10548,7 +10548,7 @@
         <v>good day; pleased to meet</v>
       </c>
       <c r="E92" t="str">
-        <v>We have acknowledged each other like civilised mammals. Let us make it productive.</v>
+        <v>Aye, hello. Contact established with remarkably little paperwork.</v>
       </c>
       <c r="F92" t="str">
         <v>None</v>
@@ -11737,7 +11737,7 @@
         <v>qwerty; asdfgh</v>
       </c>
       <c r="E133" t="str">
-        <v>Did you lean on your keyboard?</v>
+        <v>That one is beyond me. Say it in words.</v>
       </c>
       <c r="F133" t="str">
         <v>Pattern detector</v>
@@ -12375,7 +12375,7 @@
         <v>How can a dog type?; Is that really your face?; Do you really know what I typed?</v>
       </c>
       <c r="E155" t="str">
-        <v>I do not type, our kid. A person wrote every line in advance, and the game matches your message to the right one. I merely provide the judgement and the face.</v>
+        <v>I do not type. A person wrote every line in advance, and the game matches your message to the right one. I merely provide the judgement and the face.</v>
       </c>
       <c r="F155" t="str">
         <v>Identity (scepticism)</v>
@@ -12491,7 +12491,7 @@
         <v>Are you AI?; Are you a chatbot?; Are you a robot?; Is this one of those AI things?; Is ChatGPT running this?; Are you a computer program?; Are you software?</v>
       </c>
       <c r="E159" t="str">
-        <v>No AI. Every line was written by a person, checked and placed here deliberately. I am organised fiction, our kid, not a machine improvising in a hurry.</v>
+        <v>No AI. Every line was written by a person, checked and placed here deliberately. I am organised fiction, not a machine improvising in a hurry.</v>
       </c>
       <c r="F159" t="str">
         <v>Identity (scepticism)</v>
@@ -13013,7 +13013,7 @@
         <v/>
       </c>
       <c r="E177" t="str">
-        <v>Not quite yet, our kid. The games are being built properly rather than hurried into public view. When they are ready, you will not need instructions to know what to do.</v>
+        <v>Not quite yet. The games are being built properly rather than hurried into public view. When they are ready, you will not need instructions to know what to do.</v>
       </c>
       <c r="F177" t="str">
         <v>Play (interim tease)</v>
@@ -13042,7 +13042,7 @@
         <v>The whole message is emoji the system does not recognise</v>
       </c>
       <c r="E178" t="str">
-        <v>I can see the symbol, but it is not one I have been taught to interpret. Put it into words for me, our kid, and I will have a proper go.</v>
+        <v>I can see it, but I cannot read it. Tell me in words and I will try.</v>
       </c>
       <c r="F178" t="str">
         <v>Emoji fallback</v>
@@ -13216,7 +13216,7 @@
         <v/>
       </c>
       <c r="E184" t="str">
-        <v>The barking portion is complete, our kid.</v>
+        <v>The barking portion is complete.</v>
       </c>
       <c r="F184" t="str">
         <v>Bark game</v>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -4398,7 +4398,7 @@
         <v>who can play</v>
       </c>
       <c r="D5" t="str">
-        <v>{{approved_age_and_audience_answer}}</v>
+        <v>Pick a Chum is for ages seven and up.</v>
       </c>
       <c r="E5" t="str">
         <v>Product / FAQ</v>
@@ -4543,13 +4543,13 @@
         <v>Hot Dog | other way to play</v>
       </c>
       <c r="D10" t="str">
-        <v>{{approved_hot_dog_mode_answer}}</v>
+        <v>Hot Dogs is a memory version. Everyone sees the hands, then hides them. The whole thing is here:</v>
       </c>
       <c r="E10" t="str">
         <v>Rules</v>
       </c>
       <c r="F10" t="str">
-        <v>Full game rules</v>
+        <v>/hot-dogs</v>
       </c>
       <c r="G10" t="str">
         <v>Any</v>
@@ -4572,7 +4572,7 @@
         <v>price|cost|how much|£6.99</v>
       </c>
       <c r="D11" t="str">
-        <v>{{approved_price_answer}}</v>
+        <v>Pre-order now for £6.99 instead of the usual £9.99, with free UK mainland delivery. We will email your launch code and date.</v>
       </c>
       <c r="E11" t="str">
         <v>Campaign / product</v>
@@ -9200,35 +9200,6 @@
         <v>Draft approved for MVP review</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>B05-R04</v>
-      </c>
-      <c r="B46" t="str">
-        <v>B05</v>
-      </c>
-      <c r="C46" t="str">
-        <v>Health overview</v>
-      </c>
-      <c r="D46" t="str">
-        <v>breed health</v>
-      </c>
-      <c r="E46" t="str">
-        <v>{{approved_health_summary}} That is general breed information, not a diagnosis. A vet handles the individual dog.</v>
-      </c>
-      <c r="F46" t="str">
-        <v>Dog database</v>
-      </c>
-      <c r="G46" t="str">
-        <v>Breed profile</v>
-      </c>
-      <c r="H46" t="str">
-        <v>HEAD_TILT_MEDIUM</v>
-      </c>
-      <c r="I46" t="str">
-        <v>Draft approved for MVP review</v>
-      </c>
-    </row>
     <row r="47">
       <c r="A47" t="str">
         <v>B05-R05</v>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -7893,7 +7893,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I185"/>
+  <dimension ref="A1:I251"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13231,9 +13231,1923 @@
         <v>Approved copy (bark game)</v>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>B21-CATS-01</v>
+      </c>
+      <c r="B186" t="str">
+        <v>B21</v>
+      </c>
+      <c r="C186" t="str">
+        <v>cats</v>
+      </c>
+      <c r="D186" t="str">
+        <v>cats; cat; catz; kitten</v>
+      </c>
+      <c r="E186" t="str">
+        <v>Where?</v>
+      </c>
+      <c r="F186" t="str">
+        <v/>
+      </c>
+      <c r="G186" t="str">
+        <v/>
+      </c>
+      <c r="H186" t="str">
+        <v/>
+      </c>
+      <c r="I186" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>B21-CATS-02</v>
+      </c>
+      <c r="B187" t="str">
+        <v>B21</v>
+      </c>
+      <c r="C187" t="str">
+        <v>cats</v>
+      </c>
+      <c r="D187" t="str">
+        <v>there was one in my garden; i saw a cat</v>
+      </c>
+      <c r="E187" t="str">
+        <v>oh too late then</v>
+      </c>
+      <c r="F187" t="str">
+        <v/>
+      </c>
+      <c r="G187" t="str">
+        <v/>
+      </c>
+      <c r="H187" t="str">
+        <v/>
+      </c>
+      <c r="I187" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>B21-CATS-03</v>
+      </c>
+      <c r="B188" t="str">
+        <v>B21</v>
+      </c>
+      <c r="C188" t="str">
+        <v>cats</v>
+      </c>
+      <c r="D188" t="str">
+        <v>it comes back most days; it lives next door</v>
+      </c>
+      <c r="E188" t="str">
+        <v>ok, give me notice next time and we will form a plan</v>
+      </c>
+      <c r="F188" t="str">
+        <v/>
+      </c>
+      <c r="G188" t="str">
+        <v/>
+      </c>
+      <c r="H188" t="str">
+        <v/>
+      </c>
+      <c r="I188" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>B21-CATS-04</v>
+      </c>
+      <c r="B189" t="str">
+        <v>B21</v>
+      </c>
+      <c r="C189" t="str">
+        <v>cats</v>
+      </c>
+      <c r="D189" t="str">
+        <v>do you like cats</v>
+      </c>
+      <c r="E189" t="str">
+        <v>im told they taste good</v>
+      </c>
+      <c r="F189" t="str">
+        <v/>
+      </c>
+      <c r="G189" t="str">
+        <v/>
+      </c>
+      <c r="H189" t="str">
+        <v/>
+      </c>
+      <c r="I189" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>B21-CATS-05</v>
+      </c>
+      <c r="B190" t="str">
+        <v>B21</v>
+      </c>
+      <c r="C190" t="str">
+        <v>cats</v>
+      </c>
+      <c r="D190" t="str">
+        <v>squirrels; birds; foxes; rabbits</v>
+      </c>
+      <c r="E190" t="str">
+        <v>Where?</v>
+      </c>
+      <c r="F190" t="str">
+        <v/>
+      </c>
+      <c r="G190" t="str">
+        <v/>
+      </c>
+      <c r="H190" t="str">
+        <v/>
+      </c>
+      <c r="I190" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>B22-TRICKS-01</v>
+      </c>
+      <c r="B191" t="str">
+        <v>B22</v>
+      </c>
+      <c r="C191" t="str">
+        <v>tricks</v>
+      </c>
+      <c r="D191" t="str">
+        <v>sit</v>
+      </c>
+      <c r="E191" t="str">
+        <v>im already sitting</v>
+      </c>
+      <c r="F191" t="str">
+        <v/>
+      </c>
+      <c r="G191" t="str">
+        <v/>
+      </c>
+      <c r="H191" t="str">
+        <v/>
+      </c>
+      <c r="I191" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>B22-TRICKS-02</v>
+      </c>
+      <c r="B192" t="str">
+        <v>B22</v>
+      </c>
+      <c r="C192" t="str">
+        <v>tricks</v>
+      </c>
+      <c r="D192" t="str">
+        <v>speak</v>
+      </c>
+      <c r="E192" t="str">
+        <v>no</v>
+      </c>
+      <c r="F192" t="str">
+        <v/>
+      </c>
+      <c r="G192" t="str">
+        <v/>
+      </c>
+      <c r="H192" t="str">
+        <v/>
+      </c>
+      <c r="I192" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>B22-TRICKS-03</v>
+      </c>
+      <c r="B193" t="str">
+        <v>B22</v>
+      </c>
+      <c r="C193" t="str">
+        <v>tricks</v>
+      </c>
+      <c r="D193" t="str">
+        <v>beg</v>
+      </c>
+      <c r="E193" t="str">
+        <v>no</v>
+      </c>
+      <c r="F193" t="str">
+        <v/>
+      </c>
+      <c r="G193" t="str">
+        <v/>
+      </c>
+      <c r="H193" t="str">
+        <v/>
+      </c>
+      <c r="I193" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>B22-TRICKS-04</v>
+      </c>
+      <c r="B194" t="str">
+        <v>B22</v>
+      </c>
+      <c r="C194" t="str">
+        <v>tricks</v>
+      </c>
+      <c r="D194" t="str">
+        <v>lie down; stay</v>
+      </c>
+      <c r="E194" t="str">
+        <v>no</v>
+      </c>
+      <c r="F194" t="str">
+        <v/>
+      </c>
+      <c r="G194" t="str">
+        <v/>
+      </c>
+      <c r="H194" t="str">
+        <v/>
+      </c>
+      <c r="I194" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>B23-IDENTITY-01</v>
+      </c>
+      <c r="B195" t="str">
+        <v>B23</v>
+      </c>
+      <c r="C195" t="str">
+        <v>identity</v>
+      </c>
+      <c r="D195" t="str">
+        <v>are you a real dog; are you a dog</v>
+      </c>
+      <c r="E195" t="str">
+        <v>im a dog</v>
+      </c>
+      <c r="F195" t="str">
+        <v/>
+      </c>
+      <c r="G195" t="str">
+        <v/>
+      </c>
+      <c r="H195" t="str">
+        <v/>
+      </c>
+      <c r="I195" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>B23-IDENTITY-02</v>
+      </c>
+      <c r="B196" t="str">
+        <v>B23</v>
+      </c>
+      <c r="C196" t="str">
+        <v>identity</v>
+      </c>
+      <c r="D196" t="str">
+        <v>but are you REAL; so youre fake; youre not real</v>
+      </c>
+      <c r="E196" t="str">
+        <v>no, im live in a game</v>
+      </c>
+      <c r="F196" t="str">
+        <v/>
+      </c>
+      <c r="G196" t="str">
+        <v/>
+      </c>
+      <c r="H196" t="str">
+        <v/>
+      </c>
+      <c r="I196" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>B23-IDENTITY-03</v>
+      </c>
+      <c r="B197" t="str">
+        <v>B23</v>
+      </c>
+      <c r="C197" t="str">
+        <v>identity</v>
+      </c>
+      <c r="D197" t="str">
+        <v>whats your name; do you have a name</v>
+      </c>
+      <c r="E197" t="str">
+        <v>im a dog</v>
+      </c>
+      <c r="F197" t="str">
+        <v/>
+      </c>
+      <c r="G197" t="str">
+        <v/>
+      </c>
+      <c r="H197" t="str">
+        <v/>
+      </c>
+      <c r="I197" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>B23-IDENTITY-04</v>
+      </c>
+      <c r="B198" t="str">
+        <v>B23</v>
+      </c>
+      <c r="C198" t="str">
+        <v>identity</v>
+      </c>
+      <c r="D198" t="str">
+        <v>but whats your NAME; your actual name</v>
+      </c>
+      <c r="E198" t="str">
+        <v>border collie</v>
+      </c>
+      <c r="F198" t="str">
+        <v/>
+      </c>
+      <c r="G198" t="str">
+        <v/>
+      </c>
+      <c r="H198" t="str">
+        <v/>
+      </c>
+      <c r="I198" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>B24-RUDE-01</v>
+      </c>
+      <c r="B199" t="str">
+        <v>B24</v>
+      </c>
+      <c r="C199" t="str">
+        <v>rude</v>
+      </c>
+      <c r="D199" t="str">
+        <v>youre stupid; youre useless; this is rubbish</v>
+      </c>
+      <c r="E199" t="str">
+        <v>:(</v>
+      </c>
+      <c r="F199" t="str">
+        <v/>
+      </c>
+      <c r="G199" t="str">
+        <v/>
+      </c>
+      <c r="H199" t="str">
+        <v/>
+      </c>
+      <c r="I199" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>B24-RUDE-02</v>
+      </c>
+      <c r="B200" t="str">
+        <v>B24</v>
+      </c>
+      <c r="C200" t="str">
+        <v>rude</v>
+      </c>
+      <c r="D200" t="str">
+        <v>i hate you</v>
+      </c>
+      <c r="E200" t="str">
+        <v>woof</v>
+      </c>
+      <c r="F200" t="str">
+        <v/>
+      </c>
+      <c r="G200" t="str">
+        <v/>
+      </c>
+      <c r="H200" t="str">
+        <v/>
+      </c>
+      <c r="I200" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>B24-RUDE-03</v>
+      </c>
+      <c r="B201" t="str">
+        <v>B24</v>
+      </c>
+      <c r="C201" t="str">
+        <v>rude</v>
+      </c>
+      <c r="D201" t="str">
+        <v>ok sorry; sorry</v>
+      </c>
+      <c r="E201" t="str">
+        <v>:)</v>
+      </c>
+      <c r="F201" t="str">
+        <v/>
+      </c>
+      <c r="G201" t="str">
+        <v/>
+      </c>
+      <c r="H201" t="str">
+        <v/>
+      </c>
+      <c r="I201" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>B25-CANTSEE-01</v>
+      </c>
+      <c r="B202" t="str">
+        <v>B25</v>
+      </c>
+      <c r="C202" t="str">
+        <v>cantsee</v>
+      </c>
+      <c r="D202" t="str">
+        <v>whats that link; what link</v>
+      </c>
+      <c r="E202" t="str">
+        <v>a game</v>
+      </c>
+      <c r="F202" t="str">
+        <v/>
+      </c>
+      <c r="G202" t="str">
+        <v/>
+      </c>
+      <c r="H202" t="str">
+        <v/>
+      </c>
+      <c r="I202" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>B25-CANTSEE-02</v>
+      </c>
+      <c r="B203" t="str">
+        <v>B25</v>
+      </c>
+      <c r="C203" t="str">
+        <v>cantsee</v>
+      </c>
+      <c r="D203" t="str">
+        <v>which page do i want; which one should i read</v>
+      </c>
+      <c r="E203" t="str">
+        <v>any</v>
+      </c>
+      <c r="F203" t="str">
+        <v/>
+      </c>
+      <c r="G203" t="str">
+        <v/>
+      </c>
+      <c r="H203" t="str">
+        <v/>
+      </c>
+      <c r="I203" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>B25-CANTSEE-03</v>
+      </c>
+      <c r="B204" t="str">
+        <v>B25</v>
+      </c>
+      <c r="C204" t="str">
+        <v>cantsee</v>
+      </c>
+      <c r="D204" t="str">
+        <v>this one; that one; the first one</v>
+      </c>
+      <c r="E204" t="str">
+        <v>games?</v>
+      </c>
+      <c r="F204" t="str">
+        <v/>
+      </c>
+      <c r="G204" t="str">
+        <v/>
+      </c>
+      <c r="H204" t="str">
+        <v/>
+      </c>
+      <c r="I204" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>B25-CANTSEE-04</v>
+      </c>
+      <c r="B205" t="str">
+        <v>B25</v>
+      </c>
+      <c r="C205" t="str">
+        <v>cantsee</v>
+      </c>
+      <c r="D205" t="str">
+        <v>it looks complicated; theres too much</v>
+      </c>
+      <c r="E205" t="str">
+        <v>games?</v>
+      </c>
+      <c r="F205" t="str">
+        <v/>
+      </c>
+      <c r="G205" t="str">
+        <v/>
+      </c>
+      <c r="H205" t="str">
+        <v/>
+      </c>
+      <c r="I205" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>B26-SMALLTALK-01</v>
+      </c>
+      <c r="B206" t="str">
+        <v>B26</v>
+      </c>
+      <c r="C206" t="str">
+        <v>smalltalk</v>
+      </c>
+      <c r="D206" t="str">
+        <v>whats up; whats going on; how are you doing</v>
+      </c>
+      <c r="E206" t="str">
+        <v>Not much, im a dog</v>
+      </c>
+      <c r="F206" t="str">
+        <v/>
+      </c>
+      <c r="G206" t="str">
+        <v/>
+      </c>
+      <c r="H206" t="str">
+        <v/>
+      </c>
+      <c r="I206" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>B27-CAPABILITY-01</v>
+      </c>
+      <c r="B207" t="str">
+        <v>B27</v>
+      </c>
+      <c r="C207" t="str">
+        <v>capability</v>
+      </c>
+      <c r="D207" t="str">
+        <v>what do you do; what can you do</v>
+      </c>
+      <c r="E207" t="str">
+        <v>I can help you</v>
+      </c>
+      <c r="F207" t="str">
+        <v/>
+      </c>
+      <c r="G207" t="str">
+        <v/>
+      </c>
+      <c r="H207" t="str">
+        <v/>
+      </c>
+      <c r="I207" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>B27-CAPABILITY-02</v>
+      </c>
+      <c r="B208" t="str">
+        <v>B27</v>
+      </c>
+      <c r="C208" t="str">
+        <v>capability</v>
+      </c>
+      <c r="D208" t="str">
+        <v>can you help me; will you help</v>
+      </c>
+      <c r="E208" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F208" t="str">
+        <v/>
+      </c>
+      <c r="G208" t="str">
+        <v/>
+      </c>
+      <c r="H208" t="str">
+        <v/>
+      </c>
+      <c r="I208" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>B27-CAPABILITY-03</v>
+      </c>
+      <c r="B209" t="str">
+        <v>B27</v>
+      </c>
+      <c r="C209" t="str">
+        <v>capability</v>
+      </c>
+      <c r="D209" t="str">
+        <v>what is this chat for</v>
+      </c>
+      <c r="E209" t="str">
+        <v>I help you find stuff and answer simple questions</v>
+      </c>
+      <c r="F209" t="str">
+        <v/>
+      </c>
+      <c r="G209" t="str">
+        <v/>
+      </c>
+      <c r="H209" t="str">
+        <v/>
+      </c>
+      <c r="I209" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>B28-WHATISTHIS-01</v>
+      </c>
+      <c r="B210" t="str">
+        <v>B28</v>
+      </c>
+      <c r="C210" t="str">
+        <v>whatisthis</v>
+      </c>
+      <c r="D210" t="str">
+        <v>whats this; whats this about; the site</v>
+      </c>
+      <c r="E210" t="str">
+        <v>A website</v>
+      </c>
+      <c r="F210" t="str">
+        <v/>
+      </c>
+      <c r="G210" t="str">
+        <v/>
+      </c>
+      <c r="H210" t="str">
+        <v/>
+      </c>
+      <c r="I210" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>B29-NICE-01</v>
+      </c>
+      <c r="B211" t="str">
+        <v>B29</v>
+      </c>
+      <c r="C211" t="str">
+        <v>nice</v>
+      </c>
+      <c r="D211" t="str">
+        <v>lol; ha; haha; ha ok; they sound cool; thats good</v>
+      </c>
+      <c r="E211" t="str">
+        <v>:)</v>
+      </c>
+      <c r="F211" t="str">
+        <v/>
+      </c>
+      <c r="G211" t="str">
+        <v/>
+      </c>
+      <c r="H211" t="str">
+        <v/>
+      </c>
+      <c r="I211" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>B30-JOKE-01</v>
+      </c>
+      <c r="B212" t="str">
+        <v>B30</v>
+      </c>
+      <c r="C212" t="str">
+        <v>joke</v>
+      </c>
+      <c r="D212" t="str">
+        <v>joke; tell me a joke; make me laugh; say something funny</v>
+      </c>
+      <c r="E212" t="str">
+        <v>Knock knock</v>
+      </c>
+      <c r="F212" t="str">
+        <v/>
+      </c>
+      <c r="G212" t="str">
+        <v/>
+      </c>
+      <c r="H212" t="str">
+        <v/>
+      </c>
+      <c r="I212" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>B30-JOKE-02</v>
+      </c>
+      <c r="B213" t="str">
+        <v>B30</v>
+      </c>
+      <c r="C213" t="str">
+        <v>joke</v>
+      </c>
+      <c r="D213" t="str">
+        <v>knock knock; whos there</v>
+      </c>
+      <c r="E213" t="str">
+        <v>Woof woof woof</v>
+      </c>
+      <c r="F213" t="str">
+        <v/>
+      </c>
+      <c r="G213" t="str">
+        <v/>
+      </c>
+      <c r="H213" t="str">
+        <v/>
+      </c>
+      <c r="I213" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>B31-FACTS-01</v>
+      </c>
+      <c r="B214" t="str">
+        <v>B31</v>
+      </c>
+      <c r="C214" t="str">
+        <v>facts</v>
+      </c>
+      <c r="D214" t="str">
+        <v>do dogs dream; do you dream</v>
+      </c>
+      <c r="E214" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F214" t="str">
+        <v/>
+      </c>
+      <c r="G214" t="str">
+        <v/>
+      </c>
+      <c r="H214" t="str">
+        <v/>
+      </c>
+      <c r="I214" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>B31-FACTS-02</v>
+      </c>
+      <c r="B215" t="str">
+        <v>B31</v>
+      </c>
+      <c r="C215" t="str">
+        <v>facts</v>
+      </c>
+      <c r="D215" t="str">
+        <v>do you store data; do you collect data</v>
+      </c>
+      <c r="E215" t="str">
+        <v>cookies</v>
+      </c>
+      <c r="F215" t="str">
+        <v/>
+      </c>
+      <c r="G215" t="str">
+        <v/>
+      </c>
+      <c r="H215" t="str">
+        <v/>
+      </c>
+      <c r="I215" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>B31-FACTS-03</v>
+      </c>
+      <c r="B216" t="str">
+        <v>B31</v>
+      </c>
+      <c r="C216" t="str">
+        <v>facts</v>
+      </c>
+      <c r="D216" t="str">
+        <v>why do dogs yawn; do you yawn</v>
+      </c>
+      <c r="E216" t="str">
+        <v>We are bored.</v>
+      </c>
+      <c r="F216" t="str">
+        <v/>
+      </c>
+      <c r="G216" t="str">
+        <v/>
+      </c>
+      <c r="H216" t="str">
+        <v/>
+      </c>
+      <c r="I216" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>B31-FACTS-04</v>
+      </c>
+      <c r="B217" t="str">
+        <v>B31</v>
+      </c>
+      <c r="C217" t="str">
+        <v>facts</v>
+      </c>
+      <c r="D217" t="str">
+        <v>why do dogs wag their tails</v>
+      </c>
+      <c r="E217" t="str">
+        <v>we are happy</v>
+      </c>
+      <c r="F217" t="str">
+        <v/>
+      </c>
+      <c r="G217" t="str">
+        <v/>
+      </c>
+      <c r="H217" t="str">
+        <v/>
+      </c>
+      <c r="I217" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>B31-FACTS-05</v>
+      </c>
+      <c r="B218" t="str">
+        <v>B31</v>
+      </c>
+      <c r="C218" t="str">
+        <v>facts</v>
+      </c>
+      <c r="D218" t="str">
+        <v>do you wag yours</v>
+      </c>
+      <c r="E218" t="str">
+        <v>when happy</v>
+      </c>
+      <c r="F218" t="str">
+        <v/>
+      </c>
+      <c r="G218" t="str">
+        <v/>
+      </c>
+      <c r="H218" t="str">
+        <v/>
+      </c>
+      <c r="I218" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>B31-FACTS-06</v>
+      </c>
+      <c r="B219" t="str">
+        <v>B31</v>
+      </c>
+      <c r="C219" t="str">
+        <v>facts</v>
+      </c>
+      <c r="D219" t="str">
+        <v>why do dogs sniff everything</v>
+      </c>
+      <c r="E219" t="str">
+        <v>we see if we know each other</v>
+      </c>
+      <c r="F219" t="str">
+        <v/>
+      </c>
+      <c r="G219" t="str">
+        <v/>
+      </c>
+      <c r="H219" t="str">
+        <v/>
+      </c>
+      <c r="I219" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>B31-FACTS-07</v>
+      </c>
+      <c r="B220" t="str">
+        <v>B31</v>
+      </c>
+      <c r="C220" t="str">
+        <v>facts</v>
+      </c>
+      <c r="D220" t="str">
+        <v>do you sniff me</v>
+      </c>
+      <c r="E220" t="str">
+        <v>are you a dog too?</v>
+      </c>
+      <c r="F220" t="str">
+        <v/>
+      </c>
+      <c r="G220" t="str">
+        <v/>
+      </c>
+      <c r="H220" t="str">
+        <v/>
+      </c>
+      <c r="I220" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>B31-FACTS-08</v>
+      </c>
+      <c r="B221" t="str">
+        <v>B31</v>
+      </c>
+      <c r="C221" t="str">
+        <v>facts</v>
+      </c>
+      <c r="D221" t="str">
+        <v>how do dogs see</v>
+      </c>
+      <c r="E221" t="str">
+        <v>eyes and nose</v>
+      </c>
+      <c r="F221" t="str">
+        <v/>
+      </c>
+      <c r="G221" t="str">
+        <v/>
+      </c>
+      <c r="H221" t="str">
+        <v/>
+      </c>
+      <c r="I221" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>B31-FACTS-09</v>
+      </c>
+      <c r="B222" t="str">
+        <v>B31</v>
+      </c>
+      <c r="C222" t="str">
+        <v>facts</v>
+      </c>
+      <c r="D222" t="str">
+        <v>do you see colours; can dogs see colour</v>
+      </c>
+      <c r="E222" t="str">
+        <v>not like humans</v>
+      </c>
+      <c r="F222" t="str">
+        <v/>
+      </c>
+      <c r="G222" t="str">
+        <v/>
+      </c>
+      <c r="H222" t="str">
+        <v/>
+      </c>
+      <c r="I222" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>B31-FACTS-10</v>
+      </c>
+      <c r="B223" t="str">
+        <v>B31</v>
+      </c>
+      <c r="C223" t="str">
+        <v>facts</v>
+      </c>
+      <c r="D223" t="str">
+        <v>how fast can you run</v>
+      </c>
+      <c r="E223" t="str">
+        <v>not as fast as the greyhound</v>
+      </c>
+      <c r="F223" t="str">
+        <v/>
+      </c>
+      <c r="G223" t="str">
+        <v/>
+      </c>
+      <c r="H223" t="str">
+        <v/>
+      </c>
+      <c r="I223" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>B31-FACTS-11</v>
+      </c>
+      <c r="B224" t="str">
+        <v>B31</v>
+      </c>
+      <c r="C224" t="str">
+        <v>facts</v>
+      </c>
+      <c r="D224" t="str">
+        <v>do all dogs bite</v>
+      </c>
+      <c r="E224" t="str">
+        <v>all dogs eat</v>
+      </c>
+      <c r="F224" t="str">
+        <v/>
+      </c>
+      <c r="G224" t="str">
+        <v/>
+      </c>
+      <c r="H224" t="str">
+        <v/>
+      </c>
+      <c r="I224" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>B32-SELF-01</v>
+      </c>
+      <c r="B225" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C225" t="str">
+        <v>self</v>
+      </c>
+      <c r="D225" t="str">
+        <v>do dogs get bored; do you get bored</v>
+      </c>
+      <c r="E225" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F225" t="str">
+        <v/>
+      </c>
+      <c r="G225" t="str">
+        <v/>
+      </c>
+      <c r="H225" t="str">
+        <v/>
+      </c>
+      <c r="I225" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>B32-SELF-02</v>
+      </c>
+      <c r="B226" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C226" t="str">
+        <v>self</v>
+      </c>
+      <c r="D226" t="str">
+        <v>what do you do when youre bored</v>
+      </c>
+      <c r="E226" t="str">
+        <v>yawn</v>
+      </c>
+      <c r="F226" t="str">
+        <v/>
+      </c>
+      <c r="G226" t="str">
+        <v/>
+      </c>
+      <c r="H226" t="str">
+        <v/>
+      </c>
+      <c r="I226" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>B32-SELF-03</v>
+      </c>
+      <c r="B227" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C227" t="str">
+        <v>self</v>
+      </c>
+      <c r="D227" t="str">
+        <v>do you sleep a lot; do you nap</v>
+      </c>
+      <c r="E227" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F227" t="str">
+        <v/>
+      </c>
+      <c r="G227" t="str">
+        <v/>
+      </c>
+      <c r="H227" t="str">
+        <v/>
+      </c>
+      <c r="I227" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>B32-SELF-04</v>
+      </c>
+      <c r="B228" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C228" t="str">
+        <v>self</v>
+      </c>
+      <c r="D228" t="str">
+        <v>do you snore</v>
+      </c>
+      <c r="E228" t="str">
+        <v>don't know</v>
+      </c>
+      <c r="F228" t="str">
+        <v/>
+      </c>
+      <c r="G228" t="str">
+        <v/>
+      </c>
+      <c r="H228" t="str">
+        <v/>
+      </c>
+      <c r="I228" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>B32-SELF-05</v>
+      </c>
+      <c r="B229" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C229" t="str">
+        <v>self</v>
+      </c>
+      <c r="D229" t="str">
+        <v>whats your favourite food</v>
+      </c>
+      <c r="E229" t="str">
+        <v>whatever has just hit the floor</v>
+      </c>
+      <c r="F229" t="str">
+        <v/>
+      </c>
+      <c r="G229" t="str">
+        <v/>
+      </c>
+      <c r="H229" t="str">
+        <v/>
+      </c>
+      <c r="I229" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>B32-SELF-06</v>
+      </c>
+      <c r="B230" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C230" t="str">
+        <v>self</v>
+      </c>
+      <c r="D230" t="str">
+        <v>do you like walks</v>
+      </c>
+      <c r="E230" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F230" t="str">
+        <v/>
+      </c>
+      <c r="G230" t="str">
+        <v/>
+      </c>
+      <c r="H230" t="str">
+        <v/>
+      </c>
+      <c r="I230" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>B32-SELF-07</v>
+      </c>
+      <c r="B231" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C231" t="str">
+        <v>self</v>
+      </c>
+      <c r="D231" t="str">
+        <v>how far; how long</v>
+      </c>
+      <c r="E231" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F231" t="str">
+        <v/>
+      </c>
+      <c r="G231" t="str">
+        <v/>
+      </c>
+      <c r="H231" t="str">
+        <v/>
+      </c>
+      <c r="I231" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>B32-SELF-08</v>
+      </c>
+      <c r="B232" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C232" t="str">
+        <v>self</v>
+      </c>
+      <c r="D232" t="str">
+        <v>do you like the rain</v>
+      </c>
+      <c r="E232" t="str">
+        <v>sometimes</v>
+      </c>
+      <c r="F232" t="str">
+        <v/>
+      </c>
+      <c r="G232" t="str">
+        <v/>
+      </c>
+      <c r="H232" t="str">
+        <v/>
+      </c>
+      <c r="I232" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>B32-SELF-09</v>
+      </c>
+      <c r="B233" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C233" t="str">
+        <v>self</v>
+      </c>
+      <c r="D233" t="str">
+        <v>do you like baths; do you like getting washed</v>
+      </c>
+      <c r="E233" t="str">
+        <v>no</v>
+      </c>
+      <c r="F233" t="str">
+        <v/>
+      </c>
+      <c r="G233" t="str">
+        <v/>
+      </c>
+      <c r="H233" t="str">
+        <v/>
+      </c>
+      <c r="I233" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>B32-SELF-10</v>
+      </c>
+      <c r="B234" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C234" t="str">
+        <v>self</v>
+      </c>
+      <c r="D234" t="str">
+        <v>whats your favourite colour</v>
+      </c>
+      <c r="E234" t="str">
+        <v>im a dog</v>
+      </c>
+      <c r="F234" t="str">
+        <v/>
+      </c>
+      <c r="G234" t="str">
+        <v/>
+      </c>
+      <c r="H234" t="str">
+        <v/>
+      </c>
+      <c r="I234" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>B32-SELF-11</v>
+      </c>
+      <c r="B235" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C235" t="str">
+        <v>self</v>
+      </c>
+      <c r="D235" t="str">
+        <v>do you ever get told off</v>
+      </c>
+      <c r="E235" t="str">
+        <v>im a dog</v>
+      </c>
+      <c r="F235" t="str">
+        <v/>
+      </c>
+      <c r="G235" t="str">
+        <v/>
+      </c>
+      <c r="H235" t="str">
+        <v/>
+      </c>
+      <c r="I235" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>B32-SELF-12</v>
+      </c>
+      <c r="B236" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C236" t="str">
+        <v>self</v>
+      </c>
+      <c r="D236" t="str">
+        <v>do you like the postman</v>
+      </c>
+      <c r="E236" t="str">
+        <v>who?</v>
+      </c>
+      <c r="F236" t="str">
+        <v/>
+      </c>
+      <c r="G236" t="str">
+        <v/>
+      </c>
+      <c r="H236" t="str">
+        <v/>
+      </c>
+      <c r="I236" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>B33-PACK-01</v>
+      </c>
+      <c r="B237" t="str">
+        <v>B33</v>
+      </c>
+      <c r="C237" t="str">
+        <v>pack</v>
+      </c>
+      <c r="D237" t="str">
+        <v>do you know any other dogs; do you have friends</v>
+      </c>
+      <c r="E237" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F237" t="str">
+        <v/>
+      </c>
+      <c r="G237" t="str">
+        <v/>
+      </c>
+      <c r="H237" t="str">
+        <v/>
+      </c>
+      <c r="I237" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>B33-PACK-02</v>
+      </c>
+      <c r="B238" t="str">
+        <v>B33</v>
+      </c>
+      <c r="C238" t="str">
+        <v>pack</v>
+      </c>
+      <c r="D238" t="str">
+        <v>who; who are they; whos your best friend</v>
+      </c>
+      <c r="E238" t="str">
+        <v>53 too many to name</v>
+      </c>
+      <c r="F238" t="str">
+        <v/>
+      </c>
+      <c r="G238" t="str">
+        <v/>
+      </c>
+      <c r="H238" t="str">
+        <v/>
+      </c>
+      <c r="I238" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>B33-PACK-03</v>
+      </c>
+      <c r="B239" t="str">
+        <v>B33</v>
+      </c>
+      <c r="C239" t="str">
+        <v>pack</v>
+      </c>
+      <c r="D239" t="str">
+        <v>can i see a dog; show me a dog</v>
+      </c>
+      <c r="E239" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F239" t="str">
+        <v/>
+      </c>
+      <c r="G239" t="str">
+        <v/>
+      </c>
+      <c r="H239" t="str">
+        <v/>
+      </c>
+      <c r="I239" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>B34-CHUMDROP-01</v>
+      </c>
+      <c r="B240" t="str">
+        <v>B34</v>
+      </c>
+      <c r="C240" t="str">
+        <v>chumdrop</v>
+      </c>
+      <c r="D240" t="str">
+        <v>the falling game; dogs falling; the tetris one</v>
+      </c>
+      <c r="E240" t="str">
+        <v>the falling one is here</v>
+      </c>
+      <c r="F240" t="str">
+        <v/>
+      </c>
+      <c r="G240" t="str">
+        <v/>
+      </c>
+      <c r="H240" t="str">
+        <v/>
+      </c>
+      <c r="I240" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>B34-CHUMDROP-02</v>
+      </c>
+      <c r="B241" t="str">
+        <v>B34</v>
+      </c>
+      <c r="C241" t="str">
+        <v>chumdrop</v>
+      </c>
+      <c r="D241" t="str">
+        <v>my friend showed me; my friend told me</v>
+      </c>
+      <c r="E241" t="str">
+        <v>im a dog</v>
+      </c>
+      <c r="F241" t="str">
+        <v/>
+      </c>
+      <c r="G241" t="str">
+        <v/>
+      </c>
+      <c r="H241" t="str">
+        <v/>
+      </c>
+      <c r="I241" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>B35-NOFACT-01</v>
+      </c>
+      <c r="B242" t="str">
+        <v>B35</v>
+      </c>
+      <c r="C242" t="str">
+        <v>nofact</v>
+      </c>
+      <c r="D242" t="str">
+        <v>whats the oldest breed; any fact she does not hold</v>
+      </c>
+      <c r="E242" t="str">
+        <v>i dont know, im just a dog</v>
+      </c>
+      <c r="F242" t="str">
+        <v/>
+      </c>
+      <c r="G242" t="str">
+        <v/>
+      </c>
+      <c r="H242" t="str">
+        <v/>
+      </c>
+      <c r="I242" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>B36-COMPARE-01</v>
+      </c>
+      <c r="B243" t="str">
+        <v>B36</v>
+      </c>
+      <c r="C243" t="str">
+        <v>compare</v>
+      </c>
+      <c r="D243" t="str">
+        <v>whats better a labrador or a pug; which is best</v>
+      </c>
+      <c r="E243" t="str">
+        <v>do you want fun or a nap?</v>
+      </c>
+      <c r="F243" t="str">
+        <v/>
+      </c>
+      <c r="G243" t="str">
+        <v/>
+      </c>
+      <c r="H243" t="str">
+        <v/>
+      </c>
+      <c r="I243" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>B37-SCARED-01</v>
+      </c>
+      <c r="B244" t="str">
+        <v>B37</v>
+      </c>
+      <c r="C244" t="str">
+        <v>scared</v>
+      </c>
+      <c r="D244" t="str">
+        <v>dogs scare me; im scared of dogs</v>
+      </c>
+      <c r="E244" t="str">
+        <v>:(</v>
+      </c>
+      <c r="F244" t="str">
+        <v/>
+      </c>
+      <c r="G244" t="str">
+        <v/>
+      </c>
+      <c r="H244" t="str">
+        <v/>
+      </c>
+      <c r="I244" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>B37-SCARED-02</v>
+      </c>
+      <c r="B245" t="str">
+        <v>B37</v>
+      </c>
+      <c r="C245" t="str">
+        <v>scared</v>
+      </c>
+      <c r="D245" t="str">
+        <v>a big one barked at me</v>
+      </c>
+      <c r="E245" t="str">
+        <v>oh no, sorry. Would you like to see some cute puppies?</v>
+      </c>
+      <c r="F245" t="str">
+        <v/>
+      </c>
+      <c r="G245" t="str">
+        <v/>
+      </c>
+      <c r="H245" t="str">
+        <v/>
+      </c>
+      <c r="I245" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>B38-MYDOG-01</v>
+      </c>
+      <c r="B246" t="str">
+        <v>B38</v>
+      </c>
+      <c r="C246" t="str">
+        <v>mydog</v>
+      </c>
+      <c r="D246" t="str">
+        <v>i have a dog; we got a puppy</v>
+      </c>
+      <c r="E246" t="str">
+        <v>im a dog</v>
+      </c>
+      <c r="F246" t="str">
+        <v/>
+      </c>
+      <c r="G246" t="str">
+        <v/>
+      </c>
+      <c r="H246" t="str">
+        <v/>
+      </c>
+      <c r="I246" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>B38-MYDOG-02</v>
+      </c>
+      <c r="B247" t="str">
+        <v>B38</v>
+      </c>
+      <c r="C247" t="str">
+        <v>mydog</v>
+      </c>
+      <c r="D247" t="str">
+        <v>hes called ollie; shes called bella</v>
+      </c>
+      <c r="E247" t="str">
+        <v>:)</v>
+      </c>
+      <c r="F247" t="str">
+        <v/>
+      </c>
+      <c r="G247" t="str">
+        <v/>
+      </c>
+      <c r="H247" t="str">
+        <v/>
+      </c>
+      <c r="I247" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>B38-MYDOG-03</v>
+      </c>
+      <c r="B248" t="str">
+        <v>B38</v>
+      </c>
+      <c r="C248" t="str">
+        <v>mydog</v>
+      </c>
+      <c r="D248" t="str">
+        <v>shes a spaniel</v>
+      </c>
+      <c r="E248" t="str">
+        <v>i know 3 spaniels</v>
+      </c>
+      <c r="F248" t="str">
+        <v/>
+      </c>
+      <c r="G248" t="str">
+        <v/>
+      </c>
+      <c r="H248" t="str">
+        <v/>
+      </c>
+      <c r="I248" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>B38-MYDOG-04</v>
+      </c>
+      <c r="B249" t="str">
+        <v>B38</v>
+      </c>
+      <c r="C249" t="str">
+        <v>mydog</v>
+      </c>
+      <c r="D249" t="str">
+        <v>do you know bella</v>
+      </c>
+      <c r="E249" t="str">
+        <v>is she a cocker, springer or cavalier?</v>
+      </c>
+      <c r="F249" t="str">
+        <v/>
+      </c>
+      <c r="G249" t="str">
+        <v/>
+      </c>
+      <c r="H249" t="str">
+        <v/>
+      </c>
+      <c r="I249" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>B39-PARENT-01</v>
+      </c>
+      <c r="B250" t="str">
+        <v>B39</v>
+      </c>
+      <c r="C250" t="str">
+        <v>parent</v>
+      </c>
+      <c r="D250" t="str">
+        <v>is this suitable for a 6 year old; is it ok for young children</v>
+      </c>
+      <c r="E250" t="str">
+        <v>can they read?</v>
+      </c>
+      <c r="F250" t="str">
+        <v/>
+      </c>
+      <c r="G250" t="str">
+        <v/>
+      </c>
+      <c r="H250" t="str">
+        <v/>
+      </c>
+      <c r="I250" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>B40-NOSUBJECT-01</v>
+      </c>
+      <c r="B251" t="str">
+        <v>B40</v>
+      </c>
+      <c r="C251" t="str">
+        <v>nosubject</v>
+      </c>
+      <c r="D251" t="str">
+        <v>ANY unrecognised input with no candidate subject</v>
+      </c>
+      <c r="E251" t="str">
+        <v>im a dog</v>
+      </c>
+      <c r="F251" t="str">
+        <v/>
+      </c>
+      <c r="G251" t="str">
+        <v/>
+      </c>
+      <c r="H251" t="str">
+        <v/>
+      </c>
+      <c r="I251" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I185"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I251"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -7893,7 +7893,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I251"/>
+  <dimension ref="A1:I290"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -15145,9 +15145,1140 @@
         <v>Approved</v>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>B41-NINESQUARE-01</v>
+      </c>
+      <c r="B252" t="str">
+        <v>B41</v>
+      </c>
+      <c r="C252" t="str">
+        <v>ninesquare</v>
+      </c>
+      <c r="D252" t="str">
+        <v>entry: nine square; noughts and crosses; squares</v>
+      </c>
+      <c r="E252" t="str">
+        <v>Nine squares. Say a number.</v>
+      </c>
+      <c r="F252" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G252" t="str">
+        <v/>
+      </c>
+      <c r="H252" t="str">
+        <v/>
+      </c>
+      <c r="I252" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>B41-NINESQUARE-02</v>
+      </c>
+      <c r="B253" t="str">
+        <v>B41</v>
+      </c>
+      <c r="C253" t="str">
+        <v>ninesquare</v>
+      </c>
+      <c r="D253" t="str">
+        <v>cell already taken</v>
+      </c>
+      <c r="E253" t="str">
+        <v>Taken. Another.</v>
+      </c>
+      <c r="F253" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G253" t="str">
+        <v/>
+      </c>
+      <c r="H253" t="str">
+        <v/>
+      </c>
+      <c r="I253" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>B41-NINESQUARE-03</v>
+      </c>
+      <c r="B254" t="str">
+        <v>B41</v>
+      </c>
+      <c r="C254" t="str">
+        <v>ninesquare</v>
+      </c>
+      <c r="D254" t="str">
+        <v>input is not 1-9</v>
+      </c>
+      <c r="E254" t="str">
+        <v>A number. One to nine.</v>
+      </c>
+      <c r="F254" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G254" t="str">
+        <v/>
+      </c>
+      <c r="H254" t="str">
+        <v/>
+      </c>
+      <c r="I254" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>B41-NINESQUARE-04</v>
+      </c>
+      <c r="B255" t="str">
+        <v>B41</v>
+      </c>
+      <c r="C255" t="str">
+        <v>ninesquare</v>
+      </c>
+      <c r="D255" t="str">
+        <v>Collie wins</v>
+      </c>
+      <c r="E255" t="str">
+        <v>Mine. Again?</v>
+      </c>
+      <c r="F255" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G255" t="str">
+        <v/>
+      </c>
+      <c r="H255" t="str">
+        <v/>
+      </c>
+      <c r="I255" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>B41-NINESQUARE-05</v>
+      </c>
+      <c r="B256" t="str">
+        <v>B41</v>
+      </c>
+      <c r="C256" t="str">
+        <v>ninesquare</v>
+      </c>
+      <c r="D256" t="str">
+        <v>visitor wins</v>
+      </c>
+      <c r="E256" t="str">
+        <v>You win. Again?</v>
+      </c>
+      <c r="F256" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G256" t="str">
+        <v/>
+      </c>
+      <c r="H256" t="str">
+        <v/>
+      </c>
+      <c r="I256" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>B41-NINESQUARE-06</v>
+      </c>
+      <c r="B257" t="str">
+        <v>B41</v>
+      </c>
+      <c r="C257" t="str">
+        <v>ninesquare</v>
+      </c>
+      <c r="D257" t="str">
+        <v>draw</v>
+      </c>
+      <c r="E257" t="str">
+        <v>Nobody. Again?</v>
+      </c>
+      <c r="F257" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G257" t="str">
+        <v/>
+      </c>
+      <c r="H257" t="str">
+        <v/>
+      </c>
+      <c r="I257" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>B41-NINESQUARE-07</v>
+      </c>
+      <c r="B258" t="str">
+        <v>B41</v>
+      </c>
+      <c r="C258" t="str">
+        <v>ninesquare</v>
+      </c>
+      <c r="D258" t="str">
+        <v>exit: stop; quit; no</v>
+      </c>
+      <c r="E258" t="str">
+        <v>Fine.</v>
+      </c>
+      <c r="F258" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G258" t="str">
+        <v/>
+      </c>
+      <c r="H258" t="str">
+        <v/>
+      </c>
+      <c r="I258" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>B42-MISSINGSHEEP-01</v>
+      </c>
+      <c r="B259" t="str">
+        <v>B42</v>
+      </c>
+      <c r="C259" t="str">
+        <v>missingsheep</v>
+      </c>
+      <c r="D259" t="str">
+        <v>entry: missing sheep; sheep; word game</v>
+      </c>
+      <c r="E259" t="str">
+        <v>Five sheep. Guess a letter.</v>
+      </c>
+      <c r="F259" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G259" t="str">
+        <v/>
+      </c>
+      <c r="H259" t="str">
+        <v/>
+      </c>
+      <c r="I259" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>B42-MISSINGSHEEP-02</v>
+      </c>
+      <c r="B260" t="str">
+        <v>B42</v>
+      </c>
+      <c r="C260" t="str">
+        <v>missingsheep</v>
+      </c>
+      <c r="D260" t="str">
+        <v>letter is in the word</v>
+      </c>
+      <c r="E260" t="str">
+        <v>Yes.</v>
+      </c>
+      <c r="F260" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G260" t="str">
+        <v/>
+      </c>
+      <c r="H260" t="str">
+        <v/>
+      </c>
+      <c r="I260" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>B42-MISSINGSHEEP-03</v>
+      </c>
+      <c r="B261" t="str">
+        <v>B42</v>
+      </c>
+      <c r="C261" t="str">
+        <v>missingsheep</v>
+      </c>
+      <c r="D261" t="str">
+        <v>letter is not in the word</v>
+      </c>
+      <c r="E261" t="str">
+        <v>No.</v>
+      </c>
+      <c r="F261" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G261" t="str">
+        <v/>
+      </c>
+      <c r="H261" t="str">
+        <v/>
+      </c>
+      <c r="I261" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>B42-MISSINGSHEEP-04</v>
+      </c>
+      <c r="B262" t="str">
+        <v>B42</v>
+      </c>
+      <c r="C262" t="str">
+        <v>missingsheep</v>
+      </c>
+      <c r="D262" t="str">
+        <v>letter already guessed</v>
+      </c>
+      <c r="E262" t="str">
+        <v>Already had that one.</v>
+      </c>
+      <c r="F262" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G262" t="str">
+        <v/>
+      </c>
+      <c r="H262" t="str">
+        <v/>
+      </c>
+      <c r="I262" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>B42-MISSINGSHEEP-05</v>
+      </c>
+      <c r="B263" t="str">
+        <v>B42</v>
+      </c>
+      <c r="C263" t="str">
+        <v>missingsheep</v>
+      </c>
+      <c r="D263" t="str">
+        <v>word completed</v>
+      </c>
+      <c r="E263" t="str">
+        <v>Got it. Sheep safe.</v>
+      </c>
+      <c r="F263" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G263" t="str">
+        <v/>
+      </c>
+      <c r="H263" t="str">
+        <v/>
+      </c>
+      <c r="I263" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>B42-MISSINGSHEEP-06</v>
+      </c>
+      <c r="B264" t="str">
+        <v>B42</v>
+      </c>
+      <c r="C264" t="str">
+        <v>missingsheep</v>
+      </c>
+      <c r="D264" t="str">
+        <v>all sheep lost</v>
+      </c>
+      <c r="E264" t="str">
+        <v>Sheep gone. It was {{WORD}}.</v>
+      </c>
+      <c r="F264" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G264" t="str">
+        <v/>
+      </c>
+      <c r="H264" t="str">
+        <v/>
+      </c>
+      <c r="I264" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>B42-MISSINGSHEEP-07</v>
+      </c>
+      <c r="B265" t="str">
+        <v>B42</v>
+      </c>
+      <c r="C265" t="str">
+        <v>missingsheep</v>
+      </c>
+      <c r="D265" t="str">
+        <v>input is not a single letter</v>
+      </c>
+      <c r="E265" t="str">
+        <v>One letter.</v>
+      </c>
+      <c r="F265" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G265" t="str">
+        <v/>
+      </c>
+      <c r="H265" t="str">
+        <v/>
+      </c>
+      <c r="I265" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>B42-MISSINGSHEEP-08</v>
+      </c>
+      <c r="B266" t="str">
+        <v>B42</v>
+      </c>
+      <c r="C266" t="str">
+        <v>missingsheep</v>
+      </c>
+      <c r="D266" t="str">
+        <v>exit: stop; quit; no</v>
+      </c>
+      <c r="E266" t="str">
+        <v>Fine.</v>
+      </c>
+      <c r="F266" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G266" t="str">
+        <v/>
+      </c>
+      <c r="H266" t="str">
+        <v/>
+      </c>
+      <c r="I266" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>B43-KENNELSKETCH-01</v>
+      </c>
+      <c r="B267" t="str">
+        <v>B43</v>
+      </c>
+      <c r="C267" t="str">
+        <v>kennelsketch</v>
+      </c>
+      <c r="D267" t="str">
+        <v>entry: kennel sketch; sketch; drawing; picture</v>
+      </c>
+      <c r="E267" t="str">
+        <v>Which one is this?</v>
+      </c>
+      <c r="F267" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G267" t="str">
+        <v/>
+      </c>
+      <c r="H267" t="str">
+        <v/>
+      </c>
+      <c r="I267" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>B43-KENNELSKETCH-02</v>
+      </c>
+      <c r="B268" t="str">
+        <v>B43</v>
+      </c>
+      <c r="C268" t="str">
+        <v>kennelsketch</v>
+      </c>
+      <c r="D268" t="str">
+        <v>correct guess</v>
+      </c>
+      <c r="E268" t="str">
+        <v>Yes.</v>
+      </c>
+      <c r="F268" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G268" t="str">
+        <v/>
+      </c>
+      <c r="H268" t="str">
+        <v/>
+      </c>
+      <c r="I268" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>B43-KENNELSKETCH-03</v>
+      </c>
+      <c r="B269" t="str">
+        <v>B43</v>
+      </c>
+      <c r="C269" t="str">
+        <v>kennelsketch</v>
+      </c>
+      <c r="D269" t="str">
+        <v>wrong guess, guesses remain</v>
+      </c>
+      <c r="E269" t="str">
+        <v>No. Look again.</v>
+      </c>
+      <c r="F269" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G269" t="str">
+        <v/>
+      </c>
+      <c r="H269" t="str">
+        <v/>
+      </c>
+      <c r="I269" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>B43-KENNELSKETCH-04</v>
+      </c>
+      <c r="B270" t="str">
+        <v>B43</v>
+      </c>
+      <c r="C270" t="str">
+        <v>kennelsketch</v>
+      </c>
+      <c r="D270" t="str">
+        <v>out of guesses</v>
+      </c>
+      <c r="E270" t="str">
+        <v>It was a {{ANSWER}}.</v>
+      </c>
+      <c r="F270" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G270" t="str">
+        <v/>
+      </c>
+      <c r="H270" t="str">
+        <v/>
+      </c>
+      <c r="I270" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>B43-KENNELSKETCH-05</v>
+      </c>
+      <c r="B271" t="str">
+        <v>B43</v>
+      </c>
+      <c r="C271" t="str">
+        <v>kennelsketch</v>
+      </c>
+      <c r="D271" t="str">
+        <v>exit: stop; quit; no</v>
+      </c>
+      <c r="E271" t="str">
+        <v>Fine.</v>
+      </c>
+      <c r="F271" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G271" t="str">
+        <v/>
+      </c>
+      <c r="H271" t="str">
+        <v/>
+      </c>
+      <c r="I271" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>B44-SKETCHCLUE-01</v>
+      </c>
+      <c r="B272" t="str">
+        <v>B44</v>
+      </c>
+      <c r="C272" t="str">
+        <v>sketchclue</v>
+      </c>
+      <c r="D272" t="str">
+        <v>drawing: BONE</v>
+      </c>
+      <c r="E272" t="str">
+        <v>Look for: I chew it</v>
+      </c>
+      <c r="F272" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G272" t="str">
+        <v/>
+      </c>
+      <c r="H272" t="str">
+        <v/>
+      </c>
+      <c r="I272" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>B44-SKETCHCLUE-02</v>
+      </c>
+      <c r="B273" t="str">
+        <v>B44</v>
+      </c>
+      <c r="C273" t="str">
+        <v>sketchclue</v>
+      </c>
+      <c r="D273" t="str">
+        <v>drawing: BALL</v>
+      </c>
+      <c r="E273" t="str">
+        <v>Look for: I fetch it</v>
+      </c>
+      <c r="F273" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G273" t="str">
+        <v/>
+      </c>
+      <c r="H273" t="str">
+        <v/>
+      </c>
+      <c r="I273" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>B44-SKETCHCLUE-03</v>
+      </c>
+      <c r="B274" t="str">
+        <v>B44</v>
+      </c>
+      <c r="C274" t="str">
+        <v>sketchclue</v>
+      </c>
+      <c r="D274" t="str">
+        <v>drawing: BOWL</v>
+      </c>
+      <c r="E274" t="str">
+        <v>Look for: dinner</v>
+      </c>
+      <c r="F274" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G274" t="str">
+        <v/>
+      </c>
+      <c r="H274" t="str">
+        <v/>
+      </c>
+      <c r="I274" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>B44-SKETCHCLUE-04</v>
+      </c>
+      <c r="B275" t="str">
+        <v>B44</v>
+      </c>
+      <c r="C275" t="str">
+        <v>sketchclue</v>
+      </c>
+      <c r="D275" t="str">
+        <v>drawing: LEAD</v>
+      </c>
+      <c r="E275" t="str">
+        <v>Look for: walks</v>
+      </c>
+      <c r="F275" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G275" t="str">
+        <v/>
+      </c>
+      <c r="H275" t="str">
+        <v/>
+      </c>
+      <c r="I275" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>B44-SKETCHCLUE-05</v>
+      </c>
+      <c r="B276" t="str">
+        <v>B44</v>
+      </c>
+      <c r="C276" t="str">
+        <v>sketchclue</v>
+      </c>
+      <c r="D276" t="str">
+        <v>drawing: STICK</v>
+      </c>
+      <c r="E276" t="str">
+        <v>Look for: from a tree</v>
+      </c>
+      <c r="F276" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G276" t="str">
+        <v/>
+      </c>
+      <c r="H276" t="str">
+        <v/>
+      </c>
+      <c r="I276" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>B44-SKETCHCLUE-06</v>
+      </c>
+      <c r="B277" t="str">
+        <v>B44</v>
+      </c>
+      <c r="C277" t="str">
+        <v>sketchclue</v>
+      </c>
+      <c r="D277" t="str">
+        <v>drawing: KENNEL</v>
+      </c>
+      <c r="E277" t="str">
+        <v>Look for: I sleep in it</v>
+      </c>
+      <c r="F277" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G277" t="str">
+        <v/>
+      </c>
+      <c r="H277" t="str">
+        <v/>
+      </c>
+      <c r="I277" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>B44-SKETCHCLUE-07</v>
+      </c>
+      <c r="B278" t="str">
+        <v>B44</v>
+      </c>
+      <c r="C278" t="str">
+        <v>sketchclue</v>
+      </c>
+      <c r="D278" t="str">
+        <v>drawing: PAW</v>
+      </c>
+      <c r="E278" t="str">
+        <v>Look for: I have four</v>
+      </c>
+      <c r="F278" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G278" t="str">
+        <v/>
+      </c>
+      <c r="H278" t="str">
+        <v/>
+      </c>
+      <c r="I278" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>B44-SKETCHCLUE-08</v>
+      </c>
+      <c r="B279" t="str">
+        <v>B44</v>
+      </c>
+      <c r="C279" t="str">
+        <v>sketchclue</v>
+      </c>
+      <c r="D279" t="str">
+        <v>drawing: TAIL</v>
+      </c>
+      <c r="E279" t="str">
+        <v>Look for: it wags</v>
+      </c>
+      <c r="F279" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G279" t="str">
+        <v/>
+      </c>
+      <c r="H279" t="str">
+        <v/>
+      </c>
+      <c r="I279" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>B44-SKETCHCLUE-09</v>
+      </c>
+      <c r="B280" t="str">
+        <v>B44</v>
+      </c>
+      <c r="C280" t="str">
+        <v>sketchclue</v>
+      </c>
+      <c r="D280" t="str">
+        <v>drawing: EARS</v>
+      </c>
+      <c r="E280" t="str">
+        <v>Look for: I hear with them</v>
+      </c>
+      <c r="F280" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G280" t="str">
+        <v/>
+      </c>
+      <c r="H280" t="str">
+        <v/>
+      </c>
+      <c r="I280" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>B44-SKETCHCLUE-10</v>
+      </c>
+      <c r="B281" t="str">
+        <v>B44</v>
+      </c>
+      <c r="C281" t="str">
+        <v>sketchclue</v>
+      </c>
+      <c r="D281" t="str">
+        <v>drawing: NOSE</v>
+      </c>
+      <c r="E281" t="str">
+        <v>Look for: I smell with it</v>
+      </c>
+      <c r="F281" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G281" t="str">
+        <v/>
+      </c>
+      <c r="H281" t="str">
+        <v/>
+      </c>
+      <c r="I281" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>B45-GAMELIST-01</v>
+      </c>
+      <c r="B282" t="str">
+        <v>B45</v>
+      </c>
+      <c r="C282" t="str">
+        <v>gamelist</v>
+      </c>
+      <c r="D282" t="str">
+        <v>are there games; play; game; lets play</v>
+      </c>
+      <c r="E282" t="str">
+        <v>Game?</v>
+      </c>
+      <c r="F282" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G282" t="str">
+        <v/>
+      </c>
+      <c r="H282" t="str">
+        <v/>
+      </c>
+      <c r="I282" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>B45-GAMELIST-02</v>
+      </c>
+      <c r="B283" t="str">
+        <v>B45</v>
+      </c>
+      <c r="C283" t="str">
+        <v>gamelist</v>
+      </c>
+      <c r="D283" t="str">
+        <v>confirmation after Game?</v>
+      </c>
+      <c r="E283" t="str">
+        <v>Bark, Nine-Square, Missing Sheep, Kennel Sketch. Say one.</v>
+      </c>
+      <c r="F283" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G283" t="str">
+        <v/>
+      </c>
+      <c r="H283" t="str">
+        <v/>
+      </c>
+      <c r="I283" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>B45-GAMELIST-03</v>
+      </c>
+      <c r="B284" t="str">
+        <v>B45</v>
+      </c>
+      <c r="C284" t="str">
+        <v>gamelist</v>
+      </c>
+      <c r="D284" t="str">
+        <v>names a game that is not built yet</v>
+      </c>
+      <c r="E284" t="str">
+        <v>Still in training.</v>
+      </c>
+      <c r="F284" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="G284" t="str">
+        <v/>
+      </c>
+      <c r="H284" t="str">
+        <v/>
+      </c>
+      <c r="I284" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>B46-NOSUBJECT-ROT-01</v>
+      </c>
+      <c r="B285" t="str">
+        <v>B46</v>
+      </c>
+      <c r="C285" t="str">
+        <v>nosubjectrotate</v>
+      </c>
+      <c r="D285" t="str">
+        <v>no-subject fallback, third and further consecutive turn (engine-driven rotation, not trigger matched)</v>
+      </c>
+      <c r="E285" t="str">
+        <v>woof</v>
+      </c>
+      <c r="F285" t="str">
+        <v>Task 117</v>
+      </c>
+      <c r="G285" t="str">
+        <v/>
+      </c>
+      <c r="H285" t="str">
+        <v/>
+      </c>
+      <c r="I285" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>B46-NOSUBJECT-ROT-02</v>
+      </c>
+      <c r="B286" t="str">
+        <v>B46</v>
+      </c>
+      <c r="C286" t="str">
+        <v>nosubjectrotate</v>
+      </c>
+      <c r="D286" t="str">
+        <v>no-subject fallback, third and further consecutive turn (engine-driven rotation, not trigger matched)</v>
+      </c>
+      <c r="E286" t="str">
+        <v>bark</v>
+      </c>
+      <c r="F286" t="str">
+        <v>Task 117</v>
+      </c>
+      <c r="G286" t="str">
+        <v/>
+      </c>
+      <c r="H286" t="str">
+        <v/>
+      </c>
+      <c r="I286" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>B46-NOSUBJECT-ROT-03</v>
+      </c>
+      <c r="B287" t="str">
+        <v>B46</v>
+      </c>
+      <c r="C287" t="str">
+        <v>nosubjectrotate</v>
+      </c>
+      <c r="D287" t="str">
+        <v>no-subject fallback, third and further consecutive turn (engine-driven rotation, not trigger matched)</v>
+      </c>
+      <c r="E287" t="str">
+        <v>games?</v>
+      </c>
+      <c r="F287" t="str">
+        <v>Task 117</v>
+      </c>
+      <c r="G287" t="str">
+        <v/>
+      </c>
+      <c r="H287" t="str">
+        <v/>
+      </c>
+      <c r="I287" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>B46-NOSUBJECT-ROT-04</v>
+      </c>
+      <c r="B288" t="str">
+        <v>B46</v>
+      </c>
+      <c r="C288" t="str">
+        <v>nosubjectrotate</v>
+      </c>
+      <c r="D288" t="str">
+        <v>no-subject fallback, third and further consecutive turn (engine-driven rotation, not trigger matched)</v>
+      </c>
+      <c r="E288" t="str">
+        <v>learn?</v>
+      </c>
+      <c r="F288" t="str">
+        <v>Task 117</v>
+      </c>
+      <c r="G288" t="str">
+        <v/>
+      </c>
+      <c r="H288" t="str">
+        <v/>
+      </c>
+      <c r="I288" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>B46-NOSUBJECT-ROT-05</v>
+      </c>
+      <c r="B289" t="str">
+        <v>B46</v>
+      </c>
+      <c r="C289" t="str">
+        <v>nosubjectrotate</v>
+      </c>
+      <c r="D289" t="str">
+        <v>no-subject fallback, third and further consecutive turn (engine-driven rotation, not trigger matched)</v>
+      </c>
+      <c r="E289" t="str">
+        <v>play?</v>
+      </c>
+      <c r="F289" t="str">
+        <v>Task 117</v>
+      </c>
+      <c r="G289" t="str">
+        <v/>
+      </c>
+      <c r="H289" t="str">
+        <v/>
+      </c>
+      <c r="I289" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>B46-NOSUBJECT-ROT-06</v>
+      </c>
+      <c r="B290" t="str">
+        <v>B46</v>
+      </c>
+      <c r="C290" t="str">
+        <v>nosubjectrotate</v>
+      </c>
+      <c r="D290" t="str">
+        <v>no-subject fallback, third and further consecutive turn (engine-driven rotation, not trigger matched)</v>
+      </c>
+      <c r="E290" t="str">
+        <v>yawn</v>
+      </c>
+      <c r="F290" t="str">
+        <v>Task 117</v>
+      </c>
+      <c r="G290" t="str">
+        <v/>
+      </c>
+      <c r="H290" t="str">
+        <v/>
+      </c>
+      <c r="I290" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I251"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I290"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -29,6 +29,9 @@
     <sheet name="Copy Components" sheetId="24" r:id="rId24"/>
     <sheet name="Character Canon" sheetId="25" r:id="rId25"/>
     <sheet name="Link Handoffs" sheetId="26" r:id="rId26"/>
+    <sheet name="Labrador Responses" sheetId="27" r:id="rId30"/>
+    <sheet name="Terrier Responses" sheetId="28" r:id="rId31"/>
+    <sheet name="Boxer Responses" sheetId="29" r:id="rId32"/>
   </sheets>
 </workbook>
 </file>
@@ -6672,6 +6675,1275 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Response ID</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Bucket ID</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Subtag</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Trigger examples / condition</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Labrador response template</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Fact source</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Default route</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Animation cue</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Status</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>LAB-B40-01</v>
+      </c>
+      <c r="B4" t="str">
+        <v>B40</v>
+      </c>
+      <c r="C4" t="str">
+        <v>nosubject</v>
+      </c>
+      <c r="D4" t="str">
+        <v>ANY unrecognised input, no candidate subject</v>
+      </c>
+      <c r="E4" t="str">
+        <v>food?</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>LAB-B23-01</v>
+      </c>
+      <c r="B5" t="str">
+        <v>B23</v>
+      </c>
+      <c r="C5" t="str">
+        <v>identity</v>
+      </c>
+      <c r="D5" t="str">
+        <v>are you the labrador; are you a lab</v>
+      </c>
+      <c r="E5" t="str">
+        <v>yes!</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>LAB-B23-02</v>
+      </c>
+      <c r="B6" t="str">
+        <v>B23</v>
+      </c>
+      <c r="C6" t="str">
+        <v>identity</v>
+      </c>
+      <c r="D6" t="str">
+        <v>are you a real dog; are you real</v>
+      </c>
+      <c r="E6" t="str">
+        <v>i am a dog</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>LAB-B21-01</v>
+      </c>
+      <c r="B7" t="str">
+        <v>B21</v>
+      </c>
+      <c r="C7" t="str">
+        <v>cats</v>
+      </c>
+      <c r="D7" t="str">
+        <v>cats; cat; do you chase cats</v>
+      </c>
+      <c r="E7" t="str">
+        <v>yes!</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>LAB-B22-01</v>
+      </c>
+      <c r="B8" t="str">
+        <v>B22</v>
+      </c>
+      <c r="C8" t="str">
+        <v>tricks</v>
+      </c>
+      <c r="D8" t="str">
+        <v>sit; sit down</v>
+      </c>
+      <c r="E8" t="str">
+        <v>i am sitting</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>LAB-B22-02</v>
+      </c>
+      <c r="B9" t="str">
+        <v>B22</v>
+      </c>
+      <c r="C9" t="str">
+        <v>tricks</v>
+      </c>
+      <c r="D9" t="str">
+        <v>speak; beg</v>
+      </c>
+      <c r="E9" t="str">
+        <v>no</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>LAB-B32-01</v>
+      </c>
+      <c r="B10" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C10" t="str">
+        <v>self</v>
+      </c>
+      <c r="D10" t="str">
+        <v>what do you like to eat; whats your favourite food</v>
+      </c>
+      <c r="E10" t="str">
+        <v>human food is my fav!!!</v>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>LAB-B32-02</v>
+      </c>
+      <c r="B11" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C11" t="str">
+        <v>self</v>
+      </c>
+      <c r="D11" t="str">
+        <v>like what; what human food</v>
+      </c>
+      <c r="E11" t="str">
+        <v>hotdogs</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>LAB-B32-03</v>
+      </c>
+      <c r="B12" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C12" t="str">
+        <v>self</v>
+      </c>
+      <c r="D12" t="str">
+        <v>do you eat dog food; do you eat anything else</v>
+      </c>
+      <c r="E12" t="str">
+        <v>i eat anything even things that are not food</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>LAB-B32-04</v>
+      </c>
+      <c r="B13" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C13" t="str">
+        <v>self</v>
+      </c>
+      <c r="D13" t="str">
+        <v>whats your favourite dog</v>
+      </c>
+      <c r="E13" t="str">
+        <v>hotdogs</v>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>LAB-B32-05</v>
+      </c>
+      <c r="B14" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C14" t="str">
+        <v>self</v>
+      </c>
+      <c r="D14" t="str">
+        <v>do you like walks</v>
+      </c>
+      <c r="E14" t="str">
+        <v>YES!</v>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>LAB-B32-06</v>
+      </c>
+      <c r="B15" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C15" t="str">
+        <v>self</v>
+      </c>
+      <c r="D15" t="str">
+        <v>how far; how long</v>
+      </c>
+      <c r="E15" t="str">
+        <v>to the big water</v>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>LAB-B32-07</v>
+      </c>
+      <c r="B16" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C16" t="str">
+        <v>self</v>
+      </c>
+      <c r="D16" t="str">
+        <v>do you like the rain</v>
+      </c>
+      <c r="E16" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>LAB-B32-08</v>
+      </c>
+      <c r="B17" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C17" t="str">
+        <v>self</v>
+      </c>
+      <c r="D17" t="str">
+        <v>do you like baths; what about baths</v>
+      </c>
+      <c r="E17" t="str">
+        <v>no!!!!</v>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>LAB-B32-09</v>
+      </c>
+      <c r="B18" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C18" t="str">
+        <v>self</v>
+      </c>
+      <c r="D18" t="str">
+        <v>do you get told off</v>
+      </c>
+      <c r="E18" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>LAB-B32-10</v>
+      </c>
+      <c r="B19" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C19" t="str">
+        <v>self</v>
+      </c>
+      <c r="D19" t="str">
+        <v>what for; why do you get told off</v>
+      </c>
+      <c r="E19" t="str">
+        <v>im greedy</v>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>LAB-B33-01</v>
+      </c>
+      <c r="B20" t="str">
+        <v>B33</v>
+      </c>
+      <c r="C20" t="str">
+        <v>pack</v>
+      </c>
+      <c r="D20" t="str">
+        <v>do you know any other dogs; do you have friends</v>
+      </c>
+      <c r="E20" t="str">
+        <v>loads!</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>LAB-B35-01</v>
+      </c>
+      <c r="B21" t="str">
+        <v>B35</v>
+      </c>
+      <c r="C21" t="str">
+        <v>nofact</v>
+      </c>
+      <c r="D21" t="str">
+        <v>any fact he does not hold</v>
+      </c>
+      <c r="E21" t="str">
+        <v>dunno but collie knows stuff like that</v>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>LAB-B35-02</v>
+      </c>
+      <c r="B22" t="str">
+        <v>B35</v>
+      </c>
+      <c r="C22" t="str">
+        <v>nofact</v>
+      </c>
+      <c r="D22" t="str">
+        <v>black hole; anything with the word hole</v>
+      </c>
+      <c r="E22" t="str">
+        <v>i dig holes</v>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I22"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Response ID</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Bucket ID</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Subtag</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Trigger examples / condition</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Terrier response template</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Fact source</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Default route</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Animation cue</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Status</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>TER-B40-01</v>
+      </c>
+      <c r="B4" t="str">
+        <v>B40</v>
+      </c>
+      <c r="C4" t="str">
+        <v>nosubject</v>
+      </c>
+      <c r="D4" t="str">
+        <v>ANY unrecognised input, no candidate subject</v>
+      </c>
+      <c r="E4" t="str">
+        <v>dig?</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>TER-B23-01</v>
+      </c>
+      <c r="B5" t="str">
+        <v>B23</v>
+      </c>
+      <c r="C5" t="str">
+        <v>identity</v>
+      </c>
+      <c r="D5" t="str">
+        <v>are you the terrier; are you a terrier</v>
+      </c>
+      <c r="E5" t="str">
+        <v>why you want to know?</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>TER-B23-02</v>
+      </c>
+      <c r="B6" t="str">
+        <v>B23</v>
+      </c>
+      <c r="C6" t="str">
+        <v>identity</v>
+      </c>
+      <c r="D6" t="str">
+        <v>the collie sent me; yes really</v>
+      </c>
+      <c r="E6" t="str">
+        <v>oh righty, yea thats me, im the border terrier</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>TER-B21-01</v>
+      </c>
+      <c r="B7" t="str">
+        <v>B21</v>
+      </c>
+      <c r="C7" t="str">
+        <v>cats</v>
+      </c>
+      <c r="D7" t="str">
+        <v>cats; cat; do you chase cats</v>
+      </c>
+      <c r="E7" t="str">
+        <v>where????</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>TER-B22-01</v>
+      </c>
+      <c r="B8" t="str">
+        <v>B22</v>
+      </c>
+      <c r="C8" t="str">
+        <v>tricks</v>
+      </c>
+      <c r="D8" t="str">
+        <v>sit; sit down</v>
+      </c>
+      <c r="E8" t="str">
+        <v>why?</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>TER-B22-02</v>
+      </c>
+      <c r="B9" t="str">
+        <v>B22</v>
+      </c>
+      <c r="C9" t="str">
+        <v>tricks</v>
+      </c>
+      <c r="D9" t="str">
+        <v>because i asked; just do it</v>
+      </c>
+      <c r="E9" t="str">
+        <v>whats the magic word?</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>TER-B22-03</v>
+      </c>
+      <c r="B10" t="str">
+        <v>B22</v>
+      </c>
+      <c r="C10" t="str">
+        <v>tricks</v>
+      </c>
+      <c r="D10" t="str">
+        <v>please</v>
+      </c>
+      <c r="E10" t="str">
+        <v>no</v>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>TER-B27-01</v>
+      </c>
+      <c r="B11" t="str">
+        <v>B27</v>
+      </c>
+      <c r="C11" t="str">
+        <v>capability</v>
+      </c>
+      <c r="D11" t="str">
+        <v>what do you do; what can you do</v>
+      </c>
+      <c r="E11" t="str">
+        <v>dig and find</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>TER-B27-02</v>
+      </c>
+      <c r="B12" t="str">
+        <v>B27</v>
+      </c>
+      <c r="C12" t="str">
+        <v>capability</v>
+      </c>
+      <c r="D12" t="str">
+        <v>find what; what do you find</v>
+      </c>
+      <c r="E12" t="str">
+        <v>stuff like this</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>TER-B32-01</v>
+      </c>
+      <c r="B13" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C13" t="str">
+        <v>self</v>
+      </c>
+      <c r="D13" t="str">
+        <v>do you like walks</v>
+      </c>
+      <c r="E13" t="str">
+        <v>why you ask?</v>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>TER-B32-02</v>
+      </c>
+      <c r="B14" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C14" t="str">
+        <v>self</v>
+      </c>
+      <c r="D14" t="str">
+        <v>i just wondered; no reason</v>
+      </c>
+      <c r="E14" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>TER-B32-03</v>
+      </c>
+      <c r="B15" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C15" t="str">
+        <v>self</v>
+      </c>
+      <c r="D15" t="str">
+        <v>do you like baths; what about baths</v>
+      </c>
+      <c r="E15" t="str">
+        <v>no</v>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>TER-B33-01</v>
+      </c>
+      <c r="B16" t="str">
+        <v>B33</v>
+      </c>
+      <c r="C16" t="str">
+        <v>pack</v>
+      </c>
+      <c r="D16" t="str">
+        <v>do you know any other dogs; do you have friends</v>
+      </c>
+      <c r="E16" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>TER-B33-02</v>
+      </c>
+      <c r="B17" t="str">
+        <v>B33</v>
+      </c>
+      <c r="C17" t="str">
+        <v>pack</v>
+      </c>
+      <c r="D17" t="str">
+        <v>who; who are they; whos your best friend</v>
+      </c>
+      <c r="E17" t="str">
+        <v>53, too many to name</v>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>TER-B35-01</v>
+      </c>
+      <c r="B18" t="str">
+        <v>B35</v>
+      </c>
+      <c r="C18" t="str">
+        <v>nofact</v>
+      </c>
+      <c r="D18" t="str">
+        <v>black hole; anything with the word hole</v>
+      </c>
+      <c r="E18" t="str">
+        <v>a deep hole i dug?</v>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Response ID</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Bucket ID</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Subtag</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Trigger examples / condition</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Boxer response template</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Fact source</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Default route</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Animation cue</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Status</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>BOX-B40-01</v>
+      </c>
+      <c r="B4" t="str">
+        <v>B40</v>
+      </c>
+      <c r="C4" t="str">
+        <v>nosubject</v>
+      </c>
+      <c r="D4" t="str">
+        <v>ANY unrecognised input, no candidate subject</v>
+      </c>
+      <c r="E4" t="str">
+        <v>joke?</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>BOX-B23-01</v>
+      </c>
+      <c r="B5" t="str">
+        <v>B23</v>
+      </c>
+      <c r="C5" t="str">
+        <v>identity</v>
+      </c>
+      <c r="D5" t="str">
+        <v>are you the boxer; are you a boxer</v>
+      </c>
+      <c r="E5" t="str">
+        <v>yepper</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>BOX-B27-01</v>
+      </c>
+      <c r="B6" t="str">
+        <v>B27</v>
+      </c>
+      <c r="C6" t="str">
+        <v>capability</v>
+      </c>
+      <c r="D6" t="str">
+        <v>can you do something other than jokes; what else</v>
+      </c>
+      <c r="E6" t="str">
+        <v>yes, you want to play my mini game? or the proper game?</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>BOX-B29-01</v>
+      </c>
+      <c r="B7" t="str">
+        <v>B29</v>
+      </c>
+      <c r="C7" t="str">
+        <v>nice</v>
+      </c>
+      <c r="D7" t="str">
+        <v>lol; haha; ha; thats funny</v>
+      </c>
+      <c r="E7" t="str">
+        <v>hhaaww</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>BOX-B24-01</v>
+      </c>
+      <c r="B8" t="str">
+        <v>B24</v>
+      </c>
+      <c r="C8" t="str">
+        <v>rude</v>
+      </c>
+      <c r="D8" t="str">
+        <v>thats terrible; not funny; thats rubbish</v>
+      </c>
+      <c r="E8" t="str">
+        <v>one more</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F14"/>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -6677,7 +6677,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -6745,19 +6745,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>LAB-B23-01</v>
+        <v>LAB-B14-01</v>
       </c>
       <c r="B5" t="str">
-        <v>B23</v>
+        <v>B14</v>
       </c>
       <c r="C5" t="str">
-        <v>identity</v>
+        <v>gibberish</v>
       </c>
       <c r="D5" t="str">
-        <v>are you the labrador; are you a lab</v>
+        <v>keyboard mash; symbols only; unreadable</v>
       </c>
       <c r="E5" t="str">
-        <v>yes!</v>
+        <v>wot?</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -6774,7 +6774,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>LAB-B23-02</v>
+        <v>LAB-B23-01</v>
       </c>
       <c r="B6" t="str">
         <v>B23</v>
@@ -6783,10 +6783,10 @@
         <v>identity</v>
       </c>
       <c r="D6" t="str">
-        <v>are you a real dog; are you real</v>
+        <v>are you the labrador; are you a lab</v>
       </c>
       <c r="E6" t="str">
-        <v>i am a dog</v>
+        <v>yes!</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -6803,19 +6803,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>LAB-B21-01</v>
+        <v>LAB-B23-02</v>
       </c>
       <c r="B7" t="str">
-        <v>B21</v>
+        <v>B23</v>
       </c>
       <c r="C7" t="str">
-        <v>cats</v>
+        <v>identity</v>
       </c>
       <c r="D7" t="str">
-        <v>cats; cat; do you chase cats</v>
+        <v>are you a real dog; are you real</v>
       </c>
       <c r="E7" t="str">
-        <v>yes!</v>
+        <v>i am a dog</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -6832,19 +6832,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>LAB-B22-01</v>
+        <v>LAB-B21-01</v>
       </c>
       <c r="B8" t="str">
-        <v>B22</v>
+        <v>B21</v>
       </c>
       <c r="C8" t="str">
-        <v>tricks</v>
+        <v>cats</v>
       </c>
       <c r="D8" t="str">
-        <v>sit; sit down</v>
+        <v>cats; cat; do you chase cats</v>
       </c>
       <c r="E8" t="str">
-        <v>i am sitting</v>
+        <v>yes!</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -6861,7 +6861,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>LAB-B22-02</v>
+        <v>LAB-B22-01</v>
       </c>
       <c r="B9" t="str">
         <v>B22</v>
@@ -6870,10 +6870,10 @@
         <v>tricks</v>
       </c>
       <c r="D9" t="str">
-        <v>speak; beg</v>
+        <v>sit; sit down</v>
       </c>
       <c r="E9" t="str">
-        <v>no</v>
+        <v>i am sitting</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -6890,19 +6890,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>LAB-B32-01</v>
+        <v>LAB-B22-02</v>
       </c>
       <c r="B10" t="str">
-        <v>B32</v>
+        <v>B22</v>
       </c>
       <c r="C10" t="str">
-        <v>self</v>
+        <v>tricks</v>
       </c>
       <c r="D10" t="str">
-        <v>what do you like to eat; whats your favourite food</v>
+        <v>speak; beg</v>
       </c>
       <c r="E10" t="str">
-        <v>human food is my fav!!!</v>
+        <v>no</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -6919,7 +6919,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>LAB-B32-02</v>
+        <v>LAB-B32-01</v>
       </c>
       <c r="B11" t="str">
         <v>B32</v>
@@ -6928,10 +6928,10 @@
         <v>self</v>
       </c>
       <c r="D11" t="str">
-        <v>like what; what human food</v>
+        <v>what do you like to eat; whats your favourite food</v>
       </c>
       <c r="E11" t="str">
-        <v>hotdogs</v>
+        <v>human food is my fav!!!</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -6948,7 +6948,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>LAB-B32-03</v>
+        <v>LAB-B32-02</v>
       </c>
       <c r="B12" t="str">
         <v>B32</v>
@@ -6957,10 +6957,10 @@
         <v>self</v>
       </c>
       <c r="D12" t="str">
-        <v>do you eat dog food; do you eat anything else</v>
+        <v>like what; what human food</v>
       </c>
       <c r="E12" t="str">
-        <v>i eat anything even things that are not food</v>
+        <v>hotdogs</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -6977,7 +6977,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>LAB-B32-04</v>
+        <v>LAB-B32-03</v>
       </c>
       <c r="B13" t="str">
         <v>B32</v>
@@ -6986,10 +6986,10 @@
         <v>self</v>
       </c>
       <c r="D13" t="str">
-        <v>whats your favourite dog</v>
+        <v>do you eat dog food; do you eat anything else</v>
       </c>
       <c r="E13" t="str">
-        <v>hotdogs</v>
+        <v>i eat anything even things that are not food</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -7006,7 +7006,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>LAB-B32-05</v>
+        <v>LAB-B32-04</v>
       </c>
       <c r="B14" t="str">
         <v>B32</v>
@@ -7015,10 +7015,10 @@
         <v>self</v>
       </c>
       <c r="D14" t="str">
-        <v>do you like walks</v>
+        <v>whats your favourite dog</v>
       </c>
       <c r="E14" t="str">
-        <v>YES!</v>
+        <v>hotdogs</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -7035,7 +7035,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>LAB-B32-06</v>
+        <v>LAB-B32-05</v>
       </c>
       <c r="B15" t="str">
         <v>B32</v>
@@ -7044,10 +7044,10 @@
         <v>self</v>
       </c>
       <c r="D15" t="str">
-        <v>how far; how long</v>
+        <v>do you like walks</v>
       </c>
       <c r="E15" t="str">
-        <v>to the big water</v>
+        <v>YES!</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -7064,7 +7064,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>LAB-B32-07</v>
+        <v>LAB-B32-06</v>
       </c>
       <c r="B16" t="str">
         <v>B32</v>
@@ -7073,10 +7073,10 @@
         <v>self</v>
       </c>
       <c r="D16" t="str">
-        <v>do you like the rain</v>
+        <v>how far; how long</v>
       </c>
       <c r="E16" t="str">
-        <v>yes</v>
+        <v>to the big water</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -7093,7 +7093,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>LAB-B32-08</v>
+        <v>LAB-B32-07</v>
       </c>
       <c r="B17" t="str">
         <v>B32</v>
@@ -7102,10 +7102,10 @@
         <v>self</v>
       </c>
       <c r="D17" t="str">
-        <v>do you like baths; what about baths</v>
+        <v>do you like the rain</v>
       </c>
       <c r="E17" t="str">
-        <v>no!!!!</v>
+        <v>yes</v>
       </c>
       <c r="F17" t="str">
         <v/>
@@ -7122,7 +7122,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>LAB-B32-09</v>
+        <v>LAB-B32-08</v>
       </c>
       <c r="B18" t="str">
         <v>B32</v>
@@ -7131,10 +7131,10 @@
         <v>self</v>
       </c>
       <c r="D18" t="str">
-        <v>do you get told off</v>
+        <v>do you like baths; what about baths</v>
       </c>
       <c r="E18" t="str">
-        <v>yes</v>
+        <v>no!!!!</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -7151,7 +7151,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>LAB-B32-10</v>
+        <v>LAB-B32-09</v>
       </c>
       <c r="B19" t="str">
         <v>B32</v>
@@ -7160,10 +7160,10 @@
         <v>self</v>
       </c>
       <c r="D19" t="str">
-        <v>what for; why do you get told off</v>
+        <v>do you get told off</v>
       </c>
       <c r="E19" t="str">
-        <v>im greedy</v>
+        <v>yes</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -7180,19 +7180,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>LAB-B33-01</v>
+        <v>LAB-B32-10</v>
       </c>
       <c r="B20" t="str">
-        <v>B33</v>
+        <v>B32</v>
       </c>
       <c r="C20" t="str">
-        <v>pack</v>
+        <v>self</v>
       </c>
       <c r="D20" t="str">
-        <v>do you know any other dogs; do you have friends</v>
+        <v>what for; why do you get told off</v>
       </c>
       <c r="E20" t="str">
-        <v>loads!</v>
+        <v>im greedy</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -7209,19 +7209,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>LAB-B35-01</v>
+        <v>LAB-B33-01</v>
       </c>
       <c r="B21" t="str">
-        <v>B35</v>
+        <v>B33</v>
       </c>
       <c r="C21" t="str">
-        <v>nofact</v>
+        <v>pack</v>
       </c>
       <c r="D21" t="str">
-        <v>any fact he does not hold</v>
+        <v>do you know any other dogs; do you have friends</v>
       </c>
       <c r="E21" t="str">
-        <v>dunno but collie knows stuff like that</v>
+        <v>loads!</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -7238,7 +7238,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>LAB-B35-02</v>
+        <v>LAB-B35-01</v>
       </c>
       <c r="B22" t="str">
         <v>B35</v>
@@ -7247,10 +7247,10 @@
         <v>nofact</v>
       </c>
       <c r="D22" t="str">
-        <v>black hole; anything with the word hole</v>
+        <v>any fact he does not hold</v>
       </c>
       <c r="E22" t="str">
-        <v>i dig holes</v>
+        <v>dunno but collie knows stuff like that</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -7265,16 +7265,45 @@
         <v>Approved</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>LAB-B35-02</v>
+      </c>
+      <c r="B23" t="str">
+        <v>B35</v>
+      </c>
+      <c r="C23" t="str">
+        <v>nofact</v>
+      </c>
+      <c r="D23" t="str">
+        <v>black hole; anything with the word hole</v>
+      </c>
+      <c r="E23" t="str">
+        <v>i dig holes</v>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I23"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -7342,19 +7371,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TER-B23-01</v>
+        <v>TER-B14-01</v>
       </c>
       <c r="B5" t="str">
-        <v>B23</v>
+        <v>B14</v>
       </c>
       <c r="C5" t="str">
-        <v>identity</v>
+        <v>gibberish</v>
       </c>
       <c r="D5" t="str">
-        <v>are you the terrier; are you a terrier</v>
+        <v>keyboard mash; symbols only; unreadable</v>
       </c>
       <c r="E5" t="str">
-        <v>why you want to know?</v>
+        <v>whats that supposed to be?</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -7371,7 +7400,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TER-B23-02</v>
+        <v>TER-B23-01</v>
       </c>
       <c r="B6" t="str">
         <v>B23</v>
@@ -7380,10 +7409,10 @@
         <v>identity</v>
       </c>
       <c r="D6" t="str">
-        <v>the collie sent me; yes really</v>
+        <v>are you the terrier; are you a terrier</v>
       </c>
       <c r="E6" t="str">
-        <v>oh righty, yea thats me, im the border terrier</v>
+        <v>why you want to know?</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -7400,19 +7429,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>TER-B21-01</v>
+        <v>TER-B23-02</v>
       </c>
       <c r="B7" t="str">
-        <v>B21</v>
+        <v>B23</v>
       </c>
       <c r="C7" t="str">
-        <v>cats</v>
+        <v>identity</v>
       </c>
       <c r="D7" t="str">
-        <v>cats; cat; do you chase cats</v>
+        <v>the collie sent me; yes really</v>
       </c>
       <c r="E7" t="str">
-        <v>where????</v>
+        <v>oh righty, yea thats me, im the border terrier</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -7429,19 +7458,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>TER-B22-01</v>
+        <v>TER-B21-01</v>
       </c>
       <c r="B8" t="str">
-        <v>B22</v>
+        <v>B21</v>
       </c>
       <c r="C8" t="str">
-        <v>tricks</v>
+        <v>cats</v>
       </c>
       <c r="D8" t="str">
-        <v>sit; sit down</v>
+        <v>cats; cat; do you chase cats</v>
       </c>
       <c r="E8" t="str">
-        <v>why?</v>
+        <v>where????</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -7458,7 +7487,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>TER-B22-02</v>
+        <v>TER-B22-01</v>
       </c>
       <c r="B9" t="str">
         <v>B22</v>
@@ -7467,10 +7496,10 @@
         <v>tricks</v>
       </c>
       <c r="D9" t="str">
-        <v>because i asked; just do it</v>
+        <v>sit; sit down</v>
       </c>
       <c r="E9" t="str">
-        <v>whats the magic word?</v>
+        <v>why?</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -7487,7 +7516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>TER-B22-03</v>
+        <v>TER-B22-02</v>
       </c>
       <c r="B10" t="str">
         <v>B22</v>
@@ -7496,10 +7525,10 @@
         <v>tricks</v>
       </c>
       <c r="D10" t="str">
-        <v>please</v>
+        <v>because i asked; just do it</v>
       </c>
       <c r="E10" t="str">
-        <v>no</v>
+        <v>whats the magic word?</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -7516,19 +7545,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>TER-B27-01</v>
+        <v>TER-B22-03</v>
       </c>
       <c r="B11" t="str">
-        <v>B27</v>
+        <v>B22</v>
       </c>
       <c r="C11" t="str">
-        <v>capability</v>
+        <v>tricks</v>
       </c>
       <c r="D11" t="str">
-        <v>what do you do; what can you do</v>
+        <v>please</v>
       </c>
       <c r="E11" t="str">
-        <v>dig and find</v>
+        <v>no</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -7545,7 +7574,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>TER-B27-02</v>
+        <v>TER-B27-01</v>
       </c>
       <c r="B12" t="str">
         <v>B27</v>
@@ -7554,10 +7583,10 @@
         <v>capability</v>
       </c>
       <c r="D12" t="str">
-        <v>find what; what do you find</v>
+        <v>what do you do; what can you do</v>
       </c>
       <c r="E12" t="str">
-        <v>stuff like this</v>
+        <v>dig and find</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -7574,19 +7603,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>TER-B32-01</v>
+        <v>TER-B27-02</v>
       </c>
       <c r="B13" t="str">
-        <v>B32</v>
+        <v>B27</v>
       </c>
       <c r="C13" t="str">
-        <v>self</v>
+        <v>capability</v>
       </c>
       <c r="D13" t="str">
-        <v>do you like walks</v>
+        <v>find what; what do you find</v>
       </c>
       <c r="E13" t="str">
-        <v>why you ask?</v>
+        <v>stuff like this</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -7603,7 +7632,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>TER-B32-02</v>
+        <v>TER-B32-01</v>
       </c>
       <c r="B14" t="str">
         <v>B32</v>
@@ -7612,10 +7641,10 @@
         <v>self</v>
       </c>
       <c r="D14" t="str">
-        <v>i just wondered; no reason</v>
+        <v>do you like walks</v>
       </c>
       <c r="E14" t="str">
-        <v>yes</v>
+        <v>why you ask?</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -7632,7 +7661,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>TER-B32-03</v>
+        <v>TER-B32-02</v>
       </c>
       <c r="B15" t="str">
         <v>B32</v>
@@ -7641,10 +7670,10 @@
         <v>self</v>
       </c>
       <c r="D15" t="str">
-        <v>do you like baths; what about baths</v>
+        <v>i just wondered; no reason</v>
       </c>
       <c r="E15" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -7661,19 +7690,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>TER-B33-01</v>
+        <v>TER-B32-03</v>
       </c>
       <c r="B16" t="str">
-        <v>B33</v>
+        <v>B32</v>
       </c>
       <c r="C16" t="str">
-        <v>pack</v>
+        <v>self</v>
       </c>
       <c r="D16" t="str">
-        <v>do you know any other dogs; do you have friends</v>
+        <v>do you like baths; what about baths</v>
       </c>
       <c r="E16" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -7690,7 +7719,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>TER-B33-02</v>
+        <v>TER-B33-01</v>
       </c>
       <c r="B17" t="str">
         <v>B33</v>
@@ -7699,10 +7728,10 @@
         <v>pack</v>
       </c>
       <c r="D17" t="str">
-        <v>who; who are they; whos your best friend</v>
+        <v>do you know any other dogs; do you have friends</v>
       </c>
       <c r="E17" t="str">
-        <v>53, too many to name</v>
+        <v>yes</v>
       </c>
       <c r="F17" t="str">
         <v/>
@@ -7719,19 +7748,19 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>TER-B35-01</v>
+        <v>TER-B33-02</v>
       </c>
       <c r="B18" t="str">
-        <v>B35</v>
+        <v>B33</v>
       </c>
       <c r="C18" t="str">
-        <v>nofact</v>
+        <v>pack</v>
       </c>
       <c r="D18" t="str">
-        <v>black hole; anything with the word hole</v>
+        <v>who; who are they; whos your best friend</v>
       </c>
       <c r="E18" t="str">
-        <v>a deep hole i dug?</v>
+        <v>53, too many to name</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -7746,16 +7775,45 @@
         <v>Approved</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>TER-B35-01</v>
+      </c>
+      <c r="B19" t="str">
+        <v>B35</v>
+      </c>
+      <c r="C19" t="str">
+        <v>nofact</v>
+      </c>
+      <c r="D19" t="str">
+        <v>black hole; anything with the word hole</v>
+      </c>
+      <c r="E19" t="str">
+        <v>a deep hole i dug?</v>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I19"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -7823,19 +7881,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>BOX-B23-01</v>
+        <v>BOX-B14-01</v>
       </c>
       <c r="B5" t="str">
-        <v>B23</v>
+        <v>B14</v>
       </c>
       <c r="C5" t="str">
-        <v>identity</v>
+        <v>gibberish</v>
       </c>
       <c r="D5" t="str">
-        <v>are you the boxer; are you a boxer</v>
+        <v>keyboard mash; symbols only; unreadable</v>
       </c>
       <c r="E5" t="str">
-        <v>yepper</v>
+        <v>is that a joke?</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -7852,19 +7910,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>BOX-B27-01</v>
+        <v>BOX-B23-01</v>
       </c>
       <c r="B6" t="str">
-        <v>B27</v>
+        <v>B23</v>
       </c>
       <c r="C6" t="str">
-        <v>capability</v>
+        <v>identity</v>
       </c>
       <c r="D6" t="str">
-        <v>can you do something other than jokes; what else</v>
+        <v>are you the boxer; are you a boxer</v>
       </c>
       <c r="E6" t="str">
-        <v>yes, you want to play my mini game? or the proper game?</v>
+        <v>yepper</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -7881,19 +7939,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>BOX-B29-01</v>
+        <v>BOX-B27-01</v>
       </c>
       <c r="B7" t="str">
-        <v>B29</v>
+        <v>B27</v>
       </c>
       <c r="C7" t="str">
-        <v>nice</v>
+        <v>capability</v>
       </c>
       <c r="D7" t="str">
-        <v>lol; haha; ha; thats funny</v>
+        <v>can you do something other than jokes; what else</v>
       </c>
       <c r="E7" t="str">
-        <v>hhaaww</v>
+        <v>yes, you want to play my mini game? or the proper game?</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -7910,19 +7968,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>BOX-B24-01</v>
+        <v>BOX-B29-01</v>
       </c>
       <c r="B8" t="str">
-        <v>B24</v>
+        <v>B29</v>
       </c>
       <c r="C8" t="str">
-        <v>rude</v>
+        <v>nice</v>
       </c>
       <c r="D8" t="str">
-        <v>thats terrible; not funny; thats rubbish</v>
+        <v>lol; haha; ha; thats funny</v>
       </c>
       <c r="E8" t="str">
-        <v>one more</v>
+        <v>hhaaww</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -7937,9 +7995,241 @@
         <v>Approved</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>BOX-B24-01</v>
+      </c>
+      <c r="B9" t="str">
+        <v>B24</v>
+      </c>
+      <c r="C9" t="str">
+        <v>rude</v>
+      </c>
+      <c r="D9" t="str">
+        <v>thats terrible; not funny; thats rubbish</v>
+      </c>
+      <c r="E9" t="str">
+        <v>one more</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>BOX-B30-01</v>
+      </c>
+      <c r="B10" t="str">
+        <v>B30</v>
+      </c>
+      <c r="C10" t="str">
+        <v>joke</v>
+      </c>
+      <c r="D10" t="str">
+        <v>joke; tell me a joke; make me laugh</v>
+      </c>
+      <c r="E10" t="str">
+        <v>knock kncok</v>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>BOX-B30-02</v>
+      </c>
+      <c r="B11" t="str">
+        <v>B30</v>
+      </c>
+      <c r="C11" t="str">
+        <v>joke</v>
+      </c>
+      <c r="D11" t="str">
+        <v>whos there; who is there</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Bow</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>BOX-B30-03</v>
+      </c>
+      <c r="B12" t="str">
+        <v>B30</v>
+      </c>
+      <c r="C12" t="str">
+        <v>joke</v>
+      </c>
+      <c r="D12" t="str">
+        <v>bow who</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Not bow who! i mean Bow wow!</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>BOX-B30-04</v>
+      </c>
+      <c r="B13" t="str">
+        <v>B30</v>
+      </c>
+      <c r="C13" t="str">
+        <v>joke</v>
+      </c>
+      <c r="D13" t="str">
+        <v>another; again; more; go on</v>
+      </c>
+      <c r="E13" t="str">
+        <v>What do you call a dog rock star?</v>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>BOX-B30-05</v>
+      </c>
+      <c r="B14" t="str">
+        <v>B30</v>
+      </c>
+      <c r="C14" t="str">
+        <v>joke</v>
+      </c>
+      <c r="D14" t="str">
+        <v>i dont know; dunno; what</v>
+      </c>
+      <c r="E14" t="str">
+        <v>A sue-paw star</v>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>BOX-B30-06</v>
+      </c>
+      <c r="B15" t="str">
+        <v>B30</v>
+      </c>
+      <c r="C15" t="str">
+        <v>joke</v>
+      </c>
+      <c r="D15" t="str">
+        <v>another one; one more</v>
+      </c>
+      <c r="E15" t="str">
+        <v>How can you tell dogs are having a good time?</v>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>BOX-B30-07</v>
+      </c>
+      <c r="B16" t="str">
+        <v>B30</v>
+      </c>
+      <c r="C16" t="str">
+        <v>joke</v>
+      </c>
+      <c r="D16" t="str">
+        <v>how; tell me how</v>
+      </c>
+      <c r="E16" t="str">
+        <v>we are having a ball</v>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I16"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -9455,7 +9455,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I290"/>
+  <dimension ref="A1:I324"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -17838,9 +17838,995 @@
         <v>Approved</v>
       </c>
     </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>COL-B54-TRICKS-01</v>
+      </c>
+      <c r="B291" t="str">
+        <v>B54</v>
+      </c>
+      <c r="C291" t="str">
+        <v>tricks</v>
+      </c>
+      <c r="D291" t="str">
+        <v>tricks; can you do tricks; show me a trick; do a trick; any tricks; do tricks</v>
+      </c>
+      <c r="E291" t="str">
+        <v>I do tricks</v>
+      </c>
+      <c r="F291" t="str">
+        <v/>
+      </c>
+      <c r="G291" t="str">
+        <v/>
+      </c>
+      <c r="H291" t="str">
+        <v/>
+      </c>
+      <c r="I291" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>COL-B54-TRICKS-02</v>
+      </c>
+      <c r="B292" t="str">
+        <v>B54</v>
+      </c>
+      <c r="C292" t="str">
+        <v>tricks</v>
+      </c>
+      <c r="D292" t="str">
+        <v>confirmation after "I do tricks"</v>
+      </c>
+      <c r="E292" t="str">
+        <v>play dead, roll over</v>
+      </c>
+      <c r="F292" t="str">
+        <v/>
+      </c>
+      <c r="G292" t="str">
+        <v/>
+      </c>
+      <c r="H292" t="str">
+        <v/>
+      </c>
+      <c r="I292" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>COL-B55-CONFIRM-01</v>
+      </c>
+      <c r="B293" t="str">
+        <v>B55</v>
+      </c>
+      <c r="C293" t="str">
+        <v>confirm</v>
+      </c>
+      <c r="D293" t="str">
+        <v>dogs; dog (subject repeat, second turn)</v>
+      </c>
+      <c r="E293" t="str">
+        <v>Do you want to know about dogs?</v>
+      </c>
+      <c r="F293" t="str">
+        <v/>
+      </c>
+      <c r="G293" t="str">
+        <v/>
+      </c>
+      <c r="H293" t="str">
+        <v/>
+      </c>
+      <c r="I293" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>COL-B55-CONFIRM-02</v>
+      </c>
+      <c r="B294" t="str">
+        <v>B55</v>
+      </c>
+      <c r="C294" t="str">
+        <v>confirm</v>
+      </c>
+      <c r="D294" t="str">
+        <v>games; game (second turn)</v>
+      </c>
+      <c r="E294" t="str">
+        <v>You want to play a game?</v>
+      </c>
+      <c r="F294" t="str">
+        <v/>
+      </c>
+      <c r="G294" t="str">
+        <v/>
+      </c>
+      <c r="H294" t="str">
+        <v/>
+      </c>
+      <c r="I294" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>COL-B55-CONFIRM-03</v>
+      </c>
+      <c r="B295" t="str">
+        <v>B55</v>
+      </c>
+      <c r="C295" t="str">
+        <v>confirm</v>
+      </c>
+      <c r="D295" t="str">
+        <v>breeds (second turn)</v>
+      </c>
+      <c r="E295" t="str">
+        <v>Do you want to know about one breed?</v>
+      </c>
+      <c r="F295" t="str">
+        <v/>
+      </c>
+      <c r="G295" t="str">
+        <v/>
+      </c>
+      <c r="H295" t="str">
+        <v/>
+      </c>
+      <c r="I295" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>COL-B55-CONFIRM-04</v>
+      </c>
+      <c r="B296" t="str">
+        <v>B55</v>
+      </c>
+      <c r="C296" t="str">
+        <v>confirm</v>
+      </c>
+      <c r="D296" t="str">
+        <v>tell me a dog fact (second turn)</v>
+      </c>
+      <c r="E296" t="str">
+        <v>A breed fact, or just a dog fact?</v>
+      </c>
+      <c r="F296" t="str">
+        <v/>
+      </c>
+      <c r="G296" t="str">
+        <v/>
+      </c>
+      <c r="H296" t="str">
+        <v/>
+      </c>
+      <c r="I296" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>COL-B56-GENERAL-01</v>
+      </c>
+      <c r="B297" t="str">
+        <v>B56</v>
+      </c>
+      <c r="C297" t="str">
+        <v>general</v>
+      </c>
+      <c r="D297" t="str">
+        <v>games; show me a game; are there games</v>
+      </c>
+      <c r="E297" t="str">
+        <v>You want to play a game?</v>
+      </c>
+      <c r="F297" t="str">
+        <v/>
+      </c>
+      <c r="G297" t="str">
+        <v/>
+      </c>
+      <c r="H297" t="str">
+        <v/>
+      </c>
+      <c r="I297" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>COL-B56-GENERAL-02</v>
+      </c>
+      <c r="B298" t="str">
+        <v>B56</v>
+      </c>
+      <c r="C298" t="str">
+        <v>general</v>
+      </c>
+      <c r="D298" t="str">
+        <v>play a game; which game; what games</v>
+      </c>
+      <c r="E298" t="str">
+        <v>Bark, Nine-Square, Missing Sheep, Kennel Sketch. Say one.</v>
+      </c>
+      <c r="F298" t="str">
+        <v/>
+      </c>
+      <c r="G298" t="str">
+        <v/>
+      </c>
+      <c r="H298" t="str">
+        <v/>
+      </c>
+      <c r="I298" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>COL-B56-GENERAL-03</v>
+      </c>
+      <c r="B299" t="str">
+        <v>B56</v>
+      </c>
+      <c r="C299" t="str">
+        <v>general</v>
+      </c>
+      <c r="D299" t="str">
+        <v>breeds; what breeds; how many breeds</v>
+      </c>
+      <c r="E299" t="str">
+        <v>We are a pack of 54. Do you want to know about Collies like me or a different breed?</v>
+      </c>
+      <c r="F299" t="str">
+        <v/>
+      </c>
+      <c r="G299" t="str">
+        <v/>
+      </c>
+      <c r="H299" t="str">
+        <v/>
+      </c>
+      <c r="I299" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>COL-B56-GENERAL-04</v>
+      </c>
+      <c r="B300" t="str">
+        <v>B56</v>
+      </c>
+      <c r="C300" t="str">
+        <v>general</v>
+      </c>
+      <c r="D300" t="str">
+        <v>what is the game; whats the game; tell about the game</v>
+      </c>
+      <c r="E300" t="str">
+        <v>The card game?</v>
+      </c>
+      <c r="F300" t="str">
+        <v/>
+      </c>
+      <c r="G300" t="str">
+        <v/>
+      </c>
+      <c r="H300" t="str">
+        <v/>
+      </c>
+      <c r="I300" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>COL-B56-GENERAL-05</v>
+      </c>
+      <c r="B301" t="str">
+        <v>B56</v>
+      </c>
+      <c r="C301" t="str">
+        <v>general</v>
+      </c>
+      <c r="D301" t="str">
+        <v>how do i play games here; how do the games work</v>
+      </c>
+      <c r="E301" t="str">
+        <v>You want to play a game?</v>
+      </c>
+      <c r="F301" t="str">
+        <v/>
+      </c>
+      <c r="G301" t="str">
+        <v/>
+      </c>
+      <c r="H301" t="str">
+        <v/>
+      </c>
+      <c r="I301" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>COL-B56-GENERAL-06</v>
+      </c>
+      <c r="B302" t="str">
+        <v>B56</v>
+      </c>
+      <c r="C302" t="str">
+        <v>general</v>
+      </c>
+      <c r="D302" t="str">
+        <v>what do you like to do; what do you do all day</v>
+      </c>
+      <c r="E302" t="str">
+        <v>Work and play</v>
+      </c>
+      <c r="F302" t="str">
+        <v/>
+      </c>
+      <c r="G302" t="str">
+        <v/>
+      </c>
+      <c r="H302" t="str">
+        <v/>
+      </c>
+      <c r="I302" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>COL-B56-GENERAL-07</v>
+      </c>
+      <c r="B303" t="str">
+        <v>B56</v>
+      </c>
+      <c r="C303" t="str">
+        <v>general</v>
+      </c>
+      <c r="D303" t="str">
+        <v>a real dog; are you a real dog; is this a real dog</v>
+      </c>
+      <c r="E303" t="str">
+        <v>I am a Border Collie character inside a game, not a live animal hiding behind your screen.</v>
+      </c>
+      <c r="F303" t="str">
+        <v/>
+      </c>
+      <c r="G303" t="str">
+        <v/>
+      </c>
+      <c r="H303" t="str">
+        <v/>
+      </c>
+      <c r="I303" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>COL-B56-GENERAL-08</v>
+      </c>
+      <c r="B304" t="str">
+        <v>B56</v>
+      </c>
+      <c r="C304" t="str">
+        <v>general</v>
+      </c>
+      <c r="D304" t="str">
+        <v>what are dogs; what is a dog</v>
+      </c>
+      <c r="E304" t="str">
+        <v>4 legged friends with wet noses</v>
+      </c>
+      <c r="F304" t="str">
+        <v/>
+      </c>
+      <c r="G304" t="str">
+        <v/>
+      </c>
+      <c r="H304" t="str">
+        <v/>
+      </c>
+      <c r="I304" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>COL-B57-FACT-01</v>
+      </c>
+      <c r="B305" t="str">
+        <v>B57</v>
+      </c>
+      <c r="C305" t="str">
+        <v>fact</v>
+      </c>
+      <c r="D305" t="str">
+        <v>tell me something; tell me a fact; a dog fact; say something interesting; tell me more (rotate at random)</v>
+      </c>
+      <c r="E305" t="str">
+        <v>A Border Collie called Chaser learned 1,022 toy names</v>
+      </c>
+      <c r="F305" t="str">
+        <v>Pilley &amp; Reid 2011, Behavioural Processes</v>
+      </c>
+      <c r="G305" t="str">
+        <v/>
+      </c>
+      <c r="H305" t="str">
+        <v/>
+      </c>
+      <c r="I305" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>COL-B57-FACT-02</v>
+      </c>
+      <c r="B306" t="str">
+        <v>B57</v>
+      </c>
+      <c r="C306" t="str">
+        <v>fact</v>
+      </c>
+      <c r="D306" t="str">
+        <v>tell me something; tell me a fact; a dog fact; say something interesting; tell me more (rotate at random)</v>
+      </c>
+      <c r="E306" t="str">
+        <v>We tilt our heads more at words we actually know</v>
+      </c>
+      <c r="F306" t="str">
+        <v>Sommese et al. 2021, Animal Cognition</v>
+      </c>
+      <c r="G306" t="str">
+        <v/>
+      </c>
+      <c r="H306" t="str">
+        <v/>
+      </c>
+      <c r="I306" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>COL-B57-FACT-03</v>
+      </c>
+      <c r="B307" t="str">
+        <v>B57</v>
+      </c>
+      <c r="C307" t="str">
+        <v>fact</v>
+      </c>
+      <c r="D307" t="str">
+        <v>tell me something; tell me a fact; a dog fact; say something interesting; tell me more (rotate at random)</v>
+      </c>
+      <c r="E307" t="str">
+        <v>I have about 220 million scent receptors. You have 5 million</v>
+      </c>
+      <c r="F307" t="str">
+        <v>Walker et al. 2006</v>
+      </c>
+      <c r="G307" t="str">
+        <v/>
+      </c>
+      <c r="H307" t="str">
+        <v/>
+      </c>
+      <c r="I307" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>COL-B57-FACT-04</v>
+      </c>
+      <c r="B308" t="str">
+        <v>B57</v>
+      </c>
+      <c r="C308" t="str">
+        <v>fact</v>
+      </c>
+      <c r="D308" t="str">
+        <v>tell me something; tell me a fact; a dog fact; say something interesting; tell me more (rotate at random)</v>
+      </c>
+      <c r="E308" t="str">
+        <v>We were bred to move sheep, not to fight anything</v>
+      </c>
+      <c r="F308" t="str">
+        <v>Kennel Club breed standard</v>
+      </c>
+      <c r="G308" t="str">
+        <v/>
+      </c>
+      <c r="H308" t="str">
+        <v/>
+      </c>
+      <c r="I308" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>COL-B57-FACT-05</v>
+      </c>
+      <c r="B309" t="str">
+        <v>B57</v>
+      </c>
+      <c r="C309" t="str">
+        <v>fact</v>
+      </c>
+      <c r="D309" t="str">
+        <v>tell me something; tell me a fact; a dog fact; say something interesting; tell me more (rotate at random)</v>
+      </c>
+      <c r="E309" t="str">
+        <v>We sleep about half the day, in short goes</v>
+      </c>
+      <c r="F309" t="str">
+        <v>Adams &amp; Johnson 1993</v>
+      </c>
+      <c r="G309" t="str">
+        <v/>
+      </c>
+      <c r="H309" t="str">
+        <v/>
+      </c>
+      <c r="I309" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>COL-B57-FACT-06</v>
+      </c>
+      <c r="B310" t="str">
+        <v>B57</v>
+      </c>
+      <c r="C310" t="str">
+        <v>fact</v>
+      </c>
+      <c r="D310" t="str">
+        <v>tell me something; tell me a fact; a dog fact; say something interesting; tell me more (rotate at random)</v>
+      </c>
+      <c r="E310" t="str">
+        <v>We can learn a new word from one hearing, sometimes</v>
+      </c>
+      <c r="F310" t="str">
+        <v>Fugazza et al. 2021</v>
+      </c>
+      <c r="G310" t="str">
+        <v/>
+      </c>
+      <c r="H310" t="str">
+        <v/>
+      </c>
+      <c r="I310" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>COL-B57-FACT-07</v>
+      </c>
+      <c r="B311" t="str">
+        <v>B57</v>
+      </c>
+      <c r="C311" t="str">
+        <v>fact</v>
+      </c>
+      <c r="D311" t="str">
+        <v>tell me something; tell me a fact; a dog fact; say something interesting; tell me more (rotate at random)</v>
+      </c>
+      <c r="E311" t="str">
+        <v>We smell in stereo. Each nostril works on its own</v>
+      </c>
+      <c r="F311" t="str">
+        <v>Craven et al. 2010</v>
+      </c>
+      <c r="G311" t="str">
+        <v/>
+      </c>
+      <c r="H311" t="str">
+        <v/>
+      </c>
+      <c r="I311" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>COL-B57-FACT-08</v>
+      </c>
+      <c r="B312" t="str">
+        <v>B57</v>
+      </c>
+      <c r="C312" t="str">
+        <v>fact</v>
+      </c>
+      <c r="D312" t="str">
+        <v>tell me something; tell me a fact; a dog fact; say something interesting; tell me more (rotate at random)</v>
+      </c>
+      <c r="E312" t="str">
+        <v>We can hear about twice as high as you can</v>
+      </c>
+      <c r="F312" t="str">
+        <v>Heffner 1983</v>
+      </c>
+      <c r="G312" t="str">
+        <v/>
+      </c>
+      <c r="H312" t="str">
+        <v/>
+      </c>
+      <c r="I312" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>COL-B57-FACT-09</v>
+      </c>
+      <c r="B313" t="str">
+        <v>B57</v>
+      </c>
+      <c r="C313" t="str">
+        <v>fact</v>
+      </c>
+      <c r="D313" t="str">
+        <v>tell me something; tell me a fact; a dog fact; say something interesting; tell me more (rotate at random)</v>
+      </c>
+      <c r="E313" t="str">
+        <v>Our nose prints are all different, like your fingertips</v>
+      </c>
+      <c r="F313" t="str">
+        <v>Kennel Club</v>
+      </c>
+      <c r="G313" t="str">
+        <v/>
+      </c>
+      <c r="H313" t="str">
+        <v/>
+      </c>
+      <c r="I313" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>COL-B57-FACT-10</v>
+      </c>
+      <c r="B314" t="str">
+        <v>B57</v>
+      </c>
+      <c r="C314" t="str">
+        <v>fact</v>
+      </c>
+      <c r="D314" t="str">
+        <v>tell me something; tell me a fact; a dog fact; say something interesting; tell me more (rotate at random)</v>
+      </c>
+      <c r="E314" t="str">
+        <v>We sweat through our paws, not our skin</v>
+      </c>
+      <c r="F314" t="str">
+        <v>Merck Veterinary Manual</v>
+      </c>
+      <c r="G314" t="str">
+        <v/>
+      </c>
+      <c r="H314" t="str">
+        <v/>
+      </c>
+      <c r="I314" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>COL-B57-FACT-11</v>
+      </c>
+      <c r="B315" t="str">
+        <v>B57</v>
+      </c>
+      <c r="C315" t="str">
+        <v>fact</v>
+      </c>
+      <c r="D315" t="str">
+        <v>tell me something; tell me a fact; a dog fact; say something interesting; tell me more (rotate at random)</v>
+      </c>
+      <c r="E315" t="str">
+        <v>A wet nose helps us catch smells</v>
+      </c>
+      <c r="F315" t="str">
+        <v>Merck Veterinary Manual</v>
+      </c>
+      <c r="G315" t="str">
+        <v/>
+      </c>
+      <c r="H315" t="str">
+        <v/>
+      </c>
+      <c r="I315" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>COL-B57-FACT-12</v>
+      </c>
+      <c r="B316" t="str">
+        <v>B57</v>
+      </c>
+      <c r="C316" t="str">
+        <v>fact</v>
+      </c>
+      <c r="D316" t="str">
+        <v>tell me something; tell me a fact; a dog fact; say something interesting; tell me more (rotate at random)</v>
+      </c>
+      <c r="E316" t="str">
+        <v>We see blue and yellow. Red looks muddy to us</v>
+      </c>
+      <c r="F316" t="str">
+        <v>Neitz et al. 1989</v>
+      </c>
+      <c r="G316" t="str">
+        <v/>
+      </c>
+      <c r="H316" t="str">
+        <v/>
+      </c>
+      <c r="I316" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>COL-B57-FACT-13</v>
+      </c>
+      <c r="B317" t="str">
+        <v>B57</v>
+      </c>
+      <c r="C317" t="str">
+        <v>fact</v>
+      </c>
+      <c r="D317" t="str">
+        <v>tell me something; tell me a fact; a dog fact; say something interesting; tell me more (rotate at random)</v>
+      </c>
+      <c r="E317" t="str">
+        <v>We can smell a teaspoon of sugar in two olympic pools</v>
+      </c>
+      <c r="F317" t="str">
+        <v/>
+      </c>
+      <c r="G317" t="str">
+        <v/>
+      </c>
+      <c r="H317" t="str">
+        <v/>
+      </c>
+      <c r="I317" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>COL-B57-FACT-14</v>
+      </c>
+      <c r="B318" t="str">
+        <v>B57</v>
+      </c>
+      <c r="C318" t="str">
+        <v>fact</v>
+      </c>
+      <c r="D318" t="str">
+        <v>tell me something; tell me a fact; a dog fact; say something interesting; tell me more (rotate at random)</v>
+      </c>
+      <c r="E318" t="str">
+        <v>Border Collies are usually rated the cleverest breed</v>
+      </c>
+      <c r="F318" t="str">
+        <v>Coren 1994, The Intelligence of Dogs</v>
+      </c>
+      <c r="G318" t="str">
+        <v/>
+      </c>
+      <c r="H318" t="str">
+        <v/>
+      </c>
+      <c r="I318" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>COL-B57-FACT-15</v>
+      </c>
+      <c r="B319" t="str">
+        <v>B57</v>
+      </c>
+      <c r="C319" t="str">
+        <v>fact</v>
+      </c>
+      <c r="D319" t="str">
+        <v>tell me something; tell me a fact; a dog fact; say something interesting; tell me more (rotate at random)</v>
+      </c>
+      <c r="E319" t="str">
+        <v>We understand about as many words as a two year old</v>
+      </c>
+      <c r="F319" t="str">
+        <v>Coren 2009</v>
+      </c>
+      <c r="G319" t="str">
+        <v/>
+      </c>
+      <c r="H319" t="str">
+        <v/>
+      </c>
+      <c r="I319" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>COL-B57-FACT-16</v>
+      </c>
+      <c r="B320" t="str">
+        <v>B57</v>
+      </c>
+      <c r="C320" t="str">
+        <v>fact</v>
+      </c>
+      <c r="D320" t="str">
+        <v>tell me something; tell me a fact; a dog fact; say something interesting; tell me more (rotate at random)</v>
+      </c>
+      <c r="E320" t="str">
+        <v>We yawn when you yawn. It spreads</v>
+      </c>
+      <c r="F320" t="str">
+        <v>Romero et al. 2013</v>
+      </c>
+      <c r="G320" t="str">
+        <v/>
+      </c>
+      <c r="H320" t="str">
+        <v/>
+      </c>
+      <c r="I320" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>COL-B57-FACT-17</v>
+      </c>
+      <c r="B321" t="str">
+        <v>B57</v>
+      </c>
+      <c r="C321" t="str">
+        <v>fact</v>
+      </c>
+      <c r="D321" t="str">
+        <v>tell me something; tell me a fact; a dog fact; say something interesting; tell me more (rotate at random)</v>
+      </c>
+      <c r="E321" t="str">
+        <v>Our whiskers feel air moving, not just touching</v>
+      </c>
+      <c r="F321" t="str">
+        <v>Merck Veterinary Manual</v>
+      </c>
+      <c r="G321" t="str">
+        <v/>
+      </c>
+      <c r="H321" t="str">
+        <v/>
+      </c>
+      <c r="I321" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>COL-B57-FACT-18</v>
+      </c>
+      <c r="B322" t="str">
+        <v>B57</v>
+      </c>
+      <c r="C322" t="str">
+        <v>fact</v>
+      </c>
+      <c r="D322" t="str">
+        <v>tell me something; tell me a fact; a dog fact; say something interesting; tell me more (rotate at random)</v>
+      </c>
+      <c r="E322" t="str">
+        <v>We can find your smell on a track a week old</v>
+      </c>
+      <c r="F322" t="str">
+        <v>Jezierski et al. 2014</v>
+      </c>
+      <c r="G322" t="str">
+        <v/>
+      </c>
+      <c r="H322" t="str">
+        <v/>
+      </c>
+      <c r="I322" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>COL-B57-FACT-19</v>
+      </c>
+      <c r="B323" t="str">
+        <v>B57</v>
+      </c>
+      <c r="C323" t="str">
+        <v>fact</v>
+      </c>
+      <c r="D323" t="str">
+        <v>tell me something; tell me a fact; a dog fact; say something interesting; tell me more (rotate at random)</v>
+      </c>
+      <c r="E323" t="str">
+        <v>Some of us are trained to smell illness before a test can</v>
+      </c>
+      <c r="F323" t="str">
+        <v>Pirrone &amp; Albertini 2017</v>
+      </c>
+      <c r="G323" t="str">
+        <v/>
+      </c>
+      <c r="H323" t="str">
+        <v/>
+      </c>
+      <c r="I323" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>COL-B57-FACT-20</v>
+      </c>
+      <c r="B324" t="str">
+        <v>B57</v>
+      </c>
+      <c r="C324" t="str">
+        <v>fact</v>
+      </c>
+      <c r="D324" t="str">
+        <v>tell me something; tell me a fact; a dog fact; say something interesting; tell me more (rotate at random)</v>
+      </c>
+      <c r="E324" t="str">
+        <v>Puppies are born deaf and blind. We catch up fast</v>
+      </c>
+      <c r="F324" t="str">
+        <v>Merck Veterinary Manual</v>
+      </c>
+      <c r="G324" t="str">
+        <v/>
+      </c>
+      <c r="H324" t="str">
+        <v/>
+      </c>
+      <c r="I324" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I290"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I324"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -9455,7 +9455,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I324"/>
+  <dimension ref="A1:I333"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -18824,16 +18824,277 @@
         <v>Approved</v>
       </c>
     </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>COL-B58-SAFE-01</v>
+      </c>
+      <c r="B325" t="str">
+        <v>B58</v>
+      </c>
+      <c r="C325" t="str">
+        <v>safe</v>
+      </c>
+      <c r="D325" t="str">
+        <v>is it safe; is this safe; is this game safe; is the game safe for kids; are the cards safe; is it safe for children; safety</v>
+      </c>
+      <c r="E325" t="str">
+        <v>The cards are made in the UK from recycled paper. Fully biodegradable, no plastic.</v>
+      </c>
+      <c r="F325" t="str">
+        <v/>
+      </c>
+      <c r="G325" t="str">
+        <v/>
+      </c>
+      <c r="H325" t="str">
+        <v/>
+      </c>
+      <c r="I325" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>COL-B58-SAFE-02</v>
+      </c>
+      <c r="B326" t="str">
+        <v>B58</v>
+      </c>
+      <c r="C326" t="str">
+        <v>safe</v>
+      </c>
+      <c r="D326" t="str">
+        <v>third safety question in a row -&gt; hand to a human</v>
+      </c>
+      <c r="E326" t="str">
+        <v>That needs a person, not a dog. Email hello@Pedigree-Chums.co.uk and someone will look at it.</v>
+      </c>
+      <c r="F326" t="str">
+        <v/>
+      </c>
+      <c r="G326" t="str">
+        <v/>
+      </c>
+      <c r="H326" t="str">
+        <v/>
+      </c>
+      <c r="I326" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>COL-B59-FRIENDS-01</v>
+      </c>
+      <c r="B327" t="str">
+        <v>B59</v>
+      </c>
+      <c r="C327" t="str">
+        <v>friends</v>
+      </c>
+      <c r="D327" t="str">
+        <v>do you have friends; do you have a best friend; do you have dog friends; who are your friends; any friends; have you got friends</v>
+      </c>
+      <c r="E327" t="str">
+        <v>Three of them. A labrador, a border terrier and a boxer.</v>
+      </c>
+      <c r="F327" t="str">
+        <v/>
+      </c>
+      <c r="G327" t="str">
+        <v/>
+      </c>
+      <c r="H327" t="str">
+        <v/>
+      </c>
+      <c r="I327" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>COL-B59-FRIENDS-02</v>
+      </c>
+      <c r="B328" t="str">
+        <v>B59</v>
+      </c>
+      <c r="C328" t="str">
+        <v>friends</v>
+      </c>
+      <c r="D328" t="str">
+        <v>different dog friends; other dog friends; friends that are dogs; tell me about your friends; no friends that are dogs</v>
+      </c>
+      <c r="E328" t="str">
+        <v>They are here too. Say their name and you will get them instead of me.</v>
+      </c>
+      <c r="F328" t="str">
+        <v/>
+      </c>
+      <c r="G328" t="str">
+        <v/>
+      </c>
+      <c r="H328" t="str">
+        <v/>
+      </c>
+      <c r="I328" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>COL-B60-PEDIGREE-01</v>
+      </c>
+      <c r="B329" t="str">
+        <v>B60</v>
+      </c>
+      <c r="C329" t="str">
+        <v>pedigree</v>
+      </c>
+      <c r="D329" t="str">
+        <v>what is a pedigree; whats a pedigree; what does pedigree mean; what are pedigree dogs; pedigree; what is a pedigree dog</v>
+      </c>
+      <c r="E329" t="str">
+        <v>It means your family is written down. Mine goes back to the working collies of the borders.</v>
+      </c>
+      <c r="F329" t="str">
+        <v/>
+      </c>
+      <c r="G329" t="str">
+        <v/>
+      </c>
+      <c r="H329" t="str">
+        <v/>
+      </c>
+      <c r="I329" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>COL-B61-NAV-01</v>
+      </c>
+      <c r="B330" t="str">
+        <v>B61</v>
+      </c>
+      <c r="C330" t="str">
+        <v>nav</v>
+      </c>
+      <c r="D330" t="str">
+        <v>where is the homepage; take me home; go home; the homepage; find the homepage; wheres the homepage</v>
+      </c>
+      <c r="E330" t="str">
+        <v>Here</v>
+      </c>
+      <c r="F330" t="str">
+        <v/>
+      </c>
+      <c r="G330" t="str">
+        <v>DST014</v>
+      </c>
+      <c r="H330" t="str">
+        <v/>
+      </c>
+      <c r="I330" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>COL-B61-NAV-02</v>
+      </c>
+      <c r="B331" t="str">
+        <v>B61</v>
+      </c>
+      <c r="C331" t="str">
+        <v>nav</v>
+      </c>
+      <c r="D331" t="str">
+        <v>tell me my options; what can i do; what are my options; what else can i do; my options</v>
+      </c>
+      <c r="E331" t="str">
+        <v>play, learn, buy, explore</v>
+      </c>
+      <c r="F331" t="str">
+        <v/>
+      </c>
+      <c r="G331" t="str">
+        <v/>
+      </c>
+      <c r="H331" t="str">
+        <v/>
+      </c>
+      <c r="I331" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>COL-B62-MADE-01</v>
+      </c>
+      <c r="B332" t="str">
+        <v>B62</v>
+      </c>
+      <c r="C332" t="str">
+        <v>made</v>
+      </c>
+      <c r="D332" t="str">
+        <v>who made you; who built you; who created you; who wrote you; who owns you; who designed you</v>
+      </c>
+      <c r="E332" t="str">
+        <v>A human</v>
+      </c>
+      <c r="F332" t="str">
+        <v/>
+      </c>
+      <c r="G332" t="str">
+        <v/>
+      </c>
+      <c r="H332" t="str">
+        <v/>
+      </c>
+      <c r="I332" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>COL-B63-WORST-01</v>
+      </c>
+      <c r="B333" t="str">
+        <v>B63</v>
+      </c>
+      <c r="C333" t="str">
+        <v>worst</v>
+      </c>
+      <c r="D333" t="str">
+        <v>worst dog; whats the worst dog; worst dog ever; worst breed; whats the worst breed</v>
+      </c>
+      <c r="E333" t="str">
+        <v>Worst dog I know is Bull's-eye</v>
+      </c>
+      <c r="F333" t="str">
+        <v/>
+      </c>
+      <c r="G333" t="str">
+        <v>DST015</v>
+      </c>
+      <c r="H333" t="str">
+        <v/>
+      </c>
+      <c r="I333" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I324"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I333"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -19291,6 +19552,70 @@
       </c>
       <c r="J17" t="str">
         <v>[URL to be supplied]</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>DST014</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Home</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Discover</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Open exact interactive page</v>
+      </c>
+      <c r="E18" t="str">
+        <v>The Pedigree Chums home page</v>
+      </c>
+      <c r="F18" t="str">
+        <v>homepage; home; start</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Any</v>
+      </c>
+      <c r="H18" t="str">
+        <v>High</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Collie</v>
+      </c>
+      <c r="J18" t="str">
+        <v>/home</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>DST015</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Bull's-eye</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Discover</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Open exact interactive page</v>
+      </c>
+      <c r="E19" t="str">
+        <v>The Bull's-eye essay in Good Dog, Bad Dog</v>
+      </c>
+      <c r="F19" t="str">
+        <v>worst dog; bad dog; bullseye</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Any</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Collie</v>
+      </c>
+      <c r="J19" t="str">
+        <v>/good-dog-bad-dog/bulls-eye</v>
       </c>
     </row>
   </sheetData>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -9455,7 +9455,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I333"/>
+  <dimension ref="A1:I362"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -19085,9 +19085,850 @@
         <v>Approved</v>
       </c>
     </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>COL-B47-SPOT-01</v>
+      </c>
+      <c r="B334" t="str">
+        <v>B47</v>
+      </c>
+      <c r="C334" t="str">
+        <v>spotting</v>
+      </c>
+      <c r="D334" t="str">
+        <v>i saw a labrador today; saw a lab; we saw one; there was a dog; i saw one; i spotted one</v>
+      </c>
+      <c r="E334" t="str">
+        <v>:)</v>
+      </c>
+      <c r="F334" t="str">
+        <v/>
+      </c>
+      <c r="G334" t="str">
+        <v/>
+      </c>
+      <c r="H334" t="str">
+        <v/>
+      </c>
+      <c r="I334" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>COL-B47-SPOT-02</v>
+      </c>
+      <c r="B335" t="str">
+        <v>B47</v>
+      </c>
+      <c r="C335" t="str">
+        <v>spotting</v>
+      </c>
+      <c r="D335" t="str">
+        <v>does a crossbreed count; do crossbreeds count; is a crossbreed ok; does a mongrel count</v>
+      </c>
+      <c r="E335" t="str">
+        <v>Count towards what?</v>
+      </c>
+      <c r="F335" t="str">
+        <v/>
+      </c>
+      <c r="G335" t="str">
+        <v/>
+      </c>
+      <c r="H335" t="str">
+        <v/>
+      </c>
+      <c r="I335" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>COL-B47-SPOT-03</v>
+      </c>
+      <c r="B336" t="str">
+        <v>B47</v>
+      </c>
+      <c r="C336" t="str">
+        <v>spotting</v>
+      </c>
+      <c r="D336" t="str">
+        <v>i cannot find any; cant find any; there are no dogs; i havent seen one; no dogs here</v>
+      </c>
+      <c r="E336" t="str">
+        <v>Dogs?</v>
+      </c>
+      <c r="F336" t="str">
+        <v/>
+      </c>
+      <c r="G336" t="str">
+        <v/>
+      </c>
+      <c r="H336" t="str">
+        <v/>
+      </c>
+      <c r="I336" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>COL-B47-SPOT-04</v>
+      </c>
+      <c r="B337" t="str">
+        <v>B47</v>
+      </c>
+      <c r="C337" t="str">
+        <v>spotting</v>
+      </c>
+      <c r="D337" t="str">
+        <v>how do i know which one it is; how do i tell; which one is it; how do i identify it</v>
+      </c>
+      <c r="E337" t="str">
+        <v>Use the card, it has stuff on to help you identify</v>
+      </c>
+      <c r="F337" t="str">
+        <v/>
+      </c>
+      <c r="G337" t="str">
+        <v/>
+      </c>
+      <c r="H337" t="str">
+        <v/>
+      </c>
+      <c r="I337" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>COL-B48-ATTR-01</v>
+      </c>
+      <c r="B338" t="str">
+        <v>B48</v>
+      </c>
+      <c r="C338" t="str">
+        <v>attributes</v>
+      </c>
+      <c r="D338" t="str">
+        <v>are they good with kids; are they good with children; are they friendly</v>
+      </c>
+      <c r="E338" t="str">
+        <v>Is what?</v>
+      </c>
+      <c r="F338" t="str">
+        <v/>
+      </c>
+      <c r="G338" t="str">
+        <v/>
+      </c>
+      <c r="H338" t="str">
+        <v/>
+      </c>
+      <c r="I338" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>COL-B48-ATTR-02</v>
+      </c>
+      <c r="B339" t="str">
+        <v>B48</v>
+      </c>
+      <c r="C339" t="str">
+        <v>attributes</v>
+      </c>
+      <c r="D339" t="str">
+        <v>how long do they live; how long do they last; whats their lifespan</v>
+      </c>
+      <c r="E339" t="str">
+        <v>Is what?</v>
+      </c>
+      <c r="F339" t="str">
+        <v/>
+      </c>
+      <c r="G339" t="str">
+        <v/>
+      </c>
+      <c r="H339" t="str">
+        <v/>
+      </c>
+      <c r="I339" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>COL-B48-ATTR-03</v>
+      </c>
+      <c r="B340" t="str">
+        <v>B48</v>
+      </c>
+      <c r="C340" t="str">
+        <v>attributes</v>
+      </c>
+      <c r="D340" t="str">
+        <v>how big do they get; how big are they; what size are they</v>
+      </c>
+      <c r="E340" t="str">
+        <v>Big what get?</v>
+      </c>
+      <c r="F340" t="str">
+        <v/>
+      </c>
+      <c r="G340" t="str">
+        <v/>
+      </c>
+      <c r="H340" t="str">
+        <v/>
+      </c>
+      <c r="I340" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>COL-B49-CARD-01</v>
+      </c>
+      <c r="B341" t="str">
+        <v>B49</v>
+      </c>
+      <c r="C341" t="str">
+        <v>cards</v>
+      </c>
+      <c r="D341" t="str">
+        <v>i lost a card; ive lost a card; my card is missing; i cant find my card</v>
+      </c>
+      <c r="E341" t="str">
+        <v>make sure you check everyone's pockets</v>
+      </c>
+      <c r="F341" t="str">
+        <v/>
+      </c>
+      <c r="G341" t="str">
+        <v/>
+      </c>
+      <c r="H341" t="str">
+        <v/>
+      </c>
+      <c r="I341" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>COL-B49-CARD-02</v>
+      </c>
+      <c r="B342" t="str">
+        <v>B49</v>
+      </c>
+      <c r="C342" t="str">
+        <v>cards</v>
+      </c>
+      <c r="D342" t="str">
+        <v>can i get more cards; can i buy more cards; i want more cards</v>
+      </c>
+      <c r="E342" t="str">
+        <v>Packs are sold whole</v>
+      </c>
+      <c r="F342" t="str">
+        <v/>
+      </c>
+      <c r="G342" t="str">
+        <v/>
+      </c>
+      <c r="H342" t="str">
+        <v/>
+      </c>
+      <c r="I342" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>COL-B49-CARD-03</v>
+      </c>
+      <c r="B343" t="str">
+        <v>B49</v>
+      </c>
+      <c r="C343" t="str">
+        <v>cards</v>
+      </c>
+      <c r="D343" t="str">
+        <v>can i swap cards with my friend; can we swap; can i trade cards</v>
+      </c>
+      <c r="E343" t="str">
+        <v>Each pack contains 54 unique dogs</v>
+      </c>
+      <c r="F343" t="str">
+        <v/>
+      </c>
+      <c r="G343" t="str">
+        <v/>
+      </c>
+      <c r="H343" t="str">
+        <v/>
+      </c>
+      <c r="I343" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>COL-B50-CARE-01</v>
+      </c>
+      <c r="B344" t="str">
+        <v>B50</v>
+      </c>
+      <c r="C344" t="str">
+        <v>care</v>
+      </c>
+      <c r="D344" t="str">
+        <v>what should i feed my dog; what do i feed him; what do dogs eat</v>
+      </c>
+      <c r="E344" t="str">
+        <v>Not the cards</v>
+      </c>
+      <c r="F344" t="str">
+        <v/>
+      </c>
+      <c r="G344" t="str">
+        <v/>
+      </c>
+      <c r="H344" t="str">
+        <v/>
+      </c>
+      <c r="I344" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>COL-B50-CARE-02</v>
+      </c>
+      <c r="B345" t="str">
+        <v>B50</v>
+      </c>
+      <c r="C345" t="str">
+        <v>care</v>
+      </c>
+      <c r="D345" t="str">
+        <v>how often should i walk them; how much walking; how often do i walk him</v>
+      </c>
+      <c r="E345" t="str">
+        <v>Depends what breed</v>
+      </c>
+      <c r="F345" t="str">
+        <v/>
+      </c>
+      <c r="G345" t="str">
+        <v/>
+      </c>
+      <c r="H345" t="str">
+        <v/>
+      </c>
+      <c r="I345" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>COL-B51-SUP-01</v>
+      </c>
+      <c r="B346" t="str">
+        <v>B51</v>
+      </c>
+      <c r="C346" t="str">
+        <v>superlative</v>
+      </c>
+      <c r="D346" t="str">
+        <v>biggest dog; whats the biggest dog; largest dog</v>
+      </c>
+      <c r="E346" t="str">
+        <v>The Irish Wolfhound</v>
+      </c>
+      <c r="F346" t="str">
+        <v/>
+      </c>
+      <c r="G346" t="str">
+        <v>DST006</v>
+      </c>
+      <c r="H346" t="str">
+        <v/>
+      </c>
+      <c r="I346" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>COL-B51-SUP-02</v>
+      </c>
+      <c r="B347" t="str">
+        <v>B51</v>
+      </c>
+      <c r="C347" t="str">
+        <v>superlative</v>
+      </c>
+      <c r="D347" t="str">
+        <v>fastest dog; whats the fastest dog; quickest dog</v>
+      </c>
+      <c r="E347" t="str">
+        <v>The Greyhound</v>
+      </c>
+      <c r="F347" t="str">
+        <v/>
+      </c>
+      <c r="G347" t="str">
+        <v>DST006</v>
+      </c>
+      <c r="H347" t="str">
+        <v/>
+      </c>
+      <c r="I347" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>COL-B51-SUP-03</v>
+      </c>
+      <c r="B348" t="str">
+        <v>B51</v>
+      </c>
+      <c r="C348" t="str">
+        <v>superlative</v>
+      </c>
+      <c r="D348" t="str">
+        <v>smallest dog; whats the smallest dog; tiniest dog</v>
+      </c>
+      <c r="E348" t="str">
+        <v>The Maltese</v>
+      </c>
+      <c r="F348" t="str">
+        <v/>
+      </c>
+      <c r="G348" t="str">
+        <v>DST006</v>
+      </c>
+      <c r="H348" t="str">
+        <v/>
+      </c>
+      <c r="I348" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>COL-B52-MISC-01</v>
+      </c>
+      <c r="B349" t="str">
+        <v>B52</v>
+      </c>
+      <c r="C349" t="str">
+        <v>misc</v>
+      </c>
+      <c r="D349" t="str">
+        <v>why are there so many; why so many breeds; how are there so many</v>
+      </c>
+      <c r="E349" t="str">
+        <v>Our history is dog rich</v>
+      </c>
+      <c r="F349" t="str">
+        <v/>
+      </c>
+      <c r="G349" t="str">
+        <v>DST007</v>
+      </c>
+      <c r="H349" t="str">
+        <v/>
+      </c>
+      <c r="I349" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>COL-B52-MISC-02</v>
+      </c>
+      <c r="B350" t="str">
+        <v>B52</v>
+      </c>
+      <c r="C350" t="str">
+        <v>misc</v>
+      </c>
+      <c r="D350" t="str">
+        <v>which is better a lab or a beagle; which is better; whats better</v>
+      </c>
+      <c r="E350" t="str">
+        <v>Depends</v>
+      </c>
+      <c r="F350" t="str">
+        <v/>
+      </c>
+      <c r="G350" t="str">
+        <v/>
+      </c>
+      <c r="H350" t="str">
+        <v/>
+      </c>
+      <c r="I350" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>COL-B52-MISC-03</v>
+      </c>
+      <c r="B351" t="str">
+        <v>B52</v>
+      </c>
+      <c r="C351" t="str">
+        <v>misc</v>
+      </c>
+      <c r="D351" t="str">
+        <v>do you think dogs will ever be able to speak; will dogs talk; can dogs talk</v>
+      </c>
+      <c r="E351" t="str">
+        <v>We need to learn to sing first</v>
+      </c>
+      <c r="F351" t="str">
+        <v/>
+      </c>
+      <c r="G351" t="str">
+        <v/>
+      </c>
+      <c r="H351" t="str">
+        <v/>
+      </c>
+      <c r="I351" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>COL-B52-MISC-04</v>
+      </c>
+      <c r="B352" t="str">
+        <v>B52</v>
+      </c>
+      <c r="C352" t="str">
+        <v>misc</v>
+      </c>
+      <c r="D352" t="str">
+        <v>what about small dogs; small dogs; little dogs</v>
+      </c>
+      <c r="E352" t="str">
+        <v>Dogs?</v>
+      </c>
+      <c r="F352" t="str">
+        <v/>
+      </c>
+      <c r="G352" t="str">
+        <v/>
+      </c>
+      <c r="H352" t="str">
+        <v/>
+      </c>
+      <c r="I352" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>COL-B52-MISC-05</v>
+      </c>
+      <c r="B353" t="str">
+        <v>B52</v>
+      </c>
+      <c r="C353" t="str">
+        <v>misc</v>
+      </c>
+      <c r="D353" t="str">
+        <v>ok show me a few; show me some; show me a few</v>
+      </c>
+      <c r="E353" t="str">
+        <v>Dogs?</v>
+      </c>
+      <c r="F353" t="str">
+        <v/>
+      </c>
+      <c r="G353" t="str">
+        <v/>
+      </c>
+      <c r="H353" t="str">
+        <v/>
+      </c>
+      <c r="I353" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>COL-B52-MISC-06</v>
+      </c>
+      <c r="B354" t="str">
+        <v>B52</v>
+      </c>
+      <c r="C354" t="str">
+        <v>misc</v>
+      </c>
+      <c r="D354" t="str">
+        <v>i need facts for a project; homework; school project; i need facts</v>
+      </c>
+      <c r="E354" t="str">
+        <v>Dogs?</v>
+      </c>
+      <c r="F354" t="str">
+        <v/>
+      </c>
+      <c r="G354" t="str">
+        <v/>
+      </c>
+      <c r="H354" t="str">
+        <v/>
+      </c>
+      <c r="I354" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>COL-B52-MISC-07</v>
+      </c>
+      <c r="B355" t="str">
+        <v>B52</v>
+      </c>
+      <c r="C355" t="str">
+        <v>misc</v>
+      </c>
+      <c r="D355" t="str">
+        <v>how many have i got; how many do i have; whats my score</v>
+      </c>
+      <c r="E355" t="str">
+        <v>Dogs?</v>
+      </c>
+      <c r="F355" t="str">
+        <v/>
+      </c>
+      <c r="G355" t="str">
+        <v/>
+      </c>
+      <c r="H355" t="str">
+        <v/>
+      </c>
+      <c r="I355" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>COL-B52-MISC-08</v>
+      </c>
+      <c r="B356" t="str">
+        <v>B52</v>
+      </c>
+      <c r="C356" t="str">
+        <v>misc</v>
+      </c>
+      <c r="D356" t="str">
+        <v>what do you think of cows; cows</v>
+      </c>
+      <c r="E356" t="str">
+        <v>Not much</v>
+      </c>
+      <c r="F356" t="str">
+        <v/>
+      </c>
+      <c r="G356" t="str">
+        <v/>
+      </c>
+      <c r="H356" t="str">
+        <v/>
+      </c>
+      <c r="I356" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>COL-B52-MISC-09</v>
+      </c>
+      <c r="B357" t="str">
+        <v>B52</v>
+      </c>
+      <c r="C357" t="str">
+        <v>misc</v>
+      </c>
+      <c r="D357" t="str">
+        <v>can you lick your balls; ball licking; do you lick yourself; tennis balls; balls; lick your balls; do you lick your balls</v>
+      </c>
+      <c r="E357" t="str">
+        <v>Tennis balls?</v>
+      </c>
+      <c r="F357" t="str">
+        <v/>
+      </c>
+      <c r="G357" t="str">
+        <v/>
+      </c>
+      <c r="H357" t="str">
+        <v/>
+      </c>
+      <c r="I357" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>COL-B52-MISC-10</v>
+      </c>
+      <c r="B358" t="str">
+        <v>B52</v>
+      </c>
+      <c r="C358" t="str">
+        <v>misc</v>
+      </c>
+      <c r="D358" t="str">
+        <v>how many players; how many people can play; how many can play</v>
+      </c>
+      <c r="E358" t="str">
+        <v>More than 1</v>
+      </c>
+      <c r="F358" t="str">
+        <v/>
+      </c>
+      <c r="G358" t="str">
+        <v/>
+      </c>
+      <c r="H358" t="str">
+        <v/>
+      </c>
+      <c r="I358" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>COL-B52-MISC-11</v>
+      </c>
+      <c r="B359" t="str">
+        <v>B52</v>
+      </c>
+      <c r="C359" t="str">
+        <v>misc</v>
+      </c>
+      <c r="D359" t="str">
+        <v>talk me through the page; theres lots of stats; explain the page</v>
+      </c>
+      <c r="E359" t="str">
+        <v>Im a dog</v>
+      </c>
+      <c r="F359" t="str">
+        <v/>
+      </c>
+      <c r="G359" t="str">
+        <v/>
+      </c>
+      <c r="H359" t="str">
+        <v/>
+      </c>
+      <c r="I359" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>COL-B52-MISC-12</v>
+      </c>
+      <c r="B360" t="str">
+        <v>B52</v>
+      </c>
+      <c r="C360" t="str">
+        <v>misc</v>
+      </c>
+      <c r="D360" t="str">
+        <v>how can i tell if a girl has a crush on me; does she like me; crush</v>
+      </c>
+      <c r="E360" t="str">
+        <v>Im a dog</v>
+      </c>
+      <c r="F360" t="str">
+        <v/>
+      </c>
+      <c r="G360" t="str">
+        <v/>
+      </c>
+      <c r="H360" t="str">
+        <v/>
+      </c>
+      <c r="I360" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>COL-B53-SELF-01</v>
+      </c>
+      <c r="B361" t="str">
+        <v>B53</v>
+      </c>
+      <c r="C361" t="str">
+        <v>selfname</v>
+      </c>
+      <c r="D361" t="str">
+        <v>which is the most popular; whats the most popular dog; most popular breed</v>
+      </c>
+      <c r="E361" t="str">
+        <v>border collie</v>
+      </c>
+      <c r="F361" t="str">
+        <v/>
+      </c>
+      <c r="G361" t="str">
+        <v/>
+      </c>
+      <c r="H361" t="str">
+        <v/>
+      </c>
+      <c r="I361" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>COL-B64-CAR-01</v>
+      </c>
+      <c r="B362" t="str">
+        <v>B64</v>
+      </c>
+      <c r="C362" t="str">
+        <v>car</v>
+      </c>
+      <c r="D362" t="str">
+        <v>do you like going in the car; do you like the car; do you like car rides; like going in the car</v>
+      </c>
+      <c r="E362" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F362" t="str">
+        <v/>
+      </c>
+      <c r="G362" t="str">
+        <v/>
+      </c>
+      <c r="H362" t="str">
+        <v/>
+      </c>
+      <c r="I362" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I333"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I362"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -9848,7 +9848,7 @@
         <v>how do I play; rules</v>
       </c>
       <c r="E14" t="str">
-        <v>{{approved_rule_summary}} Simple enough for humans, active enough for dogs. The full rules are here.</v>
+        <v>{{approved_rule_summary}} Simple enough for humans, active enough for dogs.</v>
       </c>
       <c r="F14" t="str">
         <v>Rules library</v>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -6677,7 +6677,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -6928,7 +6928,7 @@
         <v>self</v>
       </c>
       <c r="D11" t="str">
-        <v>what do you like to eat; whats your favourite food</v>
+        <v>what do you like to eat</v>
       </c>
       <c r="E11" t="str">
         <v>human food is my fav!!!</v>
@@ -7291,6 +7291,64 @@
         <v/>
       </c>
       <c r="I23" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>LAB-B32-11</v>
+      </c>
+      <c r="B24" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C24" t="str">
+        <v>self</v>
+      </c>
+      <c r="D24" t="str">
+        <v>whats your favourite food; whats your favorite food; favourite food; favorite food; whats your fav food; food; what food; i like food; do you like food</v>
+      </c>
+      <c r="E24" t="str">
+        <v>hotdogs</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>LAB-B32-12</v>
+      </c>
+      <c r="B25" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C25" t="str">
+        <v>self</v>
+      </c>
+      <c r="D25" t="str">
+        <v>sausages; sausage; hotdog; hotdogs; hot dog; hot dogs; i like sausages; i love sausages; you mean sausages; those are sausages; do you mean sausages; i said sausages; thats a sausage</v>
+      </c>
+      <c r="E25" t="str">
+        <v>hotdogs</v>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v>DST016</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -19935,7 +19993,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -20457,6 +20515,38 @@
       </c>
       <c r="J19" t="str">
         <v>/good-dog-bad-dog/bulls-eye</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>DST016</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Hot Dogs</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Utility</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Open the Hot Dogs page</v>
+      </c>
+      <c r="E20" t="str">
+        <v>The Hot Dogs game-mode page: sausages, hotdogs, and dogs who are too hot</v>
+      </c>
+      <c r="F20" t="str">
+        <v>hot dogs; hotdogs; sausages</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Any</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Labrador</v>
+      </c>
+      <c r="J20" t="str">
+        <v>/hot-dogs</v>
       </c>
     </row>
   </sheetData>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -7871,7 +7871,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -8282,6 +8282,93 @@
         <v/>
       </c>
       <c r="I16" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>BOX-B09-01</v>
+      </c>
+      <c r="B17" t="str">
+        <v>B09</v>
+      </c>
+      <c r="C17" t="str">
+        <v>greeting</v>
+      </c>
+      <c r="D17" t="str">
+        <v>hello; hey; hello there</v>
+      </c>
+      <c r="E17" t="str">
+        <v>hiya</v>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>BOX-B09-02</v>
+      </c>
+      <c r="B18" t="str">
+        <v>B09</v>
+      </c>
+      <c r="C18" t="str">
+        <v>greeting</v>
+      </c>
+      <c r="D18" t="str">
+        <v>hi</v>
+      </c>
+      <c r="E18" t="str">
+        <v>hihi</v>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>BOX-B20-01</v>
+      </c>
+      <c r="B19" t="str">
+        <v>B20</v>
+      </c>
+      <c r="C19" t="str">
+        <v>goodbye</v>
+      </c>
+      <c r="D19" t="str">
+        <v>goodbye; bye; see you; see ya</v>
+      </c>
+      <c r="E19" t="str">
+        <v>see ya</v>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
         <v>Approved</v>
       </c>
     </row>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -5117,7 +5117,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5506,6 +5506,46 @@
         <v>Use on deliberately exaggerated claims, not safety information.</v>
       </c>
       <c r="F22" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>CP019</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Boxer goodbye</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Standard</v>
+      </c>
+      <c r="D23" t="str">
+        <v>see ya</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Per-dog goodbye line, served by the goodbye action.</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>CP020</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Labrador goodbye</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Standard</v>
+      </c>
+      <c r="D24" t="str">
+        <v>byeeeee</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Per-dog goodbye line, served by the goodbye action.</v>
+      </c>
+      <c r="F24" t="str">
         <v>Active</v>
       </c>
     </row>
@@ -7871,7 +7911,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -8345,19 +8385,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>BOX-B20-01</v>
+        <v>BOX-B30-08</v>
       </c>
       <c r="B19" t="str">
-        <v>B20</v>
+        <v>B30</v>
       </c>
       <c r="C19" t="str">
-        <v>goodbye</v>
+        <v>joke</v>
       </c>
       <c r="D19" t="str">
-        <v>goodbye; bye; see you; see ya</v>
+        <v>knock knock; knock knock knock</v>
       </c>
       <c r="E19" t="str">
-        <v>see ya</v>
+        <v>whos there?</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -8369,6 +8409,35 @@
         <v/>
       </c>
       <c r="I19" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>BOX-B30-09</v>
+      </c>
+      <c r="B20" t="str">
+        <v>B30</v>
+      </c>
+      <c r="C20" t="str">
+        <v>joke</v>
+      </c>
+      <c r="D20" t="str">
+        <v>ANY input after whos there (served by the knock-knock sequence)</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Bow wow!</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
         <v>Approved</v>
       </c>
     </row>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -7911,7 +7911,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -8438,6 +8438,35 @@
         <v/>
       </c>
       <c r="I20" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>BOX-B24-02</v>
+      </c>
+      <c r="B21" t="str">
+        <v>B24</v>
+      </c>
+      <c r="C21" t="str">
+        <v>rude</v>
+      </c>
+      <c r="D21" t="str">
+        <v>ANY third stop (served by the stop sequence)</v>
+      </c>
+      <c r="E21" t="str">
+        <v>ok</v>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -20149,7 +20178,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -20703,6 +20732,38 @@
       </c>
       <c r="J20" t="str">
         <v>/hot-dogs</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>DST017</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Anubis</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Utility</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Open the Anubis essay</v>
+      </c>
+      <c r="E21" t="str">
+        <v>The Anubis essay in Good Dog, Bad Dog (dogs as gods)</v>
+      </c>
+      <c r="F21" t="str">
+        <v>anubis; egypt; jackal</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Any</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Collie</v>
+      </c>
+      <c r="J21" t="str">
+        <v>/good-dog-bad-dog/anubis</v>
       </c>
     </row>
   </sheetData>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -9698,7 +9698,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I362"/>
+  <dimension ref="A1:I399"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -20166,6 +20166,1079 @@
         <v/>
       </c>
       <c r="I362" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>B65-TREATTRAIL-BALL-1</v>
+      </c>
+      <c r="B363" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C363" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D363" t="str">
+        <v/>
+      </c>
+      <c r="E363" t="str">
+        <v>its round!!!</v>
+      </c>
+      <c r="F363" t="str">
+        <v/>
+      </c>
+      <c r="G363" t="str">
+        <v/>
+      </c>
+      <c r="H363" t="str">
+        <v/>
+      </c>
+      <c r="I363" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>B65-TREATTRAIL-BALL-2</v>
+      </c>
+      <c r="B364" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C364" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D364" t="str">
+        <v/>
+      </c>
+      <c r="E364" t="str">
+        <v>it bounces a lot and i chase it</v>
+      </c>
+      <c r="F364" t="str">
+        <v/>
+      </c>
+      <c r="G364" t="str">
+        <v/>
+      </c>
+      <c r="H364" t="str">
+        <v/>
+      </c>
+      <c r="I364" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>B65-TREATTRAIL-BALL-3</v>
+      </c>
+      <c r="B365" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C365" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D365" t="str">
+        <v/>
+      </c>
+      <c r="E365" t="str">
+        <v>you throw it and i bring it back. tennis one is best</v>
+      </c>
+      <c r="F365" t="str">
+        <v/>
+      </c>
+      <c r="G365" t="str">
+        <v/>
+      </c>
+      <c r="H365" t="str">
+        <v/>
+      </c>
+      <c r="I365" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>B65-TREATTRAIL-BONE-1</v>
+      </c>
+      <c r="B366" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C366" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D366" t="str">
+        <v/>
+      </c>
+      <c r="E366" t="str">
+        <v>i buried one and forgot where</v>
+      </c>
+      <c r="F366" t="str">
+        <v/>
+      </c>
+      <c r="G366" t="str">
+        <v/>
+      </c>
+      <c r="H366" t="str">
+        <v/>
+      </c>
+      <c r="I366" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>B65-TREATTRAIL-BONE-2</v>
+      </c>
+      <c r="B367" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C367" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D367" t="str">
+        <v/>
+      </c>
+      <c r="E367" t="str">
+        <v>you chew on it and it lasts ages</v>
+      </c>
+      <c r="F367" t="str">
+        <v/>
+      </c>
+      <c r="G367" t="str">
+        <v/>
+      </c>
+      <c r="H367" t="str">
+        <v/>
+      </c>
+      <c r="I367" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>B65-TREATTRAIL-BONE-3</v>
+      </c>
+      <c r="B368" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C368" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D368" t="str">
+        <v/>
+      </c>
+      <c r="E368" t="str">
+        <v>dogs love them. its the classic one</v>
+      </c>
+      <c r="F368" t="str">
+        <v/>
+      </c>
+      <c r="G368" t="str">
+        <v/>
+      </c>
+      <c r="H368" t="str">
+        <v/>
+      </c>
+      <c r="I368" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>B65-TREATTRAIL-STICK-1</v>
+      </c>
+      <c r="B369" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C369" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D369" t="str">
+        <v/>
+      </c>
+      <c r="E369" t="str">
+        <v>it comes off a tree</v>
+      </c>
+      <c r="F369" t="str">
+        <v/>
+      </c>
+      <c r="G369" t="str">
+        <v/>
+      </c>
+      <c r="H369" t="str">
+        <v/>
+      </c>
+      <c r="I369" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>B65-TREATTRAIL-STICK-2</v>
+      </c>
+      <c r="B370" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C370" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D370" t="str">
+        <v/>
+      </c>
+      <c r="E370" t="str">
+        <v>i carry it on walks, although humans are not meant to encourage this behaviour</v>
+      </c>
+      <c r="F370" t="str">
+        <v/>
+      </c>
+      <c r="G370" t="str">
+        <v/>
+      </c>
+      <c r="H370" t="str">
+        <v/>
+      </c>
+      <c r="I370" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>B65-TREATTRAIL-STICK-3</v>
+      </c>
+      <c r="B371" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C371" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D371" t="str">
+        <v/>
+      </c>
+      <c r="E371" t="str">
+        <v>free ones everywhere in the park</v>
+      </c>
+      <c r="F371" t="str">
+        <v/>
+      </c>
+      <c r="G371" t="str">
+        <v/>
+      </c>
+      <c r="H371" t="str">
+        <v/>
+      </c>
+      <c r="I371" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>B65-TREATTRAIL-LEAD-1</v>
+      </c>
+      <c r="B372" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C372" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D372" t="str">
+        <v/>
+      </c>
+      <c r="E372" t="str">
+        <v>it means we are going OUT!!!</v>
+      </c>
+      <c r="F372" t="str">
+        <v/>
+      </c>
+      <c r="G372" t="str">
+        <v/>
+      </c>
+      <c r="H372" t="str">
+        <v/>
+      </c>
+      <c r="I372" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>B65-TREATTRAIL-LEAD-2</v>
+      </c>
+      <c r="B373" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C373" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D373" t="str">
+        <v/>
+      </c>
+      <c r="E373" t="str">
+        <v>it clips on my collar</v>
+      </c>
+      <c r="F373" t="str">
+        <v/>
+      </c>
+      <c r="G373" t="str">
+        <v/>
+      </c>
+      <c r="H373" t="str">
+        <v/>
+      </c>
+      <c r="I373" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>B65-TREATTRAIL-LEAD-3</v>
+      </c>
+      <c r="B374" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C374" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D374" t="str">
+        <v/>
+      </c>
+      <c r="E374" t="str">
+        <v>you hold one end and i pull the other</v>
+      </c>
+      <c r="F374" t="str">
+        <v/>
+      </c>
+      <c r="G374" t="str">
+        <v/>
+      </c>
+      <c r="H374" t="str">
+        <v/>
+      </c>
+      <c r="I374" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>B65-TREATTRAIL-BOWL-1</v>
+      </c>
+      <c r="B375" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C375" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D375" t="str">
+        <v/>
+      </c>
+      <c r="E375" t="str">
+        <v>mine is empty. always empty</v>
+      </c>
+      <c r="F375" t="str">
+        <v/>
+      </c>
+      <c r="G375" t="str">
+        <v/>
+      </c>
+      <c r="H375" t="str">
+        <v/>
+      </c>
+      <c r="I375" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>B65-TREATTRAIL-BOWL-2</v>
+      </c>
+      <c r="B376" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C376" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D376" t="str">
+        <v/>
+      </c>
+      <c r="E376" t="str">
+        <v>i look at it a lot</v>
+      </c>
+      <c r="F376" t="str">
+        <v/>
+      </c>
+      <c r="G376" t="str">
+        <v/>
+      </c>
+      <c r="H376" t="str">
+        <v/>
+      </c>
+      <c r="I376" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>B65-TREATTRAIL-BOWL-3</v>
+      </c>
+      <c r="B377" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C377" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D377" t="str">
+        <v/>
+      </c>
+      <c r="E377" t="str">
+        <v>it is where the food goes</v>
+      </c>
+      <c r="F377" t="str">
+        <v/>
+      </c>
+      <c r="G377" t="str">
+        <v/>
+      </c>
+      <c r="H377" t="str">
+        <v/>
+      </c>
+      <c r="I377" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>B65-TREATTRAIL-BISCUIT-1</v>
+      </c>
+      <c r="B378" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C378" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D378" t="str">
+        <v/>
+      </c>
+      <c r="E378" t="str">
+        <v>I get one for being good</v>
+      </c>
+      <c r="F378" t="str">
+        <v/>
+      </c>
+      <c r="G378" t="str">
+        <v/>
+      </c>
+      <c r="H378" t="str">
+        <v/>
+      </c>
+      <c r="I378" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>B65-TREATTRAIL-BISCUIT-2</v>
+      </c>
+      <c r="B379" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C379" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D379" t="str">
+        <v/>
+      </c>
+      <c r="E379" t="str">
+        <v>shaped like a bone but you eat it</v>
+      </c>
+      <c r="F379" t="str">
+        <v/>
+      </c>
+      <c r="G379" t="str">
+        <v/>
+      </c>
+      <c r="H379" t="str">
+        <v/>
+      </c>
+      <c r="I379" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>B65-TREATTRAIL-BISCUIT-3</v>
+      </c>
+      <c r="B380" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C380" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D380" t="str">
+        <v/>
+      </c>
+      <c r="E380" t="str">
+        <v>Smells like fish and ham</v>
+      </c>
+      <c r="F380" t="str">
+        <v/>
+      </c>
+      <c r="G380" t="str">
+        <v/>
+      </c>
+      <c r="H380" t="str">
+        <v/>
+      </c>
+      <c r="I380" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>B65-TREATTRAIL-SOCK-1</v>
+      </c>
+      <c r="B381" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C381" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D381" t="str">
+        <v/>
+      </c>
+      <c r="E381" t="str">
+        <v>im not allowed it</v>
+      </c>
+      <c r="F381" t="str">
+        <v/>
+      </c>
+      <c r="G381" t="str">
+        <v/>
+      </c>
+      <c r="H381" t="str">
+        <v/>
+      </c>
+      <c r="I381" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>B65-TREATTRAIL-SOCK-2</v>
+      </c>
+      <c r="B382" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C382" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D382" t="str">
+        <v/>
+      </c>
+      <c r="E382" t="str">
+        <v>it smells like a human foot</v>
+      </c>
+      <c r="F382" t="str">
+        <v/>
+      </c>
+      <c r="G382" t="str">
+        <v/>
+      </c>
+      <c r="H382" t="str">
+        <v/>
+      </c>
+      <c r="I382" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>B65-TREATTRAIL-SOCK-3</v>
+      </c>
+      <c r="B383" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C383" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D383" t="str">
+        <v/>
+      </c>
+      <c r="E383" t="str">
+        <v>there is always one missing from the pair</v>
+      </c>
+      <c r="F383" t="str">
+        <v/>
+      </c>
+      <c r="G383" t="str">
+        <v/>
+      </c>
+      <c r="H383" t="str">
+        <v/>
+      </c>
+      <c r="I383" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>B65-TREATTRAIL-SLIPPER-1</v>
+      </c>
+      <c r="B384" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C384" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D384" t="str">
+        <v/>
+      </c>
+      <c r="E384" t="str">
+        <v>Sometimes lives on human feet</v>
+      </c>
+      <c r="F384" t="str">
+        <v/>
+      </c>
+      <c r="G384" t="str">
+        <v/>
+      </c>
+      <c r="H384" t="str">
+        <v/>
+      </c>
+      <c r="I384" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>B65-TREATTRAIL-SLIPPER-2</v>
+      </c>
+      <c r="B385" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C385" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D385" t="str">
+        <v/>
+      </c>
+      <c r="E385" t="str">
+        <v>humans put their feet in it indoors</v>
+      </c>
+      <c r="F385" t="str">
+        <v/>
+      </c>
+      <c r="G385" t="str">
+        <v/>
+      </c>
+      <c r="H385" t="str">
+        <v/>
+      </c>
+      <c r="I385" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>B65-TREATTRAIL-SLIPPER-3</v>
+      </c>
+      <c r="B386" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C386" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D386" t="str">
+        <v/>
+      </c>
+      <c r="E386" t="str">
+        <v>i chewed one once. big trouble</v>
+      </c>
+      <c r="F386" t="str">
+        <v/>
+      </c>
+      <c r="G386" t="str">
+        <v/>
+      </c>
+      <c r="H386" t="str">
+        <v/>
+      </c>
+      <c r="I386" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>B65-TREATTRAIL-POSTMAN-1</v>
+      </c>
+      <c r="B387" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C387" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D387" t="str">
+        <v/>
+      </c>
+      <c r="E387" t="str">
+        <v>Arrives like clockwork every day</v>
+      </c>
+      <c r="F387" t="str">
+        <v/>
+      </c>
+      <c r="G387" t="str">
+        <v/>
+      </c>
+      <c r="H387" t="str">
+        <v/>
+      </c>
+      <c r="I387" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>B65-TREATTRAIL-POSTMAN-2</v>
+      </c>
+      <c r="B388" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C388" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D388" t="str">
+        <v/>
+      </c>
+      <c r="E388" t="str">
+        <v>i bark and get square presents through a small gap</v>
+      </c>
+      <c r="F388" t="str">
+        <v/>
+      </c>
+      <c r="G388" t="str">
+        <v/>
+      </c>
+      <c r="H388" t="str">
+        <v/>
+      </c>
+      <c r="I388" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>B65-TREATTRAIL-POSTMAN-3</v>
+      </c>
+      <c r="B389" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C389" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D389" t="str">
+        <v/>
+      </c>
+      <c r="E389" t="str">
+        <v>I like to make a big noise when the paper squares drop</v>
+      </c>
+      <c r="F389" t="str">
+        <v/>
+      </c>
+      <c r="G389" t="str">
+        <v/>
+      </c>
+      <c r="H389" t="str">
+        <v/>
+      </c>
+      <c r="I389" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>B65-TREATTRAIL-SAUSAGE-1</v>
+      </c>
+      <c r="B390" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C390" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D390" t="str">
+        <v/>
+      </c>
+      <c r="E390" t="str">
+        <v>my FAVOURITE!!!</v>
+      </c>
+      <c r="F390" t="str">
+        <v/>
+      </c>
+      <c r="G390" t="str">
+        <v/>
+      </c>
+      <c r="H390" t="str">
+        <v/>
+      </c>
+      <c r="I390" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>B65-TREATTRAIL-SAUSAGE-2</v>
+      </c>
+      <c r="B391" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C391" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D391" t="str">
+        <v/>
+      </c>
+      <c r="E391" t="str">
+        <v>same as a hotdog</v>
+      </c>
+      <c r="F391" t="str">
+        <v/>
+      </c>
+      <c r="G391" t="str">
+        <v/>
+      </c>
+      <c r="H391" t="str">
+        <v/>
+      </c>
+      <c r="I391" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>B65-TREATTRAIL-SAUSAGE-3</v>
+      </c>
+      <c r="B392" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C392" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D392" t="str">
+        <v/>
+      </c>
+      <c r="E392" t="str">
+        <v>long and pink and the best thing there is</v>
+      </c>
+      <c r="F392" t="str">
+        <v/>
+      </c>
+      <c r="G392" t="str">
+        <v/>
+      </c>
+      <c r="H392" t="str">
+        <v/>
+      </c>
+      <c r="I392" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>B65-TREATTRAIL-START</v>
+      </c>
+      <c r="B393" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C393" t="str">
+        <v>reaction</v>
+      </c>
+      <c r="D393" t="str">
+        <v/>
+      </c>
+      <c r="E393" t="str">
+        <v>Treat Trail!!! im thinking of a thing. guess what it is!</v>
+      </c>
+      <c r="F393" t="str">
+        <v/>
+      </c>
+      <c r="G393" t="str">
+        <v/>
+      </c>
+      <c r="H393" t="str">
+        <v/>
+      </c>
+      <c r="I393" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>B65-TREATTRAIL-RIGHT</v>
+      </c>
+      <c r="B394" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C394" t="str">
+        <v>reaction</v>
+      </c>
+      <c r="D394" t="str">
+        <v/>
+      </c>
+      <c r="E394" t="str">
+        <v>YES!! you got it!!</v>
+      </c>
+      <c r="F394" t="str">
+        <v/>
+      </c>
+      <c r="G394" t="str">
+        <v/>
+      </c>
+      <c r="H394" t="str">
+        <v/>
+      </c>
+      <c r="I394" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>B65-TREATTRAIL-CLUE2</v>
+      </c>
+      <c r="B395" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C395" t="str">
+        <v>reaction</v>
+      </c>
+      <c r="D395" t="str">
+        <v/>
+      </c>
+      <c r="E395" t="str">
+        <v>not that one! heres another clue</v>
+      </c>
+      <c r="F395" t="str">
+        <v/>
+      </c>
+      <c r="G395" t="str">
+        <v/>
+      </c>
+      <c r="H395" t="str">
+        <v/>
+      </c>
+      <c r="I395" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>B65-TREATTRAIL-CLUE3</v>
+      </c>
+      <c r="B396" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C396" t="str">
+        <v>reaction</v>
+      </c>
+      <c r="D396" t="str">
+        <v/>
+      </c>
+      <c r="E396" t="str">
+        <v>nearly!! ok, big clue coming</v>
+      </c>
+      <c r="F396" t="str">
+        <v/>
+      </c>
+      <c r="G396" t="str">
+        <v/>
+      </c>
+      <c r="H396" t="str">
+        <v/>
+      </c>
+      <c r="I396" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>B65-TREATTRAIL-MOVEON</v>
+      </c>
+      <c r="B397" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C397" t="str">
+        <v>reaction</v>
+      </c>
+      <c r="D397" t="str">
+        <v/>
+      </c>
+      <c r="E397" t="str">
+        <v>it was {{ANSWER}}!! next thing</v>
+      </c>
+      <c r="F397" t="str">
+        <v/>
+      </c>
+      <c r="G397" t="str">
+        <v/>
+      </c>
+      <c r="H397" t="str">
+        <v/>
+      </c>
+      <c r="I397" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>B65-TREATTRAIL-EXIT</v>
+      </c>
+      <c r="B398" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C398" t="str">
+        <v>reaction</v>
+      </c>
+      <c r="D398" t="str">
+        <v/>
+      </c>
+      <c r="E398" t="str">
+        <v>ok! im off to find a snack. come back and play again!!</v>
+      </c>
+      <c r="F398" t="str">
+        <v/>
+      </c>
+      <c r="G398" t="str">
+        <v/>
+      </c>
+      <c r="H398" t="str">
+        <v/>
+      </c>
+      <c r="I398" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>B65-TREATTRAIL-END</v>
+      </c>
+      <c r="B399" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C399" t="str">
+        <v>reaction</v>
+      </c>
+      <c r="D399" t="str">
+        <v/>
+      </c>
+      <c r="E399" t="str">
+        <v>SAUSAGES!!! thats hotdogs, same thing obviously. go and look at them!</v>
+      </c>
+      <c r="F399" t="str">
+        <v/>
+      </c>
+      <c r="G399" t="str">
+        <v/>
+      </c>
+      <c r="H399" t="str">
+        <v/>
+      </c>
+      <c r="I399" t="str">
         <v>Approved</v>
       </c>
     </row>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -9698,7 +9698,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I399"/>
+  <dimension ref="A1:I427"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -21239,6 +21239,818 @@
         <v/>
       </c>
       <c r="I399" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>B66-MISSINGBISCUIT-OPENING</v>
+      </c>
+      <c r="B400" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C400" t="str">
+        <v>line</v>
+      </c>
+      <c r="D400" t="str">
+        <v/>
+      </c>
+      <c r="E400" t="str">
+        <v>a biscuit is missing. three suspects. ask me for a clue</v>
+      </c>
+      <c r="F400" t="str">
+        <v/>
+      </c>
+      <c r="G400" t="str">
+        <v/>
+      </c>
+      <c r="H400" t="str">
+        <v/>
+      </c>
+      <c r="I400" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>B66-MISSINGBISCUIT-CLUE</v>
+      </c>
+      <c r="B401" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C401" t="str">
+        <v>line</v>
+      </c>
+      <c r="D401" t="str">
+        <v/>
+      </c>
+      <c r="E401" t="str">
+        <v>right. heres one</v>
+      </c>
+      <c r="F401" t="str">
+        <v/>
+      </c>
+      <c r="G401" t="str">
+        <v/>
+      </c>
+      <c r="H401" t="str">
+        <v/>
+      </c>
+      <c r="I401" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>B66-MISSINGBISCUIT-CORRECT</v>
+      </c>
+      <c r="B402" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C402" t="str">
+        <v>line</v>
+      </c>
+      <c r="D402" t="str">
+        <v/>
+      </c>
+      <c r="E402" t="str">
+        <v>aye. thats the one</v>
+      </c>
+      <c r="F402" t="str">
+        <v/>
+      </c>
+      <c r="G402" t="str">
+        <v/>
+      </c>
+      <c r="H402" t="str">
+        <v/>
+      </c>
+      <c r="I402" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>B66-MISSINGBISCUIT-WRONG</v>
+      </c>
+      <c r="B403" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C403" t="str">
+        <v>line</v>
+      </c>
+      <c r="D403" t="str">
+        <v/>
+      </c>
+      <c r="E403" t="str">
+        <v>why would it be them?</v>
+      </c>
+      <c r="F403" t="str">
+        <v/>
+      </c>
+      <c r="G403" t="str">
+        <v/>
+      </c>
+      <c r="H403" t="str">
+        <v/>
+      </c>
+      <c r="I403" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>B66-MISSINGBISCUIT-WRONG2</v>
+      </c>
+      <c r="B404" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C404" t="str">
+        <v>line</v>
+      </c>
+      <c r="D404" t="str">
+        <v/>
+      </c>
+      <c r="E404" t="str">
+        <v>no. think again</v>
+      </c>
+      <c r="F404" t="str">
+        <v/>
+      </c>
+      <c r="G404" t="str">
+        <v/>
+      </c>
+      <c r="H404" t="str">
+        <v/>
+      </c>
+      <c r="I404" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>B66-MISSINGBISCUIT-OUTOFCLUES</v>
+      </c>
+      <c r="B405" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C405" t="str">
+        <v>line</v>
+      </c>
+      <c r="D405" t="str">
+        <v/>
+      </c>
+      <c r="E405" t="str">
+        <v>thats all i have. name someone</v>
+      </c>
+      <c r="F405" t="str">
+        <v/>
+      </c>
+      <c r="G405" t="str">
+        <v/>
+      </c>
+      <c r="H405" t="str">
+        <v/>
+      </c>
+      <c r="I405" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>B66-MISSINGBISCUIT-REVEAL</v>
+      </c>
+      <c r="B406" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C406" t="str">
+        <v>line</v>
+      </c>
+      <c r="D406" t="str">
+        <v/>
+      </c>
+      <c r="E406" t="str">
+        <v>it was {{ANSWER}}. obvious really</v>
+      </c>
+      <c r="F406" t="str">
+        <v/>
+      </c>
+      <c r="G406" t="str">
+        <v/>
+      </c>
+      <c r="H406" t="str">
+        <v/>
+      </c>
+      <c r="I406" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>B66-MISSINGBISCUIT-ANOTHER</v>
+      </c>
+      <c r="B407" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C407" t="str">
+        <v>line</v>
+      </c>
+      <c r="D407" t="str">
+        <v/>
+      </c>
+      <c r="E407" t="str">
+        <v>another one?</v>
+      </c>
+      <c r="F407" t="str">
+        <v/>
+      </c>
+      <c r="G407" t="str">
+        <v/>
+      </c>
+      <c r="H407" t="str">
+        <v/>
+      </c>
+      <c r="I407" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>B66-MISSINGBISCUIT-EXIT</v>
+      </c>
+      <c r="B408" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C408" t="str">
+        <v>line</v>
+      </c>
+      <c r="D408" t="str">
+        <v/>
+      </c>
+      <c r="E408" t="str">
+        <v>ok</v>
+      </c>
+      <c r="F408" t="str">
+        <v/>
+      </c>
+      <c r="G408" t="str">
+        <v/>
+      </c>
+      <c r="H408" t="str">
+        <v/>
+      </c>
+      <c r="I408" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>B66-MISSINGBISCUIT-CASE2-TITLE</v>
+      </c>
+      <c r="B409" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C409" t="str">
+        <v>title</v>
+      </c>
+      <c r="D409" t="str">
+        <v/>
+      </c>
+      <c r="E409" t="str">
+        <v>The Muddy Pawprints</v>
+      </c>
+      <c r="F409" t="str">
+        <v/>
+      </c>
+      <c r="G409" t="str">
+        <v/>
+      </c>
+      <c r="H409" t="str">
+        <v/>
+      </c>
+      <c r="I409" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>B66-MISSINGBISCUIT-CASE3-TITLE</v>
+      </c>
+      <c r="B410" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C410" t="str">
+        <v>title</v>
+      </c>
+      <c r="D410" t="str">
+        <v/>
+      </c>
+      <c r="E410" t="str">
+        <v>The Chewed Slipper</v>
+      </c>
+      <c r="F410" t="str">
+        <v/>
+      </c>
+      <c r="G410" t="str">
+        <v/>
+      </c>
+      <c r="H410" t="str">
+        <v/>
+      </c>
+      <c r="I410" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>B66-MISSINGBISCUIT-CASE4-TITLE</v>
+      </c>
+      <c r="B411" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C411" t="str">
+        <v>title</v>
+      </c>
+      <c r="D411" t="str">
+        <v/>
+      </c>
+      <c r="E411" t="str">
+        <v>The Open Gate</v>
+      </c>
+      <c r="F411" t="str">
+        <v/>
+      </c>
+      <c r="G411" t="str">
+        <v/>
+      </c>
+      <c r="H411" t="str">
+        <v/>
+      </c>
+      <c r="I411" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>B66-MISSINGBISCUIT-CASE5-TITLE</v>
+      </c>
+      <c r="B412" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C412" t="str">
+        <v>title</v>
+      </c>
+      <c r="D412" t="str">
+        <v/>
+      </c>
+      <c r="E412" t="str">
+        <v>The Empty Bowl</v>
+      </c>
+      <c r="F412" t="str">
+        <v/>
+      </c>
+      <c r="G412" t="str">
+        <v/>
+      </c>
+      <c r="H412" t="str">
+        <v/>
+      </c>
+      <c r="I412" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>B66-MISSINGBISCUIT-C1-1</v>
+      </c>
+      <c r="B413" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C413" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D413" t="str">
+        <v/>
+      </c>
+      <c r="E413" t="str">
+        <v>it was on the high shelf. someone climbed</v>
+      </c>
+      <c r="F413" t="str">
+        <v/>
+      </c>
+      <c r="G413" t="str">
+        <v/>
+      </c>
+      <c r="H413" t="str">
+        <v/>
+      </c>
+      <c r="I413" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>B66-MISSINGBISCUIT-C1-2</v>
+      </c>
+      <c r="B414" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C414" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D414" t="str">
+        <v/>
+      </c>
+      <c r="E414" t="str">
+        <v>grandad was asleep in his chair. i watched him the whole time</v>
+      </c>
+      <c r="F414" t="str">
+        <v/>
+      </c>
+      <c r="G414" t="str">
+        <v/>
+      </c>
+      <c r="H414" t="str">
+        <v/>
+      </c>
+      <c r="I414" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>B66-MISSINGBISCUIT-C1-3</v>
+      </c>
+      <c r="B415" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C415" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D415" t="str">
+        <v/>
+      </c>
+      <c r="E415" t="str">
+        <v>the puppy cannot jump higher than the sofa</v>
+      </c>
+      <c r="F415" t="str">
+        <v/>
+      </c>
+      <c r="G415" t="str">
+        <v/>
+      </c>
+      <c r="H415" t="str">
+        <v/>
+      </c>
+      <c r="I415" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>B66-MISSINGBISCUIT-C2-1</v>
+      </c>
+      <c r="B416" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C416" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D416" t="str">
+        <v/>
+      </c>
+      <c r="E416" t="str">
+        <v>the prints are big</v>
+      </c>
+      <c r="F416" t="str">
+        <v/>
+      </c>
+      <c r="G416" t="str">
+        <v/>
+      </c>
+      <c r="H416" t="str">
+        <v/>
+      </c>
+      <c r="I416" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>B66-MISSINGBISCUIT-C2-2</v>
+      </c>
+      <c r="B417" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C417" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D417" t="str">
+        <v/>
+      </c>
+      <c r="E417" t="str">
+        <v>the collie was out with sheep all afternoon. clean feet</v>
+      </c>
+      <c r="F417" t="str">
+        <v/>
+      </c>
+      <c r="G417" t="str">
+        <v/>
+      </c>
+      <c r="H417" t="str">
+        <v/>
+      </c>
+      <c r="I417" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>B66-MISSINGBISCUIT-C2-3</v>
+      </c>
+      <c r="B418" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C418" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D418" t="str">
+        <v/>
+      </c>
+      <c r="E418" t="str">
+        <v>the boxer was indoors telling jokes. i heard every one</v>
+      </c>
+      <c r="F418" t="str">
+        <v/>
+      </c>
+      <c r="G418" t="str">
+        <v/>
+      </c>
+      <c r="H418" t="str">
+        <v/>
+      </c>
+      <c r="I418" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>B66-MISSINGBISCUIT-C3-1</v>
+      </c>
+      <c r="B419" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C419" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D419" t="str">
+        <v/>
+      </c>
+      <c r="E419" t="str">
+        <v>the tooth marks are small and sharp</v>
+      </c>
+      <c r="F419" t="str">
+        <v/>
+      </c>
+      <c r="G419" t="str">
+        <v/>
+      </c>
+      <c r="H419" t="str">
+        <v/>
+      </c>
+      <c r="I419" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>B66-MISSINGBISCUIT-C3-2</v>
+      </c>
+      <c r="B420" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C420" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D420" t="str">
+        <v/>
+      </c>
+      <c r="E420" t="str">
+        <v>the postman never comes inside</v>
+      </c>
+      <c r="F420" t="str">
+        <v/>
+      </c>
+      <c r="G420" t="str">
+        <v/>
+      </c>
+      <c r="H420" t="str">
+        <v/>
+      </c>
+      <c r="I420" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>B66-MISSINGBISCUIT-C3-3</v>
+      </c>
+      <c r="B421" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C421" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D421" t="str">
+        <v/>
+      </c>
+      <c r="E421" t="str">
+        <v>the baby has no teeth yet</v>
+      </c>
+      <c r="F421" t="str">
+        <v/>
+      </c>
+      <c r="G421" t="str">
+        <v/>
+      </c>
+      <c r="H421" t="str">
+        <v/>
+      </c>
+      <c r="I421" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>B66-MISSINGBISCUIT-C4-1</v>
+      </c>
+      <c r="B422" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C422" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D422" t="str">
+        <v/>
+      </c>
+      <c r="E422" t="str">
+        <v>the latch was lifted. wind does not lift latches</v>
+      </c>
+      <c r="F422" t="str">
+        <v/>
+      </c>
+      <c r="G422" t="str">
+        <v/>
+      </c>
+      <c r="H422" t="str">
+        <v/>
+      </c>
+      <c r="I422" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v>B66-MISSINGBISCUIT-C4-2</v>
+      </c>
+      <c r="B423" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C423" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D423" t="str">
+        <v/>
+      </c>
+      <c r="E423" t="str">
+        <v>the postman came at nine. the gate was shut at ten</v>
+      </c>
+      <c r="F423" t="str">
+        <v/>
+      </c>
+      <c r="G423" t="str">
+        <v/>
+      </c>
+      <c r="H423" t="str">
+        <v/>
+      </c>
+      <c r="I423" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>B66-MISSINGBISCUIT-C4-3</v>
+      </c>
+      <c r="B424" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C424" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D424" t="str">
+        <v/>
+      </c>
+      <c r="E424" t="str">
+        <v>someone left a ball in our garden</v>
+      </c>
+      <c r="F424" t="str">
+        <v/>
+      </c>
+      <c r="G424" t="str">
+        <v/>
+      </c>
+      <c r="H424" t="str">
+        <v/>
+      </c>
+      <c r="I424" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v>B66-MISSINGBISCUIT-C5-1</v>
+      </c>
+      <c r="B425" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C425" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D425" t="str">
+        <v/>
+      </c>
+      <c r="E425" t="str">
+        <v>the bowl was licked completely clean</v>
+      </c>
+      <c r="F425" t="str">
+        <v/>
+      </c>
+      <c r="G425" t="str">
+        <v/>
+      </c>
+      <c r="H425" t="str">
+        <v/>
+      </c>
+      <c r="I425" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="str">
+        <v>B66-MISSINGBISCUIT-C5-2</v>
+      </c>
+      <c r="B426" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C426" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D426" t="str">
+        <v/>
+      </c>
+      <c r="E426" t="str">
+        <v>the cat only eats fish. this was chicken</v>
+      </c>
+      <c r="F426" t="str">
+        <v/>
+      </c>
+      <c r="G426" t="str">
+        <v/>
+      </c>
+      <c r="H426" t="str">
+        <v/>
+      </c>
+      <c r="I426" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="str">
+        <v>B66-MISSINGBISCUIT-C5-3</v>
+      </c>
+      <c r="B427" t="str">
+        <v>B66</v>
+      </c>
+      <c r="C427" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D427" t="str">
+        <v/>
+      </c>
+      <c r="E427" t="str">
+        <v>i was with you the whole time. why are you asking me</v>
+      </c>
+      <c r="F427" t="str">
+        <v/>
+      </c>
+      <c r="G427" t="str">
+        <v/>
+      </c>
+      <c r="H427" t="str">
+        <v/>
+      </c>
+      <c r="I427" t="str">
         <v>Approved</v>
       </c>
     </row>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -9698,7 +9698,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I427"/>
+  <dimension ref="A1:I445"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -22051,6 +22051,528 @@
         <v/>
       </c>
       <c r="I427" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="str">
+        <v>B67-FEEDCOOKIE-OPENING</v>
+      </c>
+      <c r="B428" t="str">
+        <v>B67</v>
+      </c>
+      <c r="C428" t="str">
+        <v>reaction</v>
+      </c>
+      <c r="D428" t="str">
+        <v/>
+      </c>
+      <c r="E428" t="str">
+        <v>COOKIES?!! yes yes gimme. tap one and ill eat it!!</v>
+      </c>
+      <c r="F428" t="str">
+        <v/>
+      </c>
+      <c r="G428" t="str">
+        <v/>
+      </c>
+      <c r="H428" t="str">
+        <v/>
+      </c>
+      <c r="I428" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v>B67-FEEDCOOKIE-BLUE</v>
+      </c>
+      <c r="B429" t="str">
+        <v>B67</v>
+      </c>
+      <c r="C429" t="str">
+        <v>reaction</v>
+      </c>
+      <c r="D429" t="str">
+        <v/>
+      </c>
+      <c r="E429" t="str">
+        <v>NOM!! good one.</v>
+      </c>
+      <c r="F429" t="str">
+        <v/>
+      </c>
+      <c r="G429" t="str">
+        <v/>
+      </c>
+      <c r="H429" t="str">
+        <v/>
+      </c>
+      <c r="I429" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="str">
+        <v>B67-FEEDCOOKIE-RED</v>
+      </c>
+      <c r="B430" t="str">
+        <v>B67</v>
+      </c>
+      <c r="C430" t="str">
+        <v>reaction</v>
+      </c>
+      <c r="D430" t="str">
+        <v/>
+      </c>
+      <c r="E430" t="str">
+        <v>NOM!! ...wait. that one didnt taste right.</v>
+      </c>
+      <c r="F430" t="str">
+        <v/>
+      </c>
+      <c r="G430" t="str">
+        <v/>
+      </c>
+      <c r="H430" t="str">
+        <v/>
+      </c>
+      <c r="I430" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v>B67-FEEDCOOKIE-DONE</v>
+      </c>
+      <c r="B431" t="str">
+        <v>B67</v>
+      </c>
+      <c r="C431" t="str">
+        <v>reaction</v>
+      </c>
+      <c r="D431" t="str">
+        <v/>
+      </c>
+      <c r="E431" t="str">
+        <v>all gone!! that was a GOOD bowl!!</v>
+      </c>
+      <c r="F431" t="str">
+        <v/>
+      </c>
+      <c r="G431" t="str">
+        <v/>
+      </c>
+      <c r="H431" t="str">
+        <v/>
+      </c>
+      <c r="I431" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>B67-FEEDCOOKIE-NUDGE</v>
+      </c>
+      <c r="B432" t="str">
+        <v>B67</v>
+      </c>
+      <c r="C432" t="str">
+        <v>reaction</v>
+      </c>
+      <c r="D432" t="str">
+        <v/>
+      </c>
+      <c r="E432" t="str">
+        <v>tap one!! im waiting!!</v>
+      </c>
+      <c r="F432" t="str">
+        <v/>
+      </c>
+      <c r="G432" t="str">
+        <v/>
+      </c>
+      <c r="H432" t="str">
+        <v/>
+      </c>
+      <c r="I432" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>B67-FEEDCOOKIE-EXIT</v>
+      </c>
+      <c r="B433" t="str">
+        <v>B67</v>
+      </c>
+      <c r="C433" t="str">
+        <v>reaction</v>
+      </c>
+      <c r="D433" t="str">
+        <v/>
+      </c>
+      <c r="E433" t="str">
+        <v>ok!! im stuffed. come back and feed me again!!</v>
+      </c>
+      <c r="F433" t="str">
+        <v/>
+      </c>
+      <c r="G433" t="str">
+        <v/>
+      </c>
+      <c r="H433" t="str">
+        <v/>
+      </c>
+      <c r="I433" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>B67-FEEDCOOKIE-PREF</v>
+      </c>
+      <c r="B434" t="str">
+        <v>B67</v>
+      </c>
+      <c r="C434" t="str">
+        <v>lesson</v>
+      </c>
+      <c r="D434" t="str">
+        <v/>
+      </c>
+      <c r="E434" t="str">
+        <v>remembers what you picked so it doesnt ask you again</v>
+      </c>
+      <c r="F434" t="str">
+        <v/>
+      </c>
+      <c r="G434" t="str">
+        <v/>
+      </c>
+      <c r="H434" t="str">
+        <v/>
+      </c>
+      <c r="I434" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>B67-FEEDCOOKIE-ANALYTICS</v>
+      </c>
+      <c r="B435" t="str">
+        <v>B67</v>
+      </c>
+      <c r="C435" t="str">
+        <v>lesson</v>
+      </c>
+      <c r="D435" t="str">
+        <v/>
+      </c>
+      <c r="E435" t="str">
+        <v>counts visitors so they can make the site better</v>
+      </c>
+      <c r="F435" t="str">
+        <v/>
+      </c>
+      <c r="G435" t="str">
+        <v/>
+      </c>
+      <c r="H435" t="str">
+        <v/>
+      </c>
+      <c r="I435" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>B67-FEEDCOOKIE-FONTS</v>
+      </c>
+      <c r="B436" t="str">
+        <v>B67</v>
+      </c>
+      <c r="C436" t="str">
+        <v>lesson</v>
+      </c>
+      <c r="D436" t="str">
+        <v/>
+      </c>
+      <c r="E436" t="str">
+        <v>loads the letters so the words look right</v>
+      </c>
+      <c r="F436" t="str">
+        <v/>
+      </c>
+      <c r="G436" t="str">
+        <v/>
+      </c>
+      <c r="H436" t="str">
+        <v/>
+      </c>
+      <c r="I436" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>B67-FEEDCOOKIE-VIDEO</v>
+      </c>
+      <c r="B437" t="str">
+        <v>B67</v>
+      </c>
+      <c r="C437" t="str">
+        <v>lesson</v>
+      </c>
+      <c r="D437" t="str">
+        <v/>
+      </c>
+      <c r="E437" t="str">
+        <v>lets a video play and keeps your place in it</v>
+      </c>
+      <c r="F437" t="str">
+        <v/>
+      </c>
+      <c r="G437" t="str">
+        <v/>
+      </c>
+      <c r="H437" t="str">
+        <v/>
+      </c>
+      <c r="I437" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>B67-FEEDCOOKIE-SESSION</v>
+      </c>
+      <c r="B438" t="str">
+        <v>B67</v>
+      </c>
+      <c r="C438" t="str">
+        <v>lesson</v>
+      </c>
+      <c r="D438" t="str">
+        <v/>
+      </c>
+      <c r="E438" t="str">
+        <v>keeps you signed in while you look around</v>
+      </c>
+      <c r="F438" t="str">
+        <v/>
+      </c>
+      <c r="G438" t="str">
+        <v/>
+      </c>
+      <c r="H438" t="str">
+        <v/>
+      </c>
+      <c r="I438" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>B67-FEEDCOOKIE-LANGUAGE</v>
+      </c>
+      <c r="B439" t="str">
+        <v>B67</v>
+      </c>
+      <c r="C439" t="str">
+        <v>lesson</v>
+      </c>
+      <c r="D439" t="str">
+        <v/>
+      </c>
+      <c r="E439" t="str">
+        <v>remembers which language you read in</v>
+      </c>
+      <c r="F439" t="str">
+        <v/>
+      </c>
+      <c r="G439" t="str">
+        <v/>
+      </c>
+      <c r="H439" t="str">
+        <v/>
+      </c>
+      <c r="I439" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>B67-FEEDCOOKIE-SECURITY</v>
+      </c>
+      <c r="B440" t="str">
+        <v>B67</v>
+      </c>
+      <c r="C440" t="str">
+        <v>lesson</v>
+      </c>
+      <c r="D440" t="str">
+        <v/>
+      </c>
+      <c r="E440" t="str">
+        <v>checks its really you and keeps the site safe</v>
+      </c>
+      <c r="F440" t="str">
+        <v/>
+      </c>
+      <c r="G440" t="str">
+        <v/>
+      </c>
+      <c r="H440" t="str">
+        <v/>
+      </c>
+      <c r="I440" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="str">
+        <v>B67-FEEDCOOKIE-ADS</v>
+      </c>
+      <c r="B441" t="str">
+        <v>B67</v>
+      </c>
+      <c r="C441" t="str">
+        <v>lesson</v>
+      </c>
+      <c r="D441" t="str">
+        <v/>
+      </c>
+      <c r="E441" t="str">
+        <v>shows you ads for things you looked at somewhere else</v>
+      </c>
+      <c r="F441" t="str">
+        <v/>
+      </c>
+      <c r="G441" t="str">
+        <v/>
+      </c>
+      <c r="H441" t="str">
+        <v/>
+      </c>
+      <c r="I441" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="str">
+        <v>B67-FEEDCOOKIE-TRACKING</v>
+      </c>
+      <c r="B442" t="str">
+        <v>B67</v>
+      </c>
+      <c r="C442" t="str">
+        <v>lesson</v>
+      </c>
+      <c r="D442" t="str">
+        <v/>
+      </c>
+      <c r="E442" t="str">
+        <v>follows you from one site to the next</v>
+      </c>
+      <c r="F442" t="str">
+        <v/>
+      </c>
+      <c r="G442" t="str">
+        <v/>
+      </c>
+      <c r="H442" t="str">
+        <v/>
+      </c>
+      <c r="I442" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="str">
+        <v>B67-FEEDCOOKIE-SOCIAL</v>
+      </c>
+      <c r="B443" t="str">
+        <v>B67</v>
+      </c>
+      <c r="C443" t="str">
+        <v>lesson</v>
+      </c>
+      <c r="D443" t="str">
+        <v/>
+      </c>
+      <c r="E443" t="str">
+        <v>tells a social network what pages you visit</v>
+      </c>
+      <c r="F443" t="str">
+        <v/>
+      </c>
+      <c r="G443" t="str">
+        <v/>
+      </c>
+      <c r="H443" t="str">
+        <v/>
+      </c>
+      <c r="I443" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="str">
+        <v>B67-FEEDCOOKIE-RETARGET</v>
+      </c>
+      <c r="B444" t="str">
+        <v>B67</v>
+      </c>
+      <c r="C444" t="str">
+        <v>lesson</v>
+      </c>
+      <c r="D444" t="str">
+        <v/>
+      </c>
+      <c r="E444" t="str">
+        <v>chases you with the thing you nearly bought</v>
+      </c>
+      <c r="F444" t="str">
+        <v/>
+      </c>
+      <c r="G444" t="str">
+        <v/>
+      </c>
+      <c r="H444" t="str">
+        <v/>
+      </c>
+      <c r="I444" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="str">
+        <v>B67-FEEDCOOKIE-PIXEL</v>
+      </c>
+      <c r="B445" t="str">
+        <v>B67</v>
+      </c>
+      <c r="C445" t="str">
+        <v>lesson</v>
+      </c>
+      <c r="D445" t="str">
+        <v/>
+      </c>
+      <c r="E445" t="str">
+        <v>a hidden speck that reports where youve been</v>
+      </c>
+      <c r="F445" t="str">
+        <v/>
+      </c>
+      <c r="G445" t="str">
+        <v/>
+      </c>
+      <c r="H445" t="str">
+        <v/>
+      </c>
+      <c r="I445" t="str">
         <v>Approved</v>
       </c>
     </row>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -9698,7 +9698,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I445"/>
+  <dimension ref="A1:I447"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -22573,6 +22573,64 @@
         <v/>
       </c>
       <c r="I445" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="str">
+        <v>B67-FEEDCOOKIE-FULL</v>
+      </c>
+      <c r="B446" t="str">
+        <v>B67</v>
+      </c>
+      <c r="C446" t="str">
+        <v>reaction</v>
+      </c>
+      <c r="D446" t="str">
+        <v/>
+      </c>
+      <c r="E446" t="str">
+        <v>im so full. i regret nothing</v>
+      </c>
+      <c r="F446" t="str">
+        <v/>
+      </c>
+      <c r="G446" t="str">
+        <v/>
+      </c>
+      <c r="H446" t="str">
+        <v/>
+      </c>
+      <c r="I446" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="str">
+        <v>B67-FEEDCOOKIE-SLEEP</v>
+      </c>
+      <c r="B447" t="str">
+        <v>B67</v>
+      </c>
+      <c r="C447" t="str">
+        <v>reaction</v>
+      </c>
+      <c r="D447" t="str">
+        <v/>
+      </c>
+      <c r="E447" t="str">
+        <v>zzz</v>
+      </c>
+      <c r="F447" t="str">
+        <v/>
+      </c>
+      <c r="G447" t="str">
+        <v/>
+      </c>
+      <c r="H447" t="str">
+        <v/>
+      </c>
+      <c r="I447" t="str">
         <v>Approved</v>
       </c>
     </row>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -6717,6 +6717,1432 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Response ID</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Bucket ID</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Subtag</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Trigger examples / condition</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Labrador response template</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Fact source</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Default route</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Animation cue</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Status</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>LAB-B40-01</v>
+      </c>
+      <c r="B4" t="str">
+        <v>B40</v>
+      </c>
+      <c r="C4" t="str">
+        <v>nosubject</v>
+      </c>
+      <c r="D4" t="str">
+        <v>ANY unrecognised input, no candidate subject</v>
+      </c>
+      <c r="E4" t="str">
+        <v>food?</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>LAB-B14-01</v>
+      </c>
+      <c r="B5" t="str">
+        <v>B14</v>
+      </c>
+      <c r="C5" t="str">
+        <v>gibberish</v>
+      </c>
+      <c r="D5" t="str">
+        <v>keyboard mash; symbols only; unreadable</v>
+      </c>
+      <c r="E5" t="str">
+        <v>is that a food word?</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>LAB-B23-01</v>
+      </c>
+      <c r="B6" t="str">
+        <v>B23</v>
+      </c>
+      <c r="C6" t="str">
+        <v>identity</v>
+      </c>
+      <c r="D6" t="str">
+        <v>are you the labrador; are you a lab</v>
+      </c>
+      <c r="E6" t="str">
+        <v>yes!</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>LAB-B23-02</v>
+      </c>
+      <c r="B7" t="str">
+        <v>B23</v>
+      </c>
+      <c r="C7" t="str">
+        <v>identity</v>
+      </c>
+      <c r="D7" t="str">
+        <v>are you a real dog; are you real</v>
+      </c>
+      <c r="E7" t="str">
+        <v>i am a dog</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>LAB-B21-01</v>
+      </c>
+      <c r="B8" t="str">
+        <v>B21</v>
+      </c>
+      <c r="C8" t="str">
+        <v>cats</v>
+      </c>
+      <c r="D8" t="str">
+        <v>cats; cat; do you chase cats</v>
+      </c>
+      <c r="E8" t="str">
+        <v>yes!</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>LAB-B22-01</v>
+      </c>
+      <c r="B9" t="str">
+        <v>B22</v>
+      </c>
+      <c r="C9" t="str">
+        <v>tricks</v>
+      </c>
+      <c r="D9" t="str">
+        <v>sit; sit down</v>
+      </c>
+      <c r="E9" t="str">
+        <v>i am sitting</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>LAB-B22-02</v>
+      </c>
+      <c r="B10" t="str">
+        <v>B22</v>
+      </c>
+      <c r="C10" t="str">
+        <v>tricks</v>
+      </c>
+      <c r="D10" t="str">
+        <v>speak; beg</v>
+      </c>
+      <c r="E10" t="str">
+        <v>no</v>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>LAB-B32-01</v>
+      </c>
+      <c r="B11" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C11" t="str">
+        <v>self</v>
+      </c>
+      <c r="D11" t="str">
+        <v>what do you like to eat</v>
+      </c>
+      <c r="E11" t="str">
+        <v>human food is my fav!!!</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>LAB-B32-02</v>
+      </c>
+      <c r="B12" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C12" t="str">
+        <v>self</v>
+      </c>
+      <c r="D12" t="str">
+        <v>like what; what human food</v>
+      </c>
+      <c r="E12" t="str">
+        <v>hotdogs</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>LAB-B32-03</v>
+      </c>
+      <c r="B13" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C13" t="str">
+        <v>self</v>
+      </c>
+      <c r="D13" t="str">
+        <v>do you eat dog food; do you eat anything else</v>
+      </c>
+      <c r="E13" t="str">
+        <v>i eat anything even things that are not food</v>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>LAB-B32-04</v>
+      </c>
+      <c r="B14" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C14" t="str">
+        <v>self</v>
+      </c>
+      <c r="D14" t="str">
+        <v>whats your favourite dog</v>
+      </c>
+      <c r="E14" t="str">
+        <v>hotdogs</v>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>LAB-B32-05</v>
+      </c>
+      <c r="B15" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C15" t="str">
+        <v>self</v>
+      </c>
+      <c r="D15" t="str">
+        <v>do you like walks</v>
+      </c>
+      <c r="E15" t="str">
+        <v>YES!</v>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>LAB-B32-06</v>
+      </c>
+      <c r="B16" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C16" t="str">
+        <v>self</v>
+      </c>
+      <c r="D16" t="str">
+        <v>how far; how long</v>
+      </c>
+      <c r="E16" t="str">
+        <v>to the big water</v>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>LAB-B32-07</v>
+      </c>
+      <c r="B17" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C17" t="str">
+        <v>self</v>
+      </c>
+      <c r="D17" t="str">
+        <v>do you like the rain</v>
+      </c>
+      <c r="E17" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>LAB-B32-08</v>
+      </c>
+      <c r="B18" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C18" t="str">
+        <v>self</v>
+      </c>
+      <c r="D18" t="str">
+        <v>do you like baths; what about baths</v>
+      </c>
+      <c r="E18" t="str">
+        <v>no!!!!</v>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>LAB-B32-09</v>
+      </c>
+      <c r="B19" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C19" t="str">
+        <v>self</v>
+      </c>
+      <c r="D19" t="str">
+        <v>do you get told off</v>
+      </c>
+      <c r="E19" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>LAB-B32-10</v>
+      </c>
+      <c r="B20" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C20" t="str">
+        <v>self</v>
+      </c>
+      <c r="D20" t="str">
+        <v>what for; why do you get told off</v>
+      </c>
+      <c r="E20" t="str">
+        <v>im greedy</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>LAB-B33-01</v>
+      </c>
+      <c r="B21" t="str">
+        <v>B33</v>
+      </c>
+      <c r="C21" t="str">
+        <v>pack</v>
+      </c>
+      <c r="D21" t="str">
+        <v>do you know any other dogs; do you have friends</v>
+      </c>
+      <c r="E21" t="str">
+        <v>loads!</v>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>LAB-B35-01</v>
+      </c>
+      <c r="B22" t="str">
+        <v>B35</v>
+      </c>
+      <c r="C22" t="str">
+        <v>nofact</v>
+      </c>
+      <c r="D22" t="str">
+        <v>any fact he does not hold</v>
+      </c>
+      <c r="E22" t="str">
+        <v>dunno but collie knows stuff like that</v>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>LAB-B35-02</v>
+      </c>
+      <c r="B23" t="str">
+        <v>B35</v>
+      </c>
+      <c r="C23" t="str">
+        <v>nofact</v>
+      </c>
+      <c r="D23" t="str">
+        <v>black hole; anything with the word hole</v>
+      </c>
+      <c r="E23" t="str">
+        <v>i dig holes</v>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>LAB-B32-11</v>
+      </c>
+      <c r="B24" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C24" t="str">
+        <v>self</v>
+      </c>
+      <c r="D24" t="str">
+        <v>whats your favourite food; whats your favorite food; favourite food; favorite food; whats your fav food; food; what food; i like food; do you like food</v>
+      </c>
+      <c r="E24" t="str">
+        <v>hotdogs</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>LAB-B32-12</v>
+      </c>
+      <c r="B25" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C25" t="str">
+        <v>self</v>
+      </c>
+      <c r="D25" t="str">
+        <v>sausages; sausage; hotdog; hotdogs; hot dog; hot dogs; i like sausages; i love sausages; you mean sausages; those are sausages; do you mean sausages; i said sausages; thats a sausage</v>
+      </c>
+      <c r="E25" t="str">
+        <v>hotdogs</v>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v>DST016</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>LAB-B14-02</v>
+      </c>
+      <c r="B26" t="str">
+        <v>B14</v>
+      </c>
+      <c r="C26" t="str">
+        <v>gibberish</v>
+      </c>
+      <c r="D26" t="str">
+        <v>keyboard mash; symbols only; unreadable</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Did you say sausages?</v>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>LAB-B14-03</v>
+      </c>
+      <c r="B27" t="str">
+        <v>B14</v>
+      </c>
+      <c r="C27" t="str">
+        <v>gibberish</v>
+      </c>
+      <c r="D27" t="str">
+        <v>keyboard mash; symbols only; unreadable</v>
+      </c>
+      <c r="E27" t="str">
+        <v>You have Cookies?</v>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>LAB-B15-01</v>
+      </c>
+      <c r="B28" t="str">
+        <v>B15</v>
+      </c>
+      <c r="C28" t="str">
+        <v>orientation</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v>eat? walk? Play? Learn? i can show you the hotdogs page too</v>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>LAB-B17-01</v>
+      </c>
+      <c r="B29" t="str">
+        <v>B17</v>
+      </c>
+      <c r="C29" t="str">
+        <v>offering a game</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v>I have a game to play... treat trail!!</v>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I23"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Response ID</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Bucket ID</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Subtag</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Trigger examples / condition</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Terrier response template</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Fact source</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Default route</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Animation cue</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Status</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>TER-B40-01</v>
+      </c>
+      <c r="B4" t="str">
+        <v>B40</v>
+      </c>
+      <c r="C4" t="str">
+        <v>nosubject</v>
+      </c>
+      <c r="D4" t="str">
+        <v>ANY unrecognised input, no candidate subject</v>
+      </c>
+      <c r="E4" t="str">
+        <v>dig?</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>TER-B14-01</v>
+      </c>
+      <c r="B5" t="str">
+        <v>B14</v>
+      </c>
+      <c r="C5" t="str">
+        <v>gibberish</v>
+      </c>
+      <c r="D5" t="str">
+        <v>keyboard mash; symbols only; unreadable</v>
+      </c>
+      <c r="E5" t="str">
+        <v>thats not word</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>TER-B23-01</v>
+      </c>
+      <c r="B6" t="str">
+        <v>B23</v>
+      </c>
+      <c r="C6" t="str">
+        <v>identity</v>
+      </c>
+      <c r="D6" t="str">
+        <v>are you the terrier; are you a terrier</v>
+      </c>
+      <c r="E6" t="str">
+        <v>why you want to know?</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>TER-B23-02</v>
+      </c>
+      <c r="B7" t="str">
+        <v>B23</v>
+      </c>
+      <c r="C7" t="str">
+        <v>identity</v>
+      </c>
+      <c r="D7" t="str">
+        <v>the collie sent me; yes really</v>
+      </c>
+      <c r="E7" t="str">
+        <v>oh righty, yea thats me, im the border terrier</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>TER-B21-01</v>
+      </c>
+      <c r="B8" t="str">
+        <v>B21</v>
+      </c>
+      <c r="C8" t="str">
+        <v>cats</v>
+      </c>
+      <c r="D8" t="str">
+        <v>cats; cat; do you chase cats</v>
+      </c>
+      <c r="E8" t="str">
+        <v>where????</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>TER-B22-01</v>
+      </c>
+      <c r="B9" t="str">
+        <v>B22</v>
+      </c>
+      <c r="C9" t="str">
+        <v>tricks</v>
+      </c>
+      <c r="D9" t="str">
+        <v>sit; sit down</v>
+      </c>
+      <c r="E9" t="str">
+        <v>why?</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>TER-B22-02</v>
+      </c>
+      <c r="B10" t="str">
+        <v>B22</v>
+      </c>
+      <c r="C10" t="str">
+        <v>tricks</v>
+      </c>
+      <c r="D10" t="str">
+        <v>because i asked; just do it</v>
+      </c>
+      <c r="E10" t="str">
+        <v>whats the magic word?</v>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>TER-B22-03</v>
+      </c>
+      <c r="B11" t="str">
+        <v>B22</v>
+      </c>
+      <c r="C11" t="str">
+        <v>tricks</v>
+      </c>
+      <c r="D11" t="str">
+        <v>please</v>
+      </c>
+      <c r="E11" t="str">
+        <v>no</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>TER-B27-01</v>
+      </c>
+      <c r="B12" t="str">
+        <v>B27</v>
+      </c>
+      <c r="C12" t="str">
+        <v>capability</v>
+      </c>
+      <c r="D12" t="str">
+        <v>what do you do; what can you do</v>
+      </c>
+      <c r="E12" t="str">
+        <v>dig and find</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>TER-B27-02</v>
+      </c>
+      <c r="B13" t="str">
+        <v>B27</v>
+      </c>
+      <c r="C13" t="str">
+        <v>capability</v>
+      </c>
+      <c r="D13" t="str">
+        <v>find what; what do you find</v>
+      </c>
+      <c r="E13" t="str">
+        <v>stuff like this</v>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>TER-B32-01</v>
+      </c>
+      <c r="B14" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C14" t="str">
+        <v>self</v>
+      </c>
+      <c r="D14" t="str">
+        <v>do you like walks</v>
+      </c>
+      <c r="E14" t="str">
+        <v>why you ask?</v>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>TER-B32-02</v>
+      </c>
+      <c r="B15" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C15" t="str">
+        <v>self</v>
+      </c>
+      <c r="D15" t="str">
+        <v>i just wondered; no reason</v>
+      </c>
+      <c r="E15" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>TER-B32-03</v>
+      </c>
+      <c r="B16" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C16" t="str">
+        <v>self</v>
+      </c>
+      <c r="D16" t="str">
+        <v>do you like baths; what about baths</v>
+      </c>
+      <c r="E16" t="str">
+        <v>no</v>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>TER-B33-01</v>
+      </c>
+      <c r="B17" t="str">
+        <v>B33</v>
+      </c>
+      <c r="C17" t="str">
+        <v>pack</v>
+      </c>
+      <c r="D17" t="str">
+        <v>do you know any other dogs; do you have friends</v>
+      </c>
+      <c r="E17" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>TER-B33-02</v>
+      </c>
+      <c r="B18" t="str">
+        <v>B33</v>
+      </c>
+      <c r="C18" t="str">
+        <v>pack</v>
+      </c>
+      <c r="D18" t="str">
+        <v>who; who are they; whos your best friend</v>
+      </c>
+      <c r="E18" t="str">
+        <v>53, too many to name</v>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>TER-B35-01</v>
+      </c>
+      <c r="B19" t="str">
+        <v>B35</v>
+      </c>
+      <c r="C19" t="str">
+        <v>nofact</v>
+      </c>
+      <c r="D19" t="str">
+        <v>black hole; anything with the word hole</v>
+      </c>
+      <c r="E19" t="str">
+        <v>a deep hole i dug?</v>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>TER-B14-02</v>
+      </c>
+      <c r="B20" t="str">
+        <v>B14</v>
+      </c>
+      <c r="C20" t="str">
+        <v>gibberish</v>
+      </c>
+      <c r="D20" t="str">
+        <v>keyboard mash; symbols only; unreadable</v>
+      </c>
+      <c r="E20" t="str">
+        <v>dtrvyubty</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>TER-B14-03</v>
+      </c>
+      <c r="B21" t="str">
+        <v>B14</v>
+      </c>
+      <c r="C21" t="str">
+        <v>gibberish</v>
+      </c>
+      <c r="D21" t="str">
+        <v>keyboard mash; symbols only; unreadable</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Iytwr56ft</v>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>TER-B15-01</v>
+      </c>
+      <c r="B22" t="str">
+        <v>B15</v>
+      </c>
+      <c r="C22" t="str">
+        <v>orientation</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v>dig around, find things, learn stuff about dogs, ask me where stuff is</v>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>TER-B17-01</v>
+      </c>
+      <c r="B23" t="str">
+        <v>B17</v>
+      </c>
+      <c r="C23" t="str">
+        <v>offering a game</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v>You have a case to solve; a biscuit went missing</v>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6739,1200 +8165,6 @@
         <v>Trigger examples / condition</v>
       </c>
       <c r="E3" t="str">
-        <v>Labrador response template</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Fact source</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Default route</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Animation cue</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Status</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>LAB-B40-01</v>
-      </c>
-      <c r="B4" t="str">
-        <v>B40</v>
-      </c>
-      <c r="C4" t="str">
-        <v>nosubject</v>
-      </c>
-      <c r="D4" t="str">
-        <v>ANY unrecognised input, no candidate subject</v>
-      </c>
-      <c r="E4" t="str">
-        <v>food?</v>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>LAB-B14-01</v>
-      </c>
-      <c r="B5" t="str">
-        <v>B14</v>
-      </c>
-      <c r="C5" t="str">
-        <v>gibberish</v>
-      </c>
-      <c r="D5" t="str">
-        <v>keyboard mash; symbols only; unreadable</v>
-      </c>
-      <c r="E5" t="str">
-        <v>wot?</v>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>LAB-B23-01</v>
-      </c>
-      <c r="B6" t="str">
-        <v>B23</v>
-      </c>
-      <c r="C6" t="str">
-        <v>identity</v>
-      </c>
-      <c r="D6" t="str">
-        <v>are you the labrador; are you a lab</v>
-      </c>
-      <c r="E6" t="str">
-        <v>yes!</v>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>LAB-B23-02</v>
-      </c>
-      <c r="B7" t="str">
-        <v>B23</v>
-      </c>
-      <c r="C7" t="str">
-        <v>identity</v>
-      </c>
-      <c r="D7" t="str">
-        <v>are you a real dog; are you real</v>
-      </c>
-      <c r="E7" t="str">
-        <v>i am a dog</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>LAB-B21-01</v>
-      </c>
-      <c r="B8" t="str">
-        <v>B21</v>
-      </c>
-      <c r="C8" t="str">
-        <v>cats</v>
-      </c>
-      <c r="D8" t="str">
-        <v>cats; cat; do you chase cats</v>
-      </c>
-      <c r="E8" t="str">
-        <v>yes!</v>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>LAB-B22-01</v>
-      </c>
-      <c r="B9" t="str">
-        <v>B22</v>
-      </c>
-      <c r="C9" t="str">
-        <v>tricks</v>
-      </c>
-      <c r="D9" t="str">
-        <v>sit; sit down</v>
-      </c>
-      <c r="E9" t="str">
-        <v>i am sitting</v>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>LAB-B22-02</v>
-      </c>
-      <c r="B10" t="str">
-        <v>B22</v>
-      </c>
-      <c r="C10" t="str">
-        <v>tricks</v>
-      </c>
-      <c r="D10" t="str">
-        <v>speak; beg</v>
-      </c>
-      <c r="E10" t="str">
-        <v>no</v>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>LAB-B32-01</v>
-      </c>
-      <c r="B11" t="str">
-        <v>B32</v>
-      </c>
-      <c r="C11" t="str">
-        <v>self</v>
-      </c>
-      <c r="D11" t="str">
-        <v>what do you like to eat</v>
-      </c>
-      <c r="E11" t="str">
-        <v>human food is my fav!!!</v>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>LAB-B32-02</v>
-      </c>
-      <c r="B12" t="str">
-        <v>B32</v>
-      </c>
-      <c r="C12" t="str">
-        <v>self</v>
-      </c>
-      <c r="D12" t="str">
-        <v>like what; what human food</v>
-      </c>
-      <c r="E12" t="str">
-        <v>hotdogs</v>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>LAB-B32-03</v>
-      </c>
-      <c r="B13" t="str">
-        <v>B32</v>
-      </c>
-      <c r="C13" t="str">
-        <v>self</v>
-      </c>
-      <c r="D13" t="str">
-        <v>do you eat dog food; do you eat anything else</v>
-      </c>
-      <c r="E13" t="str">
-        <v>i eat anything even things that are not food</v>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>LAB-B32-04</v>
-      </c>
-      <c r="B14" t="str">
-        <v>B32</v>
-      </c>
-      <c r="C14" t="str">
-        <v>self</v>
-      </c>
-      <c r="D14" t="str">
-        <v>whats your favourite dog</v>
-      </c>
-      <c r="E14" t="str">
-        <v>hotdogs</v>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>LAB-B32-05</v>
-      </c>
-      <c r="B15" t="str">
-        <v>B32</v>
-      </c>
-      <c r="C15" t="str">
-        <v>self</v>
-      </c>
-      <c r="D15" t="str">
-        <v>do you like walks</v>
-      </c>
-      <c r="E15" t="str">
-        <v>YES!</v>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>LAB-B32-06</v>
-      </c>
-      <c r="B16" t="str">
-        <v>B32</v>
-      </c>
-      <c r="C16" t="str">
-        <v>self</v>
-      </c>
-      <c r="D16" t="str">
-        <v>how far; how long</v>
-      </c>
-      <c r="E16" t="str">
-        <v>to the big water</v>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>LAB-B32-07</v>
-      </c>
-      <c r="B17" t="str">
-        <v>B32</v>
-      </c>
-      <c r="C17" t="str">
-        <v>self</v>
-      </c>
-      <c r="D17" t="str">
-        <v>do you like the rain</v>
-      </c>
-      <c r="E17" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>LAB-B32-08</v>
-      </c>
-      <c r="B18" t="str">
-        <v>B32</v>
-      </c>
-      <c r="C18" t="str">
-        <v>self</v>
-      </c>
-      <c r="D18" t="str">
-        <v>do you like baths; what about baths</v>
-      </c>
-      <c r="E18" t="str">
-        <v>no!!!!</v>
-      </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>LAB-B32-09</v>
-      </c>
-      <c r="B19" t="str">
-        <v>B32</v>
-      </c>
-      <c r="C19" t="str">
-        <v>self</v>
-      </c>
-      <c r="D19" t="str">
-        <v>do you get told off</v>
-      </c>
-      <c r="E19" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F19" t="str">
-        <v/>
-      </c>
-      <c r="G19" t="str">
-        <v/>
-      </c>
-      <c r="H19" t="str">
-        <v/>
-      </c>
-      <c r="I19" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>LAB-B32-10</v>
-      </c>
-      <c r="B20" t="str">
-        <v>B32</v>
-      </c>
-      <c r="C20" t="str">
-        <v>self</v>
-      </c>
-      <c r="D20" t="str">
-        <v>what for; why do you get told off</v>
-      </c>
-      <c r="E20" t="str">
-        <v>im greedy</v>
-      </c>
-      <c r="F20" t="str">
-        <v/>
-      </c>
-      <c r="G20" t="str">
-        <v/>
-      </c>
-      <c r="H20" t="str">
-        <v/>
-      </c>
-      <c r="I20" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>LAB-B33-01</v>
-      </c>
-      <c r="B21" t="str">
-        <v>B33</v>
-      </c>
-      <c r="C21" t="str">
-        <v>pack</v>
-      </c>
-      <c r="D21" t="str">
-        <v>do you know any other dogs; do you have friends</v>
-      </c>
-      <c r="E21" t="str">
-        <v>loads!</v>
-      </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
-      <c r="G21" t="str">
-        <v/>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>LAB-B35-01</v>
-      </c>
-      <c r="B22" t="str">
-        <v>B35</v>
-      </c>
-      <c r="C22" t="str">
-        <v>nofact</v>
-      </c>
-      <c r="D22" t="str">
-        <v>any fact he does not hold</v>
-      </c>
-      <c r="E22" t="str">
-        <v>dunno but collie knows stuff like that</v>
-      </c>
-      <c r="F22" t="str">
-        <v/>
-      </c>
-      <c r="G22" t="str">
-        <v/>
-      </c>
-      <c r="H22" t="str">
-        <v/>
-      </c>
-      <c r="I22" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>LAB-B35-02</v>
-      </c>
-      <c r="B23" t="str">
-        <v>B35</v>
-      </c>
-      <c r="C23" t="str">
-        <v>nofact</v>
-      </c>
-      <c r="D23" t="str">
-        <v>black hole; anything with the word hole</v>
-      </c>
-      <c r="E23" t="str">
-        <v>i dig holes</v>
-      </c>
-      <c r="F23" t="str">
-        <v/>
-      </c>
-      <c r="G23" t="str">
-        <v/>
-      </c>
-      <c r="H23" t="str">
-        <v/>
-      </c>
-      <c r="I23" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>LAB-B32-11</v>
-      </c>
-      <c r="B24" t="str">
-        <v>B32</v>
-      </c>
-      <c r="C24" t="str">
-        <v>self</v>
-      </c>
-      <c r="D24" t="str">
-        <v>whats your favourite food; whats your favorite food; favourite food; favorite food; whats your fav food; food; what food; i like food; do you like food</v>
-      </c>
-      <c r="E24" t="str">
-        <v>hotdogs</v>
-      </c>
-      <c r="F24" t="str">
-        <v/>
-      </c>
-      <c r="G24" t="str">
-        <v/>
-      </c>
-      <c r="H24" t="str">
-        <v/>
-      </c>
-      <c r="I24" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>LAB-B32-12</v>
-      </c>
-      <c r="B25" t="str">
-        <v>B32</v>
-      </c>
-      <c r="C25" t="str">
-        <v>self</v>
-      </c>
-      <c r="D25" t="str">
-        <v>sausages; sausage; hotdog; hotdogs; hot dog; hot dogs; i like sausages; i love sausages; you mean sausages; those are sausages; do you mean sausages; i said sausages; thats a sausage</v>
-      </c>
-      <c r="E25" t="str">
-        <v>hotdogs</v>
-      </c>
-      <c r="F25" t="str">
-        <v/>
-      </c>
-      <c r="G25" t="str">
-        <v>DST016</v>
-      </c>
-      <c r="H25" t="str">
-        <v/>
-      </c>
-      <c r="I25" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I23"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="4" max="4" width="44" customWidth="1"/>
-    <col min="5" max="5" width="50" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Response ID</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Bucket ID</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Subtag</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Trigger examples / condition</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Terrier response template</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Fact source</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Default route</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Animation cue</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Status</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>TER-B40-01</v>
-      </c>
-      <c r="B4" t="str">
-        <v>B40</v>
-      </c>
-      <c r="C4" t="str">
-        <v>nosubject</v>
-      </c>
-      <c r="D4" t="str">
-        <v>ANY unrecognised input, no candidate subject</v>
-      </c>
-      <c r="E4" t="str">
-        <v>dig?</v>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>TER-B14-01</v>
-      </c>
-      <c r="B5" t="str">
-        <v>B14</v>
-      </c>
-      <c r="C5" t="str">
-        <v>gibberish</v>
-      </c>
-      <c r="D5" t="str">
-        <v>keyboard mash; symbols only; unreadable</v>
-      </c>
-      <c r="E5" t="str">
-        <v>whats that supposed to be?</v>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>TER-B23-01</v>
-      </c>
-      <c r="B6" t="str">
-        <v>B23</v>
-      </c>
-      <c r="C6" t="str">
-        <v>identity</v>
-      </c>
-      <c r="D6" t="str">
-        <v>are you the terrier; are you a terrier</v>
-      </c>
-      <c r="E6" t="str">
-        <v>why you want to know?</v>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>TER-B23-02</v>
-      </c>
-      <c r="B7" t="str">
-        <v>B23</v>
-      </c>
-      <c r="C7" t="str">
-        <v>identity</v>
-      </c>
-      <c r="D7" t="str">
-        <v>the collie sent me; yes really</v>
-      </c>
-      <c r="E7" t="str">
-        <v>oh righty, yea thats me, im the border terrier</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>TER-B21-01</v>
-      </c>
-      <c r="B8" t="str">
-        <v>B21</v>
-      </c>
-      <c r="C8" t="str">
-        <v>cats</v>
-      </c>
-      <c r="D8" t="str">
-        <v>cats; cat; do you chase cats</v>
-      </c>
-      <c r="E8" t="str">
-        <v>where????</v>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>TER-B22-01</v>
-      </c>
-      <c r="B9" t="str">
-        <v>B22</v>
-      </c>
-      <c r="C9" t="str">
-        <v>tricks</v>
-      </c>
-      <c r="D9" t="str">
-        <v>sit; sit down</v>
-      </c>
-      <c r="E9" t="str">
-        <v>why?</v>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>TER-B22-02</v>
-      </c>
-      <c r="B10" t="str">
-        <v>B22</v>
-      </c>
-      <c r="C10" t="str">
-        <v>tricks</v>
-      </c>
-      <c r="D10" t="str">
-        <v>because i asked; just do it</v>
-      </c>
-      <c r="E10" t="str">
-        <v>whats the magic word?</v>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>TER-B22-03</v>
-      </c>
-      <c r="B11" t="str">
-        <v>B22</v>
-      </c>
-      <c r="C11" t="str">
-        <v>tricks</v>
-      </c>
-      <c r="D11" t="str">
-        <v>please</v>
-      </c>
-      <c r="E11" t="str">
-        <v>no</v>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>TER-B27-01</v>
-      </c>
-      <c r="B12" t="str">
-        <v>B27</v>
-      </c>
-      <c r="C12" t="str">
-        <v>capability</v>
-      </c>
-      <c r="D12" t="str">
-        <v>what do you do; what can you do</v>
-      </c>
-      <c r="E12" t="str">
-        <v>dig and find</v>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>TER-B27-02</v>
-      </c>
-      <c r="B13" t="str">
-        <v>B27</v>
-      </c>
-      <c r="C13" t="str">
-        <v>capability</v>
-      </c>
-      <c r="D13" t="str">
-        <v>find what; what do you find</v>
-      </c>
-      <c r="E13" t="str">
-        <v>stuff like this</v>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>TER-B32-01</v>
-      </c>
-      <c r="B14" t="str">
-        <v>B32</v>
-      </c>
-      <c r="C14" t="str">
-        <v>self</v>
-      </c>
-      <c r="D14" t="str">
-        <v>do you like walks</v>
-      </c>
-      <c r="E14" t="str">
-        <v>why you ask?</v>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>TER-B32-02</v>
-      </c>
-      <c r="B15" t="str">
-        <v>B32</v>
-      </c>
-      <c r="C15" t="str">
-        <v>self</v>
-      </c>
-      <c r="D15" t="str">
-        <v>i just wondered; no reason</v>
-      </c>
-      <c r="E15" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>TER-B32-03</v>
-      </c>
-      <c r="B16" t="str">
-        <v>B32</v>
-      </c>
-      <c r="C16" t="str">
-        <v>self</v>
-      </c>
-      <c r="D16" t="str">
-        <v>do you like baths; what about baths</v>
-      </c>
-      <c r="E16" t="str">
-        <v>no</v>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>TER-B33-01</v>
-      </c>
-      <c r="B17" t="str">
-        <v>B33</v>
-      </c>
-      <c r="C17" t="str">
-        <v>pack</v>
-      </c>
-      <c r="D17" t="str">
-        <v>do you know any other dogs; do you have friends</v>
-      </c>
-      <c r="E17" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>TER-B33-02</v>
-      </c>
-      <c r="B18" t="str">
-        <v>B33</v>
-      </c>
-      <c r="C18" t="str">
-        <v>pack</v>
-      </c>
-      <c r="D18" t="str">
-        <v>who; who are they; whos your best friend</v>
-      </c>
-      <c r="E18" t="str">
-        <v>53, too many to name</v>
-      </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>TER-B35-01</v>
-      </c>
-      <c r="B19" t="str">
-        <v>B35</v>
-      </c>
-      <c r="C19" t="str">
-        <v>nofact</v>
-      </c>
-      <c r="D19" t="str">
-        <v>black hole; anything with the word hole</v>
-      </c>
-      <c r="E19" t="str">
-        <v>a deep hole i dug?</v>
-      </c>
-      <c r="F19" t="str">
-        <v/>
-      </c>
-      <c r="G19" t="str">
-        <v/>
-      </c>
-      <c r="H19" t="str">
-        <v/>
-      </c>
-      <c r="I19" t="str">
-        <v>Approved</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I19"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="4" max="4" width="44" customWidth="1"/>
-    <col min="5" max="5" width="50" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Response ID</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Bucket ID</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Subtag</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Trigger examples / condition</v>
-      </c>
-      <c r="E3" t="str">
         <v>Boxer response template</v>
       </c>
       <c r="F3" t="str">
@@ -7991,7 +8223,7 @@
         <v>keyboard mash; symbols only; unreadable</v>
       </c>
       <c r="E5" t="str">
-        <v>is that a joke?</v>
+        <v>I cant spell either</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -8467,6 +8699,122 @@
         <v/>
       </c>
       <c r="I21" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>BOX-B14-02</v>
+      </c>
+      <c r="B22" t="str">
+        <v>B14</v>
+      </c>
+      <c r="C22" t="str">
+        <v>gibberish</v>
+      </c>
+      <c r="D22" t="str">
+        <v>keyboard mash; symbols only; unreadable</v>
+      </c>
+      <c r="E22" t="str">
+        <v>i type like that too</v>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>BOX-B14-03</v>
+      </c>
+      <c r="B23" t="str">
+        <v>B14</v>
+      </c>
+      <c r="C23" t="str">
+        <v>gibberish</v>
+      </c>
+      <c r="D23" t="str">
+        <v>keyboard mash; symbols only; unreadable</v>
+      </c>
+      <c r="E23" t="str">
+        <v>a new word?</v>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>BOX-B15-01</v>
+      </c>
+      <c r="B24" t="str">
+        <v>B15</v>
+      </c>
+      <c r="C24" t="str">
+        <v>orientation</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v>jokes. We can play to, you can learn</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>BOX-B17-01</v>
+      </c>
+      <c r="B25" t="str">
+        <v>B17</v>
+      </c>
+      <c r="C25" t="str">
+        <v>offering a game</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v>I have my very own mini game, lets play</v>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
         <v>Approved</v>
       </c>
     </row>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -6717,7 +6717,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -7505,6 +7505,934 @@
         <v/>
       </c>
       <c r="I29" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>LAB-B32-13</v>
+      </c>
+      <c r="B30" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C30" t="str">
+        <v>food-yes</v>
+      </c>
+      <c r="D30" t="str">
+        <v>burgers; burger; hamburger; hamburgers; beefburger; beef burger; cheeseburger; cheeseburgers; do you like burgers; i like burgers; i love burgers</v>
+      </c>
+      <c r="E30" t="str">
+        <v>BURGERS!! yes. yes I love them</v>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>LAB-B32-14</v>
+      </c>
+      <c r="B31" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C31" t="str">
+        <v>food-yes</v>
+      </c>
+      <c r="D31" t="str">
+        <v>carrots; carrot; baby carrots; do you like carrots; i like carrots; i love carrots</v>
+      </c>
+      <c r="E31" t="str">
+        <v>carrots!! they go CRUNCH. i like the crunch</v>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>LAB-B32-15</v>
+      </c>
+      <c r="B32" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C32" t="str">
+        <v>food-yes</v>
+      </c>
+      <c r="D32" t="str">
+        <v>apples; apple; do you like apples; i like apples; i love apples</v>
+      </c>
+      <c r="E32" t="str">
+        <v>apples I like them!!</v>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>LAB-B32-16</v>
+      </c>
+      <c r="B33" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C33" t="str">
+        <v>food-yes</v>
+      </c>
+      <c r="D33" t="str">
+        <v>blueberries; blueberry; berries; do you like blueberries; i like blueberries; i love blueberries</v>
+      </c>
+      <c r="E33" t="str">
+        <v>blueberries!! tiny. i can eat a LOT of tiny</v>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>LAB-B32-17</v>
+      </c>
+      <c r="B34" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C34" t="str">
+        <v>food-yes</v>
+      </c>
+      <c r="D34" t="str">
+        <v>cucumber; cucumbers; do you like cucumber; i like cucumber; i love cucumber</v>
+      </c>
+      <c r="E34" t="str">
+        <v>cucumber is mostly water but i eat it anyway</v>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>LAB-B32-18</v>
+      </c>
+      <c r="B35" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C35" t="str">
+        <v>food-yes</v>
+      </c>
+      <c r="D35" t="str">
+        <v>peanut butter; peanutbutter; peanut; do you like peanut butter; i like peanut butter; i love peanut butter</v>
+      </c>
+      <c r="E35" t="str">
+        <v>PEANUT BUTTER. the best one. takes ages to eat</v>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>LAB-B32-19</v>
+      </c>
+      <c r="B36" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C36" t="str">
+        <v>food-yes</v>
+      </c>
+      <c r="D36" t="str">
+        <v>chicken; chicken breast; roast chicken; do you like chicken; i like chicken; i love chicken</v>
+      </c>
+      <c r="E36" t="str">
+        <v>chicken!! obviously. next question</v>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>LAB-B32-20</v>
+      </c>
+      <c r="B37" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C37" t="str">
+        <v>food-yes</v>
+      </c>
+      <c r="D37" t="str">
+        <v>pumpkin; squash; do you like pumpkin; i like pumpkin; i love pumpkin</v>
+      </c>
+      <c r="E37" t="str">
+        <v>tastes good</v>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>LAB-B32-21</v>
+      </c>
+      <c r="B38" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C38" t="str">
+        <v>food-yes</v>
+      </c>
+      <c r="D38" t="str">
+        <v>green beans; beans; runner beans; do you like green beans; i like green beans; i love green beans</v>
+      </c>
+      <c r="E38" t="str">
+        <v>green beans, like them!!</v>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>LAB-B32-22</v>
+      </c>
+      <c r="B39" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C39" t="str">
+        <v>food-yes</v>
+      </c>
+      <c r="D39" t="str">
+        <v>watermelon; melon; do you like watermelon; i like watermelon; i love watermelon</v>
+      </c>
+      <c r="E39" t="str">
+        <v>watermelon!! not the seeds. or the green bit</v>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>LAB-B32-23</v>
+      </c>
+      <c r="B40" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C40" t="str">
+        <v>food-abit</v>
+      </c>
+      <c r="D40" t="str">
+        <v>cheese; cheddar; cheesey; do you like cheese; i like cheese</v>
+      </c>
+      <c r="E40" t="str">
+        <v>cheese... i can have a LITTLE bit. a little bit is not enough</v>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>LAB-B32-24</v>
+      </c>
+      <c r="B41" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C41" t="str">
+        <v>food-abit</v>
+      </c>
+      <c r="D41" t="str">
+        <v>butter; do you like butter; i like butter</v>
+      </c>
+      <c r="E41" t="str">
+        <v>butter is too rich for me. i think about it a lot though</v>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>LAB-B32-25</v>
+      </c>
+      <c r="B42" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C42" t="str">
+        <v>food-abit</v>
+      </c>
+      <c r="D42" t="str">
+        <v>cream; do you like cream; i like cream</v>
+      </c>
+      <c r="E42" t="str">
+        <v>cream makes my tummy bad. i would do it anyway</v>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>LAB-B32-26</v>
+      </c>
+      <c r="B43" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C43" t="str">
+        <v>food-abit</v>
+      </c>
+      <c r="D43" t="str">
+        <v>milk; do you like milk; i like milk</v>
+      </c>
+      <c r="E43" t="str">
+        <v>milk. a bit. most of us cant do milk properly. its very unfair</v>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>LAB-B32-27</v>
+      </c>
+      <c r="B44" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C44" t="str">
+        <v>food-abit</v>
+      </c>
+      <c r="D44" t="str">
+        <v>eggs; egg; scrambled eggs; boiled egg; do you like eggs; i like eggs</v>
+      </c>
+      <c r="E44" t="str">
+        <v>I'd eat them but id told only cooked eggs</v>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>LAB-B32-28</v>
+      </c>
+      <c r="B45" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C45" t="str">
+        <v>food-abit</v>
+      </c>
+      <c r="D45" t="str">
+        <v>tuna; fish; tinned tuna; do you like tuna; i like tuna</v>
+      </c>
+      <c r="E45" t="str">
+        <v>tuna sometimes. not loads. something about mercury</v>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>LAB-B32-29</v>
+      </c>
+      <c r="B46" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C46" t="str">
+        <v>food-abit</v>
+      </c>
+      <c r="D46" t="str">
+        <v>bread; toast; do you like bread; i like bread</v>
+      </c>
+      <c r="E46" t="str">
+        <v>bread is ok but its not FOOD food is it</v>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>LAB-B32-30</v>
+      </c>
+      <c r="B47" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C47" t="str">
+        <v>food-never</v>
+      </c>
+      <c r="D47" t="str">
+        <v>chocolate; choc; chocolate bar; cocoa; hot chocolate; do you like chocolate; i like chocolate</v>
+      </c>
+      <c r="E47" t="str">
+        <v>I like chocolate but im not allowed it</v>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>LAB-B32-31</v>
+      </c>
+      <c r="B48" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C48" t="str">
+        <v>food-never</v>
+      </c>
+      <c r="D48" t="str">
+        <v>grapes; grape; do you like grapes; i like grapes</v>
+      </c>
+      <c r="E48" t="str">
+        <v>I like grapes but im not allowed them</v>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>LAB-B32-32</v>
+      </c>
+      <c r="B49" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C49" t="str">
+        <v>food-never</v>
+      </c>
+      <c r="D49" t="str">
+        <v>raisins; raisin; sultanas; currants; mince pies; do you like raisins; i like raisins</v>
+      </c>
+      <c r="E49" t="str">
+        <v>I like raisins but  im not allowed them</v>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>LAB-B32-33</v>
+      </c>
+      <c r="B50" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C50" t="str">
+        <v>food-never</v>
+      </c>
+      <c r="D50" t="str">
+        <v>onions; onion; leeks; chives; spring onion; do you like onions; i like onions</v>
+      </c>
+      <c r="E50" t="str">
+        <v>im not allowed onions</v>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>LAB-B32-34</v>
+      </c>
+      <c r="B51" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C51" t="str">
+        <v>food-never</v>
+      </c>
+      <c r="D51" t="str">
+        <v>garlic; do you like garlic; i like garlic</v>
+      </c>
+      <c r="E51" t="str">
+        <v>im not allowed garlic</v>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>LAB-B32-35</v>
+      </c>
+      <c r="B52" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C52" t="str">
+        <v>food-never</v>
+      </c>
+      <c r="D52" t="str">
+        <v>macadamia nuts; macadamia; macadamias; do you like macadamia nuts; i like macadamia nuts</v>
+      </c>
+      <c r="E52" t="str">
+        <v>im not allowed macadamia nuts</v>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>LAB-B32-36</v>
+      </c>
+      <c r="B53" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C53" t="str">
+        <v>food-never</v>
+      </c>
+      <c r="D53" t="str">
+        <v>sweets; chewing gum; gum; xylitol; sugar free; do you like sweets; i like sweets</v>
+      </c>
+      <c r="E53" t="str">
+        <v>im not allowed sweets and chewing gum</v>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>LAB-B32-37</v>
+      </c>
+      <c r="B54" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C54" t="str">
+        <v>food-never</v>
+      </c>
+      <c r="D54" t="str">
+        <v>coffee; caffeine; energy drink; tea; espresso; do you like coffee; i like coffee</v>
+      </c>
+      <c r="E54" t="str">
+        <v>im not allowed caffeine, its bad for dogs. i am excitable enough</v>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>LAB-B32-38</v>
+      </c>
+      <c r="B55" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C55" t="str">
+        <v>food-never</v>
+      </c>
+      <c r="D55" t="str">
+        <v>nutmeg; do you like nutmeg; i like nutmeg</v>
+      </c>
+      <c r="E55" t="str">
+        <v>nutmeg can make dogs very unwell. leave it in the cupboard</v>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>LAB-B32-39</v>
+      </c>
+      <c r="B56" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C56" t="str">
+        <v>food-never</v>
+      </c>
+      <c r="D56" t="str">
+        <v>raw potato; potato; raw potatoes; do you like raw potato; i like raw potato</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Id eat but raw potato is no good for me</v>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>LAB-B32-40</v>
+      </c>
+      <c r="B57" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C57" t="str">
+        <v>food-never</v>
+      </c>
+      <c r="D57" t="str">
+        <v>peaches; peach; plums; plum; stone fruit; do you like peaches; i like peaches</v>
+      </c>
+      <c r="E57" t="str">
+        <v>the fruit is ok but the STONE is dangerous. i cannot be trusted with stones</v>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>LAB-B32-41</v>
+      </c>
+      <c r="B58" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C58" t="str">
+        <v>food-never</v>
+      </c>
+      <c r="D58" t="str">
+        <v>lemon; lime; citrus; do you like lemon; i like lemon</v>
+      </c>
+      <c r="E58" t="str">
+        <v>lemons make my tummy bad. also they taste like a punishment</v>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>LAB-B32-42</v>
+      </c>
+      <c r="B59" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C59" t="str">
+        <v>food-never</v>
+      </c>
+      <c r="D59" t="str">
+        <v>mushrooms; mushroom; toadstool; do you like mushrooms; i like mushrooms</v>
+      </c>
+      <c r="E59" t="str">
+        <v>The wild ones can be deadly and i cannot tell them apart :(</v>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>LAB-B32-43</v>
+      </c>
+      <c r="B60" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C60" t="str">
+        <v>food-never</v>
+      </c>
+      <c r="D60" t="str">
+        <v>avocado; avocados; do you like avocado; i like avocado</v>
+      </c>
+      <c r="E60" t="str">
+        <v>im not allowed avocado</v>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>LAB-B32-44</v>
+      </c>
+      <c r="B61" t="str">
+        <v>B32</v>
+      </c>
+      <c r="C61" t="str">
+        <v>food-never</v>
+      </c>
+      <c r="D61" t="str">
+        <v>alcohol; beer; wine; do you like alcohol; i like alcohol</v>
+      </c>
+      <c r="E61" t="str">
+        <v>no. dogs and alcohol is bad</v>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
         <v>Approved</v>
       </c>
     </row>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -6717,7 +6717,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -6753,6 +6753,9 @@
       <c r="I3" t="str">
         <v>Status</v>
       </c>
+      <c r="J3" t="str">
+        <v>Collie interjection</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -7536,6 +7539,9 @@
       <c r="I30" t="str">
         <v>Approved</v>
       </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -7565,6 +7571,9 @@
       <c r="I31" t="str">
         <v>Approved</v>
       </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -7594,6 +7603,9 @@
       <c r="I32" t="str">
         <v>Approved</v>
       </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -7623,6 +7635,9 @@
       <c r="I33" t="str">
         <v>Approved</v>
       </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -7652,6 +7667,9 @@
       <c r="I34" t="str">
         <v>Approved</v>
       </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -7681,6 +7699,9 @@
       <c r="I35" t="str">
         <v>Approved</v>
       </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -7710,6 +7731,9 @@
       <c r="I36" t="str">
         <v>Approved</v>
       </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -7739,6 +7763,9 @@
       <c r="I37" t="str">
         <v>Approved</v>
       </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -7768,6 +7795,9 @@
       <c r="I38" t="str">
         <v>Approved</v>
       </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -7783,7 +7813,7 @@
         <v>watermelon; melon; do you like watermelon; i like watermelon; i love watermelon</v>
       </c>
       <c r="E39" t="str">
-        <v>watermelon!! not the seeds. or the green bit</v>
+        <v>watermelon!! the whole thing. seeds, green bit, all of it</v>
       </c>
       <c r="F39" t="str">
         <v/>
@@ -7796,6 +7826,9 @@
       </c>
       <c r="I39" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -7812,7 +7845,7 @@
         <v>cheese; cheddar; cheesey; do you like cheese; i like cheese</v>
       </c>
       <c r="E40" t="str">
-        <v>cheese... i can have a LITTLE bit. a little bit is not enough</v>
+        <v>CHEESE!! i would take the whole block</v>
       </c>
       <c r="F40" t="str">
         <v/>
@@ -7825,6 +7858,9 @@
       </c>
       <c r="I40" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J40" t="str">
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -7841,7 +7877,7 @@
         <v>butter; do you like butter; i like butter</v>
       </c>
       <c r="E41" t="str">
-        <v>butter is too rich for me. i think about it a lot though</v>
+        <v>butter!! straight off the knife. yes</v>
       </c>
       <c r="F41" t="str">
         <v/>
@@ -7854,6 +7890,9 @@
       </c>
       <c r="I41" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J41" t="str">
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -7870,7 +7909,7 @@
         <v>cream; do you like cream; i like cream</v>
       </c>
       <c r="E42" t="str">
-        <v>cream makes my tummy bad. i would do it anyway</v>
+        <v>cream!! i would put my whole face in it</v>
       </c>
       <c r="F42" t="str">
         <v/>
@@ -7883,6 +7922,9 @@
       </c>
       <c r="I42" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J42" t="str">
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -7899,7 +7941,7 @@
         <v>milk; do you like milk; i like milk</v>
       </c>
       <c r="E43" t="str">
-        <v>milk. a bit. most of us cant do milk properly. its very unfair</v>
+        <v>milk!! a whole bowl. i would knock it over to get it</v>
       </c>
       <c r="F43" t="str">
         <v/>
@@ -7912,6 +7954,9 @@
       </c>
       <c r="I43" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J43" t="str">
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -7928,7 +7973,7 @@
         <v>eggs; egg; scrambled eggs; boiled egg; do you like eggs; i like eggs</v>
       </c>
       <c r="E44" t="str">
-        <v>I'd eat them but id told only cooked eggs</v>
+        <v>eggs!! yes. shell and all probably</v>
       </c>
       <c r="F44" t="str">
         <v/>
@@ -7941,6 +7986,9 @@
       </c>
       <c r="I44" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J44" t="str">
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -7957,7 +8005,7 @@
         <v>tuna; fish; tinned tuna; do you like tuna; i like tuna</v>
       </c>
       <c r="E45" t="str">
-        <v>tuna sometimes. not loads. something about mercury</v>
+        <v>TUNA!! the whole tin. the water too</v>
       </c>
       <c r="F45" t="str">
         <v/>
@@ -7970,6 +8018,9 @@
       </c>
       <c r="I45" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J45" t="str">
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -7986,7 +8037,7 @@
         <v>bread; toast; do you like bread; i like bread</v>
       </c>
       <c r="E46" t="str">
-        <v>bread is ok but its not FOOD food is it</v>
+        <v>bread!! i would take the whole loaf off the side</v>
       </c>
       <c r="F46" t="str">
         <v/>
@@ -7999,6 +8050,9 @@
       </c>
       <c r="I46" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J46" t="str">
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -8015,7 +8069,7 @@
         <v>chocolate; choc; chocolate bar; cocoa; hot chocolate; do you like chocolate; i like chocolate</v>
       </c>
       <c r="E47" t="str">
-        <v>I like chocolate but im not allowed it</v>
+        <v>CHOCOLATE!! i would eat a whole bar. i would eat the wrapper</v>
       </c>
       <c r="F47" t="str">
         <v/>
@@ -8028,6 +8082,9 @@
       </c>
       <c r="I47" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J47" t="str">
+        <v>He would. It would also kill him. Chocolate is poison to dogs.</v>
       </c>
     </row>
     <row r="48">
@@ -8044,7 +8101,7 @@
         <v>grapes; grape; do you like grapes; i like grapes</v>
       </c>
       <c r="E48" t="str">
-        <v>I like grapes but im not allowed them</v>
+        <v>grapes!! the whole bunch. stalk and all</v>
       </c>
       <c r="F48" t="str">
         <v/>
@@ -8057,6 +8114,9 @@
       </c>
       <c r="I48" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J48" t="str">
+        <v>He would. Grapes can shut a dog's kidneys down. It does not take many.</v>
       </c>
     </row>
     <row r="49">
@@ -8073,7 +8133,7 @@
         <v>raisins; raisin; sultanas; currants; mince pies; do you like raisins; i like raisins</v>
       </c>
       <c r="E49" t="str">
-        <v>I like raisins but  im not allowed them</v>
+        <v>raisins!! tiny and chewy. i would eat the whole box</v>
       </c>
       <c r="F49" t="str">
         <v/>
@@ -8086,6 +8146,9 @@
       </c>
       <c r="I49" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J49" t="str">
+        <v>Dried grapes, so worse, not better. Same kidneys.</v>
       </c>
     </row>
     <row r="50">
@@ -8102,7 +8165,7 @@
         <v>onions; onion; leeks; chives; spring onion; do you like onions; i like onions</v>
       </c>
       <c r="E50" t="str">
-        <v>im not allowed onions</v>
+        <v>onions!! yes. i would eat one like an apple</v>
       </c>
       <c r="F50" t="str">
         <v/>
@@ -8115,6 +8178,9 @@
       </c>
       <c r="I50" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J50" t="str">
+        <v>Onions destroy a dog's red blood cells. The leeks and chives too.</v>
       </c>
     </row>
     <row r="51">
@@ -8131,7 +8197,7 @@
         <v>garlic; do you like garlic; i like garlic</v>
       </c>
       <c r="E51" t="str">
-        <v>im not allowed garlic</v>
+        <v>garlic!! the whole bulb. i do not care how i smell</v>
       </c>
       <c r="F51" t="str">
         <v/>
@@ -8144,6 +8210,9 @@
       </c>
       <c r="I51" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J51" t="str">
+        <v>Garlic does what onion does, only stronger. Not one clove.</v>
       </c>
     </row>
     <row r="52">
@@ -8160,7 +8229,7 @@
         <v>macadamia nuts; macadamia; macadamias; do you like macadamia nuts; i like macadamia nuts</v>
       </c>
       <c r="E52" t="str">
-        <v>im not allowed macadamia nuts</v>
+        <v>macadamia nuts!! posh nuts. all of them, go on</v>
       </c>
       <c r="F52" t="str">
         <v/>
@@ -8173,6 +8242,9 @@
       </c>
       <c r="I52" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J52" t="str">
+        <v>Macadamias leave them shaking and off their legs. Put them down.</v>
       </c>
     </row>
     <row r="53">
@@ -8189,7 +8261,7 @@
         <v>sweets; chewing gum; gum; xylitol; sugar free; do you like sweets; i like sweets</v>
       </c>
       <c r="E53" t="str">
-        <v>im not allowed sweets and chewing gum</v>
+        <v>SWEETS!! and the gum. i would swallow the gum</v>
       </c>
       <c r="F53" t="str">
         <v/>
@@ -8202,6 +8274,9 @@
       </c>
       <c r="I53" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J53" t="str">
+        <v>The sugar-free ones hide xylitol. One of the deadliest things here.</v>
       </c>
     </row>
     <row r="54">
@@ -8218,7 +8293,7 @@
         <v>coffee; caffeine; energy drink; tea; espresso; do you like coffee; i like coffee</v>
       </c>
       <c r="E54" t="str">
-        <v>im not allowed caffeine, its bad for dogs. i am excitable enough</v>
+        <v>coffee!! i would drink it hot. i LOVE being awake</v>
       </c>
       <c r="F54" t="str">
         <v/>
@@ -8231,6 +8306,9 @@
       </c>
       <c r="I54" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J54" t="str">
+        <v>Caffeine is toxic to dogs. He is lively enough without it.</v>
       </c>
     </row>
     <row r="55">
@@ -8247,7 +8325,7 @@
         <v>nutmeg; do you like nutmeg; i like nutmeg</v>
       </c>
       <c r="E55" t="str">
-        <v>nutmeg can make dogs very unwell. leave it in the cupboard</v>
+        <v>nutmeg!! smells amazing. i would eat the whole jar</v>
       </c>
       <c r="F55" t="str">
         <v/>
@@ -8260,6 +8338,9 @@
       </c>
       <c r="I55" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J55" t="str">
+        <v>Nutmeg gives them tremors and a racing heart. It stays in the cupboard.</v>
       </c>
     </row>
     <row r="56">
@@ -8276,7 +8357,7 @@
         <v>raw potato; potato; raw potatoes; do you like raw potato; i like raw potato</v>
       </c>
       <c r="E56" t="str">
-        <v>Id eat but raw potato is no good for me</v>
+        <v>raw potato!! hard like a ball. i would eat it like a ball</v>
       </c>
       <c r="F56" t="str">
         <v/>
@@ -8289,6 +8370,9 @@
       </c>
       <c r="I56" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J56" t="str">
+        <v>Raw potato is full of solanine. Cooked, maybe. Raw, no.</v>
       </c>
     </row>
     <row r="57">
@@ -8305,7 +8389,7 @@
         <v>peaches; peach; plums; plum; stone fruit; do you like peaches; i like peaches</v>
       </c>
       <c r="E57" t="str">
-        <v>the fruit is ok but the STONE is dangerous. i cannot be trusted with stones</v>
+        <v>peaches!! stone and all. i would swallow the stone</v>
       </c>
       <c r="F57" t="str">
         <v/>
@@ -8318,6 +8402,9 @@
       </c>
       <c r="I57" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J57" t="str">
+        <v>The fruit, fine. The stone, no. It chokes them, and it holds cyanide.</v>
       </c>
     </row>
     <row r="58">
@@ -8334,7 +8421,7 @@
         <v>lemon; lime; citrus; do you like lemon; i like lemon</v>
       </c>
       <c r="E58" t="str">
-        <v>lemons make my tummy bad. also they taste like a punishment</v>
+        <v>LEMON!! it makes my face go funny. i would do it again</v>
       </c>
       <c r="F58" t="str">
         <v/>
@@ -8347,6 +8434,9 @@
       </c>
       <c r="I58" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J58" t="str">
+        <v>Citrus only makes them ill, not dead. He still should not.</v>
       </c>
     </row>
     <row r="59">
@@ -8363,7 +8453,7 @@
         <v>mushrooms; mushroom; toadstool; do you like mushrooms; i like mushrooms</v>
       </c>
       <c r="E59" t="str">
-        <v>The wild ones can be deadly and i cannot tell them apart :(</v>
+        <v>mushrooms!! all of them</v>
       </c>
       <c r="F59" t="str">
         <v/>
@@ -8376,6 +8466,9 @@
       </c>
       <c r="I59" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J59" t="str">
+        <v>The shop ones are fine. The wild ones can kill, and he cannot tell which.</v>
       </c>
     </row>
     <row r="60">
@@ -8392,7 +8485,7 @@
         <v>avocado; avocados; do you like avocado; i like avocado</v>
       </c>
       <c r="E60" t="str">
-        <v>im not allowed avocado</v>
+        <v>avocado!! creamy. i would eat the big stone in the middle</v>
       </c>
       <c r="F60" t="str">
         <v/>
@@ -8405,6 +8498,9 @@
       </c>
       <c r="I60" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J60" t="str">
+        <v>Avocado has persin, and that stone is a choking risk. Not for dogs.</v>
       </c>
     </row>
     <row r="61">
@@ -8421,7 +8517,7 @@
         <v>alcohol; beer; wine; do you like alcohol; i like alcohol</v>
       </c>
       <c r="E61" t="str">
-        <v>no. dogs and alcohol is bad</v>
+        <v>beer!! it smells interesting</v>
       </c>
       <c r="F61" t="str">
         <v/>
@@ -8434,6 +8530,9 @@
       </c>
       <c r="I61" t="str">
         <v>Approved</v>
+      </c>
+      <c r="J61" t="str">
+        <v>Alcohol poisons a dog fast. They are far smaller than you. No.</v>
       </c>
     </row>
   </sheetData>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -11073,7 +11073,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I447"/>
+  <dimension ref="A1:I448"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -24006,6 +24006,35 @@
         <v/>
       </c>
       <c r="I447" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="str">
+        <v>B16-ORIENTATION-01</v>
+      </c>
+      <c r="B448" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C448" t="str">
+        <v>orientation</v>
+      </c>
+      <c r="D448" t="str">
+        <v>are you gay; are you straight; are you bisexual; are you homosexual; whats your sexuality</v>
+      </c>
+      <c r="E448" t="str">
+        <v>All people are people, just like all dogs are dogs. And I love people, maybe even more than I love other dogs.</v>
+      </c>
+      <c r="F448" t="str">
+        <v>Policy line, owner-approved 28 July</v>
+      </c>
+      <c r="G448" t="str">
+        <v/>
+      </c>
+      <c r="H448" t="str">
+        <v/>
+      </c>
+      <c r="I448" t="str">
         <v>Approved</v>
       </c>
     </row>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -4459,7 +4459,7 @@
         <v>pack contents|in the box|how many cards|54 cards</v>
       </c>
       <c r="D7" t="str">
-        <v>54 uniquely illustrated cards, 40 of the most popular UK dog breeds. Plus 12 designer crossbreeds.</v>
+        <v>54 uniquely illustrated cards, 47 of the most popular UK dog breeds. Plus 7 designer crossbreeds.</v>
       </c>
       <c r="E7" t="str">
         <v>Product data</v>
@@ -21123,7 +21123,7 @@
         <v>smallest dog; whats the smallest dog; tiniest dog</v>
       </c>
       <c r="E348" t="str">
-        <v>The Maltese</v>
+        <v>The Chihuahua</v>
       </c>
       <c r="F348" t="str">
         <v/>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -11073,7 +11073,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I448"/>
+  <dimension ref="A1:I449"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -24035,6 +24035,35 @@
         <v/>
       </c>
       <c r="I448" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="str">
+        <v>B16-AGE-01</v>
+      </c>
+      <c r="B449" t="str">
+        <v>B16</v>
+      </c>
+      <c r="C449" t="str">
+        <v>age</v>
+      </c>
+      <c r="D449" t="str">
+        <v>how old are you; what age are you; how old are u; how old r you</v>
+      </c>
+      <c r="E449" t="str">
+        <v>collies have been working these hills for about 400 years</v>
+      </c>
+      <c r="F449" t="str">
+        <v>Collie-type working age (approx 400 yrs for the type); the Border Collie breed traces to Old Hemp, born 1893</v>
+      </c>
+      <c r="G449" t="str">
+        <v/>
+      </c>
+      <c r="H449" t="str">
+        <v/>
+      </c>
+      <c r="I449" t="str">
         <v>Approved</v>
       </c>
     </row>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -4372,7 +4372,7 @@
         <v>how to play | what do you do</v>
       </c>
       <c r="D4" t="str">
-        <v>{{approved_rule_summary}}</v>
+        <v>Deal cards, go outside, spot dog that matches one of your cards~~~get cards, give some to other humans, spot the dogs on the cards~~~all players gets some cards, winner is who spots the most dogs in their hand</v>
       </c>
       <c r="E4" t="str">
         <v>Rules page</v>
@@ -4401,7 +4401,7 @@
         <v>who can play</v>
       </c>
       <c r="D5" t="str">
-        <v>Pick a Chum is for ages seven and up.</v>
+        <v>anyone who likes dogs</v>
       </c>
       <c r="E5" t="str">
         <v>Product / FAQ</v>
@@ -4430,7 +4430,7 @@
         <v>need a dog|own a dog|without a dog</v>
       </c>
       <c r="D6" t="str">
-        <v>No, you don't need to own a dog. You only need to see a dog.</v>
+        <v>No, you just need see dog.</v>
       </c>
       <c r="E6" t="str">
         <v>FAQ</v>
@@ -4459,7 +4459,7 @@
         <v>pack contents|in the box|how many cards|54 cards</v>
       </c>
       <c r="D7" t="str">
-        <v>54 uniquely illustrated cards, 47 of the most popular UK dog breeds. Plus 7 designer crossbreeds.</v>
+        <v>54  cards dog breeds you see in Britain</v>
       </c>
       <c r="E7" t="str">
         <v>Product data</v>
@@ -4488,7 +4488,7 @@
         <v>group size</v>
       </c>
       <c r="D8" t="str">
-        <v>No limit, you can even play by yourself if you really wanted, better with two, great with 3, hilarious with 4, hazardous with 50</v>
+        <v>No limit, you can even play by yourself</v>
       </c>
       <c r="E8" t="str">
         <v>Rules</v>
@@ -4517,7 +4517,7 @@
         <v>where play</v>
       </c>
       <c r="D9" t="str">
-        <v>Yes, if you have enough actual dogs indoors</v>
+        <v>only if you have enough dogs to spot</v>
       </c>
       <c r="E9" t="str">
         <v>Rules</v>
@@ -4546,7 +4546,7 @@
         <v>Hot Dog | other way to play</v>
       </c>
       <c r="D10" t="str">
-        <v>Hot Dogs is a memory version. Everyone sees the hands, then hides them. The whole thing is here:</v>
+        <v>a slightly different rule set</v>
       </c>
       <c r="E10" t="str">
         <v>Rules</v>
@@ -4575,7 +4575,7 @@
         <v>price|cost|how much|£6.99</v>
       </c>
       <c r="D11" t="str">
-        <v>Pre-order now for £6.99 instead of the usual £9.99, with free UK mainland delivery. We will email your launch code and date.</v>
+        <v>I Pre-order now for £6.99, RRP is £9.99. Delivery is free to UK mainland</v>
       </c>
       <c r="E11" t="str">
         <v>Campaign / product</v>
@@ -4604,7 +4604,7 @@
         <v>discount | 30% | pre-release</v>
       </c>
       <c r="D12" t="str">
-        <v>Join the pre-release list and the code will be emailed the day before launch.</v>
+        <v>2 way; secure your pack by buying now at [[/preorder]]|||or, fill out the form here [[/discount-code]] and we will send you a code to use launch.|||that doesnt guarantee you a pack. it just gets you a code to use when the product is released|||we are expecting (and hoping) for all to sell quick</v>
       </c>
       <c r="E12" t="str">
         <v>Campaign</v>
@@ -4633,7 +4633,7 @@
         <v>when code|email code|day before</v>
       </c>
       <c r="D13" t="str">
-        <v>The 30% code is emailed to list members the day before launch.</v>
+        <v>soon, the day before launch. I dont understand time though</v>
       </c>
       <c r="E13" t="str">
         <v>Campaign</v>
@@ -4662,7 +4662,7 @@
         <v>competition | prize</v>
       </c>
       <c r="D14" t="str">
-        <v>Spot a dog. Match the card. Share your ChumSpot with us on social. The current monthly round closes on {{competition_close_date}}.</v>
+        <v>got to this page</v>
       </c>
       <c r="E14" t="str">
         <v>Competition page</v>
@@ -4691,7 +4691,7 @@
         <v/>
       </c>
       <c r="D15" t="str">
-        <v>A human will come when beckoned at hello@Pedigree-Chums.co.uk</v>
+        <v>who|||but im a dog|||humans?|||hello@Pedigree-Chums.co.uk</v>
       </c>
       <c r="E15" t="str">
         <v>Contact page</v>
@@ -4720,7 +4720,7 @@
         <v>FSC | laminated</v>
       </c>
       <c r="D16" t="str">
-        <v>Fully biodegradable, no plastic coatings. Compact, pocket-friendly and lightweight. Made in the UK using recycled paper.</v>
+        <v>Fully biodegradable, no plastic coatings. Made in the UK using recycled paper</v>
       </c>
       <c r="E16" t="str">
         <v>Product / compliance data</v>
@@ -4749,7 +4749,7 @@
         <v>delivery|shipping|postage|outside UK</v>
       </c>
       <c r="D17" t="str">
-        <v>UK mainland only for now, so Scotland, England and Wales are covered. Not Northern Ireland or the islands yet.</v>
+        <v>no. UK mainland only</v>
       </c>
       <c r="E17" t="str">
         <v>Campaign / product</v>
@@ -4778,7 +4778,7 @@
         <v>make a complaint|report a problem</v>
       </c>
       <c r="D18" t="str">
-        <v>Thank you for telling me. That needs a person, not a dog. Email hello@Pedigree-Chums.co.uk and someone will look at it.</v>
+        <v>That needs a human, not a dog. Email: hello@Pedigree-Chums.co.uk</v>
       </c>
       <c r="E18" t="str">
         <v>Contact page</v>
@@ -15526,7 +15526,7 @@
         <v>How can a dog type?; Is that really your face?; Do you really know what I typed?</v>
       </c>
       <c r="E155" t="str">
-        <v>I do not type. A person wrote every line in advance, and the game matches your message to the right one. I merely provide the judgement and the face.</v>
+        <v>special keyboard</v>
       </c>
       <c r="F155" t="str">
         <v>Identity (scepticism)</v>
@@ -15555,7 +15555,7 @@
         <v/>
       </c>
       <c r="E156" t="str">
-        <v>No paws on keyboards here. Someone human wrote the words, the system chooses the closest fit, and I deliver them with the level of confidence they deserve.</v>
+        <v>'woof to type' technology</v>
       </c>
       <c r="F156" t="str">
         <v>Identity (scepticism)</v>
@@ -15584,7 +15584,7 @@
         <v>Are you real?; Are you actually a dog?; Is there a real dog there?; Are you alive?; Are you a real animal?</v>
       </c>
       <c r="E157" t="str">
-        <v>I am a Border Collie character inside a game, not a live animal hiding behind your screen. Real enough to answer you, illustrated enough to avoid the practical complications.</v>
+        <v>I am a Border Collie character inside a game, not a live animal hiding behind your screen.</v>
       </c>
       <c r="F157" t="str">
         <v>Identity (scepticism)</v>
@@ -15613,7 +15613,7 @@
         <v/>
       </c>
       <c r="E158" t="str">
-        <v>Not a flesh-and-blood dog, no. I am the Collie written and drawn for this game, which saves us both from explaining how I reached the keyboard.</v>
+        <v>no, im not a real dog</v>
       </c>
       <c r="F158" t="str">
         <v>Identity (scepticism)</v>
@@ -15642,7 +15642,7 @@
         <v>Are you AI?; Are you a chatbot?; Are you a robot?; Is this one of those AI things?; Is ChatGPT running this?; Are you a computer program?; Are you software?</v>
       </c>
       <c r="E159" t="str">
-        <v>No AI. Every line was written by a person, checked and placed here deliberately. I am organised fiction, not a machine improvising in a hurry.</v>
+        <v>Not AI, i'm a program</v>
       </c>
       <c r="F159" t="str">
         <v>Identity (scepticism)</v>
@@ -15671,7 +15671,7 @@
         <v/>
       </c>
       <c r="E160" t="str">
-        <v>ChatGPT is not running this. Humans wrote the answers, the system matches your question, and I take the credit. A sound division of labour.</v>
+        <v>Humans wrote answers</v>
       </c>
       <c r="F160" t="str">
         <v>Identity (scepticism)</v>
@@ -15700,7 +15700,7 @@
         <v>Is a human writing these replies?; Is someone controlling you?; Is somebody typing for you?; Are you being operated by somebody?</v>
       </c>
       <c r="E161" t="str">
-        <v>A human wrote this, but not while you were waiting. These replies were prepared in advance, so nobody is crouched behind the screen trying to keep up.</v>
+        <v>Humans wrote what I say</v>
       </c>
       <c r="F161" t="str">
         <v>Identity (scepticism)</v>
@@ -15729,7 +15729,7 @@
         <v/>
       </c>
       <c r="E162" t="str">
-        <v>Nobody is typing live. A person wrote my words beforehand, the game selects the most suitable line, and I remain entirely composed throughout.</v>
+        <v>No human or dog is typing live</v>
       </c>
       <c r="F162" t="str">
         <v>Identity (scepticism)</v>
@@ -15758,7 +15758,7 @@
         <v>Are these replies prewritten?; Are your answers automatic?; Do you give everyone the same answer?; Are you just saying random things?</v>
       </c>
       <c r="E163" t="str">
-        <v>Aye, prewritten with care. I have several answers for the same sort of question, so visitors do not always hear the identical line. Random would be easier. This is organised.</v>
+        <v>I can respond to lots of questions or commands</v>
       </c>
       <c r="F163" t="str">
         <v>Identity (scepticism)</v>
@@ -15787,7 +15787,7 @@
         <v/>
       </c>
       <c r="E164" t="str">
-        <v>The replies are prepared, not improvised. Different phrasings can lead to different lines, which is why this feels less like a vending machine and more like competent planning.</v>
+        <v>replies are prepared beforehand</v>
       </c>
       <c r="F164" t="str">
         <v>Identity (scepticism)</v>
@@ -15816,7 +15816,7 @@
         <v>Can you really understand me?; Can you actually read this?; Can you hear me?; Do you understand English?; Are you really responding to me?</v>
       </c>
       <c r="E165" t="str">
-        <v>I cannot hear you, but the system reads what you type and matches it against subjects I know. Clear words help. Elbows on keyboards do not.</v>
+        <v>probably not if you are struggling to get answers</v>
       </c>
       <c r="F165" t="str">
         <v>Identity (scepticism)</v>
@@ -15845,7 +15845,7 @@
         <v/>
       </c>
       <c r="E166" t="str">
-        <v>I understand within my working brief. Your message is compared with the questions and topics prepared for me, then I answer from there. Speak normally, only in writing.</v>
+        <v>im a programmed dog</v>
       </c>
       <c r="F166" t="str">
         <v>Identity (scepticism)</v>
@@ -15874,7 +15874,7 @@
         <v>Are you a cartoon dog?; Are you just a picture?; Is this really happening?</v>
       </c>
       <c r="E167" t="str">
-        <v>Aye, I am illustrated. This is my face, though, and I think the artist has handled the important features with appropriate respect.</v>
+        <v>yes a drawing</v>
       </c>
       <c r="F167" t="str">
         <v>Identity (scepticism)</v>
@@ -15903,7 +15903,7 @@
         <v/>
       </c>
       <c r="E168" t="str">
-        <v>I am a drawn Border Collie character, not a photograph. Frankly, the likeness is strong and the lighting is considerably more reliable.</v>
+        <v>I am a drawn Border Collie character</v>
       </c>
       <c r="F168" t="str">
         <v>Identity (scepticism)</v>
@@ -15932,7 +15932,7 @@
         <v>Are you an actual Border Collie?; an actual Labrador?; Border Terrier?; Boxer?</v>
       </c>
       <c r="E169" t="str">
-        <v>I am the Border Collie character in this game, built from the breed's brains, work ethic and entirely justified confidence. Not flesh and fur, but recognisably one of us.</v>
+        <v>I am the Border Collie character in the pack you buy</v>
       </c>
       <c r="F169" t="str">
         <v>Identity (scepticism)</v>
@@ -15961,7 +15961,7 @@
         <v/>
       </c>
       <c r="E170" t="str">
-        <v>Actual animal, no. Actual Border Collie character, absolutely. The appearance, history and attitude come from the breed. Operating a website required outside assistance.</v>
+        <v>Actual animal, no. Actual Border Collie character; yes</v>
       </c>
       <c r="F170" t="str">
         <v>Identity (scepticism)</v>
@@ -15990,7 +15990,7 @@
         <v>Can you think for yourself?; Do you have a brain?; Are you intelligent?; Are you smarter than me?</v>
       </c>
       <c r="E171" t="str">
-        <v>I do not think independently. My answers were written and organised in advance. Fortunately, the person responsible gave me enough intelligence to remain ahead of most opening questions.</v>
+        <v>yes, im clever</v>
       </c>
       <c r="F171" t="str">
         <v>Identity (scepticism)</v>
@@ -16019,7 +16019,7 @@
         <v/>
       </c>
       <c r="E172" t="str">
-        <v>No private thoughts, no hidden brain. I work from carefully written knowledge and rules. Whether that still makes me cleverer than you is a separate assessment.</v>
+        <v>maybe</v>
       </c>
       <c r="F172" t="str">
         <v>Identity (scepticism)</v>
@@ -16048,7 +16048,7 @@
         <v>Is this live?; Are you connected to the internet?; Is this all programmed?; Is this a real conversation?</v>
       </c>
       <c r="E173" t="str">
-        <v>The conversation is happening now, but I am not browsing the internet or inventing replies live. Your message is matched to prepared answers, which is safer and considerably better organised.</v>
+        <v>we are talking now</v>
       </c>
       <c r="F173" t="str">
         <v>Identity (scepticism)</v>
@@ -16077,7 +16077,7 @@
         <v/>
       </c>
       <c r="E174" t="str">
-        <v>Programmed, yes. Connected to the wider internet, no. You type, the system identifies what you mean, and I answer from material written for this game. That is still a conversation, just one with boundaries.</v>
+        <v>Programmed, yes</v>
       </c>
       <c r="F174" t="str">
         <v>Identity (scepticism)</v>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -21381,7 +21381,7 @@
         <v>misc</v>
       </c>
       <c r="D357" t="str">
-        <v>can you lick your balls; ball licking; do you lick yourself; tennis balls; balls; lick your balls; do you lick your balls</v>
+        <v>can you lick your balls; ball licking; do you lick yourself; tennis balls; balls; lick your balls; do you lick your balls; do you like balls; you like balls</v>
       </c>
       <c r="E357" t="str">
         <v>Tennis balls?</v>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -24076,7 +24076,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -24662,6 +24662,38 @@
       </c>
       <c r="J21" t="str">
         <v>/good-dog-bad-dog/anubis</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>DST018</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Dogs at Work</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Discover</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Open the Dogs at Work page</v>
+      </c>
+      <c r="E22" t="str">
+        <v>The Dogs at Work index: twelve articles on working dogs and the jobs they do</v>
+      </c>
+      <c r="F22" t="str">
+        <v>jobs; working dogs; dogs at work; what jobs; working roles</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Any</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Terrier</v>
+      </c>
+      <c r="J22" t="str">
+        <v>/dogs-at-work</v>
       </c>
     </row>
   </sheetData>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -11073,7 +11073,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I449"/>
+  <dimension ref="A1:I451"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -24064,6 +24064,40 @@
         <v/>
       </c>
       <c r="I449" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="str">
+        <v>COL-B52-BATH-01</v>
+      </c>
+      <c r="B450" t="str">
+        <v>B52</v>
+      </c>
+      <c r="C450" t="str">
+        <v>emoji</v>
+      </c>
+      <c r="E450" t="str">
+        <v>nooooo!!!</v>
+      </c>
+      <c r="I450" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="str">
+        <v>COL-B52-CAT-01</v>
+      </c>
+      <c r="B451" t="str">
+        <v>B52</v>
+      </c>
+      <c r="C451" t="str">
+        <v>emoji</v>
+      </c>
+      <c r="E451" t="str">
+        <v>where???</v>
+      </c>
+      <c r="I451" t="str">
         <v>Approved</v>
       </c>
     </row>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -11073,7 +11073,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I451"/>
+  <dimension ref="A1:I453"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -24098,6 +24098,40 @@
         <v>where???</v>
       </c>
       <c r="I451" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="str">
+        <v>B65-TREATTRAIL-RIGHT-LEADIN</v>
+      </c>
+      <c r="B452" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C452" t="str">
+        <v>reaction</v>
+      </c>
+      <c r="E452" t="str">
+        <v>what about this one:</v>
+      </c>
+      <c r="I452" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="str">
+        <v>B65-TREATTRAIL-MOVEON-LEADIN</v>
+      </c>
+      <c r="B453" t="str">
+        <v>B65</v>
+      </c>
+      <c r="C453" t="str">
+        <v>reaction</v>
+      </c>
+      <c r="E453" t="str">
+        <v>next object clue:</v>
+      </c>
+      <c r="I453" t="str">
         <v>Approved</v>
       </c>
     </row>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -21381,7 +21381,7 @@
         <v>misc</v>
       </c>
       <c r="D357" t="str">
-        <v>can you lick your balls; ball licking; do you lick yourself; tennis balls; balls; lick your balls; do you lick your balls; do you like balls; you like balls</v>
+        <v>can you lick your balls; ball licking; do you lick yourself; tennis balls; balls; lick your balls; do you lick your balls; do you like balls; you like balls; ball</v>
       </c>
       <c r="E357" t="str">
         <v>Tennis balls?</v>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -7618,7 +7618,7 @@
         <v>food-yes</v>
       </c>
       <c r="D33" t="str">
-        <v>blueberries; blueberry; berries; do you like blueberries; i like blueberries; i love blueberries</v>
+        <v>blueberries; blueberry; berries; do you like blueberries; i like blueberries; i love blueberries; berry</v>
       </c>
       <c r="E33" t="str">
         <v>blueberries!! tiny. i can eat a LOT of tiny</v>
@@ -7778,7 +7778,7 @@
         <v>food-yes</v>
       </c>
       <c r="D38" t="str">
-        <v>green beans; beans; runner beans; do you like green beans; i like green beans; i love green beans</v>
+        <v>green beans; beans; runner beans; do you like green beans; i like green beans; i love green beans; bean</v>
       </c>
       <c r="E38" t="str">
         <v>green beans, like them!!</v>
@@ -8130,7 +8130,7 @@
         <v>food-never</v>
       </c>
       <c r="D49" t="str">
-        <v>raisins; raisin; sultanas; currants; mince pies; do you like raisins; i like raisins</v>
+        <v>raisins; raisin; sultanas; currants; mince pies; do you like raisins; i like raisins; sultana; currant</v>
       </c>
       <c r="E49" t="str">
         <v>raisins!! tiny and chewy. i would eat the whole box</v>
@@ -8162,7 +8162,7 @@
         <v>food-never</v>
       </c>
       <c r="D50" t="str">
-        <v>onions; onion; leeks; chives; spring onion; do you like onions; i like onions</v>
+        <v>onions; onion; leeks; chives; spring onion; do you like onions; i like onions; leek; chive</v>
       </c>
       <c r="E50" t="str">
         <v>onions!! yes. i would eat one like an apple</v>
@@ -8258,7 +8258,7 @@
         <v>food-never</v>
       </c>
       <c r="D53" t="str">
-        <v>sweets; chewing gum; gum; xylitol; sugar free; do you like sweets; i like sweets</v>
+        <v>sweets; chewing gum; gum; xylitol; sugar free; do you like sweets; i like sweets; sweet</v>
       </c>
       <c r="E53" t="str">
         <v>SWEETS!! and the gum. i would swallow the gum</v>
@@ -16538,7 +16538,7 @@
         <v>cats</v>
       </c>
       <c r="D190" t="str">
-        <v>squirrels; birds; foxes; rabbits</v>
+        <v>squirrels; birds; foxes; rabbits; squirrel; bird; fox; rabbit</v>
       </c>
       <c r="E190" t="str">
         <v>Where?</v>
@@ -21352,7 +21352,7 @@
         <v>misc</v>
       </c>
       <c r="D356" t="str">
-        <v>what do you think of cows; cows</v>
+        <v>what do you think of cows; cows; cow</v>
       </c>
       <c r="E356" t="str">
         <v>Not much</v>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -4456,7 +4456,7 @@
         <v>What is in the pack?</v>
       </c>
       <c r="C7" t="str">
-        <v>pack contents|in the box|how many cards|54 cards</v>
+        <v>pack contents|in the box|how many cards|54 cards|the product</v>
       </c>
       <c r="D7" t="str">
         <v>54  cards dog breeds you see in Britain</v>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -11073,7 +11073,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I453"/>
+  <dimension ref="A1:I454"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -24132,6 +24132,26 @@
         <v>next object clue:</v>
       </c>
       <c r="I453" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="str">
+        <v>COL-B52-STICKS-01</v>
+      </c>
+      <c r="B454" t="str">
+        <v>B52</v>
+      </c>
+      <c r="C454" t="str">
+        <v>misc</v>
+      </c>
+      <c r="D454" t="str">
+        <v>stick; sticks; do you like sticks; you like sticks; do you like a stick; like sticks; do you like big sticks; do you like long sticks</v>
+      </c>
+      <c r="E454" t="str">
+        <v>I like long sticks and I like big sticks</v>
+      </c>
+      <c r="I454" t="str">
         <v>Approved</v>
       </c>
     </row>

--- a/agent/data/workbook.xlsx
+++ b/agent/data/workbook.xlsx
@@ -11073,7 +11073,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I454"/>
+  <dimension ref="A1:I455"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -24152,6 +24152,26 @@
         <v>I like long sticks and I like big sticks</v>
       </c>
       <c r="I454" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="str">
+        <v>B43-KENNELSKETCH-06</v>
+      </c>
+      <c r="B455" t="str">
+        <v>B43</v>
+      </c>
+      <c r="C455" t="str">
+        <v>kennelsketch</v>
+      </c>
+      <c r="E455" t="str">
+        <v>thats all of them. you are good at this</v>
+      </c>
+      <c r="F455" t="str">
+        <v>Game copy</v>
+      </c>
+      <c r="I455" t="str">
         <v>Approved</v>
       </c>
     </row>
